--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -259,7 +259,7 @@
     <numFmt numFmtId="300" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="301" formatCode="m&quot;月&quot;d&quot;号&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Microsoft YaHei"/>
     </font>
@@ -296,10 +296,18 @@
       <color rgb="FF319B62"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -363,6 +371,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF4B183"/>
         <bgColor rgb="FFF4B183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF88825"/>
       </patternFill>
     </fill>
   </fills>
@@ -525,11 +543,11 @@
     </border>
   </borders>
   <cellStyleXfs>
-    <xf fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -961,6 +979,33 @@
     </xf>
     <xf fontId="3" fillId="0" borderId="13" xfId="0">
       <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="8" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="7" fillId="8" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="5" fillId="14" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="9" fillId="14" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="15" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="15" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -1556,7 +1601,7 @@
         <f>=SUM(A8:P8)</f>
         <v>1980</v>
       </c>
-      <c r="R8" s="19" t="s">
+      <c r="R8" s="148" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1939,8 +1984,8 @@
         <f>=SUM(A19:N19)</f>
         <v>1890</v>
       </c>
-      <c r="P19" s="23" t="s">
-        <v>17</v>
+      <c r="P19" s="150" t="s">
+        <v>16</v>
       </c>
       <c r="Q19" s="23" t="s"/>
     </row>
@@ -2176,8 +2221,8 @@
         <f>=SUM(A8:H8)</f>
         <v>750</v>
       </c>
-      <c r="J8" t="s">
-        <v>24</v>
+      <c r="J8" s="152" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:22"/>
@@ -2891,8 +2936,8 @@
         <f>=SUM(A16:N16)</f>
         <v>2010</v>
       </c>
-      <c r="P16" t="s">
-        <v>24</v>
+      <c r="P16" s="151" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -3004,8 +3049,12 @@
       <c r="F21" s="28">
         <v>90</v>
       </c>
-      <c r="G21" s="27" t="s"/>
-      <c r="H21" s="28" t="s"/>
+      <c r="G21" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="28">
+        <v>90</v>
+      </c>
       <c r="I21" s="27" t="s"/>
       <c r="J21" s="29" t="s"/>
       <c r="K21" s="28" t="s"/>
@@ -3033,8 +3082,12 @@
       <c r="F22" s="28">
         <v>90</v>
       </c>
-      <c r="G22" s="31" t="s"/>
-      <c r="H22" s="28" t="s"/>
+      <c r="G22" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="28">
+        <v>90</v>
+      </c>
       <c r="I22" s="31" t="s"/>
       <c r="J22" s="29" t="s"/>
       <c r="K22" s="40" t="s"/>
@@ -3062,8 +3115,12 @@
       <c r="F23" s="28">
         <v>90</v>
       </c>
-      <c r="G23" s="27" t="s"/>
-      <c r="H23" s="28" t="s"/>
+      <c r="G23" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="28">
+        <v>90</v>
+      </c>
       <c r="I23" s="27" t="s"/>
       <c r="J23" s="29" t="s"/>
       <c r="K23" s="28" t="s"/>
@@ -3091,8 +3148,12 @@
       <c r="F24" s="28">
         <v>60</v>
       </c>
-      <c r="G24" s="32" t="s"/>
-      <c r="H24" s="28" t="s"/>
+      <c r="G24" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="28">
+        <v>60</v>
+      </c>
       <c r="I24" s="32" t="s"/>
       <c r="J24" s="29" t="s"/>
       <c r="K24" s="41" t="s"/>
@@ -3120,8 +3181,12 @@
       <c r="F25" s="28">
         <v>60</v>
       </c>
-      <c r="G25" s="27" t="s"/>
-      <c r="H25" s="28" t="s"/>
+      <c r="G25" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="28">
+        <v>60</v>
+      </c>
       <c r="I25" s="27" t="s"/>
       <c r="J25" s="29" t="s"/>
       <c r="K25" s="28" t="s"/>
@@ -3149,8 +3214,12 @@
       <c r="F26" s="28">
         <v>60</v>
       </c>
-      <c r="G26" s="27" t="s"/>
-      <c r="H26" s="28" t="s"/>
+      <c r="G26" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="28">
+        <v>60</v>
+      </c>
       <c r="I26" s="32" t="s"/>
       <c r="J26" s="29" t="s"/>
       <c r="K26" s="41" t="s"/>
@@ -3174,8 +3243,12 @@
       <c r="F27" s="28">
         <v>60</v>
       </c>
-      <c r="G27" s="27" t="s"/>
-      <c r="H27" s="28" t="s"/>
+      <c r="G27" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="28">
+        <v>60</v>
+      </c>
       <c r="I27" s="27" t="s"/>
       <c r="J27" s="29" t="s"/>
       <c r="K27" s="28" t="s"/>
@@ -3197,8 +3270,12 @@
       <c r="F28" s="28">
         <v>60</v>
       </c>
-      <c r="G28" s="27" t="s"/>
-      <c r="H28" s="28" t="s"/>
+      <c r="G28" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" s="28">
+        <v>90</v>
+      </c>
       <c r="I28" s="27" t="s"/>
       <c r="J28" s="29" t="s"/>
       <c r="K28" s="28" t="s"/>
@@ -3222,8 +3299,12 @@
       <c r="F29" s="28">
         <v>60</v>
       </c>
-      <c r="G29" s="27" t="s"/>
-      <c r="H29" s="28" t="s"/>
+      <c r="G29" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29" s="28">
+        <v>60</v>
+      </c>
       <c r="I29" s="27" t="s"/>
       <c r="J29" s="29" t="s"/>
       <c r="K29" s="28" t="s"/>
@@ -3291,8 +3372,12 @@
       <c r="F32" s="28">
         <v>60</v>
       </c>
-      <c r="G32" s="27" t="s"/>
-      <c r="H32" s="28" t="s"/>
+      <c r="G32" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="H32" s="28">
+        <v>60</v>
+      </c>
       <c r="I32" s="27" t="s"/>
       <c r="J32" s="29" t="s"/>
       <c r="K32" s="28" t="s"/>
@@ -3312,8 +3397,12 @@
       <c r="F33" s="28">
         <v>60</v>
       </c>
-      <c r="G33" s="27" t="s"/>
-      <c r="H33" s="28" t="s"/>
+      <c r="G33" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="28">
+        <v>60</v>
+      </c>
       <c r="I33" s="27" t="s"/>
       <c r="J33" s="29" t="s"/>
       <c r="K33" s="28" t="s"/>
@@ -3333,8 +3422,12 @@
       <c r="F34" s="28">
         <v>60</v>
       </c>
-      <c r="G34" s="27" t="s"/>
-      <c r="H34" s="28" t="s"/>
+      <c r="G34" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="28">
+        <v>60</v>
+      </c>
       <c r="I34" s="27" t="s"/>
       <c r="J34" s="29" t="s"/>
       <c r="K34" s="28" t="s"/>
@@ -3354,8 +3447,12 @@
       <c r="F35" s="28">
         <v>60</v>
       </c>
-      <c r="G35" s="27" t="s"/>
-      <c r="H35" s="28" t="s"/>
+      <c r="G35" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="28">
+        <v>60</v>
+      </c>
       <c r="I35" s="27" t="s"/>
       <c r="J35" s="29" t="s"/>
       <c r="K35" s="28" t="s"/>
@@ -3371,8 +3468,12 @@
       <c r="D36" s="28" t="s"/>
       <c r="E36" s="27" t="s"/>
       <c r="F36" s="28" t="s"/>
-      <c r="G36" s="27" t="s"/>
-      <c r="H36" s="28" t="s"/>
+      <c r="G36" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="28">
+        <v>60</v>
+      </c>
       <c r="I36" s="27" t="s"/>
       <c r="J36" s="29" t="s"/>
       <c r="K36" s="28" t="s"/>
@@ -3438,7 +3539,7 @@
       </c>
       <c r="H39" s="37">
         <f>=SUM(H21:H38)</f>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="I39" s="36" t="s"/>
       <c r="J39" s="38">
@@ -3457,7 +3558,7 @@
       </c>
       <c r="O39" s="39">
         <f>=SUM(A39:N39)</f>
-        <v>2070</v>
+        <v>3030</v>
       </c>
     </row>
   </sheetData>
@@ -3818,8 +3919,8 @@
         <f>=SUM(A13:H13)</f>
         <v>2280</v>
       </c>
-      <c r="J13" t="s">
-        <v>17</v>
+      <c r="J13" s="152" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4277,37 +4378,37 @@
         <f>=SUM(B2:K5)</f>
         <v>745</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="145" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="69">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B8" s="70" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="69">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D8" s="70" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="69">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F8" s="70" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="69">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="H8" s="70" t="s">
         <v>5</v>
       </c>
       <c r="I8" s="69">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="J8" s="71" t="s">
         <v>6</v>
@@ -4378,7 +4479,7 @@
         <v>42</v>
       </c>
       <c r="H10" s="80">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I10" s="82" t="s"/>
       <c r="J10" s="83" t="s"/>
@@ -4404,10 +4505,10 @@
         <v>90</v>
       </c>
       <c r="G11" s="79" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H11" s="80">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I11" s="82" t="s"/>
       <c r="J11" s="83" t="s"/>
@@ -4432,12 +4533,8 @@
       <c r="F12" s="80">
         <v>60</v>
       </c>
-      <c r="G12" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="80">
-        <v>60</v>
-      </c>
+      <c r="G12" s="79" t="s"/>
+      <c r="H12" s="80" t="s"/>
       <c r="I12" s="82" t="s"/>
       <c r="J12" s="83" t="s"/>
       <c r="K12" s="83" t="s"/>
@@ -4502,7 +4599,7 @@
       <c r="G16" s="85" t="s"/>
       <c r="H16" s="86">
         <f>=SUM(H10:H15)</f>
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I16" s="85" t="s"/>
       <c r="J16" s="87">
@@ -4511,7 +4608,7 @@
       </c>
       <c r="K16" s="88">
         <f>=SUM(A16:J16)</f>
-        <v>870</v>
+        <v>810</v>
       </c>
     </row>
     <row r="17" spans="4:4">
@@ -4678,37 +4775,37 @@
         <f>=SUM(B2:K5)</f>
         <v>730</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="145" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="I8" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>6</v>
@@ -5078,37 +5175,37 @@
         <f>=SUM(B2:K5)</f>
         <v>970</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="145" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="I8" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>6</v>
@@ -5171,7 +5268,7 @@
         <v>54</v>
       </c>
       <c r="H10" s="89">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="I10" s="82" t="s"/>
       <c r="J10" s="83" t="s"/>
@@ -5225,12 +5322,8 @@
       <c r="F12" s="89">
         <v>60</v>
       </c>
-      <c r="G12" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="89">
-        <v>60</v>
-      </c>
+      <c r="G12" s="27" t="s"/>
+      <c r="H12" s="89" t="s"/>
       <c r="I12" s="82" t="s"/>
       <c r="J12" s="83" t="s"/>
       <c r="K12" s="83" t="s"/>
@@ -5295,7 +5388,7 @@
       <c r="G16" s="85" t="s"/>
       <c r="H16" s="86">
         <f>=SUM(H10:H15)</f>
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I16" s="85" t="s"/>
       <c r="J16" s="87">
@@ -5304,7 +5397,7 @@
       </c>
       <c r="K16" s="88">
         <f>=SUM(A16:J16)</f>
-        <v>870</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -5431,37 +5524,37 @@
         <f>=SUM(B2:K4)</f>
         <v>810</v>
       </c>
-      <c r="M4" s="68" t="s">
+      <c r="M4" s="145" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>5</v>
       </c>
       <c r="I7" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>6</v>
@@ -5781,7 +5874,7 @@
         <f>=SUM(B2:K5)</f>
         <v>560</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="145" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5938,37 +6031,37 @@
         <f>=SUM(B2:K5)</f>
         <v>910</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="M5" s="145" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="I8" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>6</v>

--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t/>
   </si>
@@ -75,28 +75,25 @@
     <t>已结清</t>
   </si>
   <si>
+    <t>陈贤乡</t>
+  </si>
+  <si>
+    <t>谢佳俊</t>
+  </si>
+  <si>
+    <t>雷文新</t>
+  </si>
+  <si>
+    <t>詹佳龙</t>
+  </si>
+  <si>
+    <t>简双玲</t>
+  </si>
+  <si>
+    <t>谭运亮</t>
+  </si>
+  <si>
     <t>申请中</t>
-  </si>
-  <si>
-    <t>陈贤乡</t>
-  </si>
-  <si>
-    <t>谢佳俊</t>
-  </si>
-  <si>
-    <t>雷文新</t>
-  </si>
-  <si>
-    <t>詹佳龙</t>
-  </si>
-  <si>
-    <t>简双玲</t>
-  </si>
-  <si>
-    <t>谭运亮</t>
-  </si>
-  <si>
-    <t>已申请</t>
   </si>
   <si>
     <t>余姣</t>
@@ -249,6 +246,43 @@
   </si>
   <si>
     <t>张炳英</t>
+  </si>
+  <si>
+    <t>期二四</t>
+  </si>
+  <si>
+    <t>张永乐</t>
+  </si>
+  <si>
+    <t>温</t>
+  </si>
+  <si>
+    <t>温凯</t>
+  </si>
+  <si>
+    <t>温凯瀚</t>
+  </si>
+  <si>
+    <t>古</t>
+  </si>
+  <si>
+    <t>古庆文</t>
+  </si>
+  <si>
+    <t>陈</t>
+  </si>
+  <si>
+    <t>陈绿</t>
+  </si>
+  <si>
+    <t>陈绿茵</t>
+  </si>
+  <si>
+    <t>物料保管</t>
+  </si>
+  <si>
+    <t xml:space="preserve">谢佳俊
+</t>
   </si>
 </sst>
 </file>
@@ -259,7 +293,7 @@
     <numFmt numFmtId="300" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="301" formatCode="m&quot;月&quot;d&quot;号&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Microsoft YaHei"/>
     </font>
@@ -286,22 +320,14 @@
     </font>
     <font>
       <name val="宋体"/>
-      <color rgb="FF319B62"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
     </font>
     <font>
-      <color rgb="FF319B62"/>
-    </font>
-    <font>
       <color rgb="FF000000"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -330,7 +356,22 @@
       </patternFill>
     </fill>
     <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
       <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF88825"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -341,11 +382,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill/>
@@ -371,16 +407,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF4B183"/>
         <bgColor rgb="FFF4B183"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF88825"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,11 +569,11 @@
     </border>
   </borders>
   <cellStyleXfs>
-    <xf fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -605,7 +631,7 @@
     <xf fontId="3" fillId="2" borderId="9" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="5" fillId="3" borderId="0" xfId="0">
+    <xf fontId="5" fillId="5" borderId="0" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" xfId="0">
@@ -629,6 +655,9 @@
     <xf fontId="3" fillId="2" borderId="12" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
+    <xf fontId="0" fillId="6" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="3" fillId="0" borderId="4" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
@@ -647,7 +676,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="3" fillId="5" borderId="11" xfId="0">
+    <xf fontId="3" fillId="7" borderId="11" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
     <xf fontId="3" fillId="3" borderId="11" xfId="0">
@@ -667,6 +696,9 @@
     </xf>
     <xf fontId="3" fillId="2" borderId="10" xfId="0">
       <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="8" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="5" xfId="0">
       <alignment vertical="bottom" textRotation="0"/>
@@ -695,10 +727,13 @@
     <xf fontId="6" fillId="0" borderId="4" xfId="0">
       <alignment vertical="bottom" textRotation="0"/>
     </xf>
+    <xf fontId="0" fillId="6" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="3" fillId="0" borderId="17" xfId="0">
       <alignment vertical="bottom" textRotation="0" wrapText="0"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="6" borderId="18" xfId="0">
+    <xf numFmtId="300" fontId="3" fillId="9" borderId="18" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="18" xfId="0">
@@ -707,7 +742,7 @@
     <xf fontId="0" fillId="0" borderId="19" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="3" fillId="6" borderId="17" xfId="0">
+    <xf fontId="3" fillId="9" borderId="17" xfId="0">
       <alignment vertical="center" textRotation="0" wrapText="0"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="17" xfId="0">
@@ -749,10 +784,10 @@
     <xf fontId="3" fillId="0" borderId="8" xfId="0">
       <alignment vertical="center" textRotation="0" wrapText="0"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="12" xfId="0">
+    <xf fontId="0" fillId="10" borderId="12" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="0" xfId="0">
+    <xf fontId="7" fillId="6" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
@@ -800,34 +835,34 @@
     <xf fontId="0" fillId="0" borderId="6" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="6" xfId="0">
+    <xf fontId="0" fillId="6" borderId="6" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="1" xfId="0">
+    <xf fontId="0" fillId="10" borderId="1" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="2" xfId="0">
+    <xf fontId="0" fillId="10" borderId="2" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="3" xfId="0">
+    <xf fontId="0" fillId="10" borderId="3" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="3" xfId="0">
+    <xf fontId="0" fillId="6" borderId="3" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="3" fillId="9" borderId="17" xfId="0">
+    <xf fontId="3" fillId="11" borderId="17" xfId="0">
       <alignment vertical="bottom" textRotation="0"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="6" borderId="18" xfId="0">
+    <xf numFmtId="300" fontId="3" fillId="9" borderId="18" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="19" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="10" borderId="17" xfId="0">
+    <xf fontId="3" fillId="12" borderId="17" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="17" xfId="0">
@@ -854,7 +889,7 @@
     <xf fontId="3" fillId="0" borderId="8" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="12" xfId="0">
+    <xf fontId="0" fillId="10" borderId="12" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="7" xfId="0">
@@ -872,19 +907,19 @@
     <xf fontId="3" fillId="0" borderId="17" xfId="0">
       <alignment vertical="bottom" textRotation="0"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="11" borderId="18" xfId="0">
+    <xf numFmtId="300" fontId="3" fillId="13" borderId="18" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="11" borderId="18" xfId="0">
+    <xf numFmtId="300" fontId="3" fillId="13" borderId="18" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="6" borderId="17" xfId="0">
+    <xf fontId="3" fillId="9" borderId="17" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
     <xf fontId="3" fillId="4" borderId="4" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="3" fillId="12" borderId="17" xfId="0">
+    <xf fontId="3" fillId="14" borderId="17" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="17" xfId="0">
@@ -917,13 +952,13 @@
     <xf fontId="0" fillId="0" borderId="9" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="9" xfId="0">
+    <xf fontId="0" fillId="10" borderId="9" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="18" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="6" borderId="17" xfId="0">
+    <xf numFmtId="300" fontId="3" fillId="9" borderId="17" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="13" xfId="0">
@@ -932,7 +967,7 @@
     <xf fontId="0" fillId="0" borderId="19" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="13" borderId="17" xfId="0">
+    <xf fontId="3" fillId="15" borderId="17" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="6" xfId="0">
@@ -950,6 +985,9 @@
     <xf fontId="3" fillId="0" borderId="18" xfId="0">
       <alignment vertical="bottom" textRotation="0"/>
     </xf>
+    <xf fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
     <xf numFmtId="58" fontId="3" fillId="0" borderId="22" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
@@ -959,16 +997,16 @@
     <xf fontId="0" fillId="0" borderId="5" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="11" xfId="0">
+    <xf fontId="0" fillId="6" borderId="11" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="7" xfId="0">
+    <xf fontId="0" fillId="10" borderId="7" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="8" xfId="0">
+    <xf fontId="0" fillId="10" borderId="8" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="8" borderId="12" xfId="0">
+    <xf fontId="0" fillId="6" borderId="12" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="301" fontId="0" fillId="0" borderId="1" xfId="0">
@@ -977,35 +1015,35 @@
     <xf fontId="0" fillId="0" borderId="3" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="8" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="8" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="7" fillId="8" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="5" fillId="14" borderId="0" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="9" fillId="14" borderId="0" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="15" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="15" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="8" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="7" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="9" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="bottom" textRotation="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -1601,7 +1639,7 @@
         <f>=SUM(A8:P8)</f>
         <v>1980</v>
       </c>
-      <c r="R8" s="148" t="s">
+      <c r="R8" s="19" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1984,7 +2022,7 @@
         <f>=SUM(A19:N19)</f>
         <v>1890</v>
       </c>
-      <c r="P19" s="150" t="s">
+      <c r="P19" s="27" t="s">
         <v>16</v>
       </c>
       <c r="Q19" s="23" t="s"/>
@@ -2061,405 +2099,550 @@
   <dimension ref="B200"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:15">
       <c r="A1" s="4">
         <v>46191</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="4">
+      <c r="C1" s="5" t="s"/>
+      <c r="D1" s="4">
         <v>46192</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s"/>
+      <c r="F1" s="5" t="s"/>
+      <c r="G1" s="5" t="s"/>
+      <c r="H1" s="5" t="s"/>
+      <c r="I1" s="5" t="s"/>
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4">
+      <c r="K1" s="4">
         <v>46193</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="134">
+      <c r="M1" s="138">
         <v>46194</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="135" t="s"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="117" t="s">
+      <c r="O1" s="139" t="s"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="140">
+        <v>90</v>
+      </c>
+      <c r="D2" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="136">
-        <v>90</v>
-      </c>
-      <c r="C2" s="117" t="s">
+      <c r="J2" s="140">
+        <v>90</v>
+      </c>
+      <c r="K2" s="120" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="140">
+        <v>60</v>
+      </c>
+      <c r="M2" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="136">
-        <v>90</v>
-      </c>
-      <c r="E2" s="117" t="s">
+      <c r="N2" s="140">
+        <v>60</v>
+      </c>
+      <c r="O2" s="99" t="s"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="136">
-        <v>60</v>
-      </c>
-      <c r="G2" s="117" t="s">
+      <c r="B3" s="140">
+        <v>60</v>
+      </c>
+      <c r="D3" s="120" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="140">
+        <v>90</v>
+      </c>
+      <c r="K3" s="120" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="140">
+        <v>60</v>
+      </c>
+      <c r="M3" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="136">
-        <v>60</v>
-      </c>
-      <c r="I2" s="96" t="s"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="117" t="s">
+      <c r="N3" s="140">
+        <v>90</v>
+      </c>
+      <c r="O3" s="99" t="s"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="120" t="s"/>
+      <c r="B4" s="140" t="s"/>
+      <c r="D4" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="136">
-        <v>60</v>
-      </c>
-      <c r="C3" s="117" t="s">
+      <c r="J4" s="140">
+        <v>60</v>
+      </c>
+      <c r="K4" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="136">
-        <v>90</v>
-      </c>
-      <c r="E3" s="117" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="136">
-        <v>60</v>
-      </c>
-      <c r="G3" s="117" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" s="136">
-        <v>90</v>
-      </c>
-      <c r="I3" s="96" t="s"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="117" t="s"/>
-      <c r="B4" s="136" t="s"/>
-      <c r="C4" s="117" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="136">
-        <v>60</v>
-      </c>
-      <c r="E4" s="117" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4" s="136">
-        <v>90</v>
-      </c>
-      <c r="G4" s="117" t="s"/>
-      <c r="H4" s="136" t="s"/>
-      <c r="I4" s="96" t="s"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="117" t="s"/>
-      <c r="B5" s="136" t="s"/>
-      <c r="C5" s="117" t="s"/>
-      <c r="D5" s="136" t="s"/>
-      <c r="E5" s="117" t="s"/>
-      <c r="F5" s="136" t="s"/>
-      <c r="G5" s="117" t="s"/>
-      <c r="H5" s="136" t="s"/>
-      <c r="I5" s="96" t="s"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="117" t="s"/>
-      <c r="B6" s="136" t="s"/>
-      <c r="C6" s="117" t="s"/>
-      <c r="D6" s="136" t="s"/>
-      <c r="E6" s="117" t="s"/>
-      <c r="F6" s="136" t="s"/>
-      <c r="G6" s="117" t="s"/>
-      <c r="H6" s="136" t="s"/>
-      <c r="I6" s="96" t="s"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="117" t="s"/>
-      <c r="B7" s="136" t="s"/>
-      <c r="C7" s="117" t="s"/>
-      <c r="D7" s="136" t="s"/>
-      <c r="E7" s="117" t="s"/>
-      <c r="F7" s="136" t="s"/>
-      <c r="G7" s="117" t="s"/>
-      <c r="H7" s="136" t="s"/>
-      <c r="I7" s="137" t="s">
+      <c r="L4" s="140">
+        <v>90</v>
+      </c>
+      <c r="M4" s="120" t="s"/>
+      <c r="N4" s="140" t="s"/>
+      <c r="O4" s="99" t="s"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="120" t="s"/>
+      <c r="B5" s="140" t="s"/>
+      <c r="D5" s="120" t="s"/>
+      <c r="J5" s="140" t="s"/>
+      <c r="K5" s="120" t="s"/>
+      <c r="L5" s="140" t="s"/>
+      <c r="M5" s="120" t="s"/>
+      <c r="N5" s="140" t="s"/>
+      <c r="O5" s="99" t="s"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="120" t="s"/>
+      <c r="B6" s="140" t="s"/>
+      <c r="D6" s="120" t="s"/>
+      <c r="J6" s="140" t="s"/>
+      <c r="K6" s="120" t="s"/>
+      <c r="L6" s="140" t="s"/>
+      <c r="M6" s="120" t="s"/>
+      <c r="N6" s="140" t="s"/>
+      <c r="O6" s="99" t="s"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="120" t="s"/>
+      <c r="B7" s="140" t="s"/>
+      <c r="D7" s="120" t="s"/>
+      <c r="J7" s="140" t="s"/>
+      <c r="K7" s="120" t="s"/>
+      <c r="L7" s="140" t="s"/>
+      <c r="M7" s="120" t="s"/>
+      <c r="N7" s="140" t="s"/>
+      <c r="O7" s="141" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="138" t="s"/>
-      <c r="B8" s="139">
+    <row r="8" spans="1:16">
+      <c r="A8" s="142" t="s"/>
+      <c r="B8" s="143">
         <f>=SUM(B2:B7)</f>
         <v>150</v>
       </c>
-      <c r="C8" s="138" t="s"/>
-      <c r="D8" s="139">
-        <f>=SUM(D2:D7)</f>
+      <c r="C8" s="143" t="s"/>
+      <c r="D8" s="142" t="s"/>
+      <c r="E8" s="143" t="s"/>
+      <c r="F8" s="143" t="s"/>
+      <c r="G8" s="143" t="s"/>
+      <c r="H8" s="143" t="s"/>
+      <c r="I8" s="143" t="s"/>
+      <c r="J8" s="143">
+        <f>=SUM(J2:J7)</f>
         <v>240</v>
       </c>
-      <c r="E8" s="138" t="s"/>
-      <c r="F8" s="139">
-        <f>=SUM(F2:F7)</f>
+      <c r="K8" s="142" t="s"/>
+      <c r="L8" s="143">
+        <f>=SUM(L2:L7)</f>
         <v>210</v>
       </c>
-      <c r="G8" s="138" t="s"/>
-      <c r="H8" s="139">
-        <f>=SUM(H2:H7)</f>
+      <c r="M8" s="142" t="s"/>
+      <c r="N8" s="143">
+        <f>=SUM(N2:N7)</f>
         <v>150</v>
       </c>
-      <c r="I8" s="140">
-        <f>=SUM(A8:H8)</f>
+      <c r="O8" s="144">
+        <f>=SUM(A8:N8)</f>
         <v>750</v>
       </c>
-      <c r="J8" s="152" t="s">
+      <c r="P8" s="51" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:22"/>
-    <row r="10" spans="1:22"/>
-    <row r="11" spans="1:2">
-      <c r="A11" s="141">
+    <row r="9" spans="1:28"/>
+    <row r="10" spans="1:28"/>
+    <row r="11" spans="1:15">
+      <c r="A11" s="145">
         <v>46195</v>
       </c>
-      <c r="B11" s="142" t="s">
+      <c r="B11" s="146" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="117" t="s">
+      <c r="C11" s="147">
+        <v>46196</v>
+      </c>
+      <c r="D11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="147">
+        <v>46197</v>
+      </c>
+      <c r="F11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="147">
+        <v>46198</v>
+      </c>
+      <c r="H11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I11" s="147">
+        <v>46199</v>
+      </c>
+      <c r="J11" t="s">
+        <v>74</v>
+      </c>
+      <c r="K11" s="147">
+        <v>46200</v>
+      </c>
+      <c r="L11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" s="147">
+        <v>46201</v>
+      </c>
+      <c r="N11" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" s="147" t="s"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="118">
+        <v>75</v>
+      </c>
+      <c r="C12" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12">
+        <v>75</v>
+      </c>
+      <c r="E12" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12">
+        <v>135</v>
+      </c>
+      <c r="G12" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="120" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="118">
+        <v>60</v>
+      </c>
+      <c r="C13" s="120" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13">
+        <v>75</v>
+      </c>
+      <c r="E13" s="120" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13">
+        <v>60</v>
+      </c>
+      <c r="G13" s="120" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="120" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="118">
+        <v>90</v>
+      </c>
+      <c r="C14" s="120" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="120" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14">
+        <v>90</v>
+      </c>
+      <c r="G14" s="120" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="120" t="s"/>
+      <c r="B15" s="118" t="s"/>
+      <c r="C15" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="115">
+      <c r="D15">
         <v>75</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="117" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="115">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="117" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="115">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="117" t="s"/>
-      <c r="B15" s="115" t="s"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="117" t="s"/>
-      <c r="B16" s="115" t="s"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="117" t="s"/>
-      <c r="B17" s="115" t="s"/>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15">
+        <v>60</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="120" t="s"/>
+      <c r="B16" s="118" t="s"/>
+      <c r="E16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="120" t="s"/>
+      <c r="B17" s="118" t="s"/>
+      <c r="E17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17">
+        <v>60</v>
+      </c>
+      <c r="G17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17">
+        <v>60</v>
+      </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="138" t="s"/>
-      <c r="B18" s="123">
+      <c r="A18" s="142" t="s"/>
+      <c r="B18" s="126">
         <f>=SUM(B12:B17)</f>
         <v>225</v>
       </c>
     </row>
-    <row r="19" spans="1:22"/>
-    <row r="20" spans="1:22"/>
-    <row r="21" spans="1:22"/>
-    <row r="22" spans="1:22"/>
-    <row r="23" spans="1:22"/>
-    <row r="24" spans="1:22"/>
-    <row r="25" spans="1:22"/>
-    <row r="26" spans="1:22"/>
-    <row r="27" spans="1:22"/>
-    <row r="28" spans="1:22"/>
-    <row r="29" spans="1:22"/>
-    <row r="30" spans="1:22"/>
-    <row r="31" spans="1:22"/>
-    <row r="32" spans="1:22"/>
-    <row r="33" spans="1:22"/>
-    <row r="34" spans="1:22"/>
-    <row r="35" spans="1:22"/>
-    <row r="36" spans="1:22"/>
-    <row r="37" spans="1:22"/>
-    <row r="38" spans="1:22"/>
-    <row r="39" spans="1:22"/>
-    <row r="40" spans="1:22"/>
-    <row r="41" spans="1:22"/>
-    <row r="42" spans="1:22"/>
-    <row r="43" spans="1:22"/>
-    <row r="44" spans="1:22"/>
-    <row r="45" spans="1:22"/>
-    <row r="46" spans="1:22"/>
-    <row r="47" spans="1:22"/>
-    <row r="48" spans="1:22"/>
-    <row r="49" spans="1:22"/>
-    <row r="50" spans="1:22"/>
-    <row r="51" spans="1:22"/>
-    <row r="52" spans="1:22"/>
-    <row r="53" spans="1:22"/>
-    <row r="54" spans="1:22"/>
-    <row r="55" spans="1:22"/>
-    <row r="56" spans="1:22"/>
-    <row r="57" spans="1:22"/>
-    <row r="58" spans="1:22"/>
-    <row r="59" spans="1:22"/>
-    <row r="60" spans="1:22"/>
-    <row r="61" spans="1:22"/>
-    <row r="62" spans="1:22"/>
-    <row r="63" spans="1:22"/>
-    <row r="64" spans="1:22"/>
-    <row r="65" spans="1:22"/>
-    <row r="66" spans="1:22"/>
-    <row r="67" spans="1:22"/>
-    <row r="68" spans="1:22"/>
-    <row r="69" spans="1:22"/>
-    <row r="70" spans="1:22"/>
-    <row r="71" spans="1:22"/>
-    <row r="72" spans="1:22"/>
-    <row r="73" spans="1:22"/>
-    <row r="74" spans="1:22"/>
-    <row r="75" spans="1:22"/>
-    <row r="76" spans="1:22"/>
-    <row r="77" spans="1:22"/>
-    <row r="78" spans="1:22"/>
-    <row r="79" spans="1:22"/>
-    <row r="80" spans="1:22"/>
-    <row r="81" spans="1:22"/>
-    <row r="82" spans="1:22"/>
-    <row r="83" spans="1:22"/>
-    <row r="84" spans="1:22"/>
-    <row r="85" spans="1:22"/>
-    <row r="86" spans="1:22"/>
-    <row r="87" spans="1:22"/>
-    <row r="88" spans="1:22"/>
-    <row r="89" spans="1:22"/>
-    <row r="90" spans="1:22"/>
-    <row r="91" spans="1:22"/>
-    <row r="92" spans="1:22"/>
-    <row r="93" spans="1:22"/>
-    <row r="94" spans="1:22"/>
-    <row r="95" spans="1:22"/>
-    <row r="96" spans="1:22"/>
-    <row r="97" spans="1:22"/>
-    <row r="98" spans="1:22"/>
-    <row r="99" spans="1:22"/>
-    <row r="100" spans="1:22"/>
-    <row r="101" spans="1:22"/>
-    <row r="102" spans="1:22"/>
-    <row r="103" spans="1:22"/>
-    <row r="104" spans="1:22"/>
-    <row r="105" spans="1:22"/>
-    <row r="106" spans="1:22"/>
-    <row r="107" spans="1:22"/>
-    <row r="108" spans="1:22"/>
-    <row r="109" spans="1:22"/>
-    <row r="110" spans="1:22"/>
-    <row r="111" spans="1:22"/>
-    <row r="112" spans="1:22"/>
-    <row r="113" spans="1:22"/>
-    <row r="114" spans="1:22"/>
-    <row r="115" spans="1:22"/>
-    <row r="116" spans="1:22"/>
-    <row r="117" spans="1:22"/>
-    <row r="118" spans="1:22"/>
-    <row r="119" spans="1:22"/>
-    <row r="120" spans="1:22"/>
-    <row r="121" spans="1:22"/>
-    <row r="122" spans="1:22"/>
-    <row r="123" spans="1:22"/>
-    <row r="124" spans="1:22"/>
-    <row r="125" spans="1:22"/>
-    <row r="126" spans="1:22"/>
-    <row r="127" spans="1:22"/>
-    <row r="128" spans="1:22"/>
-    <row r="129" spans="1:22"/>
-    <row r="130" spans="1:22"/>
-    <row r="131" spans="1:22"/>
-    <row r="132" spans="1:22"/>
-    <row r="133" spans="1:22"/>
-    <row r="134" spans="1:22"/>
-    <row r="135" spans="1:22"/>
-    <row r="136" spans="1:22"/>
-    <row r="137" spans="1:22"/>
-    <row r="138" spans="1:22"/>
-    <row r="139" spans="1:22"/>
-    <row r="140" spans="1:22"/>
-    <row r="141" spans="1:22"/>
-    <row r="142" spans="1:22"/>
-    <row r="143" spans="1:22"/>
-    <row r="144" spans="1:22"/>
-    <row r="145" spans="1:22"/>
-    <row r="146" spans="1:22"/>
-    <row r="147" spans="1:22"/>
-    <row r="148" spans="1:22"/>
-    <row r="149" spans="1:22"/>
-    <row r="150" spans="1:22"/>
-    <row r="151" spans="1:22"/>
-    <row r="152" spans="1:22"/>
-    <row r="153" spans="1:22"/>
-    <row r="154" spans="1:22"/>
-    <row r="155" spans="1:22"/>
-    <row r="156" spans="1:22"/>
-    <row r="157" spans="1:22"/>
-    <row r="158" spans="1:22"/>
-    <row r="159" spans="1:22"/>
-    <row r="160" spans="1:22"/>
-    <row r="161" spans="1:22"/>
-    <row r="162" spans="1:22"/>
-    <row r="163" spans="1:22"/>
-    <row r="164" spans="1:22"/>
-    <row r="165" spans="1:22"/>
-    <row r="166" spans="1:22"/>
-    <row r="167" spans="1:22"/>
-    <row r="168" spans="1:22"/>
-    <row r="169" spans="1:22"/>
-    <row r="170" spans="1:22"/>
-    <row r="171" spans="1:22"/>
-    <row r="172" spans="1:22"/>
-    <row r="173" spans="1:22"/>
-    <row r="174" spans="1:22"/>
-    <row r="175" spans="1:22"/>
-    <row r="176" spans="1:22"/>
-    <row r="177" spans="1:22"/>
-    <row r="178" spans="1:22"/>
-    <row r="179" spans="1:22"/>
-    <row r="180" spans="1:22"/>
-    <row r="181" spans="1:22"/>
-    <row r="182" spans="1:22"/>
-    <row r="183" spans="1:22"/>
-    <row r="184" spans="1:22"/>
-    <row r="185" spans="1:22"/>
-    <row r="186" spans="1:22"/>
-    <row r="187" spans="1:22"/>
-    <row r="188" spans="1:22"/>
-    <row r="189" spans="1:22"/>
-    <row r="190" spans="1:22"/>
-    <row r="191" spans="1:22"/>
-    <row r="192" spans="1:22"/>
-    <row r="193" spans="1:22"/>
-    <row r="194" spans="1:22"/>
-    <row r="195" spans="1:22"/>
-    <row r="196" spans="1:22"/>
-    <row r="197" spans="1:22"/>
-    <row r="198" spans="1:22"/>
-    <row r="199" spans="1:22"/>
-    <row r="200" spans="1:22"/>
+    <row r="19" spans="1:28"/>
+    <row r="20" spans="1:28"/>
+    <row r="21" spans="1:28"/>
+    <row r="22" spans="1:28"/>
+    <row r="23" spans="1:28"/>
+    <row r="24" spans="1:28"/>
+    <row r="25" spans="1:28"/>
+    <row r="26" spans="1:28"/>
+    <row r="27" spans="1:28"/>
+    <row r="28" spans="1:28"/>
+    <row r="29" spans="1:28"/>
+    <row r="30" spans="1:28"/>
+    <row r="31" spans="1:28"/>
+    <row r="32" spans="1:28"/>
+    <row r="33" spans="1:28"/>
+    <row r="34" spans="1:28"/>
+    <row r="35" spans="1:28"/>
+    <row r="36" spans="1:28"/>
+    <row r="37" spans="1:28"/>
+    <row r="38" spans="1:28"/>
+    <row r="39" spans="1:28"/>
+    <row r="40" spans="1:28"/>
+    <row r="41" spans="1:28"/>
+    <row r="42" spans="1:28"/>
+    <row r="43" spans="1:28"/>
+    <row r="44" spans="1:28"/>
+    <row r="45" spans="1:28"/>
+    <row r="46" spans="1:28"/>
+    <row r="47" spans="1:28"/>
+    <row r="48" spans="1:28"/>
+    <row r="49" spans="1:28"/>
+    <row r="50" spans="1:28"/>
+    <row r="51" spans="1:28"/>
+    <row r="52" spans="1:28"/>
+    <row r="53" spans="1:28"/>
+    <row r="54" spans="1:28"/>
+    <row r="55" spans="1:28"/>
+    <row r="56" spans="1:28"/>
+    <row r="57" spans="1:28"/>
+    <row r="58" spans="1:28"/>
+    <row r="59" spans="1:28"/>
+    <row r="60" spans="1:28"/>
+    <row r="61" spans="1:28"/>
+    <row r="62" spans="1:28"/>
+    <row r="63" spans="1:28"/>
+    <row r="64" spans="1:28"/>
+    <row r="65" spans="1:28"/>
+    <row r="66" spans="1:28"/>
+    <row r="67" spans="1:28"/>
+    <row r="68" spans="1:28"/>
+    <row r="69" spans="1:28"/>
+    <row r="70" spans="1:28"/>
+    <row r="71" spans="1:28"/>
+    <row r="72" spans="1:28"/>
+    <row r="73" spans="1:28"/>
+    <row r="74" spans="1:28"/>
+    <row r="75" spans="1:28"/>
+    <row r="76" spans="1:28"/>
+    <row r="77" spans="1:28"/>
+    <row r="78" spans="1:28"/>
+    <row r="79" spans="1:28"/>
+    <row r="80" spans="1:28"/>
+    <row r="81" spans="1:28"/>
+    <row r="82" spans="1:28"/>
+    <row r="83" spans="1:28"/>
+    <row r="84" spans="1:28"/>
+    <row r="85" spans="1:28"/>
+    <row r="86" spans="1:28"/>
+    <row r="87" spans="1:28"/>
+    <row r="88" spans="1:28"/>
+    <row r="89" spans="1:28"/>
+    <row r="90" spans="1:28"/>
+    <row r="91" spans="1:28"/>
+    <row r="92" spans="1:28"/>
+    <row r="93" spans="1:28"/>
+    <row r="94" spans="1:28"/>
+    <row r="95" spans="1:28"/>
+    <row r="96" spans="1:28"/>
+    <row r="97" spans="1:28"/>
+    <row r="98" spans="1:28"/>
+    <row r="99" spans="1:28"/>
+    <row r="100" spans="1:28"/>
+    <row r="101" spans="1:28"/>
+    <row r="102" spans="1:28"/>
+    <row r="103" spans="1:28"/>
+    <row r="104" spans="1:28"/>
+    <row r="105" spans="1:28"/>
+    <row r="106" spans="1:28"/>
+    <row r="107" spans="1:28"/>
+    <row r="108" spans="1:28"/>
+    <row r="109" spans="1:28"/>
+    <row r="110" spans="1:28"/>
+    <row r="111" spans="1:28"/>
+    <row r="112" spans="1:28"/>
+    <row r="113" spans="1:28"/>
+    <row r="114" spans="1:28"/>
+    <row r="115" spans="1:28"/>
+    <row r="116" spans="1:28"/>
+    <row r="117" spans="1:28"/>
+    <row r="118" spans="1:28"/>
+    <row r="119" spans="1:28"/>
+    <row r="120" spans="1:28"/>
+    <row r="121" spans="1:28"/>
+    <row r="122" spans="1:28"/>
+    <row r="123" spans="1:28"/>
+    <row r="124" spans="1:28"/>
+    <row r="125" spans="1:28"/>
+    <row r="126" spans="1:28"/>
+    <row r="127" spans="1:28"/>
+    <row r="128" spans="1:28"/>
+    <row r="129" spans="1:28"/>
+    <row r="130" spans="1:28"/>
+    <row r="131" spans="1:28"/>
+    <row r="132" spans="1:28"/>
+    <row r="133" spans="1:28"/>
+    <row r="134" spans="1:28"/>
+    <row r="135" spans="1:28"/>
+    <row r="136" spans="1:28"/>
+    <row r="137" spans="1:28"/>
+    <row r="138" spans="1:28"/>
+    <row r="139" spans="1:28"/>
+    <row r="140" spans="1:28"/>
+    <row r="141" spans="1:28"/>
+    <row r="142" spans="1:28"/>
+    <row r="143" spans="1:28"/>
+    <row r="144" spans="1:28"/>
+    <row r="145" spans="1:28"/>
+    <row r="146" spans="1:28"/>
+    <row r="147" spans="1:28"/>
+    <row r="148" spans="1:28"/>
+    <row r="149" spans="1:28"/>
+    <row r="150" spans="1:28"/>
+    <row r="151" spans="1:28"/>
+    <row r="152" spans="1:28"/>
+    <row r="153" spans="1:28"/>
+    <row r="154" spans="1:28"/>
+    <row r="155" spans="1:28"/>
+    <row r="156" spans="1:28"/>
+    <row r="157" spans="1:28"/>
+    <row r="158" spans="1:28"/>
+    <row r="159" spans="1:28"/>
+    <row r="160" spans="1:28"/>
+    <row r="161" spans="1:28"/>
+    <row r="162" spans="1:28"/>
+    <row r="163" spans="1:28"/>
+    <row r="164" spans="1:28"/>
+    <row r="165" spans="1:28"/>
+    <row r="166" spans="1:28"/>
+    <row r="167" spans="1:28"/>
+    <row r="168" spans="1:28"/>
+    <row r="169" spans="1:28"/>
+    <row r="170" spans="1:28"/>
+    <row r="171" spans="1:28"/>
+    <row r="172" spans="1:28"/>
+    <row r="173" spans="1:28"/>
+    <row r="174" spans="1:28"/>
+    <row r="175" spans="1:28"/>
+    <row r="176" spans="1:28"/>
+    <row r="177" spans="1:28"/>
+    <row r="178" spans="1:28"/>
+    <row r="179" spans="1:28"/>
+    <row r="180" spans="1:28"/>
+    <row r="181" spans="1:28"/>
+    <row r="182" spans="1:28"/>
+    <row r="183" spans="1:28"/>
+    <row r="184" spans="1:28"/>
+    <row r="185" spans="1:28"/>
+    <row r="186" spans="1:28"/>
+    <row r="187" spans="1:28"/>
+    <row r="188" spans="1:28"/>
+    <row r="189" spans="1:28"/>
+    <row r="190" spans="1:28"/>
+    <row r="191" spans="1:28"/>
+    <row r="192" spans="1:28"/>
+    <row r="193" spans="1:28"/>
+    <row r="194" spans="1:28"/>
+    <row r="195" spans="1:28"/>
+    <row r="196" spans="1:28"/>
+    <row r="197" spans="1:28"/>
+    <row r="198" spans="1:28"/>
+    <row r="199" spans="1:28"/>
+    <row r="200" spans="1:28"/>
   </sheetData>
 </worksheet>
 </file>
@@ -2521,423 +2704,423 @@
       <c r="O1" s="21" t="s"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="28" t="s">
+      <c r="H2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="J2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="L2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="28" t="s">
+      <c r="M2" s="29" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="30" t="s"/>
+      <c r="O2" s="31" t="s"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="31" t="s"/>
-      <c r="B3" s="28" t="s"/>
-      <c r="C3" s="27" t="s"/>
-      <c r="D3" s="28" t="s"/>
-      <c r="E3" s="27" t="s">
+      <c r="A3" s="32" t="s"/>
+      <c r="B3" s="29" t="s"/>
+      <c r="C3" s="28" t="s"/>
+      <c r="D3" s="29" t="s"/>
+      <c r="E3" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="29">
+        <v>90</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="29">
+        <v>90</v>
+      </c>
+      <c r="I3" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="29">
+        <v>90</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="29">
+        <v>90</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="29">
+        <v>90</v>
+      </c>
+      <c r="O3" s="31" t="s"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="28" t="s"/>
+      <c r="B4" s="29" t="s"/>
+      <c r="C4" s="32" t="s"/>
+      <c r="D4" s="29" t="s"/>
+      <c r="E4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="28">
-        <v>90</v>
-      </c>
-      <c r="G3" s="27" t="s">
+      <c r="F4" s="29">
+        <v>90</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="28">
-        <v>90</v>
-      </c>
-      <c r="I3" s="27" t="s">
+      <c r="H4" s="29">
+        <v>90</v>
+      </c>
+      <c r="I4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="28">
-        <v>90</v>
-      </c>
-      <c r="K3" s="27" t="s">
+      <c r="J4" s="29">
+        <v>90</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="28">
-        <v>90</v>
-      </c>
-      <c r="M3" s="27" t="s">
+      <c r="L4" s="29">
+        <v>90</v>
+      </c>
+      <c r="M4" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="28">
-        <v>90</v>
-      </c>
-      <c r="O3" s="30" t="s"/>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="27" t="s"/>
-      <c r="B4" s="28" t="s"/>
-      <c r="C4" s="31" t="s"/>
-      <c r="D4" s="28" t="s"/>
-      <c r="E4" s="31" t="s">
+      <c r="N4" s="29">
+        <v>90</v>
+      </c>
+      <c r="O4" s="31" t="s"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="28" t="s"/>
+      <c r="B5" s="29" t="s"/>
+      <c r="C5" s="28" t="s"/>
+      <c r="D5" s="29" t="s"/>
+      <c r="E5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="28">
-        <v>90</v>
-      </c>
-      <c r="G4" s="31" t="s">
+      <c r="F5" s="29">
+        <v>90</v>
+      </c>
+      <c r="G5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="28">
-        <v>90</v>
-      </c>
-      <c r="I4" s="31" t="s">
+      <c r="H5" s="29">
+        <v>90</v>
+      </c>
+      <c r="I5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="28">
-        <v>90</v>
-      </c>
-      <c r="K4" s="31" t="s">
+      <c r="J5" s="29">
+        <v>90</v>
+      </c>
+      <c r="K5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="28">
-        <v>90</v>
-      </c>
-      <c r="M4" s="31" t="s">
+      <c r="L5" s="29">
+        <v>90</v>
+      </c>
+      <c r="M5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="28">
-        <v>90</v>
-      </c>
-      <c r="O4" s="30" t="s"/>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="27" t="s"/>
-      <c r="B5" s="28" t="s"/>
-      <c r="C5" s="27" t="s"/>
-      <c r="D5" s="28" t="s"/>
-      <c r="E5" s="27" t="s">
+      <c r="N5" s="29">
+        <v>90</v>
+      </c>
+      <c r="O5" s="31" t="s"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="28" t="s"/>
+      <c r="B6" s="29" t="s"/>
+      <c r="C6" s="28" t="s"/>
+      <c r="D6" s="29" t="s"/>
+      <c r="E6" s="28" t="s"/>
+      <c r="F6" s="29" t="s"/>
+      <c r="G6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="28">
-        <v>90</v>
-      </c>
-      <c r="G5" s="27" t="s">
+      <c r="H6" s="29">
+        <v>60</v>
+      </c>
+      <c r="I6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="28">
-        <v>90</v>
-      </c>
-      <c r="I5" s="27" t="s">
+      <c r="J6" s="29">
+        <v>60</v>
+      </c>
+      <c r="K6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="28">
-        <v>90</v>
-      </c>
-      <c r="K5" s="27" t="s">
+      <c r="L6" s="29">
+        <v>60</v>
+      </c>
+      <c r="M6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="28">
-        <v>90</v>
-      </c>
-      <c r="M5" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="N5" s="28">
-        <v>90</v>
-      </c>
-      <c r="O5" s="30" t="s"/>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="27" t="s"/>
-      <c r="B6" s="28" t="s"/>
-      <c r="C6" s="27" t="s"/>
-      <c r="D6" s="28" t="s"/>
-      <c r="E6" s="27" t="s"/>
-      <c r="F6" s="28" t="s"/>
-      <c r="G6" s="32" t="s">
+      <c r="N6" s="29">
+        <v>60</v>
+      </c>
+      <c r="O6" s="31" t="s"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="28" t="s"/>
+      <c r="B7" s="29" t="s"/>
+      <c r="C7" s="28" t="s"/>
+      <c r="D7" s="29" t="s"/>
+      <c r="E7" s="28" t="s"/>
+      <c r="F7" s="29" t="s"/>
+      <c r="G7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="28">
-        <v>60</v>
-      </c>
-      <c r="I6" s="32" t="s">
+      <c r="H7" s="29">
+        <v>60</v>
+      </c>
+      <c r="I7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="28">
-        <v>60</v>
-      </c>
-      <c r="K6" s="32" t="s">
+      <c r="J7" s="29">
+        <v>60</v>
+      </c>
+      <c r="K7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="28">
-        <v>60</v>
-      </c>
-      <c r="M6" s="32" t="s">
+      <c r="L7" s="29">
+        <v>60</v>
+      </c>
+      <c r="M7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="28">
-        <v>60</v>
-      </c>
-      <c r="O6" s="30" t="s"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="27" t="s"/>
-      <c r="B7" s="28" t="s"/>
-      <c r="C7" s="27" t="s"/>
-      <c r="D7" s="28" t="s"/>
-      <c r="E7" s="27" t="s"/>
-      <c r="F7" s="28" t="s"/>
-      <c r="G7" s="27" t="s">
+      <c r="N7" s="29">
+        <v>60</v>
+      </c>
+      <c r="O7" s="34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="28" t="s"/>
+      <c r="B8" s="29" t="s"/>
+      <c r="C8" s="28" t="s"/>
+      <c r="D8" s="29" t="s"/>
+      <c r="E8" s="28" t="s"/>
+      <c r="F8" s="29" t="s"/>
+      <c r="G8" s="28" t="s"/>
+      <c r="H8" s="29" t="s"/>
+      <c r="I8" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="28">
-        <v>60</v>
-      </c>
-      <c r="I7" s="27" t="s">
+      <c r="J8" s="29">
+        <v>60</v>
+      </c>
+      <c r="K8" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="28">
-        <v>60</v>
-      </c>
-      <c r="K7" s="27" t="s">
+      <c r="L8" s="29">
+        <v>60</v>
+      </c>
+      <c r="M8" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="28">
-        <v>60</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="28">
-        <v>60</v>
-      </c>
-      <c r="O7" s="33" t="s">
+      <c r="N8" s="29">
+        <v>60</v>
+      </c>
+      <c r="O8" s="35" t="s"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="28" t="s"/>
+      <c r="B9" s="29" t="s"/>
+      <c r="C9" s="28" t="s"/>
+      <c r="D9" s="29" t="s"/>
+      <c r="E9" s="28" t="s"/>
+      <c r="F9" s="29" t="s"/>
+      <c r="G9" s="28" t="s"/>
+      <c r="H9" s="29" t="s"/>
+      <c r="I9" s="28" t="s"/>
+      <c r="J9" s="29" t="s"/>
+      <c r="K9" s="28" t="s"/>
+      <c r="L9" s="30" t="s"/>
+      <c r="M9" s="29" t="s"/>
+      <c r="N9" s="8" t="s"/>
+      <c r="O9" s="35" t="s"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="28" t="s"/>
+      <c r="B10" s="29" t="s"/>
+      <c r="C10" s="28" t="s"/>
+      <c r="D10" s="29" t="s"/>
+      <c r="E10" s="28" t="s"/>
+      <c r="F10" s="29" t="s"/>
+      <c r="G10" s="28" t="s"/>
+      <c r="H10" s="29" t="s"/>
+      <c r="I10" s="28" t="s"/>
+      <c r="J10" s="29" t="s"/>
+      <c r="K10" s="28" t="s"/>
+      <c r="L10" s="30" t="s"/>
+      <c r="M10" s="29" t="s"/>
+      <c r="N10" s="8" t="s"/>
+      <c r="O10" s="35" t="s"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="28" t="s"/>
+      <c r="B11" s="29" t="s"/>
+      <c r="C11" s="28" t="s"/>
+      <c r="D11" s="29" t="s"/>
+      <c r="E11" s="28" t="s"/>
+      <c r="F11" s="29" t="s"/>
+      <c r="G11" s="28" t="s"/>
+      <c r="H11" s="29" t="s"/>
+      <c r="I11" s="28" t="s"/>
+      <c r="J11" s="29" t="s"/>
+      <c r="K11" s="28" t="s"/>
+      <c r="L11" s="30" t="s"/>
+      <c r="M11" s="29" t="s"/>
+      <c r="N11" s="8" t="s"/>
+      <c r="O11" s="35" t="s"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="28" t="s"/>
+      <c r="B12" s="29" t="s"/>
+      <c r="C12" s="28" t="s"/>
+      <c r="D12" s="29" t="s"/>
+      <c r="E12" s="28" t="s"/>
+      <c r="F12" s="29" t="s"/>
+      <c r="G12" s="28" t="s"/>
+      <c r="H12" s="29" t="s"/>
+      <c r="I12" s="28" t="s"/>
+      <c r="J12" s="29" t="s"/>
+      <c r="K12" s="28" t="s"/>
+      <c r="L12" s="30" t="s"/>
+      <c r="M12" s="29" t="s"/>
+      <c r="N12" s="8" t="s"/>
+      <c r="O12" s="35" t="s"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="28" t="s"/>
+      <c r="B13" s="29" t="s"/>
+      <c r="C13" s="28" t="s"/>
+      <c r="D13" s="29" t="s"/>
+      <c r="E13" s="28" t="s"/>
+      <c r="F13" s="29" t="s"/>
+      <c r="G13" s="28" t="s"/>
+      <c r="H13" s="29" t="s"/>
+      <c r="I13" s="28" t="s"/>
+      <c r="J13" s="29" t="s"/>
+      <c r="K13" s="28" t="s"/>
+      <c r="L13" s="30" t="s"/>
+      <c r="M13" s="29" t="s"/>
+      <c r="N13" s="8" t="s"/>
+      <c r="O13" s="35" t="s"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="28" t="s"/>
+      <c r="B14" s="29" t="s"/>
+      <c r="C14" s="28" t="s"/>
+      <c r="D14" s="29" t="s"/>
+      <c r="E14" s="28" t="s"/>
+      <c r="F14" s="29" t="s"/>
+      <c r="G14" s="28" t="s"/>
+      <c r="H14" s="29" t="s"/>
+      <c r="I14" s="28" t="s"/>
+      <c r="J14" s="29" t="s"/>
+      <c r="K14" s="28" t="s"/>
+      <c r="L14" s="30" t="s"/>
+      <c r="M14" s="29" t="s"/>
+      <c r="N14" s="8" t="s"/>
+      <c r="O14" s="35" t="s"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="28" t="s"/>
+      <c r="B15" s="29" t="s"/>
+      <c r="C15" s="28" t="s"/>
+      <c r="D15" s="29" t="s"/>
+      <c r="E15" s="28" t="s"/>
+      <c r="F15" s="29" t="s"/>
+      <c r="G15" s="28" t="s"/>
+      <c r="H15" s="29" t="s"/>
+      <c r="I15" s="28" t="s"/>
+      <c r="J15" s="29" t="s"/>
+      <c r="K15" s="28" t="s"/>
+      <c r="L15" s="30" t="s"/>
+      <c r="M15" s="29" t="s"/>
+      <c r="N15" s="8" t="s"/>
+      <c r="O15" s="36" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="27" t="s"/>
-      <c r="B8" s="28" t="s"/>
-      <c r="C8" s="27" t="s"/>
-      <c r="D8" s="28" t="s"/>
-      <c r="E8" s="27" t="s"/>
-      <c r="F8" s="28" t="s"/>
-      <c r="G8" s="27" t="s"/>
-      <c r="H8" s="28" t="s"/>
-      <c r="I8" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="28">
-        <v>60</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="28">
-        <v>60</v>
-      </c>
-      <c r="M8" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" s="28">
-        <v>60</v>
-      </c>
-      <c r="O8" s="34" t="s"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="27" t="s"/>
-      <c r="B9" s="28" t="s"/>
-      <c r="C9" s="27" t="s"/>
-      <c r="D9" s="28" t="s"/>
-      <c r="E9" s="27" t="s"/>
-      <c r="F9" s="28" t="s"/>
-      <c r="G9" s="27" t="s"/>
-      <c r="H9" s="28" t="s"/>
-      <c r="I9" s="27" t="s"/>
-      <c r="J9" s="28" t="s"/>
-      <c r="K9" s="27" t="s"/>
-      <c r="L9" s="29" t="s"/>
-      <c r="M9" s="28" t="s"/>
-      <c r="N9" s="8" t="s"/>
-      <c r="O9" s="34" t="s"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="27" t="s"/>
-      <c r="B10" s="28" t="s"/>
-      <c r="C10" s="27" t="s"/>
-      <c r="D10" s="28" t="s"/>
-      <c r="E10" s="27" t="s"/>
-      <c r="F10" s="28" t="s"/>
-      <c r="G10" s="27" t="s"/>
-      <c r="H10" s="28" t="s"/>
-      <c r="I10" s="27" t="s"/>
-      <c r="J10" s="28" t="s"/>
-      <c r="K10" s="27" t="s"/>
-      <c r="L10" s="29" t="s"/>
-      <c r="M10" s="28" t="s"/>
-      <c r="N10" s="8" t="s"/>
-      <c r="O10" s="34" t="s"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="27" t="s"/>
-      <c r="B11" s="28" t="s"/>
-      <c r="C11" s="27" t="s"/>
-      <c r="D11" s="28" t="s"/>
-      <c r="E11" s="27" t="s"/>
-      <c r="F11" s="28" t="s"/>
-      <c r="G11" s="27" t="s"/>
-      <c r="H11" s="28" t="s"/>
-      <c r="I11" s="27" t="s"/>
-      <c r="J11" s="28" t="s"/>
-      <c r="K11" s="27" t="s"/>
-      <c r="L11" s="29" t="s"/>
-      <c r="M11" s="28" t="s"/>
-      <c r="N11" s="8" t="s"/>
-      <c r="O11" s="34" t="s"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="27" t="s"/>
-      <c r="B12" s="28" t="s"/>
-      <c r="C12" s="27" t="s"/>
-      <c r="D12" s="28" t="s"/>
-      <c r="E12" s="27" t="s"/>
-      <c r="F12" s="28" t="s"/>
-      <c r="G12" s="27" t="s"/>
-      <c r="H12" s="28" t="s"/>
-      <c r="I12" s="27" t="s"/>
-      <c r="J12" s="28" t="s"/>
-      <c r="K12" s="27" t="s"/>
-      <c r="L12" s="29" t="s"/>
-      <c r="M12" s="28" t="s"/>
-      <c r="N12" s="8" t="s"/>
-      <c r="O12" s="34" t="s"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="27" t="s"/>
-      <c r="B13" s="28" t="s"/>
-      <c r="C13" s="27" t="s"/>
-      <c r="D13" s="28" t="s"/>
-      <c r="E13" s="27" t="s"/>
-      <c r="F13" s="28" t="s"/>
-      <c r="G13" s="27" t="s"/>
-      <c r="H13" s="28" t="s"/>
-      <c r="I13" s="27" t="s"/>
-      <c r="J13" s="28" t="s"/>
-      <c r="K13" s="27" t="s"/>
-      <c r="L13" s="29" t="s"/>
-      <c r="M13" s="28" t="s"/>
-      <c r="N13" s="8" t="s"/>
-      <c r="O13" s="34" t="s"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="27" t="s"/>
-      <c r="B14" s="28" t="s"/>
-      <c r="C14" s="27" t="s"/>
-      <c r="D14" s="28" t="s"/>
-      <c r="E14" s="27" t="s"/>
-      <c r="F14" s="28" t="s"/>
-      <c r="G14" s="27" t="s"/>
-      <c r="H14" s="28" t="s"/>
-      <c r="I14" s="27" t="s"/>
-      <c r="J14" s="28" t="s"/>
-      <c r="K14" s="27" t="s"/>
-      <c r="L14" s="29" t="s"/>
-      <c r="M14" s="28" t="s"/>
-      <c r="N14" s="8" t="s"/>
-      <c r="O14" s="34" t="s"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="27" t="s"/>
-      <c r="B15" s="28" t="s"/>
-      <c r="C15" s="27" t="s"/>
-      <c r="D15" s="28" t="s"/>
-      <c r="E15" s="27" t="s"/>
-      <c r="F15" s="28" t="s"/>
-      <c r="G15" s="27" t="s"/>
-      <c r="H15" s="28" t="s"/>
-      <c r="I15" s="27" t="s"/>
-      <c r="J15" s="28" t="s"/>
-      <c r="K15" s="27" t="s"/>
-      <c r="L15" s="29" t="s"/>
-      <c r="M15" s="28" t="s"/>
-      <c r="N15" s="8" t="s"/>
-      <c r="O15" s="35" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="36" t="s"/>
-      <c r="B16" s="37">
+      <c r="A16" s="37" t="s"/>
+      <c r="B16" s="38">
         <f>=SUM(B3:B7)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="36" t="s"/>
-      <c r="D16" s="37">
+      <c r="C16" s="37" t="s"/>
+      <c r="D16" s="38">
         <f>=SUM(D3:D7)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="36" t="s"/>
-      <c r="F16" s="37">
+      <c r="E16" s="37" t="s"/>
+      <c r="F16" s="38">
         <f>=SUM(F3:F15)</f>
         <v>270</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="37">
         <v>0</v>
       </c>
-      <c r="H16" s="38">
+      <c r="H16" s="39">
         <f>=SUM(H3:H15)</f>
         <v>390</v>
       </c>
-      <c r="I16" s="37" t="s"/>
-      <c r="J16" s="37">
+      <c r="I16" s="38" t="s"/>
+      <c r="J16" s="38">
         <f>=SUM(J3:J15)</f>
         <v>450</v>
       </c>
-      <c r="K16" s="36" t="s"/>
-      <c r="L16" s="38">
+      <c r="K16" s="37" t="s"/>
+      <c r="L16" s="39">
         <f>=SUM(L3:L15)</f>
         <v>450</v>
       </c>
-      <c r="M16" s="37" t="s"/>
-      <c r="N16" s="37">
+      <c r="M16" s="38" t="s"/>
+      <c r="N16" s="38">
         <f>=SUM(N3:N15)</f>
         <v>450</v>
       </c>
-      <c r="O16" s="39">
+      <c r="O16" s="40">
         <f>=SUM(A16:N16)</f>
         <v>2010</v>
       </c>
-      <c r="P16" s="151" t="s">
-        <v>17</v>
+      <c r="P16" s="41" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -2986,579 +3169,663 @@
       <c r="O19" s="21" t="s"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="H20" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="29" t="s">
+      <c r="J20" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K20" s="28" t="s">
+      <c r="K20" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="29" t="s">
+      <c r="L20" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="M20" s="28" t="s">
+      <c r="M20" s="29" t="s">
         <v>8</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="O20" s="30" t="s"/>
+      <c r="O20" s="31" t="s"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="29">
+        <v>90</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="29">
+        <v>90</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="29">
+        <v>90</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="29">
+        <v>90</v>
+      </c>
+      <c r="I21" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="28">
-        <v>90</v>
-      </c>
-      <c r="C21" s="27" t="s">
+      <c r="J21" s="29">
+        <v>90</v>
+      </c>
+      <c r="K21" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="28">
-        <v>90</v>
-      </c>
-      <c r="E21" s="27" t="s">
+      <c r="L21" s="29">
+        <v>90</v>
+      </c>
+      <c r="M21" s="28" t="s"/>
+      <c r="N21" s="29" t="s"/>
+      <c r="O21" s="31" t="s"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="28">
-        <v>90</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="B22" s="29">
+        <v>90</v>
+      </c>
+      <c r="C22" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="28">
-        <v>90</v>
-      </c>
-      <c r="I21" s="27" t="s"/>
-      <c r="J21" s="29" t="s"/>
-      <c r="K21" s="28" t="s"/>
-      <c r="L21" s="28" t="s"/>
-      <c r="M21" s="27" t="s"/>
-      <c r="N21" s="28" t="s"/>
-      <c r="O21" s="30" t="s"/>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="31" t="s">
+      <c r="D22" s="29">
+        <v>90</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="29">
+        <v>90</v>
+      </c>
+      <c r="G22" s="156" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="29">
+        <v>90</v>
+      </c>
+      <c r="I22" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="28">
-        <v>90</v>
-      </c>
-      <c r="C22" s="31" t="s">
+      <c r="J22" s="29">
+        <v>90</v>
+      </c>
+      <c r="K22" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="28">
-        <v>90</v>
-      </c>
-      <c r="E22" s="31" t="s">
+      <c r="L22" s="29">
+        <v>90</v>
+      </c>
+      <c r="M22" s="32" t="s"/>
+      <c r="N22" s="29" t="s"/>
+      <c r="O22" s="31" t="s"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="28">
-        <v>90</v>
-      </c>
-      <c r="G22" s="31" t="s">
+      <c r="B23" s="29">
+        <v>90</v>
+      </c>
+      <c r="C23" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H22" s="28">
-        <v>90</v>
-      </c>
-      <c r="I22" s="31" t="s"/>
-      <c r="J22" s="29" t="s"/>
-      <c r="K22" s="40" t="s"/>
-      <c r="L22" s="28" t="s"/>
-      <c r="M22" s="31" t="s"/>
-      <c r="N22" s="28" t="s"/>
-      <c r="O22" s="30" t="s"/>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="27" t="s">
+      <c r="D23" s="29">
+        <v>90</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="29">
+        <v>90</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="29">
+        <v>90</v>
+      </c>
+      <c r="I23" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="28">
-        <v>90</v>
-      </c>
-      <c r="C23" s="27" t="s">
+      <c r="J23" s="29">
+        <v>60</v>
+      </c>
+      <c r="K23" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="28">
-        <v>90</v>
-      </c>
-      <c r="E23" s="27" t="s">
+      <c r="L23" s="29">
+        <v>60</v>
+      </c>
+      <c r="M23" s="28" t="s"/>
+      <c r="N23" s="29" t="s"/>
+      <c r="O23" s="31" t="s"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="28">
-        <v>90</v>
-      </c>
-      <c r="G23" s="27" t="s">
+      <c r="B24" s="29">
+        <v>60</v>
+      </c>
+      <c r="C24" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="28">
-        <v>90</v>
-      </c>
-      <c r="I23" s="27" t="s"/>
-      <c r="J23" s="29" t="s"/>
-      <c r="K23" s="28" t="s"/>
-      <c r="L23" s="28" t="s"/>
-      <c r="M23" s="27" t="s"/>
-      <c r="N23" s="28" t="s"/>
-      <c r="O23" s="30" t="s"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="32" t="s">
+      <c r="D24" s="29">
+        <v>60</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="29">
+        <v>60</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="29">
+        <v>60</v>
+      </c>
+      <c r="I24" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="28">
-        <v>60</v>
-      </c>
-      <c r="C24" s="32" t="s">
+      <c r="J24" s="29">
+        <v>60</v>
+      </c>
+      <c r="K24" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="28">
-        <v>60</v>
-      </c>
-      <c r="E24" s="32" t="s">
+      <c r="L24" s="29">
+        <v>60</v>
+      </c>
+      <c r="M24" s="33" t="s"/>
+      <c r="N24" s="29" t="s"/>
+      <c r="O24" s="31" t="s"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="28">
-        <v>60</v>
-      </c>
-      <c r="G24" s="32" t="s">
+      <c r="B25" s="29">
+        <v>60</v>
+      </c>
+      <c r="C25" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="28">
-        <v>60</v>
-      </c>
-      <c r="I24" s="32" t="s"/>
-      <c r="J24" s="29" t="s"/>
-      <c r="K24" s="41" t="s"/>
-      <c r="L24" s="28" t="s"/>
-      <c r="M24" s="32" t="s"/>
-      <c r="N24" s="28" t="s"/>
-      <c r="O24" s="30" t="s"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="27" t="s">
+      <c r="D25" s="29">
+        <v>60</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="29">
+        <v>60</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="29">
+        <v>60</v>
+      </c>
+      <c r="I25" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="28">
-        <v>60</v>
-      </c>
-      <c r="C25" s="27" t="s">
+      <c r="J25" s="29">
+        <v>60</v>
+      </c>
+      <c r="K25" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="28">
-        <v>60</v>
-      </c>
-      <c r="E25" s="27" t="s">
+      <c r="L25" s="29">
+        <v>60</v>
+      </c>
+      <c r="M25" s="28" t="s"/>
+      <c r="N25" s="29" t="s"/>
+      <c r="O25" s="34" t="s"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="28">
-        <v>60</v>
-      </c>
-      <c r="G25" s="27" t="s">
+      <c r="B26" s="29">
+        <v>60</v>
+      </c>
+      <c r="C26" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="28">
-        <v>60</v>
-      </c>
-      <c r="I25" s="27" t="s"/>
-      <c r="J25" s="29" t="s"/>
-      <c r="K25" s="28" t="s"/>
-      <c r="L25" s="28" t="s"/>
-      <c r="M25" s="27" t="s"/>
-      <c r="N25" s="28" t="s"/>
-      <c r="O25" s="33" t="s"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="28">
-        <v>60</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="28">
-        <v>60</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="28">
-        <v>60</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="28">
-        <v>60</v>
-      </c>
-      <c r="I26" s="32" t="s"/>
-      <c r="J26" s="29" t="s"/>
-      <c r="K26" s="41" t="s"/>
-      <c r="L26" s="28" t="s"/>
-      <c r="M26" s="32" t="s"/>
-      <c r="N26" s="28" t="s"/>
-      <c r="O26" s="34" t="s"/>
+      <c r="D26" s="29">
+        <v>60</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="29">
+        <v>60</v>
+      </c>
+      <c r="G26" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="29">
+        <v>60</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="29">
+        <v>60</v>
+      </c>
+      <c r="K26" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="29">
+        <v>90</v>
+      </c>
+      <c r="M26" s="33" t="s"/>
+      <c r="N26" s="29" t="s"/>
+      <c r="O26" s="35" t="s"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="27" t="s"/>
-      <c r="B27" s="28" t="s"/>
-      <c r="C27" s="27" t="s">
+      <c r="A27" s="28" t="s"/>
+      <c r="B27" s="29" t="s"/>
+      <c r="C27" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="29">
+        <v>60</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="29">
+        <v>60</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="29">
+        <v>60</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="29">
+        <v>90</v>
+      </c>
+      <c r="K27" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="L27" s="29">
+        <v>60</v>
+      </c>
+      <c r="M27" s="29" t="s"/>
+      <c r="N27" s="8" t="s"/>
+      <c r="O27" s="35" t="s"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="28" t="s"/>
+      <c r="B28" s="29" t="s"/>
+      <c r="C28" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="28">
-        <v>60</v>
-      </c>
-      <c r="E27" s="27" t="s">
+      <c r="D28" s="29" t="s"/>
+      <c r="E28" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" s="29">
+        <v>60</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="29">
+        <v>90</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="29">
+        <v>60</v>
+      </c>
+      <c r="K28" s="29" t="s"/>
+      <c r="L28" s="30" t="s"/>
+      <c r="M28" s="29" t="s"/>
+      <c r="N28" s="8" t="s"/>
+      <c r="O28" s="35" t="s"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="28" t="s"/>
+      <c r="B29" s="29" t="s"/>
+      <c r="C29" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="29">
+        <v>60</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="29">
+        <v>60</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="29">
+        <v>60</v>
+      </c>
+      <c r="I29" s="28" t="s"/>
+      <c r="J29" s="30" t="s"/>
+      <c r="K29" s="29" t="s"/>
+      <c r="L29" s="30" t="s"/>
+      <c r="M29" s="29" t="s"/>
+      <c r="N29" s="8" t="s"/>
+      <c r="O29" s="35" t="s"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="28" t="s"/>
+      <c r="B30" s="29" t="s"/>
+      <c r="C30" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="29">
+        <v>60</v>
+      </c>
+      <c r="E30" s="28" t="s"/>
+      <c r="F30" s="29" t="s"/>
+      <c r="G30" s="28" t="s"/>
+      <c r="H30" s="29" t="s"/>
+      <c r="I30" s="28" t="s"/>
+      <c r="J30" s="30" t="s"/>
+      <c r="K30" s="29" t="s"/>
+      <c r="L30" s="30" t="s"/>
+      <c r="M30" s="29" t="s"/>
+      <c r="N30" s="8" t="s"/>
+      <c r="O30" s="35" t="s"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="28" t="s"/>
+      <c r="B31" s="29" t="s"/>
+      <c r="C31" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="29">
+        <v>60</v>
+      </c>
+      <c r="E31" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="28">
-        <v>60</v>
-      </c>
-      <c r="G27" s="27" t="s">
+      <c r="F31" s="29" t="s"/>
+      <c r="G31" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="H27" s="28">
-        <v>60</v>
-      </c>
-      <c r="I27" s="27" t="s"/>
-      <c r="J27" s="29" t="s"/>
-      <c r="K27" s="28" t="s"/>
-      <c r="L27" s="29" t="s"/>
-      <c r="M27" s="28" t="s"/>
-      <c r="N27" s="8" t="s"/>
-      <c r="O27" s="34" t="s"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="27" t="s"/>
-      <c r="B28" s="28" t="s"/>
-      <c r="C28" s="27" t="s">
+      <c r="H31" s="29" t="s"/>
+      <c r="I31" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="30" t="s"/>
+      <c r="K31" s="29" t="s"/>
+      <c r="L31" s="30" t="s"/>
+      <c r="M31" s="29" t="s"/>
+      <c r="N31" s="8" t="s"/>
+      <c r="O31" s="35" t="s"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="28" t="s"/>
+      <c r="B32" s="29" t="s"/>
+      <c r="C32" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D32" s="29">
+        <v>60</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="29">
+        <v>60</v>
+      </c>
+      <c r="G32" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="29">
+        <v>60</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="29">
+        <v>60</v>
+      </c>
+      <c r="K32" s="29" t="s"/>
+      <c r="L32" s="30" t="s"/>
+      <c r="M32" s="29" t="s"/>
+      <c r="N32" s="8" t="s"/>
+      <c r="O32" s="35" t="s"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="28" t="s"/>
+      <c r="B33" s="29" t="s"/>
+      <c r="C33" s="28" t="s"/>
+      <c r="D33" s="29" t="s"/>
+      <c r="E33" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="29">
+        <v>60</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="29">
+        <v>60</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="29">
+        <v>60</v>
+      </c>
+      <c r="K33" s="29" t="s"/>
+      <c r="L33" s="30" t="s"/>
+      <c r="M33" s="29" t="s"/>
+      <c r="N33" s="8" t="s"/>
+      <c r="O33" s="34" t="s"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="28" t="s"/>
+      <c r="B34" s="29" t="s"/>
+      <c r="C34" s="28" t="s"/>
+      <c r="D34" s="29" t="s"/>
+      <c r="E34" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="29">
+        <v>60</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="29">
+        <v>60</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="29">
+        <v>60</v>
+      </c>
+      <c r="K34" s="29" t="s"/>
+      <c r="L34" s="30" t="s"/>
+      <c r="M34" s="29" t="s"/>
+      <c r="N34" s="8" t="s"/>
+      <c r="O34" s="35" t="s"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="28" t="s"/>
+      <c r="B35" s="29" t="s"/>
+      <c r="C35" s="28" t="s"/>
+      <c r="D35" s="29" t="s"/>
+      <c r="E35" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="29">
+        <v>60</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="29">
+        <v>60</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" s="29">
+        <v>60</v>
+      </c>
+      <c r="K35" s="29" t="s"/>
+      <c r="L35" s="30" t="s"/>
+      <c r="M35" s="29" t="s"/>
+      <c r="N35" s="8" t="s"/>
+      <c r="O35" s="35" t="s"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="28" t="s"/>
+      <c r="B36" s="29" t="s"/>
+      <c r="C36" s="28" t="s"/>
+      <c r="D36" s="29" t="s"/>
+      <c r="E36" s="28" t="s"/>
+      <c r="F36" s="29" t="s"/>
+      <c r="G36" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="28" t="s"/>
-      <c r="E28" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="28">
-        <v>60</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="28">
-        <v>90</v>
-      </c>
-      <c r="I28" s="27" t="s"/>
-      <c r="J28" s="29" t="s"/>
-      <c r="K28" s="28" t="s"/>
-      <c r="L28" s="29" t="s"/>
-      <c r="M28" s="28" t="s"/>
-      <c r="N28" s="8" t="s"/>
-      <c r="O28" s="34" t="s"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="27" t="s"/>
-      <c r="B29" s="28" t="s"/>
-      <c r="C29" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="28">
-        <v>60</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="28">
-        <v>60</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" s="28">
-        <v>60</v>
-      </c>
-      <c r="I29" s="27" t="s"/>
-      <c r="J29" s="29" t="s"/>
-      <c r="K29" s="28" t="s"/>
-      <c r="L29" s="29" t="s"/>
-      <c r="M29" s="28" t="s"/>
-      <c r="N29" s="8" t="s"/>
-      <c r="O29" s="34" t="s"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="27" t="s"/>
-      <c r="B30" s="28" t="s"/>
-      <c r="C30" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="28">
-        <v>60</v>
-      </c>
-      <c r="E30" s="27" t="s"/>
-      <c r="F30" s="28" t="s"/>
-      <c r="G30" s="27" t="s"/>
-      <c r="H30" s="28" t="s"/>
-      <c r="I30" s="27" t="s"/>
-      <c r="J30" s="29" t="s"/>
-      <c r="K30" s="28" t="s"/>
-      <c r="L30" s="29" t="s"/>
-      <c r="M30" s="28" t="s"/>
-      <c r="N30" s="8" t="s"/>
-      <c r="O30" s="34" t="s"/>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="27" t="s"/>
-      <c r="B31" s="28" t="s"/>
-      <c r="C31" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="28">
-        <v>60</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="28" t="s"/>
-      <c r="G31" s="27" t="s"/>
-      <c r="H31" s="28" t="s"/>
-      <c r="I31" s="27" t="s"/>
-      <c r="J31" s="29" t="s"/>
-      <c r="K31" s="28" t="s"/>
-      <c r="L31" s="29" t="s"/>
-      <c r="M31" s="28" t="s"/>
-      <c r="N31" s="8" t="s"/>
-      <c r="O31" s="34" t="s"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="27" t="s"/>
-      <c r="B32" s="28" t="s"/>
-      <c r="C32" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="28">
-        <v>60</v>
-      </c>
-      <c r="E32" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" s="28">
-        <v>60</v>
-      </c>
-      <c r="G32" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="H32" s="28">
-        <v>60</v>
-      </c>
-      <c r="I32" s="27" t="s"/>
-      <c r="J32" s="29" t="s"/>
-      <c r="K32" s="28" t="s"/>
-      <c r="L32" s="29" t="s"/>
-      <c r="M32" s="28" t="s"/>
-      <c r="N32" s="8" t="s"/>
-      <c r="O32" s="34" t="s"/>
-    </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="27" t="s"/>
-      <c r="B33" s="28" t="s"/>
-      <c r="C33" s="27" t="s"/>
-      <c r="D33" s="28" t="s"/>
-      <c r="E33" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33" s="28">
-        <v>60</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="28">
-        <v>60</v>
-      </c>
-      <c r="I33" s="27" t="s"/>
-      <c r="J33" s="29" t="s"/>
-      <c r="K33" s="28" t="s"/>
-      <c r="L33" s="29" t="s"/>
-      <c r="M33" s="28" t="s"/>
-      <c r="N33" s="8" t="s"/>
-      <c r="O33" s="33" t="s"/>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="27" t="s"/>
-      <c r="B34" s="28" t="s"/>
-      <c r="C34" s="27" t="s"/>
-      <c r="D34" s="28" t="s"/>
-      <c r="E34" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="28">
-        <v>60</v>
-      </c>
-      <c r="G34" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="28">
-        <v>60</v>
-      </c>
-      <c r="I34" s="27" t="s"/>
-      <c r="J34" s="29" t="s"/>
-      <c r="K34" s="28" t="s"/>
-      <c r="L34" s="29" t="s"/>
-      <c r="M34" s="28" t="s"/>
-      <c r="N34" s="8" t="s"/>
-      <c r="O34" s="34" t="s"/>
-    </row>
-    <row r="35" spans="1:15">
-      <c r="A35" s="27" t="s"/>
-      <c r="B35" s="28" t="s"/>
-      <c r="C35" s="27" t="s"/>
-      <c r="D35" s="28" t="s"/>
-      <c r="E35" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F35" s="28">
-        <v>60</v>
-      </c>
-      <c r="G35" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35" s="28">
-        <v>60</v>
-      </c>
-      <c r="I35" s="27" t="s"/>
-      <c r="J35" s="29" t="s"/>
-      <c r="K35" s="28" t="s"/>
-      <c r="L35" s="29" t="s"/>
-      <c r="M35" s="28" t="s"/>
-      <c r="N35" s="8" t="s"/>
-      <c r="O35" s="34" t="s"/>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="27" t="s"/>
-      <c r="B36" s="28" t="s"/>
-      <c r="C36" s="27" t="s"/>
-      <c r="D36" s="28" t="s"/>
-      <c r="E36" s="27" t="s"/>
-      <c r="F36" s="28" t="s"/>
-      <c r="G36" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="28">
-        <v>60</v>
-      </c>
-      <c r="I36" s="27" t="s"/>
-      <c r="J36" s="29" t="s"/>
-      <c r="K36" s="28" t="s"/>
-      <c r="L36" s="29" t="s"/>
-      <c r="M36" s="28" t="s"/>
+      <c r="H36" s="29">
+        <v>60</v>
+      </c>
+      <c r="I36" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="29">
+        <v>60</v>
+      </c>
+      <c r="K36" s="29" t="s"/>
+      <c r="L36" s="30" t="s"/>
+      <c r="M36" s="29" t="s"/>
       <c r="N36" s="8" t="s"/>
-      <c r="O36" s="34" t="s"/>
+      <c r="O36" s="35" t="s"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="27" t="s"/>
-      <c r="B37" s="28" t="s"/>
-      <c r="C37" s="27" t="s"/>
-      <c r="D37" s="28" t="s"/>
-      <c r="E37" s="27" t="s"/>
-      <c r="F37" s="28" t="s"/>
-      <c r="G37" s="27" t="s"/>
-      <c r="H37" s="28" t="s"/>
-      <c r="I37" s="27" t="s"/>
-      <c r="J37" s="29" t="s"/>
-      <c r="K37" s="28" t="s"/>
-      <c r="L37" s="29" t="s"/>
-      <c r="M37" s="28" t="s"/>
+      <c r="A37" s="28" t="s"/>
+      <c r="B37" s="29" t="s"/>
+      <c r="C37" s="28" t="s"/>
+      <c r="D37" s="29" t="s"/>
+      <c r="E37" s="28" t="s"/>
+      <c r="F37" s="29" t="s"/>
+      <c r="G37" s="28" t="s"/>
+      <c r="H37" s="29" t="s"/>
+      <c r="I37" s="28" t="s"/>
+      <c r="J37" s="30" t="s"/>
+      <c r="K37" s="29" t="s"/>
+      <c r="L37" s="30" t="s"/>
+      <c r="M37" s="29" t="s"/>
       <c r="N37" s="8" t="s"/>
-      <c r="O37" s="34" t="s"/>
+      <c r="O37" s="35" t="s"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="27" t="s"/>
-      <c r="B38" s="28" t="s"/>
-      <c r="C38" s="27" t="s"/>
-      <c r="D38" s="28" t="s"/>
-      <c r="E38" s="27" t="s"/>
-      <c r="F38" s="28" t="s"/>
-      <c r="G38" s="27" t="s"/>
-      <c r="H38" s="28" t="s"/>
-      <c r="I38" s="27" t="s"/>
-      <c r="J38" s="29" t="s"/>
-      <c r="K38" s="28" t="s"/>
-      <c r="L38" s="29" t="s"/>
-      <c r="M38" s="28" t="s"/>
+      <c r="A38" s="28" t="s"/>
+      <c r="B38" s="29" t="s"/>
+      <c r="C38" s="28" t="s"/>
+      <c r="D38" s="29" t="s"/>
+      <c r="E38" s="28" t="s"/>
+      <c r="F38" s="29" t="s"/>
+      <c r="G38" s="28" t="s"/>
+      <c r="H38" s="29" t="s"/>
+      <c r="I38" s="28" t="s"/>
+      <c r="J38" s="30" t="s"/>
+      <c r="K38" s="29" t="s"/>
+      <c r="L38" s="30" t="s"/>
+      <c r="M38" s="29" t="s"/>
       <c r="N38" s="8" t="s"/>
-      <c r="O38" s="35" t="s">
+      <c r="O38" s="36" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="36" t="s"/>
-      <c r="B39" s="37">
+      <c r="A39" s="37" t="s"/>
+      <c r="B39" s="38">
         <f>=SUM(B21:B38)</f>
         <v>450</v>
       </c>
-      <c r="C39" s="36" t="s"/>
-      <c r="D39" s="37">
+      <c r="C39" s="37" t="s"/>
+      <c r="D39" s="38">
         <f>=SUM(D21:D38)</f>
         <v>750</v>
       </c>
-      <c r="E39" s="36" t="s"/>
-      <c r="F39" s="37">
+      <c r="E39" s="37" t="s"/>
+      <c r="F39" s="38">
         <f>=SUM(F21:F38)</f>
         <v>870</v>
       </c>
-      <c r="G39" s="36">
+      <c r="G39" s="37">
         <v>0</v>
       </c>
-      <c r="H39" s="37">
+      <c r="H39" s="38">
         <f>=SUM(H21:H38)</f>
         <v>960</v>
       </c>
-      <c r="I39" s="36" t="s"/>
-      <c r="J39" s="38">
+      <c r="I39" s="37" t="s"/>
+      <c r="J39" s="39">
         <f>=SUM(J21:J38)</f>
-        <v>0</v>
-      </c>
-      <c r="K39" s="37" t="s"/>
-      <c r="L39" s="38">
+        <v>870</v>
+      </c>
+      <c r="K39" s="38" t="s"/>
+      <c r="L39" s="39">
         <f>=SUM(L21:L38)</f>
-        <v>0</v>
-      </c>
-      <c r="M39" s="37" t="s"/>
-      <c r="N39" s="37">
+        <v>510</v>
+      </c>
+      <c r="M39" s="38" t="s"/>
+      <c r="N39" s="38">
         <f>=SUM(N21:N38)</f>
         <v>0</v>
       </c>
-      <c r="O39" s="39">
+      <c r="O39" s="40">
         <f>=SUM(A39:N39)</f>
-        <v>3030</v>
+        <v>4410</v>
       </c>
     </row>
   </sheetData>
@@ -3601,293 +3868,293 @@
       <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="42" t="s"/>
+      <c r="I1" s="44" t="s"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="47" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="11" t="s"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="45">
+        <v>60</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="45">
+        <v>60</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="45">
+        <v>60</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="47">
+        <v>60</v>
+      </c>
+      <c r="I3" s="11" t="s"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43">
-        <v>60</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B4" s="45">
+        <v>60</v>
+      </c>
+      <c r="C4" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="43">
-        <v>60</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="D4" s="45">
+        <v>60</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="45">
+        <v>60</v>
+      </c>
+      <c r="G4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="43">
-        <v>60</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="H4" s="47">
+        <v>60</v>
+      </c>
+      <c r="I4" s="11" t="s"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="45">
+        <v>60</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="45">
+        <v>60</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="45">
-        <v>60</v>
-      </c>
-      <c r="I3" s="11" t="s"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="44" t="s">
+      <c r="F5" s="45">
+        <v>60</v>
+      </c>
+      <c r="G5" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="43">
-        <v>60</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="43">
-        <v>60</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="43">
-        <v>60</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="45">
-        <v>60</v>
-      </c>
-      <c r="I4" s="11" t="s"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="43">
-        <v>60</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="43">
-        <v>60</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="43">
-        <v>60</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="45">
+      <c r="H5" s="47">
         <v>60</v>
       </c>
       <c r="I5" s="11" t="s"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="45">
+        <v>60</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="45">
+        <v>60</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="43">
-        <v>60</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="43">
-        <v>60</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="F6" s="45">
+        <v>60</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="47">
+        <v>60</v>
+      </c>
+      <c r="I6" s="11" t="s"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="45">
+        <v>60</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="45">
+        <v>60</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="45">
+        <v>60</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="47">
+        <v>60</v>
+      </c>
+      <c r="I7" s="11" t="s"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="45">
+        <v>60</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="45">
+        <v>60</v>
+      </c>
+      <c r="E8" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="43">
-        <v>60</v>
-      </c>
-      <c r="G6" s="44" t="s">
+      <c r="F8" s="45">
+        <v>60</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="47">
+        <v>60</v>
+      </c>
+      <c r="I8" s="11" t="s"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="45">
-        <v>60</v>
-      </c>
-      <c r="I6" s="11" t="s"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="46" t="s">
+      <c r="B9" s="45">
+        <v>60</v>
+      </c>
+      <c r="C9" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="43">
-        <v>60</v>
-      </c>
-      <c r="C7" s="46" t="s">
+      <c r="D9" s="45">
+        <v>60</v>
+      </c>
+      <c r="E9" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="43">
-        <v>60</v>
-      </c>
-      <c r="E7" s="44" t="s">
+      <c r="F9" s="45">
+        <v>60</v>
+      </c>
+      <c r="G9" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="43">
-        <v>60</v>
-      </c>
-      <c r="G7" s="44" t="s">
+      <c r="H9" s="47">
+        <v>60</v>
+      </c>
+      <c r="I9" s="11" t="s"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="45">
-        <v>60</v>
-      </c>
-      <c r="I7" s="11" t="s"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="43">
-        <v>60</v>
-      </c>
-      <c r="C8" s="44" t="s">
+      <c r="B10" s="45">
+        <v>60</v>
+      </c>
+      <c r="C10" s="48" t="s"/>
+      <c r="D10" s="45" t="s"/>
+      <c r="E10" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="45">
+        <v>60</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="43">
-        <v>60</v>
-      </c>
-      <c r="E8" s="46" t="s">
+      <c r="H10" s="47">
+        <v>60</v>
+      </c>
+      <c r="I10" s="11" t="s"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="45">
+        <v>60</v>
+      </c>
+      <c r="C11" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="43">
-        <v>60</v>
-      </c>
-      <c r="G8" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="45">
-        <v>60</v>
-      </c>
-      <c r="I8" s="11" t="s"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="46" t="s">
+      <c r="D11" s="45">
+        <v>60</v>
+      </c>
+      <c r="E11" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="43">
-        <v>60</v>
-      </c>
-      <c r="C9" s="46" t="s">
+      <c r="F11" s="45">
+        <v>60</v>
+      </c>
+      <c r="G11" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="43">
-        <v>60</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="43">
-        <v>60</v>
-      </c>
-      <c r="G9" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="45">
-        <v>60</v>
-      </c>
-      <c r="I9" s="11" t="s"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="43">
-        <v>60</v>
-      </c>
-      <c r="C10" s="46" t="s"/>
-      <c r="D10" s="43" t="s"/>
-      <c r="E10" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="43">
-        <v>60</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="45">
-        <v>60</v>
-      </c>
-      <c r="I10" s="11" t="s"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="43">
-        <v>60</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="43">
-        <v>60</v>
-      </c>
-      <c r="E11" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="43">
-        <v>60</v>
-      </c>
-      <c r="G11" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="45">
+      <c r="H11" s="47">
         <v>60</v>
       </c>
       <c r="I11" s="11" t="s"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="9" t="s"/>
-      <c r="B12" s="43" t="s"/>
-      <c r="C12" s="44" t="s">
+      <c r="B12" s="45" t="s"/>
+      <c r="C12" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="43">
-        <v>60</v>
-      </c>
-      <c r="E12" s="44" t="s">
+      <c r="D12" s="45">
+        <v>60</v>
+      </c>
+      <c r="E12" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="43">
-        <v>60</v>
-      </c>
-      <c r="G12" s="44" t="s">
+      <c r="F12" s="45">
+        <v>60</v>
+      </c>
+      <c r="G12" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="45">
+      <c r="H12" s="47">
         <v>60</v>
       </c>
       <c r="I12" s="13" t="s">
@@ -3919,7 +4186,7 @@
         <f>=SUM(A13:H13)</f>
         <v>2280</v>
       </c>
-      <c r="J13" s="152" t="s">
+      <c r="J13" s="51" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3989,37 +4256,37 @@
       <c r="A17" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="43" t="s">
+      <c r="D17" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="44" t="s">
+      <c r="G17" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="43" t="s">
+      <c r="H17" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="44" t="s">
+      <c r="I17" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="43" t="s">
+      <c r="J17" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="K17" s="44" t="s">
+      <c r="K17" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="45" t="s">
+      <c r="L17" s="47" t="s">
         <v>9</v>
       </c>
       <c r="M17" s="11" t="s"/>
@@ -4027,161 +4294,161 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="9" t="s"/>
-      <c r="B18" s="43" t="s"/>
+      <c r="B18" s="45" t="s"/>
       <c r="C18" s="9" t="s"/>
-      <c r="D18" s="43" t="s"/>
+      <c r="D18" s="45" t="s"/>
       <c r="E18" s="9" t="s"/>
-      <c r="F18" s="43" t="s"/>
+      <c r="F18" s="45" t="s"/>
       <c r="G18" s="9" t="s"/>
-      <c r="H18" s="43" t="s"/>
+      <c r="H18" s="45" t="s"/>
       <c r="I18" s="9" t="s"/>
-      <c r="J18" s="43" t="s"/>
+      <c r="J18" s="45" t="s"/>
       <c r="K18" s="9" t="s"/>
-      <c r="L18" s="45" t="s"/>
+      <c r="L18" s="47" t="s"/>
       <c r="M18" s="11" t="s"/>
       <c r="N18" s="8" t="s"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="44" t="s"/>
-      <c r="B19" s="43" t="s"/>
-      <c r="C19" s="46" t="s"/>
-      <c r="D19" s="43" t="s"/>
-      <c r="E19" s="47" t="s"/>
-      <c r="F19" s="43" t="s"/>
-      <c r="G19" s="44" t="s"/>
-      <c r="H19" s="43" t="s"/>
-      <c r="I19" s="44" t="s"/>
-      <c r="J19" s="43" t="s"/>
-      <c r="K19" s="44" t="s"/>
-      <c r="L19" s="45" t="s"/>
+      <c r="A19" s="46" t="s"/>
+      <c r="B19" s="45" t="s"/>
+      <c r="C19" s="48" t="s"/>
+      <c r="D19" s="45" t="s"/>
+      <c r="E19" s="49" t="s"/>
+      <c r="F19" s="45" t="s"/>
+      <c r="G19" s="46" t="s"/>
+      <c r="H19" s="45" t="s"/>
+      <c r="I19" s="46" t="s"/>
+      <c r="J19" s="45" t="s"/>
+      <c r="K19" s="46" t="s"/>
+      <c r="L19" s="47" t="s"/>
       <c r="M19" s="11" t="s"/>
       <c r="N19" s="8" t="s"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="46" t="s"/>
-      <c r="B20" s="43" t="s"/>
-      <c r="C20" s="46" t="s"/>
-      <c r="D20" s="43" t="s"/>
+      <c r="A20" s="48" t="s"/>
+      <c r="B20" s="45" t="s"/>
+      <c r="C20" s="48" t="s"/>
+      <c r="D20" s="45" t="s"/>
       <c r="E20" s="9" t="s"/>
-      <c r="F20" s="43" t="s"/>
-      <c r="G20" s="48" t="s"/>
-      <c r="H20" s="43" t="s"/>
-      <c r="I20" s="48" t="s"/>
-      <c r="J20" s="43" t="s"/>
-      <c r="K20" s="48" t="s"/>
-      <c r="L20" s="45" t="s"/>
+      <c r="F20" s="45" t="s"/>
+      <c r="G20" s="50" t="s"/>
+      <c r="H20" s="45" t="s"/>
+      <c r="I20" s="50" t="s"/>
+      <c r="J20" s="45" t="s"/>
+      <c r="K20" s="50" t="s"/>
+      <c r="L20" s="47" t="s"/>
       <c r="M20" s="11" t="s"/>
       <c r="N20" s="8" t="s"/>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="12" t="s"/>
-      <c r="B21" s="43" t="s"/>
-      <c r="C21" s="47" t="s"/>
-      <c r="D21" s="43" t="s"/>
+      <c r="B21" s="45" t="s"/>
+      <c r="C21" s="49" t="s"/>
+      <c r="D21" s="45" t="s"/>
       <c r="E21" s="9" t="s"/>
-      <c r="F21" s="43" t="s"/>
-      <c r="G21" s="44" t="s"/>
-      <c r="H21" s="43" t="s"/>
-      <c r="I21" s="44" t="s"/>
-      <c r="J21" s="43" t="s"/>
-      <c r="K21" s="44" t="s"/>
-      <c r="L21" s="45" t="s"/>
+      <c r="F21" s="45" t="s"/>
+      <c r="G21" s="46" t="s"/>
+      <c r="H21" s="45" t="s"/>
+      <c r="I21" s="46" t="s"/>
+      <c r="J21" s="45" t="s"/>
+      <c r="K21" s="46" t="s"/>
+      <c r="L21" s="47" t="s"/>
       <c r="M21" s="11" t="s"/>
       <c r="N21" s="8" t="s"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="46" t="s"/>
-      <c r="B22" s="43" t="s"/>
-      <c r="C22" s="46" t="s"/>
-      <c r="D22" s="43" t="s"/>
-      <c r="E22" s="44" t="s"/>
-      <c r="F22" s="43" t="s"/>
-      <c r="G22" s="44" t="s"/>
-      <c r="H22" s="43" t="s"/>
-      <c r="I22" s="44" t="s"/>
-      <c r="J22" s="43" t="s"/>
-      <c r="K22" s="44" t="s"/>
-      <c r="L22" s="45" t="s"/>
+      <c r="A22" s="48" t="s"/>
+      <c r="B22" s="45" t="s"/>
+      <c r="C22" s="48" t="s"/>
+      <c r="D22" s="45" t="s"/>
+      <c r="E22" s="46" t="s"/>
+      <c r="F22" s="45" t="s"/>
+      <c r="G22" s="46" t="s"/>
+      <c r="H22" s="45" t="s"/>
+      <c r="I22" s="46" t="s"/>
+      <c r="J22" s="45" t="s"/>
+      <c r="K22" s="46" t="s"/>
+      <c r="L22" s="47" t="s"/>
       <c r="M22" s="11" t="s"/>
       <c r="N22" s="8" t="s"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="46" t="s"/>
-      <c r="B23" s="43" t="s"/>
-      <c r="C23" s="44" t="s"/>
-      <c r="D23" s="43" t="s"/>
-      <c r="E23" s="46" t="s"/>
-      <c r="F23" s="43" t="s"/>
-      <c r="G23" s="44" t="s"/>
-      <c r="H23" s="43" t="s"/>
-      <c r="I23" s="44" t="s"/>
-      <c r="J23" s="43" t="s"/>
-      <c r="K23" s="44" t="s"/>
-      <c r="L23" s="45" t="s"/>
+      <c r="A23" s="48" t="s"/>
+      <c r="B23" s="45" t="s"/>
+      <c r="C23" s="46" t="s"/>
+      <c r="D23" s="45" t="s"/>
+      <c r="E23" s="48" t="s"/>
+      <c r="F23" s="45" t="s"/>
+      <c r="G23" s="46" t="s"/>
+      <c r="H23" s="45" t="s"/>
+      <c r="I23" s="46" t="s"/>
+      <c r="J23" s="45" t="s"/>
+      <c r="K23" s="46" t="s"/>
+      <c r="L23" s="47" t="s"/>
       <c r="M23" s="11" t="s"/>
       <c r="N23" s="8" t="s"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="46" t="s"/>
-      <c r="B24" s="43" t="s"/>
-      <c r="C24" s="46" t="s"/>
-      <c r="D24" s="43" t="s"/>
-      <c r="E24" s="44" t="s"/>
-      <c r="F24" s="43" t="s"/>
-      <c r="G24" s="44" t="s"/>
-      <c r="H24" s="43" t="s"/>
-      <c r="I24" s="44" t="s"/>
-      <c r="J24" s="43" t="s"/>
-      <c r="K24" s="44" t="s"/>
-      <c r="L24" s="45" t="s"/>
+      <c r="A24" s="48" t="s"/>
+      <c r="B24" s="45" t="s"/>
+      <c r="C24" s="48" t="s"/>
+      <c r="D24" s="45" t="s"/>
+      <c r="E24" s="46" t="s"/>
+      <c r="F24" s="45" t="s"/>
+      <c r="G24" s="46" t="s"/>
+      <c r="H24" s="45" t="s"/>
+      <c r="I24" s="46" t="s"/>
+      <c r="J24" s="45" t="s"/>
+      <c r="K24" s="46" t="s"/>
+      <c r="L24" s="47" t="s"/>
       <c r="M24" s="11" t="s"/>
       <c r="N24" s="8" t="s"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="46" t="s"/>
-      <c r="B25" s="43" t="s"/>
-      <c r="C25" s="46" t="s"/>
-      <c r="D25" s="43" t="s"/>
-      <c r="E25" s="46" t="s"/>
-      <c r="F25" s="43" t="s"/>
+      <c r="A25" s="48" t="s"/>
+      <c r="B25" s="45" t="s"/>
+      <c r="C25" s="48" t="s"/>
+      <c r="D25" s="45" t="s"/>
+      <c r="E25" s="48" t="s"/>
+      <c r="F25" s="45" t="s"/>
       <c r="G25" s="12" t="s"/>
-      <c r="H25" s="43" t="s"/>
+      <c r="H25" s="45" t="s"/>
       <c r="I25" s="12" t="s"/>
-      <c r="J25" s="43" t="s"/>
+      <c r="J25" s="45" t="s"/>
       <c r="K25" s="12" t="s"/>
-      <c r="L25" s="45" t="s"/>
+      <c r="L25" s="47" t="s"/>
       <c r="M25" s="11" t="s"/>
       <c r="N25" s="8" t="s"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="44" t="s"/>
-      <c r="B26" s="43" t="s"/>
-      <c r="C26" s="44" t="s"/>
-      <c r="D26" s="43" t="s"/>
-      <c r="E26" s="44" t="s"/>
-      <c r="F26" s="43" t="s"/>
-      <c r="G26" s="44" t="s"/>
-      <c r="H26" s="43" t="s"/>
-      <c r="I26" s="44" t="s"/>
-      <c r="J26" s="43" t="s"/>
-      <c r="K26" s="44" t="s"/>
-      <c r="L26" s="45" t="s"/>
+      <c r="A26" s="46" t="s"/>
+      <c r="B26" s="45" t="s"/>
+      <c r="C26" s="46" t="s"/>
+      <c r="D26" s="45" t="s"/>
+      <c r="E26" s="46" t="s"/>
+      <c r="F26" s="45" t="s"/>
+      <c r="G26" s="46" t="s"/>
+      <c r="H26" s="45" t="s"/>
+      <c r="I26" s="46" t="s"/>
+      <c r="J26" s="45" t="s"/>
+      <c r="K26" s="46" t="s"/>
+      <c r="L26" s="47" t="s"/>
       <c r="M26" s="11" t="s"/>
       <c r="N26" s="8" t="s"/>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="9" t="s"/>
-      <c r="B27" s="43" t="s"/>
-      <c r="C27" s="44" t="s"/>
-      <c r="D27" s="43" t="s"/>
-      <c r="E27" s="44" t="s"/>
-      <c r="F27" s="43" t="s"/>
-      <c r="G27" s="44" t="s"/>
-      <c r="H27" s="43" t="s"/>
-      <c r="I27" s="44" t="s"/>
-      <c r="J27" s="43" t="s"/>
-      <c r="K27" s="44" t="s"/>
-      <c r="L27" s="45" t="s"/>
+      <c r="B27" s="45" t="s"/>
+      <c r="C27" s="46" t="s"/>
+      <c r="D27" s="45" t="s"/>
+      <c r="E27" s="46" t="s"/>
+      <c r="F27" s="45" t="s"/>
+      <c r="G27" s="46" t="s"/>
+      <c r="H27" s="45" t="s"/>
+      <c r="I27" s="46" t="s"/>
+      <c r="J27" s="45" t="s"/>
+      <c r="K27" s="46" t="s"/>
+      <c r="L27" s="47" t="s"/>
       <c r="M27" s="13" t="s">
         <v>15</v>
       </c>
@@ -4236,383 +4503,401 @@
   <dimension ref="D17"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="11" width="12.1406" style="89" customWidth="1"/>
-    <col min="12" max="12" width="12.1406" style="89" customWidth="1"/>
+    <col min="1" max="11" width="12.1406" style="92" customWidth="1"/>
+    <col min="12" max="12" width="12.1406" style="92" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="49" t="s"/>
-      <c r="B1" s="50" t="s">
+      <c r="A1" s="52" t="s"/>
+      <c r="B1" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="54" t="s"/>
+      <c r="D1" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="51" t="s"/>
-      <c r="D1" s="50" t="s">
+      <c r="E1" s="54" t="s"/>
+      <c r="F1" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="51" t="s"/>
-      <c r="F1" s="50" t="s">
+      <c r="G1" s="54" t="s"/>
+      <c r="H1" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="51" t="s"/>
-      <c r="H1" s="50" t="s">
+      <c r="I1" s="54" t="s"/>
+      <c r="J1" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="51" t="s"/>
-      <c r="J1" s="50" t="s">
+      <c r="K1" s="54" t="s"/>
+      <c r="L1" s="55" t="s"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="51" t="s"/>
-      <c r="L1" s="52" t="s"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="53" t="s">
+      <c r="B2" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="C2" s="58">
+        <v>60</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="58">
+        <v>60</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="58">
+        <v>60</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="58">
+        <v>65</v>
+      </c>
+      <c r="J2" s="57" t="s"/>
+      <c r="K2" s="59" t="s"/>
+      <c r="L2" s="60" t="s"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="61" t="s"/>
+      <c r="B3" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="55">
-        <v>60</v>
-      </c>
-      <c r="D2" s="54" t="s">
+      <c r="C3" s="63">
+        <v>60</v>
+      </c>
+      <c r="D3" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="55">
-        <v>60</v>
-      </c>
-      <c r="F2" s="54" t="s">
+      <c r="E3" s="63">
+        <v>60</v>
+      </c>
+      <c r="F3" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="55">
-        <v>60</v>
-      </c>
-      <c r="H2" s="54" t="s">
+      <c r="G3" s="63">
+        <v>60</v>
+      </c>
+      <c r="H3" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="55">
+      <c r="I3" s="63">
         <v>65</v>
       </c>
-      <c r="J2" s="54" t="s"/>
-      <c r="K2" s="56" t="s"/>
-      <c r="L2" s="57" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="58" t="s"/>
-      <c r="B3" s="59" t="s">
+      <c r="J3" s="62" t="s"/>
+      <c r="K3" s="64" t="s"/>
+      <c r="L3" s="60" t="s"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="61" t="s"/>
+      <c r="B4" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="60">
-        <v>60</v>
-      </c>
-      <c r="D3" s="59" t="s">
+      <c r="C4" s="63">
+        <v>60</v>
+      </c>
+      <c r="D4" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="60">
-        <v>60</v>
-      </c>
-      <c r="F3" s="59" t="s">
+      <c r="E4" s="63">
+        <v>60</v>
+      </c>
+      <c r="F4" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="60">
-        <v>60</v>
-      </c>
-      <c r="H3" s="59" t="s">
+      <c r="G4" s="63">
+        <v>60</v>
+      </c>
+      <c r="H4" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="60">
+      <c r="I4" s="63">
         <v>65</v>
       </c>
-      <c r="J3" s="59" t="s"/>
-      <c r="K3" s="61" t="s"/>
-      <c r="L3" s="57" t="s"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="58" t="s"/>
-      <c r="B4" s="59" t="s">
+      <c r="J4" s="62" t="s"/>
+      <c r="K4" s="64" t="s"/>
+      <c r="L4" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="60">
-        <v>60</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="60">
-        <v>60</v>
-      </c>
-      <c r="F4" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="60">
-        <v>60</v>
-      </c>
-      <c r="H4" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="60">
-        <v>65</v>
-      </c>
-      <c r="J4" s="59" t="s"/>
-      <c r="K4" s="61" t="s"/>
-      <c r="L4" s="62" t="s">
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="66" t="s"/>
+      <c r="B5" s="67" t="s"/>
+      <c r="C5" s="68" t="s"/>
+      <c r="D5" s="67" t="s"/>
+      <c r="E5" s="68" t="s"/>
+      <c r="F5" s="67" t="s"/>
+      <c r="G5" s="68" t="s"/>
+      <c r="H5" s="67" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="63" t="s"/>
-      <c r="B5" s="64" t="s"/>
-      <c r="C5" s="65" t="s"/>
-      <c r="D5" s="64" t="s"/>
-      <c r="E5" s="65" t="s"/>
-      <c r="F5" s="64" t="s"/>
-      <c r="G5" s="65" t="s"/>
-      <c r="H5" s="64" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="65">
+      <c r="I5" s="68">
         <v>10</v>
       </c>
-      <c r="J5" s="64" t="s"/>
-      <c r="K5" s="66" t="s"/>
-      <c r="L5" s="67">
+      <c r="J5" s="67" t="s"/>
+      <c r="K5" s="69" t="s"/>
+      <c r="L5" s="70">
         <f>=SUM(B2:K5)</f>
         <v>745</v>
       </c>
-      <c r="M5" s="145" t="s">
+      <c r="M5" s="71" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="69">
+      <c r="A8" s="72">
         <v>46195</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="72">
         <v>46196</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="69">
+      <c r="E8" s="72">
         <v>46197</v>
       </c>
-      <c r="F8" s="70" t="s">
+      <c r="F8" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="69">
+      <c r="G8" s="72">
         <v>46198</v>
       </c>
-      <c r="H8" s="70" t="s">
+      <c r="H8" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="69">
+      <c r="I8" s="72">
         <v>46199</v>
       </c>
-      <c r="J8" s="71" t="s">
+      <c r="J8" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="71" t="s"/>
-      <c r="L8" s="72" t="s"/>
-      <c r="M8" s="73" t="s"/>
-      <c r="N8" s="73" t="s"/>
-      <c r="O8" s="28" t="s"/>
+      <c r="K8" s="74" t="s"/>
+      <c r="L8" s="75" t="s"/>
+      <c r="M8" s="76" t="s"/>
+      <c r="N8" s="76" t="s"/>
+      <c r="O8" s="29" t="s"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="E9" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="75" t="s">
+      <c r="F9" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="75" t="s">
+      <c r="H9" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="74" t="s">
+      <c r="I9" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="76" t="s">
+      <c r="J9" s="151" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="76" t="s"/>
-      <c r="L9" s="77" t="s"/>
-      <c r="M9" s="78" t="s"/>
-      <c r="N9" s="78" t="s"/>
-      <c r="O9" s="28" t="s"/>
+      <c r="K9" s="79" t="s"/>
+      <c r="L9" s="80" t="s"/>
+      <c r="M9" s="81" t="s"/>
+      <c r="N9" s="81" t="s"/>
+      <c r="O9" s="29" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="83">
+        <v>60</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="84">
+        <v>90</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="83">
+        <v>60</v>
+      </c>
+      <c r="G10" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="83">
+        <v>90</v>
+      </c>
+      <c r="I10" s="148" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="149">
+        <v>60</v>
+      </c>
+      <c r="K10" s="86" t="s"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="80">
-        <v>60</v>
-      </c>
-      <c r="C10" s="79" t="s">
+      <c r="B11" s="83">
+        <v>60</v>
+      </c>
+      <c r="C11" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="81">
-        <v>90</v>
-      </c>
-      <c r="E10" s="79" t="s">
+      <c r="D11" s="83">
+        <v>90</v>
+      </c>
+      <c r="E11" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="80">
-        <v>60</v>
-      </c>
-      <c r="G10" s="79" t="s">
+      <c r="F11" s="83">
+        <v>90</v>
+      </c>
+      <c r="G11" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="83">
+        <v>60</v>
+      </c>
+      <c r="I11" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="80">
-        <v>90</v>
-      </c>
-      <c r="I10" s="82" t="s"/>
-      <c r="J10" s="83" t="s"/>
-      <c r="K10" s="83" t="s"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="79" t="s">
+      <c r="J11" s="86">
+        <v>90</v>
+      </c>
+      <c r="K11" s="86" t="s"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="80">
-        <v>60</v>
-      </c>
-      <c r="C11" s="79" t="s">
+      <c r="B12" s="83">
+        <v>60</v>
+      </c>
+      <c r="C12" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="80">
-        <v>90</v>
-      </c>
-      <c r="E11" s="79" t="s">
+      <c r="D12" s="83">
+        <v>90</v>
+      </c>
+      <c r="E12" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="80">
-        <v>90</v>
-      </c>
-      <c r="G11" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="80">
-        <v>60</v>
-      </c>
-      <c r="I11" s="82" t="s"/>
-      <c r="J11" s="83" t="s"/>
-      <c r="K11" s="83" t="s"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="80">
-        <v>60</v>
-      </c>
-      <c r="C12" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="80">
-        <v>90</v>
-      </c>
-      <c r="E12" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="80">
-        <v>60</v>
-      </c>
-      <c r="G12" s="79" t="s"/>
-      <c r="H12" s="80" t="s"/>
-      <c r="I12" s="82" t="s"/>
-      <c r="J12" s="83" t="s"/>
-      <c r="K12" s="83" t="s"/>
+      <c r="F12" s="83">
+        <v>60</v>
+      </c>
+      <c r="G12" s="82" t="s"/>
+      <c r="H12" s="83" t="s"/>
+      <c r="I12" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="86">
+        <v>60</v>
+      </c>
+      <c r="K12" s="86" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="82" t="s"/>
-      <c r="B13" s="80" t="s"/>
-      <c r="C13" s="82" t="s"/>
-      <c r="D13" s="80" t="s"/>
-      <c r="E13" s="82" t="s"/>
-      <c r="F13" s="80" t="s"/>
-      <c r="G13" s="82" t="s"/>
-      <c r="H13" s="80" t="s"/>
-      <c r="I13" s="82" t="s"/>
-      <c r="J13" s="83" t="s"/>
-      <c r="K13" s="83" t="s"/>
+      <c r="A13" s="85" t="s"/>
+      <c r="B13" s="83" t="s"/>
+      <c r="C13" s="85" t="s"/>
+      <c r="D13" s="83" t="s"/>
+      <c r="E13" s="85" t="s"/>
+      <c r="F13" s="83" t="s"/>
+      <c r="G13" s="85" t="s"/>
+      <c r="H13" s="83" t="s"/>
+      <c r="I13" s="82" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="86">
+        <v>10</v>
+      </c>
+      <c r="K13" s="86" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="82" t="s"/>
-      <c r="B14" s="80" t="s"/>
-      <c r="C14" s="82" t="s"/>
-      <c r="D14" s="80" t="s"/>
-      <c r="E14" s="82" t="s"/>
-      <c r="F14" s="80" t="s"/>
-      <c r="G14" s="82" t="s"/>
-      <c r="H14" s="80" t="s"/>
-      <c r="I14" s="82" t="s"/>
-      <c r="J14" s="83" t="s"/>
-      <c r="K14" s="83" t="s"/>
+      <c r="A14" s="85" t="s"/>
+      <c r="B14" s="83" t="s"/>
+      <c r="C14" s="85" t="s"/>
+      <c r="D14" s="83" t="s"/>
+      <c r="E14" s="85" t="s"/>
+      <c r="F14" s="83" t="s"/>
+      <c r="G14" s="85" t="s"/>
+      <c r="H14" s="83" t="s"/>
+      <c r="I14" s="85" t="s"/>
+      <c r="J14" s="86" t="s"/>
+      <c r="K14" s="86" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="82" t="s"/>
-      <c r="B15" s="80" t="s"/>
-      <c r="C15" s="82" t="s"/>
-      <c r="D15" s="80" t="s"/>
-      <c r="E15" s="82" t="s"/>
-      <c r="F15" s="80" t="s"/>
-      <c r="G15" s="82" t="s"/>
-      <c r="H15" s="80" t="s"/>
-      <c r="I15" s="82" t="s"/>
-      <c r="J15" s="83" t="s"/>
-      <c r="K15" s="84" t="s">
+      <c r="A15" s="85" t="s"/>
+      <c r="B15" s="83" t="s"/>
+      <c r="C15" s="85" t="s"/>
+      <c r="D15" s="83" t="s"/>
+      <c r="E15" s="85" t="s"/>
+      <c r="F15" s="83" t="s"/>
+      <c r="G15" s="85" t="s"/>
+      <c r="H15" s="83" t="s"/>
+      <c r="I15" s="85" t="s"/>
+      <c r="J15" s="86" t="s"/>
+      <c r="K15" s="87" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="85" t="s"/>
-      <c r="B16" s="86">
+      <c r="A16" s="88" t="s"/>
+      <c r="B16" s="89">
         <f>=SUM(B10:B15)</f>
         <v>180</v>
       </c>
-      <c r="C16" s="85" t="s"/>
-      <c r="D16" s="86">
+      <c r="C16" s="88" t="s"/>
+      <c r="D16" s="89">
         <f>=SUM(D10:D15)</f>
         <v>270</v>
       </c>
-      <c r="E16" s="85" t="s"/>
-      <c r="F16" s="86">
+      <c r="E16" s="88" t="s"/>
+      <c r="F16" s="89">
         <f>=SUM(F10:F15)</f>
         <v>210</v>
       </c>
-      <c r="G16" s="85" t="s"/>
-      <c r="H16" s="86">
+      <c r="G16" s="88" t="s"/>
+      <c r="H16" s="89">
         <f>=SUM(H10:H15)</f>
         <v>150</v>
       </c>
-      <c r="I16" s="85" t="s"/>
-      <c r="J16" s="87">
+      <c r="I16" s="88" t="s"/>
+      <c r="J16" s="90">
         <f>=SUM(J10:J15)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="88">
+        <v>220</v>
+      </c>
+      <c r="K16" s="91">
         <f>=SUM(A16:J16)</f>
-        <v>810</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="17" spans="4:4">
-      <c r="D17" s="89" t="s"/>
+      <c r="D17" s="92" t="s"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4638,144 +4923,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="90" t="s"/>
-      <c r="B1" s="91" t="s">
+      <c r="A1" s="93" t="s"/>
+      <c r="B1" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="54" t="s"/>
+      <c r="D1" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="51" t="s"/>
-      <c r="D1" s="91" t="s">
+      <c r="E1" s="54" t="s"/>
+      <c r="F1" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="51" t="s"/>
-      <c r="F1" s="91" t="s">
+      <c r="G1" s="54" t="s"/>
+      <c r="H1" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="51" t="s"/>
-      <c r="H1" s="91" t="s">
+      <c r="I1" s="54" t="s"/>
+      <c r="J1" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="51" t="s"/>
-      <c r="J1" s="91" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="51" t="s"/>
-      <c r="L1" s="92" t="s"/>
+      <c r="K1" s="54" t="s"/>
+      <c r="L1" s="95" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="96" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="C2" s="44">
+        <v>60</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="44">
+        <v>60</v>
+      </c>
+      <c r="F2" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="44">
+        <v>60</v>
+      </c>
+      <c r="H2" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="44">
+        <v>60</v>
+      </c>
+      <c r="J2" s="97" t="s"/>
+      <c r="K2" s="98" t="s"/>
+      <c r="L2" s="99" t="s"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="100" t="s"/>
+      <c r="B3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="42">
-        <v>60</v>
-      </c>
-      <c r="D2" s="94" t="s">
+      <c r="C3" s="11">
+        <v>60</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="42">
-        <v>60</v>
-      </c>
-      <c r="F2" s="94" t="s">
+      <c r="E3" s="11">
+        <v>60</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="42">
-        <v>60</v>
-      </c>
-      <c r="H2" s="94" t="s">
+      <c r="G3" s="11">
+        <v>60</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="I2" s="42">
-        <v>60</v>
-      </c>
-      <c r="J2" s="94" t="s"/>
-      <c r="K2" s="95" t="s"/>
-      <c r="L2" s="96" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="97" t="s"/>
-      <c r="B3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="11">
-        <v>60</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="11">
-        <v>60</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="11">
-        <v>60</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="I3" s="11">
         <v>60</v>
       </c>
       <c r="J3" s="9" t="s"/>
       <c r="K3" s="10" t="s"/>
-      <c r="L3" s="96" t="s"/>
+      <c r="L3" s="99" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="97" t="s"/>
+      <c r="A4" s="100" t="s"/>
       <c r="B4" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="11">
         <v>60</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" s="11">
         <v>60</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" s="11">
         <v>60</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I4" s="11">
         <v>60</v>
       </c>
       <c r="J4" s="9" t="s"/>
       <c r="K4" s="10" t="s"/>
-      <c r="L4" s="62" t="s">
-        <v>45</v>
+      <c r="L4" s="65" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="98" t="s"/>
-      <c r="B5" s="99" t="s"/>
-      <c r="C5" s="100" t="s"/>
-      <c r="D5" s="99" t="s"/>
-      <c r="E5" s="100" t="s"/>
-      <c r="F5" s="99" t="s"/>
-      <c r="G5" s="100" t="s"/>
-      <c r="H5" s="99" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="100">
+      <c r="A5" s="101" t="s"/>
+      <c r="B5" s="102" t="s"/>
+      <c r="C5" s="103" t="s"/>
+      <c r="D5" s="102" t="s"/>
+      <c r="E5" s="103" t="s"/>
+      <c r="F5" s="102" t="s"/>
+      <c r="G5" s="103" t="s"/>
+      <c r="H5" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="103">
         <v>10</v>
       </c>
-      <c r="J5" s="99" t="s"/>
-      <c r="K5" s="101" t="s"/>
-      <c r="L5" s="102">
+      <c r="J5" s="102" t="s"/>
+      <c r="K5" s="104" t="s"/>
+      <c r="L5" s="105">
         <f>=SUM(B2:K5)</f>
         <v>730</v>
       </c>
-      <c r="M5" s="145" t="s">
+      <c r="M5" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4813,195 +5098,203 @@
       <c r="K8" s="6" t="s"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="104" t="s">
+      <c r="D9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="103" t="s">
+      <c r="E9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="104" t="s">
+      <c r="F9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="103" t="s">
+      <c r="G9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="104" t="s">
+      <c r="H9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="103" t="s">
+      <c r="I9" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="105" t="s">
+      <c r="J9" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="105" t="s"/>
+      <c r="K9" s="108" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="106" t="s">
+      <c r="A10" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="92">
+        <v>60</v>
+      </c>
+      <c r="C10" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="92">
+        <v>60</v>
+      </c>
+      <c r="E10" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="92">
+        <v>60</v>
+      </c>
+      <c r="G10" s="109" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="92">
+        <v>60</v>
+      </c>
+      <c r="I10" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="89">
-        <v>60</v>
-      </c>
-      <c r="C10" s="106" t="s">
+      <c r="J10" s="149">
+        <v>60</v>
+      </c>
+      <c r="K10" s="86" t="s"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="89">
-        <v>60</v>
-      </c>
-      <c r="E10" s="106" t="s">
+      <c r="B11" s="92">
+        <v>60</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="89">
-        <v>60</v>
-      </c>
-      <c r="G10" s="106" t="s">
+      <c r="D11" s="92">
+        <v>60</v>
+      </c>
+      <c r="E11" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="89">
-        <v>60</v>
-      </c>
-      <c r="I10" s="82" t="s"/>
-      <c r="J10" s="83" t="s"/>
-      <c r="K10" s="83" t="s"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="27" t="s">
+      <c r="F11" s="92">
+        <v>60</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="92">
+        <v>60</v>
+      </c>
+      <c r="I11" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="89">
-        <v>60</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="J11" s="86">
+        <v>60</v>
+      </c>
+      <c r="K11" s="86" t="s"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="89">
-        <v>60</v>
-      </c>
-      <c r="E11" s="27" t="s">
+      <c r="B12" s="92">
+        <v>60</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="89">
-        <v>60</v>
-      </c>
-      <c r="G11" s="27" t="s">
+      <c r="D12" s="92">
+        <v>60</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="89">
-        <v>60</v>
-      </c>
-      <c r="I11" s="82" t="s"/>
-      <c r="J11" s="83" t="s"/>
-      <c r="K11" s="83" t="s"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="89">
-        <v>60</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="89">
-        <v>60</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="89">
-        <v>60</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="89">
-        <v>60</v>
-      </c>
-      <c r="I12" s="82" t="s"/>
-      <c r="J12" s="83" t="s"/>
-      <c r="K12" s="83" t="s"/>
+      <c r="F12" s="92">
+        <v>60</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="92">
+        <v>60</v>
+      </c>
+      <c r="I12" s="85" t="s"/>
+      <c r="J12" s="86" t="s"/>
+      <c r="K12" s="86" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="82" t="s"/>
-      <c r="B13" s="89" t="s"/>
-      <c r="C13" s="82" t="s"/>
-      <c r="D13" s="89" t="s"/>
-      <c r="E13" s="82" t="s"/>
-      <c r="F13" s="89" t="s"/>
-      <c r="G13" s="82" t="s"/>
-      <c r="H13" s="89" t="s"/>
-      <c r="I13" s="82" t="s"/>
-      <c r="J13" s="83" t="s"/>
-      <c r="K13" s="83" t="s"/>
+      <c r="A13" s="85" t="s"/>
+      <c r="B13" s="92" t="s"/>
+      <c r="C13" s="85" t="s"/>
+      <c r="D13" s="92" t="s"/>
+      <c r="E13" s="85" t="s"/>
+      <c r="F13" s="92" t="s"/>
+      <c r="G13" s="85" t="s"/>
+      <c r="H13" s="92" t="s"/>
+      <c r="I13" s="85" t="s"/>
+      <c r="J13" s="86" t="s"/>
+      <c r="K13" s="86" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="82" t="s"/>
-      <c r="B14" s="89" t="s"/>
-      <c r="C14" s="82" t="s"/>
-      <c r="D14" s="89" t="s"/>
-      <c r="E14" s="82" t="s"/>
-      <c r="F14" s="89" t="s"/>
-      <c r="G14" s="82" t="s"/>
-      <c r="H14" s="89" t="s"/>
-      <c r="I14" s="82" t="s"/>
-      <c r="J14" s="83" t="s"/>
-      <c r="K14" s="83" t="s"/>
+      <c r="A14" s="85" t="s"/>
+      <c r="B14" s="92" t="s"/>
+      <c r="C14" s="85" t="s"/>
+      <c r="D14" s="92" t="s"/>
+      <c r="E14" s="85" t="s"/>
+      <c r="F14" s="92" t="s"/>
+      <c r="G14" s="85" t="s"/>
+      <c r="H14" s="92" t="s"/>
+      <c r="I14" s="85" t="s"/>
+      <c r="J14" s="86" t="s"/>
+      <c r="K14" s="86" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="82" t="s"/>
-      <c r="B15" s="89" t="s"/>
-      <c r="C15" s="82" t="s"/>
-      <c r="D15" s="89" t="s"/>
-      <c r="E15" s="82" t="s"/>
-      <c r="F15" s="89" t="s"/>
-      <c r="G15" s="82" t="s"/>
-      <c r="H15" s="89" t="s"/>
-      <c r="I15" s="82" t="s"/>
-      <c r="J15" s="83" t="s"/>
-      <c r="K15" s="84" t="s">
+      <c r="A15" s="85" t="s"/>
+      <c r="B15" s="92" t="s"/>
+      <c r="C15" s="85" t="s"/>
+      <c r="D15" s="92" t="s"/>
+      <c r="E15" s="85" t="s"/>
+      <c r="F15" s="92" t="s"/>
+      <c r="G15" s="85" t="s"/>
+      <c r="H15" s="92" t="s"/>
+      <c r="I15" s="152" t="s"/>
+      <c r="J15" s="153" t="s"/>
+      <c r="K15" s="87" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="85" t="s"/>
-      <c r="B16" s="86">
+      <c r="A16" s="88" t="s"/>
+      <c r="B16" s="89">
         <f>=SUM(B10:B15)</f>
         <v>180</v>
       </c>
-      <c r="C16" s="85" t="s"/>
-      <c r="D16" s="86">
+      <c r="C16" s="88" t="s"/>
+      <c r="D16" s="89">
         <f>=SUM(D10:D15)</f>
         <v>180</v>
       </c>
-      <c r="E16" s="85" t="s"/>
-      <c r="F16" s="86">
+      <c r="E16" s="88" t="s"/>
+      <c r="F16" s="89">
         <f>=SUM(F10:F15)</f>
         <v>180</v>
       </c>
-      <c r="G16" s="85" t="s"/>
-      <c r="H16" s="86">
+      <c r="G16" s="88" t="s"/>
+      <c r="H16" s="89">
         <f>=SUM(H10:H15)</f>
         <v>180</v>
       </c>
-      <c r="I16" s="85" t="s"/>
-      <c r="J16" s="87">
+      <c r="I16" s="154" t="s"/>
+      <c r="J16" s="155">
         <f>=SUM(J10:J15)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="88">
+        <v>120</v>
+      </c>
+      <c r="K16" s="91">
         <f>=SUM(A16:J16)</f>
-        <v>720</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -5028,154 +5321,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A1" s="107" t="s"/>
-      <c r="B1" s="91">
+      <c r="A1" s="110" t="s"/>
+      <c r="B1" s="94">
         <v>46188</v>
       </c>
-      <c r="C1" s="108" t="s">
+      <c r="C1" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="91">
+      <c r="D1" s="94">
         <v>46189</v>
       </c>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="91">
+      <c r="F1" s="94">
         <v>46190</v>
       </c>
-      <c r="G1" s="108" t="s">
+      <c r="G1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="91">
+      <c r="H1" s="94">
         <v>46191</v>
       </c>
-      <c r="I1" s="108" t="s">
+      <c r="I1" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="50">
+      <c r="J1" s="53">
         <v>46192</v>
       </c>
-      <c r="K1" s="109" t="s">
+      <c r="K1" s="112" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="95" t="s"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="92" t="s"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="110" t="s">
+      <c r="B2" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="C2" s="44">
+        <v>90</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="44">
+        <v>90</v>
+      </c>
+      <c r="F2" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="44">
+        <v>90</v>
+      </c>
+      <c r="H2" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="44">
+        <v>90</v>
+      </c>
+      <c r="J2" s="97" t="s"/>
+      <c r="K2" s="98" t="s"/>
+      <c r="L2" s="99" t="s"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="114" t="s"/>
+      <c r="B3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="42">
-        <v>90</v>
-      </c>
-      <c r="D2" s="94" t="s">
+      <c r="C3" s="11">
+        <v>90</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="42">
-        <v>90</v>
-      </c>
-      <c r="F2" s="94" t="s">
+      <c r="E3" s="11">
+        <v>90</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="42">
-        <v>90</v>
-      </c>
-      <c r="H2" s="94" t="s">
+      <c r="G3" s="11">
+        <v>90</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="I2" s="42">
-        <v>90</v>
-      </c>
-      <c r="J2" s="94" t="s"/>
-      <c r="K2" s="95" t="s"/>
-      <c r="L2" s="96" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="111" t="s"/>
-      <c r="B3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="11">
-        <v>90</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="11">
-        <v>90</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="11">
-        <v>90</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>55</v>
       </c>
       <c r="I3" s="11">
         <v>90</v>
       </c>
       <c r="J3" s="9" t="s"/>
       <c r="K3" s="10" t="s"/>
-      <c r="L3" s="96" t="s"/>
+      <c r="L3" s="99" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="111" t="s"/>
+      <c r="A4" s="114" t="s"/>
       <c r="B4" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="11">
         <v>60</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="11">
         <v>60</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="11">
         <v>60</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I4" s="11">
         <v>60</v>
       </c>
       <c r="J4" s="9" t="s"/>
       <c r="K4" s="10" t="s"/>
-      <c r="L4" s="62" t="s">
-        <v>45</v>
+      <c r="L4" s="65" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="15" t="s"/>
-      <c r="B5" s="99" t="s"/>
-      <c r="C5" s="100" t="s"/>
-      <c r="D5" s="99" t="s"/>
-      <c r="E5" s="100" t="s"/>
-      <c r="F5" s="99" t="s"/>
-      <c r="G5" s="100" t="s"/>
-      <c r="H5" s="99" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="100">
+      <c r="B5" s="102" t="s"/>
+      <c r="C5" s="103" t="s"/>
+      <c r="D5" s="102" t="s"/>
+      <c r="E5" s="103" t="s"/>
+      <c r="F5" s="102" t="s"/>
+      <c r="G5" s="103" t="s"/>
+      <c r="H5" s="102" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="103">
         <v>10</v>
       </c>
-      <c r="J5" s="99" t="s"/>
-      <c r="K5" s="101" t="s"/>
-      <c r="L5" s="102">
+      <c r="J5" s="102" t="s"/>
+      <c r="K5" s="104" t="s"/>
+      <c r="L5" s="105">
         <f>=SUM(B2:K5)</f>
         <v>970</v>
       </c>
-      <c r="M5" s="145" t="s">
+      <c r="M5" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5213,191 +5506,197 @@
       <c r="K8" s="6" t="s"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="104" t="s">
+      <c r="D9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="103" t="s">
+      <c r="E9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="104" t="s">
+      <c r="F9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="103" t="s">
+      <c r="G9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="104" t="s">
+      <c r="H9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="103" t="s">
+      <c r="I9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="105" t="s">
+      <c r="J9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="105" t="s"/>
+      <c r="K9" s="108" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="106" t="s">
+      <c r="A10" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="92">
+        <v>90</v>
+      </c>
+      <c r="C10" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="92">
+        <v>90</v>
+      </c>
+      <c r="E10" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="92">
+        <v>90</v>
+      </c>
+      <c r="G10" s="109" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="92">
+        <v>90</v>
+      </c>
+      <c r="I10" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="86">
+        <v>10</v>
+      </c>
+      <c r="K10" s="86" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="89">
-        <v>90</v>
-      </c>
-      <c r="C10" s="106" t="s">
+      <c r="B11" s="92">
+        <v>90</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="89">
-        <v>90</v>
-      </c>
-      <c r="E10" s="106" t="s">
+      <c r="D11" s="92">
+        <v>90</v>
+      </c>
+      <c r="E11" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="89">
-        <v>90</v>
-      </c>
-      <c r="G10" s="106" t="s">
+      <c r="F11" s="92">
+        <v>60</v>
+      </c>
+      <c r="G11" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="89">
-        <v>90</v>
-      </c>
-      <c r="I10" s="82" t="s"/>
-      <c r="J10" s="83" t="s"/>
-      <c r="K10" s="83" t="s"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="27" t="s">
+      <c r="H11" s="92">
+        <v>60</v>
+      </c>
+      <c r="I11" s="85" t="s"/>
+      <c r="J11" s="86" t="s"/>
+      <c r="K11" s="86" t="s"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="89">
-        <v>90</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="B12" s="92">
+        <v>60</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="89">
-        <v>90</v>
-      </c>
-      <c r="E11" s="27" t="s">
+      <c r="D12" s="92">
+        <v>60</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="89">
-        <v>60</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" s="89">
-        <v>60</v>
-      </c>
-      <c r="I11" s="82" t="s"/>
-      <c r="J11" s="83" t="s"/>
-      <c r="K11" s="83" t="s"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="89">
-        <v>60</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="89">
-        <v>60</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="89">
-        <v>60</v>
-      </c>
-      <c r="G12" s="27" t="s"/>
-      <c r="H12" s="89" t="s"/>
-      <c r="I12" s="82" t="s"/>
-      <c r="J12" s="83" t="s"/>
-      <c r="K12" s="83" t="s"/>
+      <c r="F12" s="92">
+        <v>60</v>
+      </c>
+      <c r="G12" s="28" t="s"/>
+      <c r="H12" s="92" t="s"/>
+      <c r="I12" s="85" t="s"/>
+      <c r="J12" s="86" t="s"/>
+      <c r="K12" s="86" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="82" t="s"/>
-      <c r="B13" s="89" t="s"/>
-      <c r="C13" s="82" t="s"/>
-      <c r="D13" s="89" t="s"/>
-      <c r="E13" s="82" t="s"/>
-      <c r="F13" s="89" t="s"/>
-      <c r="G13" s="82" t="s"/>
-      <c r="H13" s="89" t="s"/>
-      <c r="I13" s="82" t="s"/>
-      <c r="J13" s="83" t="s"/>
-      <c r="K13" s="83" t="s"/>
+      <c r="A13" s="85" t="s"/>
+      <c r="B13" s="92" t="s"/>
+      <c r="C13" s="85" t="s"/>
+      <c r="D13" s="92" t="s"/>
+      <c r="E13" s="85" t="s"/>
+      <c r="F13" s="92" t="s"/>
+      <c r="G13" s="85" t="s"/>
+      <c r="H13" s="92" t="s"/>
+      <c r="I13" s="85" t="s"/>
+      <c r="J13" s="86" t="s"/>
+      <c r="K13" s="86" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="82" t="s"/>
-      <c r="B14" s="89" t="s"/>
-      <c r="C14" s="82" t="s"/>
-      <c r="D14" s="89" t="s"/>
-      <c r="E14" s="82" t="s"/>
-      <c r="F14" s="89" t="s"/>
-      <c r="G14" s="82" t="s"/>
-      <c r="H14" s="89" t="s"/>
-      <c r="I14" s="82" t="s"/>
-      <c r="J14" s="83" t="s"/>
-      <c r="K14" s="83" t="s"/>
+      <c r="A14" s="85" t="s"/>
+      <c r="B14" s="92" t="s"/>
+      <c r="C14" s="85" t="s"/>
+      <c r="D14" s="92" t="s"/>
+      <c r="E14" s="85" t="s"/>
+      <c r="F14" s="92" t="s"/>
+      <c r="G14" s="85" t="s"/>
+      <c r="H14" s="92" t="s"/>
+      <c r="I14" s="85" t="s"/>
+      <c r="J14" s="86" t="s"/>
+      <c r="K14" s="86" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="82" t="s"/>
-      <c r="B15" s="89" t="s"/>
-      <c r="C15" s="82" t="s"/>
-      <c r="D15" s="89" t="s"/>
-      <c r="E15" s="82" t="s"/>
-      <c r="F15" s="89" t="s"/>
-      <c r="G15" s="82" t="s"/>
-      <c r="H15" s="89" t="s"/>
-      <c r="I15" s="82" t="s"/>
-      <c r="J15" s="83" t="s"/>
-      <c r="K15" s="84" t="s">
+      <c r="A15" s="85" t="s"/>
+      <c r="B15" s="92" t="s"/>
+      <c r="C15" s="85" t="s"/>
+      <c r="D15" s="92" t="s"/>
+      <c r="E15" s="85" t="s"/>
+      <c r="F15" s="92" t="s"/>
+      <c r="G15" s="85" t="s"/>
+      <c r="H15" s="92" t="s"/>
+      <c r="I15" s="85" t="s"/>
+      <c r="J15" s="86" t="s"/>
+      <c r="K15" s="87" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="85" t="s"/>
-      <c r="B16" s="86">
+      <c r="A16" s="88" t="s"/>
+      <c r="B16" s="89">
         <f>=SUM(B10:B15)</f>
         <v>240</v>
       </c>
-      <c r="C16" s="85" t="s"/>
-      <c r="D16" s="86">
+      <c r="C16" s="88" t="s"/>
+      <c r="D16" s="89">
         <f>=SUM(D10:D15)</f>
         <v>240</v>
       </c>
-      <c r="E16" s="85" t="s"/>
-      <c r="F16" s="86">
+      <c r="E16" s="88" t="s"/>
+      <c r="F16" s="89">
         <f>=SUM(F10:F15)</f>
         <v>210</v>
       </c>
-      <c r="G16" s="85" t="s"/>
-      <c r="H16" s="86">
+      <c r="G16" s="88" t="s"/>
+      <c r="H16" s="89">
         <f>=SUM(H10:H15)</f>
         <v>150</v>
       </c>
-      <c r="I16" s="85" t="s"/>
-      <c r="J16" s="87">
+      <c r="I16" s="88" t="s"/>
+      <c r="J16" s="90">
         <f>=SUM(J10:J15)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="88">
+        <v>10</v>
+      </c>
+      <c r="K16" s="91">
         <f>=SUM(A16:J16)</f>
-        <v>840</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -5417,114 +5716,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="107" t="s"/>
-      <c r="B1" s="91" t="s">
+      <c r="A1" s="110" t="s"/>
+      <c r="B1" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="54" t="s"/>
+      <c r="D1" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="51" t="s"/>
-      <c r="D1" s="91" t="s">
+      <c r="E1" s="54" t="s"/>
+      <c r="F1" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="51" t="s"/>
-      <c r="F1" s="91" t="s">
+      <c r="G1" s="54" t="s"/>
+      <c r="H1" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="51" t="s"/>
-      <c r="H1" s="91" t="s">
+      <c r="I1" s="54" t="s"/>
+      <c r="J1" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="51" t="s"/>
-      <c r="J1" s="91" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="51" t="s"/>
-      <c r="L1" s="92" t="s"/>
+      <c r="K1" s="54" t="s"/>
+      <c r="L1" s="95" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="115" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="C2" s="44">
+        <v>90</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="44">
+        <v>90</v>
+      </c>
+      <c r="F2" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="44">
+        <v>90</v>
+      </c>
+      <c r="H2" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="98">
+        <v>90</v>
+      </c>
+      <c r="J2" s="116" t="s"/>
+      <c r="K2" s="117" t="s"/>
+      <c r="L2" s="118" t="s"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="119" t="s"/>
+      <c r="B3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="42">
-        <v>90</v>
-      </c>
-      <c r="D2" s="94" t="s">
+      <c r="C3" s="11">
+        <v>90</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="42">
-        <v>90</v>
-      </c>
-      <c r="F2" s="94" t="s">
+      <c r="E3" s="11">
+        <v>90</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="42">
-        <v>90</v>
-      </c>
-      <c r="H2" s="94" t="s">
+      <c r="G3" s="11">
+        <v>90</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I2" s="95">
-        <v>90</v>
-      </c>
-      <c r="J2" s="113" t="s"/>
-      <c r="K2" s="114" t="s"/>
-      <c r="L2" s="115" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="116" t="s"/>
-      <c r="B3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="11">
-        <v>90</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="11">
-        <v>90</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="11">
-        <v>90</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="I3" s="10">
         <v>90</v>
       </c>
-      <c r="J3" s="117" t="s"/>
-      <c r="K3" s="115" t="s"/>
-      <c r="L3" s="62" t="s">
-        <v>45</v>
+      <c r="J3" s="120" t="s"/>
+      <c r="K3" s="118" t="s"/>
+      <c r="L3" s="65" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="118" t="s"/>
-      <c r="B4" s="118" t="s"/>
-      <c r="C4" s="119" t="s"/>
-      <c r="D4" s="99" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="100">
-        <v>90</v>
-      </c>
-      <c r="F4" s="118" t="s"/>
-      <c r="G4" s="119" t="s"/>
-      <c r="H4" s="118" t="s"/>
-      <c r="I4" s="120" t="s"/>
-      <c r="J4" s="121" t="s"/>
-      <c r="K4" s="122" t="s"/>
-      <c r="L4" s="123">
+      <c r="A4" s="121" t="s"/>
+      <c r="B4" s="121" t="s"/>
+      <c r="C4" s="122" t="s"/>
+      <c r="D4" s="102" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="103">
+        <v>90</v>
+      </c>
+      <c r="F4" s="121" t="s"/>
+      <c r="G4" s="122" t="s"/>
+      <c r="H4" s="121" t="s"/>
+      <c r="I4" s="123" t="s"/>
+      <c r="J4" s="124" t="s"/>
+      <c r="K4" s="125" t="s"/>
+      <c r="L4" s="126">
         <f>=SUM(B2:K4)</f>
         <v>810</v>
       </c>
-      <c r="M4" s="145" t="s">
+      <c r="M4" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5562,179 +5861,187 @@
       <c r="K7" s="6" t="s"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="104" t="s">
+      <c r="D8" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="103" t="s">
+      <c r="E8" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="104" t="s">
+      <c r="F8" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="103" t="s">
+      <c r="G8" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="104" t="s">
+      <c r="H8" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="103" t="s">
+      <c r="I8" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="105" t="s">
+      <c r="J8" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="105" t="s"/>
+      <c r="K8" s="108" t="s"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="106" t="s">
+      <c r="A9" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="92">
+        <v>90</v>
+      </c>
+      <c r="C9" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="92">
+        <v>90</v>
+      </c>
+      <c r="E9" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="92">
+        <v>90</v>
+      </c>
+      <c r="G9" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="92">
+        <v>90</v>
+      </c>
+      <c r="I9" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="149">
+        <v>90</v>
+      </c>
+      <c r="K9" s="86" t="s"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="89">
-        <v>90</v>
-      </c>
-      <c r="C9" s="106" t="s">
+      <c r="B10" s="92">
+        <v>90</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="89">
-        <v>90</v>
-      </c>
-      <c r="E9" s="106" t="s">
+      <c r="D10" s="92">
+        <v>90</v>
+      </c>
+      <c r="E10" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="89">
-        <v>90</v>
-      </c>
-      <c r="G9" s="106" t="s">
+      <c r="F10" s="92">
+        <v>90</v>
+      </c>
+      <c r="G10" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="89">
-        <v>90</v>
-      </c>
-      <c r="I9" s="82" t="s"/>
-      <c r="J9" s="83" t="s"/>
-      <c r="K9" s="83" t="s"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="89">
-        <v>90</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="89">
-        <v>90</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="89">
-        <v>90</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="89">
-        <v>90</v>
-      </c>
-      <c r="I10" s="82" t="s"/>
-      <c r="J10" s="83" t="s"/>
-      <c r="K10" s="83" t="s"/>
+      <c r="H10" s="92">
+        <v>90</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="86">
+        <v>90</v>
+      </c>
+      <c r="K10" s="86" t="s"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="27" t="s"/>
-      <c r="B11" s="89" t="s"/>
-      <c r="C11" s="27" t="s"/>
-      <c r="D11" s="89" t="s"/>
-      <c r="E11" s="27" t="s"/>
-      <c r="F11" s="89" t="s"/>
-      <c r="G11" s="27" t="s"/>
-      <c r="H11" s="89" t="s"/>
-      <c r="I11" s="82" t="s"/>
-      <c r="J11" s="83" t="s"/>
-      <c r="K11" s="83" t="s"/>
+      <c r="A11" s="28" t="s"/>
+      <c r="B11" s="92" t="s"/>
+      <c r="C11" s="28" t="s"/>
+      <c r="D11" s="92" t="s"/>
+      <c r="E11" s="28" t="s"/>
+      <c r="F11" s="92" t="s"/>
+      <c r="G11" s="28" t="s"/>
+      <c r="H11" s="92" t="s"/>
+      <c r="I11" s="85" t="s"/>
+      <c r="J11" s="86" t="s"/>
+      <c r="K11" s="86" t="s"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="82" t="s"/>
-      <c r="B12" s="89" t="s"/>
-      <c r="C12" s="82" t="s"/>
-      <c r="D12" s="89" t="s"/>
-      <c r="E12" s="82" t="s"/>
-      <c r="F12" s="89" t="s"/>
-      <c r="G12" s="82" t="s"/>
-      <c r="H12" s="89" t="s"/>
-      <c r="I12" s="82" t="s"/>
-      <c r="J12" s="83" t="s"/>
-      <c r="K12" s="83" t="s"/>
+      <c r="A12" s="85" t="s"/>
+      <c r="B12" s="92" t="s"/>
+      <c r="C12" s="85" t="s"/>
+      <c r="D12" s="92" t="s"/>
+      <c r="E12" s="85" t="s"/>
+      <c r="F12" s="92" t="s"/>
+      <c r="G12" s="85" t="s"/>
+      <c r="H12" s="92" t="s"/>
+      <c r="I12" s="85" t="s"/>
+      <c r="J12" s="86" t="s"/>
+      <c r="K12" s="86" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="82" t="s"/>
-      <c r="B13" s="89" t="s"/>
-      <c r="C13" s="82" t="s"/>
-      <c r="D13" s="89" t="s"/>
-      <c r="E13" s="82" t="s"/>
-      <c r="F13" s="89" t="s"/>
-      <c r="G13" s="82" t="s"/>
-      <c r="H13" s="89" t="s"/>
-      <c r="I13" s="82" t="s"/>
-      <c r="J13" s="83" t="s"/>
-      <c r="K13" s="83" t="s"/>
+      <c r="A13" s="85" t="s"/>
+      <c r="B13" s="92" t="s"/>
+      <c r="C13" s="85" t="s"/>
+      <c r="D13" s="92" t="s"/>
+      <c r="E13" s="85" t="s"/>
+      <c r="F13" s="92" t="s"/>
+      <c r="G13" s="85" t="s"/>
+      <c r="H13" s="92" t="s"/>
+      <c r="I13" s="85" t="s"/>
+      <c r="J13" s="86" t="s"/>
+      <c r="K13" s="86" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="82" t="s"/>
-      <c r="B14" s="89" t="s"/>
-      <c r="C14" s="82" t="s"/>
-      <c r="D14" s="89" t="s"/>
-      <c r="E14" s="82" t="s"/>
-      <c r="F14" s="89" t="s"/>
-      <c r="G14" s="82" t="s"/>
-      <c r="H14" s="89" t="s"/>
-      <c r="I14" s="82" t="s"/>
-      <c r="J14" s="83" t="s"/>
-      <c r="K14" s="84" t="s">
+      <c r="A14" s="85" t="s"/>
+      <c r="B14" s="92" t="s"/>
+      <c r="C14" s="85" t="s"/>
+      <c r="D14" s="92" t="s"/>
+      <c r="E14" s="85" t="s"/>
+      <c r="F14" s="92" t="s"/>
+      <c r="G14" s="85" t="s"/>
+      <c r="H14" s="92" t="s"/>
+      <c r="I14" s="152" t="s"/>
+      <c r="J14" s="153" t="s"/>
+      <c r="K14" s="87" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="85" t="s"/>
-      <c r="B15" s="86">
+      <c r="A15" s="88" t="s"/>
+      <c r="B15" s="89">
         <f>=SUM(B9:B14)</f>
         <v>180</v>
       </c>
-      <c r="C15" s="85" t="s"/>
-      <c r="D15" s="86">
+      <c r="C15" s="88" t="s"/>
+      <c r="D15" s="89">
         <f>=SUM(D9:D14)</f>
         <v>180</v>
       </c>
-      <c r="E15" s="85" t="s"/>
-      <c r="F15" s="86">
+      <c r="E15" s="88" t="s"/>
+      <c r="F15" s="89">
         <f>=SUM(F9:F14)</f>
         <v>180</v>
       </c>
-      <c r="G15" s="85" t="s"/>
-      <c r="H15" s="86">
+      <c r="G15" s="88" t="s"/>
+      <c r="H15" s="89">
         <f>=SUM(H9:H14)</f>
         <v>180</v>
       </c>
-      <c r="I15" s="85" t="s"/>
-      <c r="J15" s="87">
+      <c r="I15" s="154" t="s"/>
+      <c r="J15" s="155">
         <f>=SUM(J9:J14)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="88">
+        <v>180</v>
+      </c>
+      <c r="K15" s="91">
         <f>=SUM(A15:J15)</f>
-        <v>720</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -5761,120 +6068,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="107" t="s"/>
-      <c r="B1" s="91" t="s">
+      <c r="A1" s="110" t="s"/>
+      <c r="B1" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="127" t="s"/>
+      <c r="D1" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="124" t="s"/>
-      <c r="D1" s="91" t="s">
+      <c r="E1" s="127" t="s"/>
+      <c r="F1" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="124" t="s"/>
-      <c r="F1" s="91" t="s">
+      <c r="G1" s="127" t="s"/>
+      <c r="H1" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="124" t="s"/>
-      <c r="H1" s="125" t="s">
+      <c r="I1" s="129" t="s"/>
+      <c r="J1" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="126" t="s"/>
-      <c r="J1" s="91" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="124" t="s"/>
-      <c r="L1" s="127" t="s"/>
+      <c r="K1" s="127" t="s"/>
+      <c r="L1" s="130" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="128" t="s">
+      <c r="A2" s="131" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="C2" s="44">
+        <v>90</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="44">
+        <v>90</v>
+      </c>
+      <c r="F2" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="98">
+        <v>90</v>
+      </c>
+      <c r="H2" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" s="44">
+        <v>45</v>
+      </c>
+      <c r="J2" s="54" t="s"/>
+      <c r="K2" s="54" t="s"/>
+      <c r="L2" s="95" t="s"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="119" t="s"/>
+      <c r="B3" s="119" t="s"/>
+      <c r="C3" s="132" t="s"/>
+      <c r="D3" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="42">
-        <v>90</v>
-      </c>
-      <c r="D2" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="42">
-        <v>90</v>
-      </c>
-      <c r="F2" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" s="95">
-        <v>90</v>
-      </c>
-      <c r="H2" s="94" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="42">
-        <v>45</v>
-      </c>
-      <c r="J2" s="51" t="s"/>
-      <c r="K2" s="51" t="s"/>
-      <c r="L2" s="92" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="116" t="s"/>
-      <c r="B3" s="116" t="s"/>
-      <c r="C3" s="129" t="s"/>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="11">
+        <v>90</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="11">
-        <v>90</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="G3" s="10">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I3" s="11">
         <v>45</v>
       </c>
-      <c r="L3" s="96" t="s"/>
+      <c r="L3" s="99" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="116" t="s"/>
-      <c r="B4" s="116" t="s"/>
-      <c r="C4" s="129" t="s"/>
+      <c r="A4" s="119" t="s"/>
+      <c r="B4" s="119" t="s"/>
+      <c r="C4" s="132" t="s"/>
       <c r="D4" s="9" t="s"/>
       <c r="E4" s="11" t="s"/>
-      <c r="F4" s="116" t="s"/>
-      <c r="G4" s="130" t="s"/>
+      <c r="F4" s="119" t="s"/>
+      <c r="G4" s="133" t="s"/>
       <c r="H4" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" s="11">
         <v>20</v>
       </c>
-      <c r="L4" s="62" t="s">
-        <v>45</v>
+      <c r="L4" s="65" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="118" t="s"/>
-      <c r="B5" s="118" t="s"/>
-      <c r="C5" s="119" t="s"/>
-      <c r="D5" s="118" t="s"/>
-      <c r="E5" s="119" t="s"/>
-      <c r="F5" s="118" t="s"/>
-      <c r="G5" s="120" t="s"/>
-      <c r="H5" s="99" t="s"/>
-      <c r="I5" s="100" t="s"/>
-      <c r="J5" s="131" t="s"/>
-      <c r="K5" s="131" t="s"/>
-      <c r="L5" s="102">
+      <c r="A5" s="121" t="s"/>
+      <c r="B5" s="121" t="s"/>
+      <c r="C5" s="122" t="s"/>
+      <c r="D5" s="121" t="s"/>
+      <c r="E5" s="122" t="s"/>
+      <c r="F5" s="121" t="s"/>
+      <c r="G5" s="123" t="s"/>
+      <c r="H5" s="102" t="s"/>
+      <c r="I5" s="103" t="s"/>
+      <c r="J5" s="134" t="s"/>
+      <c r="K5" s="134" t="s"/>
+      <c r="L5" s="105">
         <f>=SUM(B2:K5)</f>
         <v>560</v>
       </c>
-      <c r="M5" s="145" t="s">
+      <c r="M5" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5902,136 +6209,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="107" t="s"/>
-      <c r="B1" s="91" t="s">
+      <c r="A1" s="110" t="s"/>
+      <c r="B1" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="127" t="s"/>
+      <c r="D1" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="124" t="s"/>
-      <c r="D1" s="91" t="s">
+      <c r="E1" s="127" t="s"/>
+      <c r="F1" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="124" t="s"/>
-      <c r="F1" s="91" t="s">
+      <c r="G1" s="127" t="s"/>
+      <c r="H1" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="124" t="s"/>
-      <c r="H1" s="91" t="s">
+      <c r="I1" s="127" t="s"/>
+      <c r="J1" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="124" t="s"/>
-      <c r="J1" s="91" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="124" t="s"/>
-      <c r="L1" s="127" t="s"/>
+      <c r="K1" s="127" t="s"/>
+      <c r="L1" s="130" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="113" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="97" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="C2" s="44">
+        <v>90</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="44">
+        <v>90</v>
+      </c>
+      <c r="F2" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="44">
+        <v>90</v>
+      </c>
+      <c r="H2" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="44">
+        <v>90</v>
+      </c>
+      <c r="J2" s="135" t="s"/>
+      <c r="K2" s="136" t="s"/>
+      <c r="L2" s="99" t="s"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="119" t="s"/>
+      <c r="B3" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="42">
-        <v>90</v>
-      </c>
-      <c r="D2" s="94" t="s">
+      <c r="C3" s="11">
+        <v>90</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="42">
-        <v>90</v>
-      </c>
-      <c r="F2" s="94" t="s">
+      <c r="E3" s="11">
+        <v>90</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="42">
-        <v>90</v>
-      </c>
-      <c r="H2" s="94" t="s">
+      <c r="G3" s="11">
+        <v>90</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="42">
-        <v>90</v>
-      </c>
-      <c r="J2" s="132" t="s"/>
-      <c r="K2" s="133" t="s"/>
-      <c r="L2" s="96" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="116" t="s"/>
-      <c r="B3" s="9" t="s">
+      <c r="I3" s="11">
+        <v>90</v>
+      </c>
+      <c r="J3" s="119" t="s"/>
+      <c r="K3" s="133" t="s"/>
+      <c r="L3" s="99" t="s"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="119" t="s"/>
+      <c r="B4" s="119" t="s"/>
+      <c r="C4" s="132" t="s"/>
+      <c r="D4" s="119" t="s"/>
+      <c r="E4" s="132" t="s"/>
+      <c r="F4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="11">
-        <v>90</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="G4" s="11">
+        <v>90</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="11">
-        <v>90</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="11">
-        <v>90</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" s="11">
-        <v>90</v>
-      </c>
-      <c r="J3" s="116" t="s"/>
-      <c r="K3" s="130" t="s"/>
-      <c r="L3" s="96" t="s"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="116" t="s"/>
-      <c r="B4" s="116" t="s"/>
-      <c r="C4" s="129" t="s"/>
-      <c r="D4" s="116" t="s"/>
-      <c r="E4" s="129" t="s"/>
-      <c r="F4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="11">
-        <v>90</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>70</v>
-      </c>
       <c r="I4" s="11">
         <v>90</v>
       </c>
-      <c r="J4" s="116" t="s"/>
-      <c r="K4" s="130" t="s"/>
-      <c r="L4" s="62" t="s">
-        <v>45</v>
+      <c r="J4" s="119" t="s"/>
+      <c r="K4" s="133" t="s"/>
+      <c r="L4" s="65" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="118" t="s"/>
-      <c r="B5" s="118" t="s"/>
-      <c r="C5" s="119" t="s"/>
-      <c r="D5" s="118" t="s"/>
-      <c r="E5" s="119" t="s"/>
-      <c r="F5" s="118" t="s"/>
-      <c r="G5" s="119" t="s"/>
-      <c r="H5" s="99" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="100">
+      <c r="A5" s="121" t="s"/>
+      <c r="B5" s="121" t="s"/>
+      <c r="C5" s="122" t="s"/>
+      <c r="D5" s="121" t="s"/>
+      <c r="E5" s="122" t="s"/>
+      <c r="F5" s="121" t="s"/>
+      <c r="G5" s="122" t="s"/>
+      <c r="H5" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="103">
         <v>10</v>
       </c>
-      <c r="J5" s="118" t="s"/>
-      <c r="K5" s="120" t="s"/>
-      <c r="L5" s="102">
+      <c r="J5" s="121" t="s"/>
+      <c r="K5" s="123" t="s"/>
+      <c r="L5" s="105">
         <f>=SUM(B2:K5)</f>
         <v>910</v>
       </c>
-      <c r="M5" s="145" t="s">
+      <c r="M5" s="71" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6069,195 +6376,207 @@
       <c r="K8" s="6" t="s"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="104" t="s">
+      <c r="D9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="103" t="s">
+      <c r="E9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="104" t="s">
+      <c r="F9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="103" t="s">
+      <c r="G9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="104" t="s">
+      <c r="H9" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="103" t="s">
+      <c r="I9" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="105" t="s">
+      <c r="J9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="105" t="s"/>
+      <c r="K9" s="108" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="106" t="s">
+      <c r="A10" s="109" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="137">
+        <v>90</v>
+      </c>
+      <c r="C10" s="109" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="137">
+        <v>90</v>
+      </c>
+      <c r="E10" s="109" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="137">
+        <v>60</v>
+      </c>
+      <c r="G10" s="109" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="137">
+        <v>60</v>
+      </c>
+      <c r="I10" s="109" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" s="137">
+        <v>60</v>
+      </c>
+      <c r="K10" s="86" t="s"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="143">
-        <v>90</v>
-      </c>
-      <c r="C10" s="106" t="s">
+      <c r="B11" s="30">
+        <v>90</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="143">
-        <v>90</v>
-      </c>
-      <c r="E10" s="106" t="s">
+      <c r="D11" s="30">
+        <v>90</v>
+      </c>
+      <c r="E11" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="143">
-        <v>60</v>
-      </c>
-      <c r="G10" s="106" t="s">
+      <c r="F11" s="30">
+        <v>90</v>
+      </c>
+      <c r="G11" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="143">
-        <v>60</v>
-      </c>
-      <c r="I10" s="82" t="s"/>
-      <c r="J10" s="83" t="s"/>
-      <c r="K10" s="83" t="s"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="27" t="s">
+      <c r="H11" s="30">
+        <v>90</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="30">
+        <v>90</v>
+      </c>
+      <c r="K11" s="86" t="s"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="29">
-        <v>90</v>
-      </c>
-      <c r="C11" s="27" t="s">
+      <c r="B12" s="30">
+        <v>90</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="29">
-        <v>90</v>
-      </c>
-      <c r="E11" s="27" t="s">
+      <c r="D12" s="30">
+        <v>90</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="29">
-        <v>90</v>
-      </c>
-      <c r="G11" s="27" t="s">
+      <c r="F12" s="30">
+        <v>60</v>
+      </c>
+      <c r="G12" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="29">
-        <v>90</v>
-      </c>
-      <c r="I11" s="82" t="s"/>
-      <c r="J11" s="83" t="s"/>
-      <c r="K11" s="83" t="s"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="29">
-        <v>90</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="29">
-        <v>90</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="29">
-        <v>60</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="29">
-        <v>60</v>
-      </c>
-      <c r="I12" s="82" t="s"/>
-      <c r="J12" s="83" t="s"/>
-      <c r="K12" s="83" t="s"/>
+      <c r="H12" s="30">
+        <v>60</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="J12" s="30">
+        <v>60</v>
+      </c>
+      <c r="K12" s="86" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="82" t="s"/>
-      <c r="B13" s="89" t="s"/>
-      <c r="C13" s="82" t="s"/>
-      <c r="D13" s="89" t="s"/>
-      <c r="E13" s="82" t="s"/>
-      <c r="F13" s="89" t="s"/>
-      <c r="G13" s="82" t="s"/>
-      <c r="H13" s="89" t="s"/>
-      <c r="I13" s="82" t="s"/>
-      <c r="J13" s="83" t="s"/>
-      <c r="K13" s="83" t="s"/>
+      <c r="A13" s="85" t="s"/>
+      <c r="B13" s="92" t="s"/>
+      <c r="C13" s="85" t="s"/>
+      <c r="D13" s="92" t="s"/>
+      <c r="E13" s="85" t="s"/>
+      <c r="F13" s="92" t="s"/>
+      <c r="G13" s="85" t="s"/>
+      <c r="H13" s="92" t="s"/>
+      <c r="I13" s="85" t="s"/>
+      <c r="J13" s="86" t="s"/>
+      <c r="K13" s="86" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="82" t="s"/>
-      <c r="B14" s="89" t="s"/>
-      <c r="C14" s="82" t="s"/>
-      <c r="D14" s="89" t="s"/>
-      <c r="E14" s="82" t="s"/>
-      <c r="F14" s="89" t="s"/>
-      <c r="G14" s="82" t="s"/>
-      <c r="H14" s="89" t="s"/>
-      <c r="I14" s="82" t="s"/>
-      <c r="J14" s="83" t="s"/>
-      <c r="K14" s="83" t="s"/>
+      <c r="A14" s="85" t="s"/>
+      <c r="B14" s="92" t="s"/>
+      <c r="C14" s="85" t="s"/>
+      <c r="D14" s="92" t="s"/>
+      <c r="E14" s="85" t="s"/>
+      <c r="F14" s="92" t="s"/>
+      <c r="G14" s="85" t="s"/>
+      <c r="H14" s="92" t="s"/>
+      <c r="I14" s="85" t="s"/>
+      <c r="J14" s="86" t="s"/>
+      <c r="K14" s="86" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="82" t="s"/>
-      <c r="B15" s="89" t="s"/>
-      <c r="C15" s="82" t="s"/>
-      <c r="D15" s="89" t="s"/>
-      <c r="E15" s="82" t="s"/>
-      <c r="F15" s="89" t="s"/>
-      <c r="G15" s="82" t="s"/>
-      <c r="H15" s="89" t="s"/>
-      <c r="I15" s="82" t="s"/>
-      <c r="J15" s="83" t="s"/>
-      <c r="K15" s="84" t="s">
+      <c r="A15" s="85" t="s"/>
+      <c r="B15" s="92" t="s"/>
+      <c r="C15" s="85" t="s"/>
+      <c r="D15" s="92" t="s"/>
+      <c r="E15" s="85" t="s"/>
+      <c r="F15" s="92" t="s"/>
+      <c r="G15" s="85" t="s"/>
+      <c r="H15" s="92" t="s"/>
+      <c r="I15" s="85" t="s"/>
+      <c r="J15" s="86" t="s"/>
+      <c r="K15" s="87" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="85" t="s"/>
-      <c r="B16" s="86">
+      <c r="A16" s="88" t="s"/>
+      <c r="B16" s="89">
         <f>=SUM(B10:B15)</f>
         <v>270</v>
       </c>
-      <c r="C16" s="85" t="s"/>
-      <c r="D16" s="86">
+      <c r="C16" s="88" t="s"/>
+      <c r="D16" s="89">
         <f>=SUM(D10:D15)</f>
         <v>270</v>
       </c>
-      <c r="E16" s="85" t="s"/>
-      <c r="F16" s="86">
+      <c r="E16" s="88" t="s"/>
+      <c r="F16" s="89">
         <f>=SUM(F10:F15)</f>
         <v>210</v>
       </c>
-      <c r="G16" s="85" t="s"/>
-      <c r="H16" s="86">
+      <c r="G16" s="88" t="s"/>
+      <c r="H16" s="89">
         <f>=SUM(H10:H15)</f>
         <v>210</v>
       </c>
-      <c r="I16" s="85" t="s"/>
-      <c r="J16" s="87">
+      <c r="I16" s="88" t="s"/>
+      <c r="J16" s="90">
         <f>=SUM(J10:J15)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="88">
+        <v>210</v>
+      </c>
+      <c r="K16" s="91">
         <f>=SUM(A16:J16)</f>
-        <v>960</v>
+        <v>1170</v>
       </c>
     </row>
   </sheetData>

--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t/>
   </si>
@@ -283,6 +283,12 @@
   <si>
     <t xml:space="preserve">谢佳俊
 </t>
+  </si>
+  <si>
+    <t>王利民</t>
+  </si>
+  <si>
+    <t>蔡建华</t>
   </si>
 </sst>
 </file>
@@ -573,7 +579,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1044,6 +1050,12 @@
     </xf>
     <xf fontId="4" fillId="0" borderId="4" xfId="0">
       <alignment vertical="bottom" textRotation="0" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -2322,7 +2334,7 @@
       </c>
       <c r="O11" s="147" t="s"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="A12" s="120" t="s">
         <v>70</v>
       </c>
@@ -2347,8 +2359,14 @@
       <c r="H12">
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="120" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="120" t="s">
         <v>72</v>
       </c>
@@ -2373,8 +2391,14 @@
       <c r="H13">
         <v>60</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="120" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="120" t="s">
         <v>73</v>
       </c>
@@ -2399,8 +2423,14 @@
       <c r="H14">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="120" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="120" t="s"/>
       <c r="B15" s="118" t="s"/>
       <c r="C15" t="s">
@@ -2415,14 +2445,20 @@
       <c r="F15">
         <v>60</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="158" t="s">
         <v>80</v>
       </c>
       <c r="H15">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>120</v>
+      </c>
+      <c r="I15" s="158" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="120" t="s"/>
       <c r="B16" s="118" t="s"/>
       <c r="E16" t="s">
@@ -2431,14 +2467,20 @@
       <c r="F16">
         <v>75</v>
       </c>
-      <c r="G16" t="s">
-        <v>83</v>
+      <c r="G16" s="158" t="s">
+        <v>75</v>
       </c>
       <c r="H16">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="158" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="120" t="s"/>
       <c r="B17" s="118" t="s"/>
       <c r="E17" t="s">
@@ -2447,10 +2489,16 @@
       <c r="F17">
         <v>60</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="158" t="s">
         <v>78</v>
       </c>
       <c r="H17">
+        <v>60</v>
+      </c>
+      <c r="I17" s="158" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17">
         <v>60</v>
       </c>
     </row>
@@ -3250,8 +3298,12 @@
       <c r="L21" s="29">
         <v>90</v>
       </c>
-      <c r="M21" s="28" t="s"/>
-      <c r="N21" s="29" t="s"/>
+      <c r="M21" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="N21" s="29">
+        <v>90</v>
+      </c>
       <c r="O21" s="31" t="s"/>
     </row>
     <row r="22" spans="1:15">
@@ -3291,8 +3343,12 @@
       <c r="L22" s="29">
         <v>90</v>
       </c>
-      <c r="M22" s="32" t="s"/>
-      <c r="N22" s="29" t="s"/>
+      <c r="M22" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" s="29">
+        <v>60</v>
+      </c>
       <c r="O22" s="31" t="s"/>
     </row>
     <row r="23" spans="1:15">
@@ -3332,8 +3388,12 @@
       <c r="L23" s="29">
         <v>60</v>
       </c>
-      <c r="M23" s="28" t="s"/>
-      <c r="N23" s="29" t="s"/>
+      <c r="M23" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N23" s="29">
+        <v>60</v>
+      </c>
       <c r="O23" s="31" t="s"/>
     </row>
     <row r="24" spans="1:15">
@@ -3373,8 +3433,12 @@
       <c r="L24" s="29">
         <v>60</v>
       </c>
-      <c r="M24" s="33" t="s"/>
-      <c r="N24" s="29" t="s"/>
+      <c r="M24" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="29">
+        <v>60</v>
+      </c>
       <c r="O24" s="31" t="s"/>
     </row>
     <row r="25" spans="1:15">
@@ -3414,8 +3478,12 @@
       <c r="L25" s="29">
         <v>60</v>
       </c>
-      <c r="M25" s="28" t="s"/>
-      <c r="N25" s="29" t="s"/>
+      <c r="M25" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="29">
+        <v>90</v>
+      </c>
       <c r="O25" s="34" t="s"/>
     </row>
     <row r="26" spans="1:15">
@@ -3453,10 +3521,14 @@
         <v>26</v>
       </c>
       <c r="L26" s="29">
-        <v>90</v>
-      </c>
-      <c r="M26" s="33" t="s"/>
-      <c r="N26" s="29" t="s"/>
+        <v>60</v>
+      </c>
+      <c r="M26" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="29">
+        <v>60</v>
+      </c>
       <c r="O26" s="35" t="s"/>
     </row>
     <row r="27" spans="1:15">
@@ -3492,8 +3564,12 @@
       <c r="L27" s="29">
         <v>60</v>
       </c>
-      <c r="M27" s="29" t="s"/>
-      <c r="N27" s="8" t="s"/>
+      <c r="M27" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" s="8">
+        <v>90</v>
+      </c>
       <c r="O27" s="35" t="s"/>
     </row>
     <row r="28" spans="1:15">
@@ -3598,10 +3674,14 @@
         <v>25</v>
       </c>
       <c r="J31" s="30" t="s"/>
-      <c r="K31" s="29" t="s"/>
+      <c r="K31" s="28" t="s">
+        <v>25</v>
+      </c>
       <c r="L31" s="30" t="s"/>
-      <c r="M31" s="29" t="s"/>
-      <c r="N31" s="8" t="s"/>
+      <c r="M31" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="N31" s="29" t="s"/>
       <c r="O31" s="35" t="s"/>
     </row>
     <row r="32" spans="1:15">
@@ -3631,10 +3711,18 @@
       <c r="J32" s="29">
         <v>60</v>
       </c>
-      <c r="K32" s="29" t="s"/>
-      <c r="L32" s="30" t="s"/>
-      <c r="M32" s="29" t="s"/>
-      <c r="N32" s="8" t="s"/>
+      <c r="K32" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="29">
+        <v>60</v>
+      </c>
+      <c r="M32" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" s="29">
+        <v>60</v>
+      </c>
       <c r="O32" s="35" t="s"/>
     </row>
     <row r="33" spans="1:15">
@@ -3660,10 +3748,18 @@
       <c r="J33" s="29">
         <v>60</v>
       </c>
-      <c r="K33" s="29" t="s"/>
-      <c r="L33" s="30" t="s"/>
-      <c r="M33" s="29" t="s"/>
-      <c r="N33" s="8" t="s"/>
+      <c r="K33" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="29">
+        <v>30</v>
+      </c>
+      <c r="M33" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="N33" s="29">
+        <v>60</v>
+      </c>
       <c r="O33" s="34" t="s"/>
     </row>
     <row r="34" spans="1:15">
@@ -3689,10 +3785,18 @@
       <c r="J34" s="29">
         <v>60</v>
       </c>
-      <c r="K34" s="29" t="s"/>
-      <c r="L34" s="30" t="s"/>
-      <c r="M34" s="29" t="s"/>
-      <c r="N34" s="8" t="s"/>
+      <c r="K34" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="29">
+        <v>60</v>
+      </c>
+      <c r="M34" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="29">
+        <v>60</v>
+      </c>
       <c r="O34" s="35" t="s"/>
     </row>
     <row r="35" spans="1:15">
@@ -3718,10 +3822,18 @@
       <c r="J35" s="29">
         <v>60</v>
       </c>
-      <c r="K35" s="29" t="s"/>
-      <c r="L35" s="30" t="s"/>
-      <c r="M35" s="29" t="s"/>
-      <c r="N35" s="8" t="s"/>
+      <c r="K35" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="29">
+        <v>60</v>
+      </c>
+      <c r="M35" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="29">
+        <v>60</v>
+      </c>
       <c r="O35" s="35" t="s"/>
     </row>
     <row r="36" spans="1:15">
@@ -3743,8 +3855,8 @@
       <c r="J36" s="29">
         <v>60</v>
       </c>
-      <c r="K36" s="29" t="s"/>
-      <c r="L36" s="30" t="s"/>
+      <c r="K36" s="28" t="s"/>
+      <c r="L36" s="29" t="s"/>
       <c r="M36" s="29" t="s"/>
       <c r="N36" s="8" t="s"/>
       <c r="O36" s="35" t="s"/>
@@ -3816,16 +3928,16 @@
       <c r="K39" s="38" t="s"/>
       <c r="L39" s="39">
         <f>=SUM(L21:L38)</f>
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="M39" s="38" t="s"/>
       <c r="N39" s="38">
         <f>=SUM(N21:N38)</f>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="O39" s="40">
         <f>=SUM(A39:N39)</f>
-        <v>4410</v>
+        <v>5340</v>
       </c>
     </row>
   </sheetData>
@@ -6516,8 +6628,12 @@
       <c r="F13" s="92" t="s"/>
       <c r="G13" s="85" t="s"/>
       <c r="H13" s="92" t="s"/>
-      <c r="I13" s="85" t="s"/>
-      <c r="J13" s="86" t="s"/>
+      <c r="I13" s="85" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="86">
+        <v>60</v>
+      </c>
       <c r="K13" s="86" t="s"/>
     </row>
     <row r="14" spans="1:11">
@@ -6572,11 +6688,11 @@
       <c r="I16" s="88" t="s"/>
       <c r="J16" s="90">
         <f>=SUM(J10:J15)</f>
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="K16" s="91">
         <f>=SUM(A16:J16)</f>
-        <v>1170</v>
+        <v>1230</v>
       </c>
     </row>
   </sheetData>

--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t/>
   </si>
@@ -93,21 +93,18 @@
     <t>谭运亮</t>
   </si>
   <si>
-    <t>申请中</t>
+    <t>朱则锦</t>
   </si>
   <si>
     <t>余姣</t>
   </si>
   <si>
+    <t>陆帆</t>
+  </si>
+  <si>
     <t>下午</t>
   </si>
   <si>
-    <t>朱则锦</t>
-  </si>
-  <si>
-    <t>陆帆</t>
-  </si>
-  <si>
     <t>苏伟峰</t>
   </si>
   <si>
@@ -127,6 +124,21 @@
   </si>
   <si>
     <t>黄清华</t>
+  </si>
+  <si>
+    <t>谢宝莹</t>
+  </si>
+  <si>
+    <t>黄招标</t>
+  </si>
+  <si>
+    <t>罗梓崧</t>
+  </si>
+  <si>
+    <t>李竞仙</t>
+  </si>
+  <si>
+    <t>黄晓琳</t>
   </si>
   <si>
     <t>2026/6/15星期一</t>
@@ -163,6 +175,9 @@
     <t>蔡文（物料保管）</t>
   </si>
   <si>
+    <t>物料保管</t>
+  </si>
+  <si>
     <t>北京路广百</t>
   </si>
   <si>
@@ -236,6 +251,9 @@
     <t>庄志荣</t>
   </si>
   <si>
+    <t>蔡建华</t>
+  </si>
+  <si>
     <t>林佳宁</t>
   </si>
   <si>
@@ -251,44 +269,31 @@
     <t>期二四</t>
   </si>
   <si>
+    <t>李写文</t>
+  </si>
+  <si>
+    <t>徐颖新</t>
+  </si>
+  <si>
+    <t>黎玉莲</t>
+  </si>
+  <si>
+    <t>童瑞峰</t>
+  </si>
+  <si>
+    <t>古庆文</t>
+  </si>
+  <si>
+    <t>王利民</t>
+  </si>
+  <si>
     <t>张永乐</t>
   </si>
   <si>
-    <t>温</t>
-  </si>
-  <si>
-    <t>温凯</t>
-  </si>
-  <si>
     <t>温凯瀚</t>
   </si>
   <si>
-    <t>古</t>
-  </si>
-  <si>
-    <t>古庆文</t>
-  </si>
-  <si>
-    <t>陈</t>
-  </si>
-  <si>
-    <t>陈绿</t>
-  </si>
-  <si>
-    <t>陈绿茵</t>
-  </si>
-  <si>
-    <t>物料保管</t>
-  </si>
-  <si>
-    <t xml:space="preserve">谢佳俊
-</t>
-  </si>
-  <si>
-    <t>王利民</t>
-  </si>
-  <si>
-    <t>蔡建华</t>
+    <t>申请中</t>
   </si>
 </sst>
 </file>
@@ -339,7 +344,7 @@
       <name val="Microsoft YaHei"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,8 +420,18 @@
         <bgColor rgb="FFF4B183"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -547,6 +562,34 @@
       </top>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left/>
+    </border>
+    <border>
+      <left/>
+    </border>
+    <border>
+      <left/>
+    </border>
+    <border/>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
@@ -573,13 +616,53 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs>
     <xf fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -706,355 +789,505 @@
     <xf fontId="0" fillId="8" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf fontId="4" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="bottom" textRotation="0" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="14" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="16" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="18" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="19" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="20" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="20" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="20" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="19" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="19" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="21" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="22" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="21" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="23" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="24" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="bottom" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="9" borderId="25" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="25" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="26" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="9" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="25" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="12" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="27" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="28" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="1" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="2" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="3" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="3" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="11" borderId="17" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="9" borderId="25" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="26" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="12" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="25" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="2" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="2" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="12" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="7" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="9" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="13" borderId="25" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="13" borderId="25" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="9" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="14" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="25" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="9" borderId="17" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="26" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="15" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="25" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="29" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="10" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="11" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="8" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="12" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="30" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="23" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="31" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="32" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="33" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="34" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="35" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="36" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="6" fillId="0" borderId="32" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="32" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="16" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="17" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="25" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="4" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
     <xf fontId="4" fillId="0" borderId="5" xfId="0">
       <alignment vertical="bottom" textRotation="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="14" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="16" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="17" xfId="0">
-      <alignment vertical="bottom" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="9" borderId="18" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="18" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="19" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="9" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="18" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="4" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    <xf fontId="3" fillId="0" borderId="25" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="17" xfId="0">
+      <alignment vertical="bottom" textRotation="0" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="6" xfId="0">
       <alignment vertical="center" textRotation="0" wrapText="0"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="0"/>
-    </xf>
     <xf fontId="3" fillId="4" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="12" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="7" fillId="6" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="3" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="2" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="16" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="3" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="20" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="21" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="6" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="1" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="2" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="3" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="3" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="11" borderId="17" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="9" borderId="18" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="19" xfId="0">
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="25" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="12" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="18" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" xfId="0">
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="13" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="12" xfId="0">
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="17" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="17" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="13" borderId="18" xfId="0">
+    <xf fontId="0" fillId="0" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="13" borderId="18" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="9" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="4" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="14" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="17" xfId="0">
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="26" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="13" xfId="0">
+    <xf fontId="0" fillId="0" borderId="12" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="4" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="9" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="18" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="9" borderId="17" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="19" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="15" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="17" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="18" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="22" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="10" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="5" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="6" borderId="11" xfId="0">
+    <xf fontId="0" fillId="6" borderId="9" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="10" borderId="7" xfId="0">
+    <xf fontId="0" fillId="10" borderId="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="10" borderId="8" xfId="0">
+    <xf fontId="0" fillId="10" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="6" borderId="12" xfId="0">
+    <xf fontId="0" fillId="0" borderId="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="301" fontId="0" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="3" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="301" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="17" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="7" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="9" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="bottom" textRotation="0" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf fontId="0" fillId="10" borderId="3" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1303,7 +1536,7 @@
   <sheetPr codeName="番禺万科欧泊">
     <tabColor/>
   </sheetPr>
-  <dimension ref="R22"/>
+  <dimension ref="P32"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="17" width="9.71094" customWidth="1"/>
@@ -2099,6 +2332,301 @@
       <c r="Q22" s="20" t="s"/>
       <c r="R22" s="8" t="s"/>
     </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="4">
+        <v>46195</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4">
+        <v>46196</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4">
+        <v>46197</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46198</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I25" s="4">
+        <v>46199</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="4">
+        <v>46200</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M25" s="5">
+        <v>46201</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="O25" s="21" t="s"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="O26" s="22" t="s"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="10">
+        <v>90</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="10">
+        <v>90</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="10">
+        <v>90</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="10">
+        <v>90</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" s="10">
+        <v>90</v>
+      </c>
+      <c r="K27" s="9" t="s"/>
+      <c r="L27" s="11" t="s"/>
+      <c r="M27" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="N27" s="10">
+        <v>90</v>
+      </c>
+      <c r="O27" s="22" t="s"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" s="10">
+        <v>90</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="10">
+        <v>90</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="10">
+        <v>90</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="10">
+        <v>90</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J28" s="10">
+        <v>90</v>
+      </c>
+      <c r="K28" s="12" t="s"/>
+      <c r="L28" s="11" t="s"/>
+      <c r="M28" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N28" s="10">
+        <v>90</v>
+      </c>
+      <c r="O28" s="22" t="s"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="10">
+        <v>90</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="10">
+        <v>90</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="10">
+        <v>90</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="10">
+        <v>90</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J29" s="10">
+        <v>90</v>
+      </c>
+      <c r="K29" s="9" t="s"/>
+      <c r="L29" s="11" t="s"/>
+      <c r="M29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N29" s="10">
+        <v>90</v>
+      </c>
+      <c r="O29" s="22" t="s"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="9" t="s"/>
+      <c r="B30" s="10" t="s"/>
+      <c r="C30" s="9" t="s"/>
+      <c r="D30" s="10" t="s"/>
+      <c r="E30" s="9" t="s"/>
+      <c r="F30" s="10" t="s"/>
+      <c r="G30" s="9" t="s"/>
+      <c r="H30" s="10" t="s"/>
+      <c r="I30" s="9" t="s"/>
+      <c r="J30" s="10" t="s"/>
+      <c r="K30" s="9" t="s"/>
+      <c r="L30" s="11" t="s"/>
+      <c r="M30" s="10" t="s"/>
+      <c r="N30" s="10" t="s"/>
+      <c r="O30" s="22" t="s"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="9" t="s"/>
+      <c r="B31" s="10" t="s"/>
+      <c r="C31" s="9" t="s"/>
+      <c r="D31" s="10" t="s"/>
+      <c r="E31" s="9" t="s"/>
+      <c r="F31" s="10" t="s"/>
+      <c r="G31" s="9" t="s"/>
+      <c r="H31" s="10" t="s"/>
+      <c r="I31" s="9" t="s"/>
+      <c r="J31" s="10" t="s"/>
+      <c r="K31" s="9" t="s"/>
+      <c r="L31" s="11" t="s"/>
+      <c r="M31" s="10" t="s"/>
+      <c r="N31" s="10" t="s"/>
+      <c r="O31" s="25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="15" t="s"/>
+      <c r="B32" s="16">
+        <f>=SUM(B27:B31)</f>
+        <v>270</v>
+      </c>
+      <c r="C32" s="15" t="s"/>
+      <c r="D32" s="16">
+        <f>=SUM(D27:D31)</f>
+        <v>270</v>
+      </c>
+      <c r="E32" s="15" t="s"/>
+      <c r="F32" s="16">
+        <f>=SUM(F27:F31)</f>
+        <v>270</v>
+      </c>
+      <c r="G32" s="15" t="s"/>
+      <c r="H32" s="16">
+        <f>=SUM(H27:H31)</f>
+        <v>270</v>
+      </c>
+      <c r="I32" s="15">
+        <v>0</v>
+      </c>
+      <c r="J32" s="16">
+        <f>=SUM(J27:J31)</f>
+        <v>270</v>
+      </c>
+      <c r="K32" s="15" t="s"/>
+      <c r="L32" s="17">
+        <f>=SUM(L27:L31)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="16" t="s"/>
+      <c r="N32" s="16">
+        <f>=SUM(N27:N31)</f>
+        <v>270</v>
+      </c>
+      <c r="O32" s="26">
+        <f>=SUM(A32:N32)</f>
+        <v>1620</v>
+      </c>
+      <c r="P32" s="181" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2108,8 +2636,11 @@
   <sheetPr codeName="中大附三岭南医院">
     <tabColor/>
   </sheetPr>
-  <dimension ref="B200"/>
+  <dimension ref="P200"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="15" width="11.0625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="4">
@@ -2136,150 +2667,150 @@
       <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="138">
+      <c r="M1" s="158">
         <v>46194</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="139" t="s"/>
+      <c r="O1" s="159" t="s"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="140">
-        <v>90</v>
-      </c>
-      <c r="D2" s="120" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="140">
-        <v>90</v>
-      </c>
-      <c r="K2" s="120" t="s">
-        <v>71</v>
-      </c>
-      <c r="L2" s="140">
-        <v>60</v>
-      </c>
-      <c r="M2" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2" s="140">
-        <v>60</v>
-      </c>
-      <c r="O2" s="99" t="s"/>
+      <c r="A2" s="140" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="160">
+        <v>90</v>
+      </c>
+      <c r="D2" s="140" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="160">
+        <v>90</v>
+      </c>
+      <c r="K2" s="140" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="160">
+        <v>60</v>
+      </c>
+      <c r="M2" s="140" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" s="160">
+        <v>60</v>
+      </c>
+      <c r="O2" s="115" t="s"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="140">
-        <v>60</v>
-      </c>
-      <c r="D3" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="J3" s="140">
-        <v>90</v>
-      </c>
-      <c r="K3" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="L3" s="140">
-        <v>60</v>
-      </c>
-      <c r="M3" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" s="140">
-        <v>90</v>
-      </c>
-      <c r="O3" s="99" t="s"/>
+      <c r="A3" s="140" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="160">
+        <v>60</v>
+      </c>
+      <c r="D3" s="140" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="160">
+        <v>90</v>
+      </c>
+      <c r="K3" s="140" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="160">
+        <v>60</v>
+      </c>
+      <c r="M3" s="140" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" s="160">
+        <v>90</v>
+      </c>
+      <c r="O3" s="115" t="s"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="120" t="s"/>
-      <c r="B4" s="140" t="s"/>
-      <c r="D4" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="140">
-        <v>60</v>
-      </c>
-      <c r="K4" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="L4" s="140">
-        <v>90</v>
-      </c>
-      <c r="M4" s="120" t="s"/>
-      <c r="N4" s="140" t="s"/>
-      <c r="O4" s="99" t="s"/>
+      <c r="A4" s="140" t="s"/>
+      <c r="B4" s="160" t="s"/>
+      <c r="D4" s="140" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="160">
+        <v>60</v>
+      </c>
+      <c r="K4" s="140" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="160">
+        <v>90</v>
+      </c>
+      <c r="M4" s="140" t="s"/>
+      <c r="N4" s="160" t="s"/>
+      <c r="O4" s="115" t="s"/>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="120" t="s"/>
-      <c r="B5" s="140" t="s"/>
-      <c r="D5" s="120" t="s"/>
-      <c r="J5" s="140" t="s"/>
-      <c r="K5" s="120" t="s"/>
-      <c r="L5" s="140" t="s"/>
-      <c r="M5" s="120" t="s"/>
-      <c r="N5" s="140" t="s"/>
-      <c r="O5" s="99" t="s"/>
+      <c r="A5" s="140" t="s"/>
+      <c r="B5" s="160" t="s"/>
+      <c r="D5" s="140" t="s"/>
+      <c r="J5" s="160" t="s"/>
+      <c r="K5" s="140" t="s"/>
+      <c r="L5" s="160" t="s"/>
+      <c r="M5" s="140" t="s"/>
+      <c r="N5" s="160" t="s"/>
+      <c r="O5" s="115" t="s"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="120" t="s"/>
-      <c r="B6" s="140" t="s"/>
-      <c r="D6" s="120" t="s"/>
-      <c r="J6" s="140" t="s"/>
-      <c r="K6" s="120" t="s"/>
-      <c r="L6" s="140" t="s"/>
-      <c r="M6" s="120" t="s"/>
-      <c r="N6" s="140" t="s"/>
-      <c r="O6" s="99" t="s"/>
+      <c r="A6" s="140" t="s"/>
+      <c r="B6" s="160" t="s"/>
+      <c r="D6" s="140" t="s"/>
+      <c r="J6" s="160" t="s"/>
+      <c r="K6" s="140" t="s"/>
+      <c r="L6" s="160" t="s"/>
+      <c r="M6" s="140" t="s"/>
+      <c r="N6" s="160" t="s"/>
+      <c r="O6" s="115" t="s"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="120" t="s"/>
-      <c r="B7" s="140" t="s"/>
-      <c r="D7" s="120" t="s"/>
-      <c r="J7" s="140" t="s"/>
-      <c r="K7" s="120" t="s"/>
-      <c r="L7" s="140" t="s"/>
-      <c r="M7" s="120" t="s"/>
-      <c r="N7" s="140" t="s"/>
-      <c r="O7" s="141" t="s">
+      <c r="A7" s="140" t="s"/>
+      <c r="B7" s="160" t="s"/>
+      <c r="D7" s="140" t="s"/>
+      <c r="J7" s="160" t="s"/>
+      <c r="K7" s="140" t="s"/>
+      <c r="L7" s="160" t="s"/>
+      <c r="M7" s="140" t="s"/>
+      <c r="N7" s="160" t="s"/>
+      <c r="O7" s="161" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="142" t="s"/>
-      <c r="B8" s="143">
+      <c r="A8" s="162" t="s"/>
+      <c r="B8" s="163">
         <f>=SUM(B2:B7)</f>
         <v>150</v>
       </c>
-      <c r="C8" s="143" t="s"/>
-      <c r="D8" s="142" t="s"/>
-      <c r="E8" s="143" t="s"/>
-      <c r="F8" s="143" t="s"/>
-      <c r="G8" s="143" t="s"/>
-      <c r="H8" s="143" t="s"/>
-      <c r="I8" s="143" t="s"/>
-      <c r="J8" s="143">
+      <c r="C8" s="163" t="s"/>
+      <c r="D8" s="162" t="s"/>
+      <c r="E8" s="163" t="s"/>
+      <c r="F8" s="163" t="s"/>
+      <c r="G8" s="163" t="s"/>
+      <c r="H8" s="163" t="s"/>
+      <c r="I8" s="163" t="s"/>
+      <c r="J8" s="163">
         <f>=SUM(J2:J7)</f>
         <v>240</v>
       </c>
-      <c r="K8" s="142" t="s"/>
-      <c r="L8" s="143">
+      <c r="K8" s="162" t="s"/>
+      <c r="L8" s="163">
         <f>=SUM(L2:L7)</f>
         <v>210</v>
       </c>
-      <c r="M8" s="142" t="s"/>
-      <c r="N8" s="143">
+      <c r="M8" s="162" t="s"/>
+      <c r="N8" s="163">
         <f>=SUM(N2:N7)</f>
         <v>150</v>
       </c>
-      <c r="O8" s="144">
+      <c r="O8" s="164">
         <f>=SUM(A8:N8)</f>
         <v>750</v>
       </c>
@@ -2290,223 +2821,320 @@
     <row r="9" spans="1:28"/>
     <row r="10" spans="1:28"/>
     <row r="11" spans="1:15">
-      <c r="A11" s="145">
+      <c r="A11" s="165">
         <v>46195</v>
       </c>
-      <c r="B11" s="146" t="s">
+      <c r="B11" s="199" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="147">
+      <c r="C11" s="198">
         <v>46196</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="137" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="147">
+      <c r="E11" s="196">
         <v>46197</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="147">
+      <c r="G11" s="198">
         <v>46198</v>
       </c>
-      <c r="H11" t="s">
-        <v>4</v>
-      </c>
-      <c r="I11" s="147">
+      <c r="H11" s="137" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="196">
         <v>46199</v>
       </c>
-      <c r="J11" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" s="147">
+      <c r="J11" s="137" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="196">
         <v>46200</v>
       </c>
-      <c r="L11" t="s">
-        <v>6</v>
-      </c>
-      <c r="M11" s="147">
+      <c r="L11" s="137" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="196">
         <v>46201</v>
       </c>
-      <c r="N11" t="s">
-        <v>7</v>
-      </c>
-      <c r="O11" s="147" t="s"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="118">
+      <c r="N11" s="137" t="s">
+        <v>1</v>
+      </c>
+      <c r="O11" s="197" t="s"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="140" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="160">
         <v>75</v>
       </c>
-      <c r="C12" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="136" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="137">
         <v>75</v>
       </c>
-      <c r="E12" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12">
+      <c r="E12" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="67">
         <v>135</v>
       </c>
-      <c r="G12" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12">
-        <v>60</v>
-      </c>
-      <c r="I12" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="J12">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="118">
-        <v>60</v>
-      </c>
-      <c r="C13" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13">
+      <c r="G12" s="136" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="137">
+        <v>60</v>
+      </c>
+      <c r="I12" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="137">
+        <v>60</v>
+      </c>
+      <c r="K12" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="137">
+        <v>120</v>
+      </c>
+      <c r="M12" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="N12" s="137">
+        <v>60</v>
+      </c>
+      <c r="O12" s="137" t="s"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="140" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="160">
+        <v>60</v>
+      </c>
+      <c r="C13" s="140" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="138">
         <v>75</v>
       </c>
-      <c r="E13" s="120" t="s">
-        <v>72</v>
+      <c r="E13" s="160" t="s">
+        <v>78</v>
       </c>
       <c r="F13">
         <v>60</v>
       </c>
-      <c r="G13" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13">
-        <v>60</v>
-      </c>
-      <c r="I13" s="120" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="118">
-        <v>90</v>
-      </c>
-      <c r="C14" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14">
-        <v>90</v>
-      </c>
-      <c r="E14" s="120" t="s">
-        <v>73</v>
+      <c r="G13" s="140" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="138">
+        <v>60</v>
+      </c>
+      <c r="I13" s="160" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="138">
+        <v>60</v>
+      </c>
+      <c r="K13" s="160" t="s">
+        <v>79</v>
+      </c>
+      <c r="L13" s="138">
+        <v>90</v>
+      </c>
+      <c r="M13" s="160" t="s">
+        <v>82</v>
+      </c>
+      <c r="N13" s="138">
+        <v>120</v>
+      </c>
+      <c r="O13" s="138" t="s"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="140" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="160">
+        <v>90</v>
+      </c>
+      <c r="C14" s="140" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="138">
+        <v>90</v>
+      </c>
+      <c r="E14" s="160" t="s">
+        <v>79</v>
       </c>
       <c r="F14">
         <v>90</v>
       </c>
-      <c r="G14" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14">
-        <v>90</v>
-      </c>
-      <c r="I14" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="J14">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="120" t="s"/>
-      <c r="B15" s="118" t="s"/>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15">
+      <c r="G14" s="140" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="138">
+        <v>90</v>
+      </c>
+      <c r="I14" s="160" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" s="138">
+        <v>90</v>
+      </c>
+      <c r="K14" s="203" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" s="138">
+        <v>60</v>
+      </c>
+      <c r="M14" s="160" t="s">
+        <v>84</v>
+      </c>
+      <c r="N14" s="138">
+        <v>90</v>
+      </c>
+      <c r="O14" s="138" t="s"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="140" t="s"/>
+      <c r="B15" s="160" t="s"/>
+      <c r="C15" s="140" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="138">
         <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F15">
         <v>60</v>
       </c>
-      <c r="G15" s="158" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15">
+      <c r="G15" s="202" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="138">
         <v>120</v>
       </c>
-      <c r="I15" s="158" t="s">
+      <c r="I15" s="203" t="s">
         <v>86</v>
       </c>
-      <c r="J15">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="120" t="s"/>
-      <c r="B16" s="118" t="s"/>
+      <c r="J15" s="138">
+        <v>60</v>
+      </c>
+      <c r="K15" s="160" t="s"/>
+      <c r="L15" s="138" t="s"/>
+      <c r="M15" s="160" t="s"/>
+      <c r="N15" s="138" t="s"/>
+      <c r="O15" s="138" t="s"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="140" t="s"/>
+      <c r="B16" s="160" t="s"/>
+      <c r="C16" s="140" t="s"/>
+      <c r="D16" s="138" t="s"/>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F16">
         <v>75</v>
       </c>
-      <c r="G16" s="158" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16">
-        <v>60</v>
-      </c>
-      <c r="I16" s="158" t="s">
-        <v>75</v>
-      </c>
-      <c r="J16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="120" t="s"/>
-      <c r="B17" s="118" t="s"/>
+      <c r="G16" s="202" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="138">
+        <v>60</v>
+      </c>
+      <c r="I16" s="203" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" s="138">
+        <v>60</v>
+      </c>
+      <c r="K16" s="160" t="s"/>
+      <c r="L16" s="138" t="s"/>
+      <c r="M16" s="160" t="s"/>
+      <c r="N16" s="138" t="s"/>
+      <c r="O16" s="138" t="s"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="140" t="s"/>
+      <c r="B17" s="160" t="s"/>
+      <c r="C17" s="140" t="s"/>
+      <c r="D17" s="138" t="s"/>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F17">
         <v>60</v>
       </c>
-      <c r="G17" s="158" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17">
-        <v>60</v>
-      </c>
-      <c r="I17" s="158" t="s">
-        <v>78</v>
-      </c>
-      <c r="J17">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="142" t="s"/>
-      <c r="B18" s="126">
+      <c r="G17" s="202" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="138">
+        <v>60</v>
+      </c>
+      <c r="I17" s="203" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" s="138">
+        <v>60</v>
+      </c>
+      <c r="K17" s="160" t="s"/>
+      <c r="L17" s="138" t="s"/>
+      <c r="M17" s="160" t="s"/>
+      <c r="N17" s="138" t="s"/>
+      <c r="O17" s="161" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="205" t="s"/>
+      <c r="B18" s="206">
         <f>=SUM(B12:B17)</f>
         <v>225</v>
+      </c>
+      <c r="C18" s="205" t="s"/>
+      <c r="D18" s="208">
+        <f>=SUM(D12:D17)</f>
+        <v>315</v>
+      </c>
+      <c r="E18" s="206" t="s"/>
+      <c r="F18" s="206">
+        <f>=SUM(F12:F17)</f>
+        <v>480</v>
+      </c>
+      <c r="G18" s="205" t="s"/>
+      <c r="H18" s="208">
+        <f>=SUM(H12:H17)</f>
+        <v>450</v>
+      </c>
+      <c r="I18" s="206" t="s"/>
+      <c r="J18" s="208">
+        <f>=SUM(J12:J17)</f>
+        <v>390</v>
+      </c>
+      <c r="K18" s="206" t="s"/>
+      <c r="L18" s="208">
+        <f>=SUM(L12:L17)</f>
+        <v>270</v>
+      </c>
+      <c r="M18" s="206" t="s"/>
+      <c r="N18" s="208">
+        <f>=SUM(N12:N17)</f>
+        <v>270</v>
+      </c>
+      <c r="O18" s="204">
+        <f>=SUM(A18:N18)</f>
+        <v>2400</v>
+      </c>
+      <c r="P18" s="195" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:28"/>
@@ -2700,7 +3328,7 @@
   <sheetPr codeName="中大附属第六医院">
     <tabColor/>
   </sheetPr>
-  <dimension ref="O39"/>
+  <dimension ref="P39"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="15" width="10.6523" customWidth="1"/>
@@ -3167,7 +3795,7 @@
         <f>=SUM(A16:N16)</f>
         <v>2010</v>
       </c>
-      <c r="P16" s="41" t="s">
+      <c r="P16" s="51" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3202,10 +3830,10 @@
       <c r="J19" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="183">
         <v>46200</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="173" t="s">
         <v>7</v>
       </c>
       <c r="M19" s="5">
@@ -3244,13 +3872,13 @@
       <c r="I20" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="30" t="s">
+      <c r="J20" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K20" s="29" t="s">
+      <c r="K20" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="30" t="s">
+      <c r="L20" s="157" t="s">
         <v>9</v>
       </c>
       <c r="M20" s="29" t="s">
@@ -3262,49 +3890,49 @@
       <c r="O20" s="31" t="s"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="29">
-        <v>90</v>
-      </c>
-      <c r="C21" s="28" t="s">
+      <c r="B21" s="188">
+        <v>90</v>
+      </c>
+      <c r="C21" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="29">
-        <v>90</v>
-      </c>
-      <c r="E21" s="28" t="s">
+      <c r="D21" s="188">
+        <v>90</v>
+      </c>
+      <c r="E21" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="29">
-        <v>90</v>
-      </c>
-      <c r="G21" s="28" t="s">
+      <c r="F21" s="188">
+        <v>90</v>
+      </c>
+      <c r="G21" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="29">
-        <v>90</v>
-      </c>
-      <c r="I21" s="156" t="s">
+      <c r="H21" s="188">
+        <v>90</v>
+      </c>
+      <c r="I21" s="189" t="s">
         <v>18</v>
       </c>
-      <c r="J21" s="29">
-        <v>90</v>
-      </c>
-      <c r="K21" s="156" t="s">
+      <c r="J21" s="188">
+        <v>90</v>
+      </c>
+      <c r="K21" s="189" t="s">
         <v>18</v>
       </c>
-      <c r="L21" s="29">
-        <v>90</v>
-      </c>
-      <c r="M21" s="28" t="s">
+      <c r="L21" s="157">
+        <v>90</v>
+      </c>
+      <c r="M21" s="188" t="s">
         <v>19</v>
       </c>
-      <c r="N21" s="29">
-        <v>90</v>
-      </c>
-      <c r="O21" s="31" t="s"/>
+      <c r="N21" s="157">
+        <v>90</v>
+      </c>
+      <c r="O21" s="30" t="s"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="32" t="s">
@@ -3325,7 +3953,7 @@
       <c r="F22" s="29">
         <v>90</v>
       </c>
-      <c r="G22" s="156" t="s">
+      <c r="G22" s="42" t="s">
         <v>18</v>
       </c>
       <c r="H22" s="29">
@@ -3340,16 +3968,16 @@
       <c r="K22" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L22" s="29">
-        <v>90</v>
-      </c>
-      <c r="M22" s="33" t="s">
+      <c r="L22" s="30">
+        <v>90</v>
+      </c>
+      <c r="M22" s="186" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="29">
-        <v>60</v>
-      </c>
-      <c r="O22" s="31" t="s"/>
+      <c r="N22" s="30">
+        <v>60</v>
+      </c>
+      <c r="O22" s="30" t="s"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="28" t="s">
@@ -3385,16 +4013,16 @@
       <c r="K23" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="L23" s="29">
-        <v>60</v>
-      </c>
-      <c r="M23" s="28" t="s">
+      <c r="L23" s="30">
+        <v>60</v>
+      </c>
+      <c r="M23" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="29">
-        <v>60</v>
-      </c>
-      <c r="O23" s="31" t="s"/>
+      <c r="N23" s="30">
+        <v>60</v>
+      </c>
+      <c r="O23" s="30" t="s"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="33" t="s">
@@ -3430,16 +4058,16 @@
       <c r="K24" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="L24" s="29">
-        <v>60</v>
-      </c>
-      <c r="M24" s="33" t="s">
+      <c r="L24" s="30">
+        <v>60</v>
+      </c>
+      <c r="M24" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="29">
-        <v>60</v>
-      </c>
-      <c r="O24" s="31" t="s"/>
+      <c r="N24" s="30">
+        <v>60</v>
+      </c>
+      <c r="O24" s="30" t="s"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="28" t="s">
@@ -3475,16 +4103,16 @@
       <c r="K25" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="L25" s="29">
-        <v>60</v>
-      </c>
-      <c r="M25" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="29">
-        <v>90</v>
-      </c>
-      <c r="O25" s="34" t="s"/>
+      <c r="L25" s="30">
+        <v>60</v>
+      </c>
+      <c r="M25" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" s="30">
+        <v>90</v>
+      </c>
+      <c r="O25" s="192" t="s"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="33" t="s">
@@ -3518,18 +4146,18 @@
         <v>60</v>
       </c>
       <c r="K26" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="29">
-        <v>60</v>
-      </c>
-      <c r="M26" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="29">
-        <v>60</v>
-      </c>
-      <c r="O26" s="35" t="s"/>
+        <v>23</v>
+      </c>
+      <c r="L26" s="30">
+        <v>60</v>
+      </c>
+      <c r="M26" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" s="30">
+        <v>60</v>
+      </c>
+      <c r="O26" s="193" t="s"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="28" t="s"/>
@@ -3553,55 +4181,55 @@
         <v>60</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J27" s="29">
         <v>90</v>
       </c>
       <c r="K27" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="L27" s="29">
+        <v>25</v>
+      </c>
+      <c r="L27" s="30">
         <v>60</v>
       </c>
       <c r="M27" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="N27" s="8">
-        <v>90</v>
-      </c>
-      <c r="O27" s="35" t="s"/>
+      <c r="N27" s="30">
+        <v>90</v>
+      </c>
+      <c r="O27" s="193" t="s"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="28" t="s"/>
       <c r="B28" s="29" t="s"/>
       <c r="C28" s="28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D28" s="29" t="s"/>
       <c r="E28" s="28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F28" s="29">
         <v>60</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H28" s="29">
         <v>90</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J28" s="29">
         <v>60</v>
       </c>
-      <c r="K28" s="29" t="s"/>
+      <c r="K28" s="28" t="s"/>
       <c r="L28" s="30" t="s"/>
       <c r="M28" s="29" t="s"/>
-      <c r="N28" s="8" t="s"/>
-      <c r="O28" s="35" t="s"/>
+      <c r="N28" s="30" t="s"/>
+      <c r="O28" s="193" t="s"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="28" t="s"/>
@@ -3613,24 +4241,24 @@
         <v>60</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F29" s="29">
         <v>60</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H29" s="29">
         <v>60</v>
       </c>
       <c r="I29" s="28" t="s"/>
-      <c r="J29" s="30" t="s"/>
-      <c r="K29" s="29" t="s"/>
+      <c r="J29" s="29" t="s"/>
+      <c r="K29" s="28" t="s"/>
       <c r="L29" s="30" t="s"/>
       <c r="M29" s="29" t="s"/>
-      <c r="N29" s="8" t="s"/>
-      <c r="O29" s="35" t="s"/>
+      <c r="N29" s="30" t="s"/>
+      <c r="O29" s="193" t="s"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="28" t="s"/>
@@ -3646,12 +4274,12 @@
       <c r="G30" s="28" t="s"/>
       <c r="H30" s="29" t="s"/>
       <c r="I30" s="28" t="s"/>
-      <c r="J30" s="30" t="s"/>
-      <c r="K30" s="29" t="s"/>
+      <c r="J30" s="29" t="s"/>
+      <c r="K30" s="28" t="s"/>
       <c r="L30" s="30" t="s"/>
       <c r="M30" s="29" t="s"/>
-      <c r="N30" s="8" t="s"/>
-      <c r="O30" s="35" t="s"/>
+      <c r="N30" s="30" t="s"/>
+      <c r="O30" s="193" t="s"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="28" t="s"/>
@@ -3663,26 +4291,26 @@
         <v>60</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F31" s="29" t="s"/>
       <c r="G31" s="28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H31" s="29" t="s"/>
       <c r="I31" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="30" t="s"/>
+        <v>26</v>
+      </c>
+      <c r="J31" s="29" t="s"/>
       <c r="K31" s="28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L31" s="30" t="s"/>
-      <c r="M31" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="N31" s="29" t="s"/>
-      <c r="O31" s="35" t="s"/>
+      <c r="M31" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="30" t="s"/>
+      <c r="O31" s="193" t="s"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="28" t="s"/>
@@ -3700,30 +4328,30 @@
         <v>60</v>
       </c>
       <c r="G32" s="32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H32" s="29">
         <v>60</v>
       </c>
       <c r="I32" s="32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J32" s="29">
         <v>60</v>
       </c>
       <c r="K32" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="29">
-        <v>60</v>
-      </c>
-      <c r="M32" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="N32" s="29">
-        <v>60</v>
-      </c>
-      <c r="O32" s="35" t="s"/>
+        <v>25</v>
+      </c>
+      <c r="L32" s="30">
+        <v>60</v>
+      </c>
+      <c r="M32" s="187" t="s">
+        <v>25</v>
+      </c>
+      <c r="N32" s="30">
+        <v>60</v>
+      </c>
+      <c r="O32" s="193" t="s"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="28" t="s"/>
@@ -3749,18 +4377,18 @@
         <v>60</v>
       </c>
       <c r="K33" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="29">
+        <v>23</v>
+      </c>
+      <c r="L33" s="30">
         <v>30</v>
       </c>
-      <c r="M33" s="28" t="s">
+      <c r="M33" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="N33" s="29">
-        <v>60</v>
-      </c>
-      <c r="O33" s="34" t="s"/>
+      <c r="N33" s="30">
+        <v>105</v>
+      </c>
+      <c r="O33" s="192" t="s"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="28" t="s"/>
@@ -3788,16 +4416,16 @@
       <c r="K34" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="L34" s="29">
-        <v>60</v>
-      </c>
-      <c r="M34" s="28" t="s">
+      <c r="L34" s="30">
+        <v>60</v>
+      </c>
+      <c r="M34" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="N34" s="29">
-        <v>60</v>
-      </c>
-      <c r="O34" s="35" t="s"/>
+      <c r="N34" s="30">
+        <v>60</v>
+      </c>
+      <c r="O34" s="193" t="s"/>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="28" t="s"/>
@@ -3825,16 +4453,16 @@
       <c r="K35" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="L35" s="29">
-        <v>60</v>
-      </c>
-      <c r="M35" s="33" t="s">
+      <c r="L35" s="30">
+        <v>60</v>
+      </c>
+      <c r="M35" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="N35" s="29">
-        <v>60</v>
-      </c>
-      <c r="O35" s="35" t="s"/>
+      <c r="N35" s="30">
+        <v>60</v>
+      </c>
+      <c r="O35" s="193" t="s"/>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="28" t="s"/>
@@ -3844,7 +4472,7 @@
       <c r="E36" s="28" t="s"/>
       <c r="F36" s="29" t="s"/>
       <c r="G36" s="28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H36" s="29">
         <v>60</v>
@@ -3856,10 +4484,14 @@
         <v>60</v>
       </c>
       <c r="K36" s="28" t="s"/>
-      <c r="L36" s="29" t="s"/>
-      <c r="M36" s="29" t="s"/>
-      <c r="N36" s="8" t="s"/>
-      <c r="O36" s="35" t="s"/>
+      <c r="L36" s="30" t="s"/>
+      <c r="M36" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" s="190">
+        <v>45</v>
+      </c>
+      <c r="O36" s="193" t="s"/>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="28" t="s"/>
@@ -3871,73 +4503,76 @@
       <c r="G37" s="28" t="s"/>
       <c r="H37" s="29" t="s"/>
       <c r="I37" s="28" t="s"/>
-      <c r="J37" s="30" t="s"/>
-      <c r="K37" s="29" t="s"/>
+      <c r="J37" s="29" t="s"/>
+      <c r="K37" s="28" t="s"/>
       <c r="L37" s="30" t="s"/>
       <c r="M37" s="29" t="s"/>
-      <c r="N37" s="8" t="s"/>
-      <c r="O37" s="35" t="s"/>
+      <c r="N37" s="30" t="s"/>
+      <c r="O37" s="193" t="s"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="28" t="s"/>
-      <c r="B38" s="29" t="s"/>
-      <c r="C38" s="28" t="s"/>
-      <c r="D38" s="29" t="s"/>
-      <c r="E38" s="28" t="s"/>
-      <c r="F38" s="29" t="s"/>
-      <c r="G38" s="28" t="s"/>
-      <c r="H38" s="29" t="s"/>
-      <c r="I38" s="28" t="s"/>
-      <c r="J38" s="30" t="s"/>
-      <c r="K38" s="29" t="s"/>
-      <c r="L38" s="30" t="s"/>
-      <c r="M38" s="29" t="s"/>
-      <c r="N38" s="8" t="s"/>
-      <c r="O38" s="36" t="s">
+      <c r="A38" s="122" t="s"/>
+      <c r="B38" s="123" t="s"/>
+      <c r="C38" s="122" t="s"/>
+      <c r="D38" s="123" t="s"/>
+      <c r="E38" s="122" t="s"/>
+      <c r="F38" s="123" t="s"/>
+      <c r="G38" s="122" t="s"/>
+      <c r="H38" s="123" t="s"/>
+      <c r="I38" s="122" t="s"/>
+      <c r="J38" s="123" t="s"/>
+      <c r="K38" s="122" t="s"/>
+      <c r="L38" s="124" t="s"/>
+      <c r="M38" s="123" t="s"/>
+      <c r="N38" s="124" t="s"/>
+      <c r="O38" s="194" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
-      <c r="A39" s="37" t="s"/>
-      <c r="B39" s="38">
+    <row r="39" spans="1:16">
+      <c r="A39" s="191" t="s"/>
+      <c r="B39" s="184">
         <f>=SUM(B21:B38)</f>
         <v>450</v>
       </c>
-      <c r="C39" s="37" t="s"/>
-      <c r="D39" s="38">
+      <c r="C39" s="191" t="s"/>
+      <c r="D39" s="184">
         <f>=SUM(D21:D38)</f>
         <v>750</v>
       </c>
-      <c r="E39" s="37" t="s"/>
-      <c r="F39" s="38">
+      <c r="E39" s="191" t="s"/>
+      <c r="F39" s="184">
         <f>=SUM(F21:F38)</f>
         <v>870</v>
       </c>
-      <c r="G39" s="37">
+      <c r="G39" s="191">
         <v>0</v>
       </c>
-      <c r="H39" s="38">
+      <c r="H39" s="184">
         <f>=SUM(H21:H38)</f>
         <v>960</v>
       </c>
-      <c r="I39" s="37" t="s"/>
-      <c r="J39" s="39">
+      <c r="I39" s="191" t="s"/>
+      <c r="J39" s="185">
         <f>=SUM(J21:J38)</f>
         <v>870</v>
       </c>
-      <c r="K39" s="38" t="s"/>
-      <c r="L39" s="39">
+      <c r="K39" s="184" t="s"/>
+      <c r="L39" s="185">
         <f>=SUM(L21:L38)</f>
         <v>690</v>
       </c>
-      <c r="M39" s="38" t="s"/>
-      <c r="N39" s="38">
+      <c r="M39" s="184" t="s"/>
+      <c r="N39" s="184">
         <f>=SUM(N21:N38)</f>
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="O39" s="40">
         <f>=SUM(A39:N39)</f>
-        <v>5340</v>
+        <v>5430</v>
+      </c>
+      <c r="P39" s="181" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3949,10 +4584,11 @@
   <sheetPr codeName="番禺万达">
     <tabColor/>
   </sheetPr>
-  <dimension ref="N28"/>
+  <dimension ref="N29"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="9" width="10.5234" customWidth="1"/>
+    <col min="11" max="11" width="9.71094" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4011,25 +4647,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="45">
         <v>60</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="45">
         <v>60</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="45">
         <v>60</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" s="47">
         <v>60</v>
@@ -4038,25 +4674,25 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="45">
+        <v>60</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="45">
+        <v>60</v>
+      </c>
+      <c r="E4" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="45">
-        <v>60</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="45">
-        <v>60</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>30</v>
-      </c>
       <c r="F4" s="45">
         <v>60</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H4" s="47">
         <v>60</v>
@@ -4065,25 +4701,25 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="45">
+        <v>60</v>
+      </c>
+      <c r="C5" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="45">
-        <v>60</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>31</v>
-      </c>
       <c r="D5" s="45">
         <v>60</v>
       </c>
       <c r="E5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="45">
+        <v>60</v>
+      </c>
+      <c r="G5" s="50" t="s">
         <v>29</v>
-      </c>
-      <c r="F5" s="45">
-        <v>60</v>
-      </c>
-      <c r="G5" s="50" t="s">
-        <v>30</v>
       </c>
       <c r="H5" s="47">
         <v>60</v>
@@ -4092,25 +4728,25 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="45">
+        <v>60</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="45">
+        <v>60</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="45">
-        <v>60</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="45">
-        <v>60</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="F6" s="45">
         <v>60</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6" s="47">
         <v>60</v>
@@ -4119,7 +4755,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="45">
         <v>60</v>
@@ -4152,13 +4788,13 @@
         <v>60</v>
       </c>
       <c r="C8" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="45">
+        <v>60</v>
+      </c>
+      <c r="E8" s="48" t="s">
         <v>32</v>
-      </c>
-      <c r="D8" s="45">
-        <v>60</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>33</v>
       </c>
       <c r="F8" s="45">
         <v>60</v>
@@ -4173,13 +4809,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="45">
         <v>60</v>
       </c>
       <c r="C9" s="48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="45">
         <v>60</v>
@@ -4214,7 +4850,7 @@
         <v>60</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="47">
         <v>60</v>
@@ -4229,19 +4865,19 @@
         <v>60</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="45">
         <v>60</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="45">
         <v>60</v>
       </c>
       <c r="G11" s="46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H11" s="47">
         <v>60</v>
@@ -4325,10 +4961,10 @@
       <c r="I15" s="20" t="s"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="4">
+      <c r="A16" s="172">
         <v>46195</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="173" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="5">
@@ -4365,13 +5001,13 @@
       <c r="N16" s="8" t="s"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="174" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="45" t="s">
@@ -4405,203 +5041,449 @@
       <c r="N17" s="8" t="s"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="9" t="s"/>
-      <c r="B18" s="45" t="s"/>
-      <c r="C18" s="9" t="s"/>
-      <c r="D18" s="45" t="s"/>
-      <c r="E18" s="9" t="s"/>
-      <c r="F18" s="45" t="s"/>
-      <c r="G18" s="9" t="s"/>
-      <c r="H18" s="45" t="s"/>
-      <c r="I18" s="9" t="s"/>
-      <c r="J18" s="45" t="s"/>
-      <c r="K18" s="9" t="s"/>
-      <c r="L18" s="47" t="s"/>
+      <c r="A18" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="177">
+        <v>60</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="177">
+        <v>60</v>
+      </c>
+      <c r="E18" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="177">
+        <v>60</v>
+      </c>
+      <c r="G18" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="177">
+        <v>60</v>
+      </c>
+      <c r="I18" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="177">
+        <v>60</v>
+      </c>
+      <c r="K18" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="L18" s="169">
+        <v>60</v>
+      </c>
       <c r="M18" s="11" t="s"/>
       <c r="N18" s="8" t="s"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="46" t="s"/>
-      <c r="B19" s="45" t="s"/>
-      <c r="C19" s="48" t="s"/>
-      <c r="D19" s="45" t="s"/>
-      <c r="E19" s="49" t="s"/>
-      <c r="F19" s="45" t="s"/>
-      <c r="G19" s="46" t="s"/>
-      <c r="H19" s="45" t="s"/>
-      <c r="I19" s="46" t="s"/>
-      <c r="J19" s="45" t="s"/>
-      <c r="K19" s="46" t="s"/>
-      <c r="L19" s="47" t="s"/>
+      <c r="A19" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="45">
+        <v>60</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="45">
+        <v>60</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="45">
+        <v>60</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="45">
+        <v>60</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="45">
+        <v>60</v>
+      </c>
+      <c r="K19" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="47">
+        <v>60</v>
+      </c>
       <c r="M19" s="11" t="s"/>
       <c r="N19" s="8" t="s"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="48" t="s"/>
-      <c r="B20" s="45" t="s"/>
-      <c r="C20" s="48" t="s"/>
-      <c r="D20" s="45" t="s"/>
-      <c r="E20" s="9" t="s"/>
-      <c r="F20" s="45" t="s"/>
-      <c r="G20" s="50" t="s"/>
-      <c r="H20" s="45" t="s"/>
-      <c r="I20" s="50" t="s"/>
-      <c r="J20" s="45" t="s"/>
-      <c r="K20" s="50" t="s"/>
-      <c r="L20" s="47" t="s"/>
+      <c r="A20" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="45">
+        <v>60</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="45">
+        <v>60</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="45">
+        <v>60</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="45">
+        <v>60</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="45">
+        <v>60</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="47">
+        <v>60</v>
+      </c>
       <c r="M20" s="11" t="s"/>
       <c r="N20" s="8" t="s"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="12" t="s"/>
-      <c r="B21" s="45" t="s"/>
-      <c r="C21" s="49" t="s"/>
-      <c r="D21" s="45" t="s"/>
-      <c r="E21" s="9" t="s"/>
-      <c r="F21" s="45" t="s"/>
-      <c r="G21" s="46" t="s"/>
-      <c r="H21" s="45" t="s"/>
-      <c r="I21" s="46" t="s"/>
-      <c r="J21" s="45" t="s"/>
-      <c r="K21" s="46" t="s"/>
-      <c r="L21" s="47" t="s"/>
+      <c r="A21" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="45">
+        <v>60</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="45">
+        <v>60</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="45">
+        <v>60</v>
+      </c>
+      <c r="G21" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="45">
+        <v>60</v>
+      </c>
+      <c r="I21" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="45">
+        <v>60</v>
+      </c>
+      <c r="K21" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="47">
+        <v>60</v>
+      </c>
       <c r="M21" s="11" t="s"/>
       <c r="N21" s="8" t="s"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="48" t="s"/>
-      <c r="B22" s="45" t="s"/>
-      <c r="C22" s="48" t="s"/>
-      <c r="D22" s="45" t="s"/>
-      <c r="E22" s="46" t="s"/>
-      <c r="F22" s="45" t="s"/>
-      <c r="G22" s="46" t="s"/>
-      <c r="H22" s="45" t="s"/>
-      <c r="I22" s="46" t="s"/>
-      <c r="J22" s="45" t="s"/>
+      <c r="A22" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="45">
+        <v>60</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="45">
+        <v>60</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="45">
+        <v>60</v>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="45">
+        <v>60</v>
+      </c>
+      <c r="I22" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="45">
+        <v>60</v>
+      </c>
       <c r="K22" s="46" t="s"/>
       <c r="L22" s="47" t="s"/>
       <c r="M22" s="11" t="s"/>
       <c r="N22" s="8" t="s"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="48" t="s"/>
-      <c r="B23" s="45" t="s"/>
-      <c r="C23" s="46" t="s"/>
-      <c r="D23" s="45" t="s"/>
-      <c r="E23" s="48" t="s"/>
-      <c r="F23" s="45" t="s"/>
-      <c r="G23" s="46" t="s"/>
-      <c r="H23" s="45" t="s"/>
-      <c r="I23" s="46" t="s"/>
-      <c r="J23" s="45" t="s"/>
-      <c r="K23" s="46" t="s"/>
-      <c r="L23" s="47" t="s"/>
+      <c r="A23" s="170" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="61">
+        <v>60</v>
+      </c>
+      <c r="C23" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="61">
+        <v>60</v>
+      </c>
+      <c r="E23" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="61">
+        <v>60</v>
+      </c>
+      <c r="G23" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="61">
+        <v>60</v>
+      </c>
+      <c r="I23" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="61">
+        <v>60</v>
+      </c>
+      <c r="K23" s="63" t="s"/>
+      <c r="L23" s="64" t="s"/>
       <c r="M23" s="11" t="s"/>
       <c r="N23" s="8" t="s"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="48" t="s"/>
-      <c r="B24" s="45" t="s"/>
-      <c r="C24" s="48" t="s"/>
-      <c r="D24" s="45" t="s"/>
-      <c r="E24" s="46" t="s"/>
-      <c r="F24" s="45" t="s"/>
-      <c r="G24" s="46" t="s"/>
-      <c r="H24" s="45" t="s"/>
-      <c r="I24" s="46" t="s"/>
-      <c r="J24" s="45" t="s"/>
+      <c r="A24" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="45">
+        <v>60</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="45">
+        <v>60</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="45">
+        <v>60</v>
+      </c>
+      <c r="G24" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="45">
+        <v>60</v>
+      </c>
+      <c r="I24" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="45">
+        <v>60</v>
+      </c>
       <c r="K24" s="46" t="s"/>
       <c r="L24" s="47" t="s"/>
       <c r="M24" s="11" t="s"/>
       <c r="N24" s="8" t="s"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="48" t="s"/>
-      <c r="B25" s="45" t="s"/>
-      <c r="C25" s="48" t="s"/>
-      <c r="D25" s="45" t="s"/>
-      <c r="E25" s="48" t="s"/>
-      <c r="F25" s="45" t="s"/>
-      <c r="G25" s="12" t="s"/>
-      <c r="H25" s="45" t="s"/>
-      <c r="I25" s="12" t="s"/>
-      <c r="J25" s="45" t="s"/>
-      <c r="K25" s="12" t="s"/>
+      <c r="A25" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="45">
+        <v>60</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="45">
+        <v>60</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="45">
+        <v>60</v>
+      </c>
+      <c r="G25" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="45">
+        <v>60</v>
+      </c>
+      <c r="I25" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="45">
+        <v>60</v>
+      </c>
+      <c r="K25" s="46" t="s"/>
       <c r="L25" s="47" t="s"/>
       <c r="M25" s="11" t="s"/>
       <c r="N25" s="8" t="s"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="46" t="s"/>
-      <c r="B26" s="45" t="s"/>
-      <c r="C26" s="46" t="s"/>
-      <c r="D26" s="45" t="s"/>
-      <c r="E26" s="46" t="s"/>
-      <c r="F26" s="45" t="s"/>
-      <c r="G26" s="46" t="s"/>
-      <c r="H26" s="45" t="s"/>
-      <c r="I26" s="46" t="s"/>
-      <c r="J26" s="45" t="s"/>
-      <c r="K26" s="46" t="s"/>
+      <c r="A26" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="45">
+        <v>60</v>
+      </c>
+      <c r="C26" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="45">
+        <v>60</v>
+      </c>
+      <c r="E26" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="45">
+        <v>60</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="45">
+        <v>60</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="45">
+        <v>60</v>
+      </c>
+      <c r="K26" s="12" t="s"/>
       <c r="L26" s="47" t="s"/>
       <c r="M26" s="11" t="s"/>
       <c r="N26" s="8" t="s"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="9" t="s"/>
-      <c r="B27" s="45" t="s"/>
-      <c r="C27" s="46" t="s"/>
-      <c r="D27" s="45" t="s"/>
-      <c r="E27" s="46" t="s"/>
-      <c r="F27" s="45" t="s"/>
-      <c r="G27" s="46" t="s"/>
-      <c r="H27" s="45" t="s"/>
-      <c r="I27" s="46" t="s"/>
-      <c r="J27" s="45" t="s"/>
+      <c r="A27" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="45">
+        <v>60</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="45">
+        <v>60</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="45">
+        <v>60</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="45">
+        <v>60</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="J27" s="45">
+        <v>60</v>
+      </c>
       <c r="K27" s="46" t="s"/>
       <c r="L27" s="47" t="s"/>
-      <c r="M27" s="13" t="s">
+      <c r="M27" s="11" t="s"/>
+      <c r="N27" s="8" t="s"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="118" t="s"/>
+      <c r="B28" s="178" t="s"/>
+      <c r="C28" s="176" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="178">
+        <v>60</v>
+      </c>
+      <c r="E28" s="176" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="178">
+        <v>60</v>
+      </c>
+      <c r="G28" s="176" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="178">
+        <v>60</v>
+      </c>
+      <c r="I28" s="176" t="s"/>
+      <c r="J28" s="178" t="s"/>
+      <c r="K28" s="176" t="s"/>
+      <c r="L28" s="171" t="s"/>
+      <c r="M28" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="N27" s="14" t="s"/>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="15" t="s"/>
-      <c r="B28" s="16">
-        <f>=SUM(B18:B27)</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="15" t="s"/>
-      <c r="D28" s="16">
-        <f>=SUM(D18:D27)</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="15" t="s"/>
-      <c r="F28" s="16">
-        <f>=SUM(F18:F27)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="15" t="s"/>
-      <c r="H28" s="16">
-        <f>=SUM(H18:H27)</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="15" t="s"/>
-      <c r="J28" s="16">
-        <f>=SUM(J18:J27)</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="15" t="s"/>
-      <c r="L28" s="17">
-        <f>=SUM(L18:L27)</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="18">
-        <f>=SUM(A28:L28)</f>
-        <v>0</v>
-      </c>
       <c r="N28" s="14" t="s"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="15" t="s"/>
+      <c r="B29" s="16">
+        <f>=SUM(B18:B28)</f>
+        <v>600</v>
+      </c>
+      <c r="C29" s="15" t="s"/>
+      <c r="D29" s="16">
+        <f>=SUM(D18:D28)</f>
+        <v>660</v>
+      </c>
+      <c r="E29" s="15" t="s"/>
+      <c r="F29" s="16">
+        <f>=SUM(F18:F28)</f>
+        <v>660</v>
+      </c>
+      <c r="G29" s="15" t="s"/>
+      <c r="H29" s="16">
+        <f>=SUM(H18:H28)</f>
+        <v>660</v>
+      </c>
+      <c r="I29" s="15" t="s"/>
+      <c r="J29" s="16">
+        <f>=SUM(J18:J28)</f>
+        <v>600</v>
+      </c>
+      <c r="K29" s="15" t="s"/>
+      <c r="L29" s="17">
+        <f>=SUM(L18:L28)</f>
+        <v>240</v>
+      </c>
+      <c r="M29" s="18">
+        <f>=SUM(A29:L29)</f>
+        <v>3420</v>
+      </c>
+      <c r="N29" s="182" t="s">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -4615,401 +5497,404 @@
   <dimension ref="D17"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="11" width="12.1406" style="92" customWidth="1"/>
-    <col min="12" max="12" width="12.1406" style="92" customWidth="1"/>
+    <col min="1" max="11" width="12.1406" style="109" customWidth="1"/>
+    <col min="12" max="12" width="12.1406" style="109" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="52" t="s"/>
-      <c r="B1" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="54" t="s"/>
-      <c r="D1" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="54" t="s"/>
-      <c r="F1" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="54" t="s"/>
-      <c r="H1" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="54" t="s"/>
-      <c r="J1" s="53" t="s">
+      <c r="A1" s="65" t="s"/>
+      <c r="B1" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="54" t="s"/>
-      <c r="L1" s="55" t="s"/>
+      <c r="C1" s="67" t="s"/>
+      <c r="D1" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="67" t="s"/>
+      <c r="F1" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="67" t="s"/>
+      <c r="H1" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="67" t="s"/>
+      <c r="J1" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="67" t="s"/>
+      <c r="L1" s="68" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="56" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="58">
-        <v>60</v>
-      </c>
-      <c r="D2" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="58">
-        <v>60</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="58">
-        <v>60</v>
-      </c>
-      <c r="H2" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="58">
+      <c r="A2" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="71">
+        <v>60</v>
+      </c>
+      <c r="D2" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="71">
+        <v>60</v>
+      </c>
+      <c r="F2" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="71">
+        <v>60</v>
+      </c>
+      <c r="H2" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="71">
         <v>65</v>
       </c>
-      <c r="J2" s="57" t="s"/>
-      <c r="K2" s="59" t="s"/>
-      <c r="L2" s="60" t="s"/>
+      <c r="J2" s="70" t="s"/>
+      <c r="K2" s="72" t="s"/>
+      <c r="L2" s="73" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="61" t="s"/>
-      <c r="B3" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="63">
-        <v>60</v>
-      </c>
-      <c r="D3" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="63">
-        <v>60</v>
-      </c>
-      <c r="F3" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="63">
-        <v>60</v>
-      </c>
-      <c r="H3" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="63">
+      <c r="A3" s="74" t="s"/>
+      <c r="B3" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="76">
+        <v>60</v>
+      </c>
+      <c r="D3" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="76">
+        <v>60</v>
+      </c>
+      <c r="F3" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="76">
+        <v>60</v>
+      </c>
+      <c r="H3" s="75" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="76">
         <v>65</v>
       </c>
-      <c r="J3" s="62" t="s"/>
-      <c r="K3" s="64" t="s"/>
-      <c r="L3" s="60" t="s"/>
+      <c r="J3" s="75" t="s"/>
+      <c r="K3" s="77" t="s"/>
+      <c r="L3" s="73" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="61" t="s"/>
-      <c r="B4" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="63">
-        <v>60</v>
-      </c>
-      <c r="D4" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="63">
-        <v>60</v>
-      </c>
-      <c r="F4" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="63">
-        <v>60</v>
-      </c>
-      <c r="H4" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="63">
+      <c r="A4" s="74" t="s"/>
+      <c r="B4" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="76">
+        <v>60</v>
+      </c>
+      <c r="D4" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="76">
+        <v>60</v>
+      </c>
+      <c r="F4" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="76">
+        <v>60</v>
+      </c>
+      <c r="H4" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="76">
         <v>65</v>
       </c>
-      <c r="J4" s="62" t="s"/>
-      <c r="K4" s="64" t="s"/>
-      <c r="L4" s="65" t="s">
-        <v>44</v>
+      <c r="J4" s="75" t="s"/>
+      <c r="K4" s="77" t="s"/>
+      <c r="L4" s="78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="66" t="s"/>
-      <c r="B5" s="67" t="s"/>
-      <c r="C5" s="68" t="s"/>
-      <c r="D5" s="67" t="s"/>
-      <c r="E5" s="68" t="s"/>
-      <c r="F5" s="67" t="s"/>
-      <c r="G5" s="68" t="s"/>
-      <c r="H5" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="68">
+      <c r="A5" s="79" t="s"/>
+      <c r="B5" s="80" t="s"/>
+      <c r="C5" s="81" t="s"/>
+      <c r="D5" s="80" t="s"/>
+      <c r="E5" s="81" t="s"/>
+      <c r="F5" s="80" t="s"/>
+      <c r="G5" s="81" t="s"/>
+      <c r="H5" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="81">
         <v>10</v>
       </c>
-      <c r="J5" s="67" t="s"/>
-      <c r="K5" s="69" t="s"/>
-      <c r="L5" s="70">
+      <c r="J5" s="80" t="s"/>
+      <c r="K5" s="82" t="s"/>
+      <c r="L5" s="83">
         <f>=SUM(B2:K5)</f>
         <v>745</v>
       </c>
-      <c r="M5" s="71" t="s">
+      <c r="M5" s="84" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="72">
+      <c r="A8" s="85">
         <v>46195</v>
       </c>
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="85">
         <v>46196</v>
       </c>
-      <c r="D8" s="73" t="s">
+      <c r="D8" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="72">
+      <c r="E8" s="85">
         <v>46197</v>
       </c>
-      <c r="F8" s="73" t="s">
+      <c r="F8" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="72">
+      <c r="G8" s="85">
         <v>46198</v>
       </c>
-      <c r="H8" s="73" t="s">
+      <c r="H8" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="72">
+      <c r="I8" s="85">
         <v>46199</v>
       </c>
-      <c r="J8" s="74" t="s">
+      <c r="J8" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="K8" s="74" t="s"/>
-      <c r="L8" s="75" t="s"/>
-      <c r="M8" s="76" t="s"/>
-      <c r="N8" s="76" t="s"/>
+      <c r="K8" s="87" t="s"/>
+      <c r="L8" s="88" t="s"/>
+      <c r="M8" s="89" t="s"/>
+      <c r="N8" s="89" t="s"/>
       <c r="O8" s="29" t="s"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="B9" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="77" t="s">
+      <c r="C9" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="78" t="s">
+      <c r="D9" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="78" t="s">
+      <c r="F9" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="77" t="s">
+      <c r="G9" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="78" t="s">
+      <c r="H9" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="150" t="s">
+      <c r="I9" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="151" t="s">
+      <c r="J9" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="79" t="s"/>
-      <c r="L9" s="80" t="s"/>
-      <c r="M9" s="81" t="s"/>
-      <c r="N9" s="81" t="s"/>
+      <c r="K9" s="94" t="s"/>
+      <c r="L9" s="95" t="s"/>
+      <c r="M9" s="96" t="s"/>
+      <c r="N9" s="96" t="s"/>
       <c r="O9" s="29" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="82" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="83">
-        <v>60</v>
-      </c>
-      <c r="C10" s="82" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="84">
-        <v>90</v>
-      </c>
-      <c r="E10" s="82" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="83">
-        <v>60</v>
-      </c>
-      <c r="G10" s="82" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="83">
-        <v>90</v>
-      </c>
-      <c r="I10" s="148" t="s">
-        <v>41</v>
-      </c>
-      <c r="J10" s="149">
-        <v>60</v>
-      </c>
-      <c r="K10" s="86" t="s"/>
+      <c r="A10" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="98">
+        <v>60</v>
+      </c>
+      <c r="C10" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="99">
+        <v>90</v>
+      </c>
+      <c r="E10" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="98">
+        <v>60</v>
+      </c>
+      <c r="G10" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="98">
+        <v>90</v>
+      </c>
+      <c r="I10" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="101">
+        <v>60</v>
+      </c>
+      <c r="K10" s="102" t="s"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="82" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="83">
-        <v>60</v>
-      </c>
-      <c r="C11" s="82" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="83">
-        <v>90</v>
-      </c>
-      <c r="E11" s="82" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="83">
-        <v>90</v>
-      </c>
-      <c r="G11" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="83">
-        <v>60</v>
-      </c>
-      <c r="I11" s="82" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="86">
-        <v>90</v>
-      </c>
-      <c r="K11" s="86" t="s"/>
+      <c r="A11" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="98">
+        <v>60</v>
+      </c>
+      <c r="C11" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="98">
+        <v>90</v>
+      </c>
+      <c r="E11" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="98">
+        <v>90</v>
+      </c>
+      <c r="G11" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="98">
+        <v>60</v>
+      </c>
+      <c r="I11" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="102">
+        <v>90</v>
+      </c>
+      <c r="K11" s="102" t="s"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="83">
-        <v>60</v>
-      </c>
-      <c r="C12" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="83">
-        <v>90</v>
-      </c>
-      <c r="E12" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="83">
-        <v>60</v>
-      </c>
-      <c r="G12" s="82" t="s"/>
-      <c r="H12" s="83" t="s"/>
-      <c r="I12" s="82" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="86">
-        <v>60</v>
-      </c>
-      <c r="K12" s="86" t="s"/>
+      <c r="A12" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="98">
+        <v>60</v>
+      </c>
+      <c r="C12" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="98">
+        <v>90</v>
+      </c>
+      <c r="E12" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="98">
+        <v>60</v>
+      </c>
+      <c r="G12" s="97" t="s"/>
+      <c r="H12" s="98" t="s"/>
+      <c r="I12" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="102">
+        <v>60</v>
+      </c>
+      <c r="K12" s="102" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="85" t="s"/>
-      <c r="B13" s="83" t="s"/>
-      <c r="C13" s="85" t="s"/>
-      <c r="D13" s="83" t="s"/>
-      <c r="E13" s="85" t="s"/>
-      <c r="F13" s="83" t="s"/>
-      <c r="G13" s="85" t="s"/>
-      <c r="H13" s="83" t="s"/>
-      <c r="I13" s="82" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="86">
+      <c r="A13" s="103" t="s"/>
+      <c r="B13" s="98" t="s"/>
+      <c r="C13" s="103" t="s"/>
+      <c r="D13" s="98" t="s"/>
+      <c r="E13" s="103" t="s"/>
+      <c r="F13" s="98" t="s"/>
+      <c r="G13" s="103" t="s"/>
+      <c r="H13" s="98" t="s"/>
+      <c r="I13" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="102">
         <v>10</v>
       </c>
-      <c r="K13" s="86" t="s">
-        <v>84</v>
+      <c r="K13" s="102" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="85" t="s"/>
-      <c r="B14" s="83" t="s"/>
-      <c r="C14" s="85" t="s"/>
-      <c r="D14" s="83" t="s"/>
-      <c r="E14" s="85" t="s"/>
-      <c r="F14" s="83" t="s"/>
-      <c r="G14" s="85" t="s"/>
-      <c r="H14" s="83" t="s"/>
-      <c r="I14" s="85" t="s"/>
-      <c r="J14" s="86" t="s"/>
-      <c r="K14" s="86" t="s"/>
+      <c r="A14" s="103" t="s"/>
+      <c r="B14" s="98" t="s"/>
+      <c r="C14" s="103" t="s"/>
+      <c r="D14" s="98" t="s"/>
+      <c r="E14" s="103" t="s"/>
+      <c r="F14" s="98" t="s"/>
+      <c r="G14" s="103" t="s"/>
+      <c r="H14" s="98" t="s"/>
+      <c r="I14" s="103" t="s"/>
+      <c r="J14" s="102" t="s"/>
+      <c r="K14" s="102" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="85" t="s"/>
-      <c r="B15" s="83" t="s"/>
-      <c r="C15" s="85" t="s"/>
-      <c r="D15" s="83" t="s"/>
-      <c r="E15" s="85" t="s"/>
-      <c r="F15" s="83" t="s"/>
-      <c r="G15" s="85" t="s"/>
-      <c r="H15" s="83" t="s"/>
-      <c r="I15" s="85" t="s"/>
-      <c r="J15" s="86" t="s"/>
-      <c r="K15" s="87" t="s">
+      <c r="A15" s="103" t="s"/>
+      <c r="B15" s="98" t="s"/>
+      <c r="C15" s="103" t="s"/>
+      <c r="D15" s="98" t="s"/>
+      <c r="E15" s="103" t="s"/>
+      <c r="F15" s="98" t="s"/>
+      <c r="G15" s="103" t="s"/>
+      <c r="H15" s="98" t="s"/>
+      <c r="I15" s="103" t="s"/>
+      <c r="J15" s="102" t="s"/>
+      <c r="K15" s="104" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="88" t="s"/>
-      <c r="B16" s="89">
+    <row r="16" spans="1:12">
+      <c r="A16" s="105" t="s"/>
+      <c r="B16" s="106">
         <f>=SUM(B10:B15)</f>
         <v>180</v>
       </c>
-      <c r="C16" s="88" t="s"/>
-      <c r="D16" s="89">
+      <c r="C16" s="105" t="s"/>
+      <c r="D16" s="106">
         <f>=SUM(D10:D15)</f>
         <v>270</v>
       </c>
-      <c r="E16" s="88" t="s"/>
-      <c r="F16" s="89">
+      <c r="E16" s="105" t="s"/>
+      <c r="F16" s="106">
         <f>=SUM(F10:F15)</f>
         <v>210</v>
       </c>
-      <c r="G16" s="88" t="s"/>
-      <c r="H16" s="89">
+      <c r="G16" s="105" t="s"/>
+      <c r="H16" s="106">
         <f>=SUM(H10:H15)</f>
         <v>150</v>
       </c>
-      <c r="I16" s="88" t="s"/>
-      <c r="J16" s="90">
+      <c r="I16" s="105" t="s"/>
+      <c r="J16" s="107">
         <f>=SUM(J10:J15)</f>
         <v>220</v>
       </c>
-      <c r="K16" s="91">
+      <c r="K16" s="108">
         <f>=SUM(A16:J16)</f>
         <v>1030</v>
       </c>
+      <c r="L16" s="195" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="17" spans="4:4">
-      <c r="D17" s="92" t="s"/>
+      <c r="D17" s="109" t="s"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5027,7 +5912,7 @@
   <sheetPr codeName="北京路广百">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K16"/>
+  <dimension ref="L16"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="11" width="12.6836" customWidth="1"/>
@@ -5035,144 +5920,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="93" t="s"/>
-      <c r="B1" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="54" t="s"/>
-      <c r="D1" s="94" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="54" t="s"/>
-      <c r="F1" s="94" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="54" t="s"/>
-      <c r="H1" s="94" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="54" t="s"/>
-      <c r="J1" s="94" t="s">
+      <c r="A1" s="110" t="s"/>
+      <c r="B1" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="54" t="s"/>
-      <c r="L1" s="95" t="s"/>
+      <c r="C1" s="67" t="s"/>
+      <c r="D1" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="67" t="s"/>
+      <c r="F1" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="67" t="s"/>
+      <c r="H1" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="67" t="s"/>
+      <c r="J1" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="67" t="s"/>
+      <c r="L1" s="112" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="96" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="97" t="s">
-        <v>47</v>
+      <c r="A2" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>52</v>
       </c>
       <c r="C2" s="44">
         <v>60</v>
       </c>
-      <c r="D2" s="97" t="s">
-        <v>47</v>
+      <c r="D2" s="52" t="s">
+        <v>52</v>
       </c>
       <c r="E2" s="44">
         <v>60</v>
       </c>
-      <c r="F2" s="97" t="s">
-        <v>47</v>
+      <c r="F2" s="52" t="s">
+        <v>52</v>
       </c>
       <c r="G2" s="44">
         <v>60</v>
       </c>
-      <c r="H2" s="97" t="s">
-        <v>47</v>
+      <c r="H2" s="52" t="s">
+        <v>52</v>
       </c>
       <c r="I2" s="44">
         <v>60</v>
       </c>
-      <c r="J2" s="97" t="s"/>
-      <c r="K2" s="98" t="s"/>
-      <c r="L2" s="99" t="s"/>
+      <c r="J2" s="52" t="s"/>
+      <c r="K2" s="114" t="s"/>
+      <c r="L2" s="115" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="100" t="s"/>
+      <c r="A3" s="116" t="s"/>
       <c r="B3" s="9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C3" s="11">
         <v>60</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E3" s="11">
         <v>60</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G3" s="11">
         <v>60</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I3" s="11">
         <v>60</v>
       </c>
       <c r="J3" s="9" t="s"/>
       <c r="K3" s="10" t="s"/>
-      <c r="L3" s="99" t="s"/>
+      <c r="L3" s="115" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="100" t="s"/>
+      <c r="A4" s="116" t="s"/>
       <c r="B4" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C4" s="11">
         <v>60</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E4" s="11">
         <v>60</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G4" s="11">
         <v>60</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I4" s="11">
         <v>60</v>
       </c>
       <c r="J4" s="9" t="s"/>
       <c r="K4" s="10" t="s"/>
-      <c r="L4" s="65" t="s">
-        <v>44</v>
+      <c r="L4" s="78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="101" t="s"/>
-      <c r="B5" s="102" t="s"/>
-      <c r="C5" s="103" t="s"/>
-      <c r="D5" s="102" t="s"/>
-      <c r="E5" s="103" t="s"/>
-      <c r="F5" s="102" t="s"/>
-      <c r="G5" s="103" t="s"/>
-      <c r="H5" s="102" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="103">
+      <c r="A5" s="117" t="s"/>
+      <c r="B5" s="118" t="s"/>
+      <c r="C5" s="119" t="s"/>
+      <c r="D5" s="118" t="s"/>
+      <c r="E5" s="119" t="s"/>
+      <c r="F5" s="118" t="s"/>
+      <c r="G5" s="119" t="s"/>
+      <c r="H5" s="118" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="119">
         <v>10</v>
       </c>
-      <c r="J5" s="102" t="s"/>
-      <c r="K5" s="104" t="s"/>
-      <c r="L5" s="105">
+      <c r="J5" s="118" t="s"/>
+      <c r="K5" s="120" t="s"/>
+      <c r="L5" s="121">
         <f>=SUM(B2:K5)</f>
         <v>730</v>
       </c>
-      <c r="M5" s="71" t="s">
+      <c r="M5" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5210,28 +6095,28 @@
       <c r="K8" s="6" t="s"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="106" t="s">
+      <c r="A9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="107" t="s">
+      <c r="B9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="106" t="s">
+      <c r="C9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="107" t="s">
+      <c r="D9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="107" t="s">
+      <c r="F9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="106" t="s">
+      <c r="G9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="107" t="s">
+      <c r="H9" s="123" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="28" t="s">
@@ -5240,173 +6125,176 @@
       <c r="J9" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="108" t="s"/>
+      <c r="K9" s="124" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="92">
-        <v>60</v>
-      </c>
-      <c r="C10" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="92">
-        <v>60</v>
-      </c>
-      <c r="E10" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="92">
-        <v>60</v>
-      </c>
-      <c r="G10" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="92">
-        <v>60</v>
-      </c>
-      <c r="I10" s="109" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="149">
-        <v>60</v>
-      </c>
-      <c r="K10" s="86" t="s"/>
+      <c r="A10" s="125" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="109">
+        <v>60</v>
+      </c>
+      <c r="C10" s="125" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="109">
+        <v>60</v>
+      </c>
+      <c r="E10" s="125" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="109">
+        <v>60</v>
+      </c>
+      <c r="G10" s="125" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="109">
+        <v>60</v>
+      </c>
+      <c r="I10" s="125" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="101">
+        <v>60</v>
+      </c>
+      <c r="K10" s="102" t="s"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="92">
+        <v>53</v>
+      </c>
+      <c r="B11" s="109">
         <v>60</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="92">
+        <v>53</v>
+      </c>
+      <c r="D11" s="109">
         <v>60</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="92">
+        <v>53</v>
+      </c>
+      <c r="F11" s="109">
         <v>60</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="92">
+        <v>53</v>
+      </c>
+      <c r="H11" s="109">
         <v>60</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" s="86">
-        <v>60</v>
-      </c>
-      <c r="K11" s="86" t="s"/>
+        <v>54</v>
+      </c>
+      <c r="J11" s="102">
+        <v>60</v>
+      </c>
+      <c r="K11" s="102" t="s"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="92">
+        <v>54</v>
+      </c>
+      <c r="B12" s="109">
         <v>60</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="92">
+        <v>54</v>
+      </c>
+      <c r="D12" s="109">
         <v>60</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="92">
+        <v>54</v>
+      </c>
+      <c r="F12" s="109">
         <v>60</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="92">
-        <v>60</v>
-      </c>
-      <c r="I12" s="85" t="s"/>
-      <c r="J12" s="86" t="s"/>
-      <c r="K12" s="86" t="s"/>
+        <v>54</v>
+      </c>
+      <c r="H12" s="109">
+        <v>60</v>
+      </c>
+      <c r="I12" s="103" t="s"/>
+      <c r="J12" s="102" t="s"/>
+      <c r="K12" s="102" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="85" t="s"/>
-      <c r="B13" s="92" t="s"/>
-      <c r="C13" s="85" t="s"/>
-      <c r="D13" s="92" t="s"/>
-      <c r="E13" s="85" t="s"/>
-      <c r="F13" s="92" t="s"/>
-      <c r="G13" s="85" t="s"/>
-      <c r="H13" s="92" t="s"/>
-      <c r="I13" s="85" t="s"/>
-      <c r="J13" s="86" t="s"/>
-      <c r="K13" s="86" t="s"/>
+      <c r="A13" s="103" t="s"/>
+      <c r="B13" s="109" t="s"/>
+      <c r="C13" s="103" t="s"/>
+      <c r="D13" s="109" t="s"/>
+      <c r="E13" s="103" t="s"/>
+      <c r="F13" s="109" t="s"/>
+      <c r="G13" s="103" t="s"/>
+      <c r="H13" s="109" t="s"/>
+      <c r="I13" s="103" t="s"/>
+      <c r="J13" s="102" t="s"/>
+      <c r="K13" s="102" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="85" t="s"/>
-      <c r="B14" s="92" t="s"/>
-      <c r="C14" s="85" t="s"/>
-      <c r="D14" s="92" t="s"/>
-      <c r="E14" s="85" t="s"/>
-      <c r="F14" s="92" t="s"/>
-      <c r="G14" s="85" t="s"/>
-      <c r="H14" s="92" t="s"/>
-      <c r="I14" s="85" t="s"/>
-      <c r="J14" s="86" t="s"/>
-      <c r="K14" s="86" t="s"/>
+      <c r="A14" s="103" t="s"/>
+      <c r="B14" s="109" t="s"/>
+      <c r="C14" s="103" t="s"/>
+      <c r="D14" s="109" t="s"/>
+      <c r="E14" s="103" t="s"/>
+      <c r="F14" s="109" t="s"/>
+      <c r="G14" s="103" t="s"/>
+      <c r="H14" s="109" t="s"/>
+      <c r="I14" s="103" t="s"/>
+      <c r="J14" s="102" t="s"/>
+      <c r="K14" s="102" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="85" t="s"/>
-      <c r="B15" s="92" t="s"/>
-      <c r="C15" s="85" t="s"/>
-      <c r="D15" s="92" t="s"/>
-      <c r="E15" s="85" t="s"/>
-      <c r="F15" s="92" t="s"/>
-      <c r="G15" s="85" t="s"/>
-      <c r="H15" s="92" t="s"/>
-      <c r="I15" s="152" t="s"/>
-      <c r="J15" s="153" t="s"/>
-      <c r="K15" s="87" t="s">
+      <c r="A15" s="103" t="s"/>
+      <c r="B15" s="109" t="s"/>
+      <c r="C15" s="103" t="s"/>
+      <c r="D15" s="109" t="s"/>
+      <c r="E15" s="103" t="s"/>
+      <c r="F15" s="109" t="s"/>
+      <c r="G15" s="103" t="s"/>
+      <c r="H15" s="109" t="s"/>
+      <c r="I15" s="126" t="s"/>
+      <c r="J15" s="127" t="s"/>
+      <c r="K15" s="104" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="88" t="s"/>
-      <c r="B16" s="89">
+    <row r="16" spans="1:12">
+      <c r="A16" s="105" t="s"/>
+      <c r="B16" s="106">
         <f>=SUM(B10:B15)</f>
         <v>180</v>
       </c>
-      <c r="C16" s="88" t="s"/>
-      <c r="D16" s="89">
+      <c r="C16" s="105" t="s"/>
+      <c r="D16" s="106">
         <f>=SUM(D10:D15)</f>
         <v>180</v>
       </c>
-      <c r="E16" s="88" t="s"/>
-      <c r="F16" s="89">
+      <c r="E16" s="105" t="s"/>
+      <c r="F16" s="106">
         <f>=SUM(F10:F15)</f>
         <v>180</v>
       </c>
-      <c r="G16" s="88" t="s"/>
-      <c r="H16" s="89">
+      <c r="G16" s="105" t="s"/>
+      <c r="H16" s="106">
         <f>=SUM(H10:H15)</f>
         <v>180</v>
       </c>
-      <c r="I16" s="154" t="s"/>
-      <c r="J16" s="155">
+      <c r="I16" s="128" t="s"/>
+      <c r="J16" s="129">
         <f>=SUM(J10:J15)</f>
         <v>120</v>
       </c>
-      <c r="K16" s="91">
+      <c r="K16" s="108">
         <f>=SUM(A16:J16)</f>
         <v>840</v>
+      </c>
+      <c r="L16" s="195" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -5425,7 +6313,7 @@
   <sheetPr codeName="金鹰大厦">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K16"/>
+  <dimension ref="L16"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="11" width="10.9219" customWidth="1"/>
@@ -5433,154 +6321,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A1" s="110" t="s"/>
-      <c r="B1" s="94">
+      <c r="A1" s="130" t="s"/>
+      <c r="B1" s="111">
         <v>46188</v>
       </c>
-      <c r="C1" s="111" t="s">
+      <c r="C1" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="94">
+      <c r="D1" s="111">
         <v>46189</v>
       </c>
-      <c r="E1" s="111" t="s">
+      <c r="E1" s="131" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="94">
+      <c r="F1" s="111">
         <v>46190</v>
       </c>
-      <c r="G1" s="111" t="s">
+      <c r="G1" s="131" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="94">
+      <c r="H1" s="111">
         <v>46191</v>
       </c>
-      <c r="I1" s="111" t="s">
+      <c r="I1" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="53">
+      <c r="J1" s="66">
         <v>46192</v>
       </c>
-      <c r="K1" s="112" t="s">
-        <v>51</v>
-      </c>
-      <c r="L1" s="95" t="s"/>
+      <c r="K1" s="132" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="112" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="97" t="s">
-        <v>53</v>
+      <c r="A2" s="133" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>58</v>
       </c>
       <c r="C2" s="44">
         <v>90</v>
       </c>
-      <c r="D2" s="97" t="s">
-        <v>53</v>
+      <c r="D2" s="52" t="s">
+        <v>58</v>
       </c>
       <c r="E2" s="44">
         <v>90</v>
       </c>
-      <c r="F2" s="97" t="s">
-        <v>53</v>
+      <c r="F2" s="52" t="s">
+        <v>58</v>
       </c>
       <c r="G2" s="44">
         <v>90</v>
       </c>
-      <c r="H2" s="97" t="s">
-        <v>53</v>
+      <c r="H2" s="52" t="s">
+        <v>58</v>
       </c>
       <c r="I2" s="44">
         <v>90</v>
       </c>
-      <c r="J2" s="97" t="s"/>
-      <c r="K2" s="98" t="s"/>
-      <c r="L2" s="99" t="s"/>
+      <c r="J2" s="52" t="s"/>
+      <c r="K2" s="114" t="s"/>
+      <c r="L2" s="115" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="114" t="s"/>
+      <c r="A3" s="134" t="s"/>
       <c r="B3" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C3" s="11">
         <v>90</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G3" s="11">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I3" s="11">
         <v>90</v>
       </c>
       <c r="J3" s="9" t="s"/>
       <c r="K3" s="10" t="s"/>
-      <c r="L3" s="99" t="s"/>
+      <c r="L3" s="115" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="114" t="s"/>
+      <c r="A4" s="134" t="s"/>
       <c r="B4" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" s="11">
         <v>60</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E4" s="11">
         <v>60</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G4" s="11">
         <v>60</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I4" s="11">
         <v>60</v>
       </c>
       <c r="J4" s="9" t="s"/>
       <c r="K4" s="10" t="s"/>
-      <c r="L4" s="65" t="s">
-        <v>44</v>
+      <c r="L4" s="78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="15" t="s"/>
-      <c r="B5" s="102" t="s"/>
-      <c r="C5" s="103" t="s"/>
-      <c r="D5" s="102" t="s"/>
-      <c r="E5" s="103" t="s"/>
-      <c r="F5" s="102" t="s"/>
-      <c r="G5" s="103" t="s"/>
-      <c r="H5" s="102" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="103">
+      <c r="B5" s="118" t="s"/>
+      <c r="C5" s="119" t="s"/>
+      <c r="D5" s="118" t="s"/>
+      <c r="E5" s="119" t="s"/>
+      <c r="F5" s="118" t="s"/>
+      <c r="G5" s="119" t="s"/>
+      <c r="H5" s="118" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="119">
         <v>10</v>
       </c>
-      <c r="J5" s="102" t="s"/>
-      <c r="K5" s="104" t="s"/>
-      <c r="L5" s="105">
+      <c r="J5" s="118" t="s"/>
+      <c r="K5" s="120" t="s"/>
+      <c r="L5" s="121">
         <f>=SUM(B2:K5)</f>
         <v>970</v>
       </c>
-      <c r="M5" s="71" t="s">
+      <c r="M5" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5618,197 +6506,200 @@
       <c r="K8" s="6" t="s"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="106" t="s">
+      <c r="A9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="107" t="s">
+      <c r="B9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="106" t="s">
+      <c r="C9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="107" t="s">
+      <c r="D9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="107" t="s">
+      <c r="F9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="106" t="s">
+      <c r="G9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="107" t="s">
+      <c r="H9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="106" t="s">
+      <c r="I9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="108" t="s">
+      <c r="J9" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="108" t="s"/>
+      <c r="K9" s="124" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="92">
-        <v>90</v>
-      </c>
-      <c r="C10" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="92">
-        <v>90</v>
-      </c>
-      <c r="E10" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="92">
-        <v>90</v>
-      </c>
-      <c r="G10" s="109" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="92">
-        <v>90</v>
-      </c>
-      <c r="I10" s="85" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="86">
+      <c r="A10" s="125" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="109">
+        <v>90</v>
+      </c>
+      <c r="C10" s="125" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="109">
+        <v>90</v>
+      </c>
+      <c r="E10" s="125" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="109">
+        <v>90</v>
+      </c>
+      <c r="G10" s="125" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="109">
+        <v>90</v>
+      </c>
+      <c r="I10" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="102">
         <v>10</v>
       </c>
-      <c r="K10" s="86" t="s">
-        <v>84</v>
+      <c r="K10" s="102" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="92">
+        <v>59</v>
+      </c>
+      <c r="B11" s="109">
         <v>90</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="92">
+        <v>59</v>
+      </c>
+      <c r="D11" s="109">
         <v>90</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="92">
+        <v>59</v>
+      </c>
+      <c r="F11" s="109">
         <v>60</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="92">
-        <v>60</v>
-      </c>
-      <c r="I11" s="85" t="s"/>
-      <c r="J11" s="86" t="s"/>
-      <c r="K11" s="86" t="s"/>
+        <v>59</v>
+      </c>
+      <c r="H11" s="109">
+        <v>60</v>
+      </c>
+      <c r="I11" s="103" t="s"/>
+      <c r="J11" s="102" t="s"/>
+      <c r="K11" s="102" t="s"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="92">
+        <v>60</v>
+      </c>
+      <c r="B12" s="109">
         <v>60</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="92">
+        <v>60</v>
+      </c>
+      <c r="D12" s="109">
         <v>60</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="92">
+        <v>60</v>
+      </c>
+      <c r="F12" s="109">
         <v>60</v>
       </c>
       <c r="G12" s="28" t="s"/>
-      <c r="H12" s="92" t="s"/>
-      <c r="I12" s="85" t="s"/>
-      <c r="J12" s="86" t="s"/>
-      <c r="K12" s="86" t="s"/>
+      <c r="H12" s="109" t="s"/>
+      <c r="I12" s="103" t="s"/>
+      <c r="J12" s="102" t="s"/>
+      <c r="K12" s="102" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="85" t="s"/>
-      <c r="B13" s="92" t="s"/>
-      <c r="C13" s="85" t="s"/>
-      <c r="D13" s="92" t="s"/>
-      <c r="E13" s="85" t="s"/>
-      <c r="F13" s="92" t="s"/>
-      <c r="G13" s="85" t="s"/>
-      <c r="H13" s="92" t="s"/>
-      <c r="I13" s="85" t="s"/>
-      <c r="J13" s="86" t="s"/>
-      <c r="K13" s="86" t="s"/>
+      <c r="A13" s="103" t="s"/>
+      <c r="B13" s="109" t="s"/>
+      <c r="C13" s="103" t="s"/>
+      <c r="D13" s="109" t="s"/>
+      <c r="E13" s="103" t="s"/>
+      <c r="F13" s="109" t="s"/>
+      <c r="G13" s="103" t="s"/>
+      <c r="H13" s="109" t="s"/>
+      <c r="I13" s="103" t="s"/>
+      <c r="J13" s="102" t="s"/>
+      <c r="K13" s="102" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="85" t="s"/>
-      <c r="B14" s="92" t="s"/>
-      <c r="C14" s="85" t="s"/>
-      <c r="D14" s="92" t="s"/>
-      <c r="E14" s="85" t="s"/>
-      <c r="F14" s="92" t="s"/>
-      <c r="G14" s="85" t="s"/>
-      <c r="H14" s="92" t="s"/>
-      <c r="I14" s="85" t="s"/>
-      <c r="J14" s="86" t="s"/>
-      <c r="K14" s="86" t="s"/>
+      <c r="A14" s="103" t="s"/>
+      <c r="B14" s="109" t="s"/>
+      <c r="C14" s="103" t="s"/>
+      <c r="D14" s="109" t="s"/>
+      <c r="E14" s="103" t="s"/>
+      <c r="F14" s="109" t="s"/>
+      <c r="G14" s="103" t="s"/>
+      <c r="H14" s="109" t="s"/>
+      <c r="I14" s="103" t="s"/>
+      <c r="J14" s="102" t="s"/>
+      <c r="K14" s="102" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="85" t="s"/>
-      <c r="B15" s="92" t="s"/>
-      <c r="C15" s="85" t="s"/>
-      <c r="D15" s="92" t="s"/>
-      <c r="E15" s="85" t="s"/>
-      <c r="F15" s="92" t="s"/>
-      <c r="G15" s="85" t="s"/>
-      <c r="H15" s="92" t="s"/>
-      <c r="I15" s="85" t="s"/>
-      <c r="J15" s="86" t="s"/>
-      <c r="K15" s="87" t="s">
+      <c r="A15" s="103" t="s"/>
+      <c r="B15" s="109" t="s"/>
+      <c r="C15" s="103" t="s"/>
+      <c r="D15" s="109" t="s"/>
+      <c r="E15" s="103" t="s"/>
+      <c r="F15" s="109" t="s"/>
+      <c r="G15" s="103" t="s"/>
+      <c r="H15" s="109" t="s"/>
+      <c r="I15" s="103" t="s"/>
+      <c r="J15" s="102" t="s"/>
+      <c r="K15" s="104" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="88" t="s"/>
-      <c r="B16" s="89">
+    <row r="16" spans="1:12">
+      <c r="A16" s="105" t="s"/>
+      <c r="B16" s="106">
         <f>=SUM(B10:B15)</f>
         <v>240</v>
       </c>
-      <c r="C16" s="88" t="s"/>
-      <c r="D16" s="89">
+      <c r="C16" s="105" t="s"/>
+      <c r="D16" s="106">
         <f>=SUM(D10:D15)</f>
         <v>240</v>
       </c>
-      <c r="E16" s="88" t="s"/>
-      <c r="F16" s="89">
+      <c r="E16" s="105" t="s"/>
+      <c r="F16" s="106">
         <f>=SUM(F10:F15)</f>
         <v>210</v>
       </c>
-      <c r="G16" s="88" t="s"/>
-      <c r="H16" s="89">
+      <c r="G16" s="105" t="s"/>
+      <c r="H16" s="106">
         <f>=SUM(H10:H15)</f>
         <v>150</v>
       </c>
-      <c r="I16" s="88" t="s"/>
-      <c r="J16" s="90">
+      <c r="I16" s="105" t="s"/>
+      <c r="J16" s="107">
         <f>=SUM(J10:J15)</f>
         <v>10</v>
       </c>
-      <c r="K16" s="91">
+      <c r="K16" s="108">
         <f>=SUM(A16:J16)</f>
         <v>850</v>
+      </c>
+      <c r="L16" s="195" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -5820,7 +6711,7 @@
   <sheetPr codeName="万菱广场">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K15"/>
+  <dimension ref="L15"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="9" width="10.6523" customWidth="1"/>
@@ -5828,114 +6719,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="110" t="s"/>
-      <c r="B1" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="54" t="s"/>
-      <c r="D1" s="94" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="54" t="s"/>
-      <c r="F1" s="94" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="54" t="s"/>
-      <c r="H1" s="94" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="54" t="s"/>
-      <c r="J1" s="94" t="s">
+      <c r="A1" s="130" t="s"/>
+      <c r="B1" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="54" t="s"/>
-      <c r="L1" s="95" t="s"/>
+      <c r="C1" s="67" t="s"/>
+      <c r="D1" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="67" t="s"/>
+      <c r="F1" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="67" t="s"/>
+      <c r="H1" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="67" t="s"/>
+      <c r="J1" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="67" t="s"/>
+      <c r="L1" s="112" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="115" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="97" t="s">
-        <v>58</v>
+      <c r="A2" s="135" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>63</v>
       </c>
       <c r="C2" s="44">
         <v>90</v>
       </c>
-      <c r="D2" s="97" t="s">
-        <v>58</v>
+      <c r="D2" s="52" t="s">
+        <v>63</v>
       </c>
       <c r="E2" s="44">
         <v>90</v>
       </c>
-      <c r="F2" s="97" t="s">
-        <v>58</v>
+      <c r="F2" s="52" t="s">
+        <v>63</v>
       </c>
       <c r="G2" s="44">
         <v>90</v>
       </c>
-      <c r="H2" s="97" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="98">
-        <v>90</v>
-      </c>
-      <c r="J2" s="116" t="s"/>
-      <c r="K2" s="117" t="s"/>
-      <c r="L2" s="118" t="s"/>
+      <c r="H2" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="114">
+        <v>90</v>
+      </c>
+      <c r="J2" s="136" t="s"/>
+      <c r="K2" s="137" t="s"/>
+      <c r="L2" s="138" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="119" t="s"/>
+      <c r="A3" s="139" t="s"/>
       <c r="B3" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C3" s="11">
         <v>90</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G3" s="11">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I3" s="10">
         <v>90</v>
       </c>
-      <c r="J3" s="120" t="s"/>
-      <c r="K3" s="118" t="s"/>
-      <c r="L3" s="65" t="s">
-        <v>44</v>
+      <c r="J3" s="140" t="s"/>
+      <c r="K3" s="138" t="s"/>
+      <c r="L3" s="78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="121" t="s"/>
-      <c r="B4" s="121" t="s"/>
-      <c r="C4" s="122" t="s"/>
-      <c r="D4" s="102" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="103">
-        <v>90</v>
-      </c>
-      <c r="F4" s="121" t="s"/>
-      <c r="G4" s="122" t="s"/>
-      <c r="H4" s="121" t="s"/>
-      <c r="I4" s="123" t="s"/>
-      <c r="J4" s="124" t="s"/>
-      <c r="K4" s="125" t="s"/>
-      <c r="L4" s="126">
+      <c r="A4" s="141" t="s"/>
+      <c r="B4" s="141" t="s"/>
+      <c r="C4" s="142" t="s"/>
+      <c r="D4" s="118" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="119">
+        <v>90</v>
+      </c>
+      <c r="F4" s="141" t="s"/>
+      <c r="G4" s="142" t="s"/>
+      <c r="H4" s="141" t="s"/>
+      <c r="I4" s="143" t="s"/>
+      <c r="J4" s="144" t="s"/>
+      <c r="K4" s="145" t="s"/>
+      <c r="L4" s="146">
         <f>=SUM(B2:K4)</f>
         <v>810</v>
       </c>
-      <c r="M4" s="71" t="s">
+      <c r="M4" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5973,28 +6864,28 @@
       <c r="K7" s="6" t="s"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="106" t="s">
+      <c r="A8" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="107" t="s">
+      <c r="B8" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="106" t="s">
+      <c r="C8" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="107" t="s">
+      <c r="D8" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="106" t="s">
+      <c r="E8" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="107" t="s">
+      <c r="F8" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="106" t="s">
+      <c r="G8" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="107" t="s">
+      <c r="H8" s="123" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="28" t="s">
@@ -6003,157 +6894,160 @@
       <c r="J8" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="108" t="s"/>
+      <c r="K8" s="124" t="s"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="92">
-        <v>90</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="92">
-        <v>90</v>
-      </c>
-      <c r="E9" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="92">
-        <v>90</v>
-      </c>
-      <c r="G9" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="92">
-        <v>90</v>
-      </c>
-      <c r="I9" s="109" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="149">
-        <v>90</v>
-      </c>
-      <c r="K9" s="86" t="s"/>
+      <c r="A9" s="125" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="109">
+        <v>90</v>
+      </c>
+      <c r="C9" s="125" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="109">
+        <v>90</v>
+      </c>
+      <c r="E9" s="125" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="109">
+        <v>90</v>
+      </c>
+      <c r="G9" s="125" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="109">
+        <v>90</v>
+      </c>
+      <c r="I9" s="125" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="101">
+        <v>90</v>
+      </c>
+      <c r="K9" s="102" t="s"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="92">
+        <v>64</v>
+      </c>
+      <c r="B10" s="109">
         <v>90</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="92">
+        <v>64</v>
+      </c>
+      <c r="D10" s="109">
         <v>90</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="92">
+        <v>64</v>
+      </c>
+      <c r="F10" s="109">
         <v>90</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="92">
+        <v>64</v>
+      </c>
+      <c r="H10" s="109">
         <v>90</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" s="86">
-        <v>90</v>
-      </c>
-      <c r="K10" s="86" t="s"/>
+        <v>64</v>
+      </c>
+      <c r="J10" s="102">
+        <v>90</v>
+      </c>
+      <c r="K10" s="102" t="s"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="28" t="s"/>
-      <c r="B11" s="92" t="s"/>
+      <c r="B11" s="109" t="s"/>
       <c r="C11" s="28" t="s"/>
-      <c r="D11" s="92" t="s"/>
+      <c r="D11" s="109" t="s"/>
       <c r="E11" s="28" t="s"/>
-      <c r="F11" s="92" t="s"/>
+      <c r="F11" s="109" t="s"/>
       <c r="G11" s="28" t="s"/>
-      <c r="H11" s="92" t="s"/>
-      <c r="I11" s="85" t="s"/>
-      <c r="J11" s="86" t="s"/>
-      <c r="K11" s="86" t="s"/>
+      <c r="H11" s="109" t="s"/>
+      <c r="I11" s="103" t="s"/>
+      <c r="J11" s="102" t="s"/>
+      <c r="K11" s="102" t="s"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="85" t="s"/>
-      <c r="B12" s="92" t="s"/>
-      <c r="C12" s="85" t="s"/>
-      <c r="D12" s="92" t="s"/>
-      <c r="E12" s="85" t="s"/>
-      <c r="F12" s="92" t="s"/>
-      <c r="G12" s="85" t="s"/>
-      <c r="H12" s="92" t="s"/>
-      <c r="I12" s="85" t="s"/>
-      <c r="J12" s="86" t="s"/>
-      <c r="K12" s="86" t="s"/>
+      <c r="A12" s="103" t="s"/>
+      <c r="B12" s="109" t="s"/>
+      <c r="C12" s="103" t="s"/>
+      <c r="D12" s="109" t="s"/>
+      <c r="E12" s="103" t="s"/>
+      <c r="F12" s="109" t="s"/>
+      <c r="G12" s="103" t="s"/>
+      <c r="H12" s="109" t="s"/>
+      <c r="I12" s="103" t="s"/>
+      <c r="J12" s="102" t="s"/>
+      <c r="K12" s="102" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="85" t="s"/>
-      <c r="B13" s="92" t="s"/>
-      <c r="C13" s="85" t="s"/>
-      <c r="D13" s="92" t="s"/>
-      <c r="E13" s="85" t="s"/>
-      <c r="F13" s="92" t="s"/>
-      <c r="G13" s="85" t="s"/>
-      <c r="H13" s="92" t="s"/>
-      <c r="I13" s="85" t="s"/>
-      <c r="J13" s="86" t="s"/>
-      <c r="K13" s="86" t="s"/>
+      <c r="A13" s="103" t="s"/>
+      <c r="B13" s="109" t="s"/>
+      <c r="C13" s="103" t="s"/>
+      <c r="D13" s="109" t="s"/>
+      <c r="E13" s="103" t="s"/>
+      <c r="F13" s="109" t="s"/>
+      <c r="G13" s="103" t="s"/>
+      <c r="H13" s="109" t="s"/>
+      <c r="I13" s="103" t="s"/>
+      <c r="J13" s="102" t="s"/>
+      <c r="K13" s="102" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="85" t="s"/>
-      <c r="B14" s="92" t="s"/>
-      <c r="C14" s="85" t="s"/>
-      <c r="D14" s="92" t="s"/>
-      <c r="E14" s="85" t="s"/>
-      <c r="F14" s="92" t="s"/>
-      <c r="G14" s="85" t="s"/>
-      <c r="H14" s="92" t="s"/>
-      <c r="I14" s="152" t="s"/>
-      <c r="J14" s="153" t="s"/>
-      <c r="K14" s="87" t="s">
+      <c r="A14" s="103" t="s"/>
+      <c r="B14" s="109" t="s"/>
+      <c r="C14" s="103" t="s"/>
+      <c r="D14" s="109" t="s"/>
+      <c r="E14" s="103" t="s"/>
+      <c r="F14" s="109" t="s"/>
+      <c r="G14" s="103" t="s"/>
+      <c r="H14" s="109" t="s"/>
+      <c r="I14" s="126" t="s"/>
+      <c r="J14" s="127" t="s"/>
+      <c r="K14" s="104" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="88" t="s"/>
-      <c r="B15" s="89">
+    <row r="15" spans="1:12">
+      <c r="A15" s="105" t="s"/>
+      <c r="B15" s="106">
         <f>=SUM(B9:B14)</f>
         <v>180</v>
       </c>
-      <c r="C15" s="88" t="s"/>
-      <c r="D15" s="89">
+      <c r="C15" s="105" t="s"/>
+      <c r="D15" s="106">
         <f>=SUM(D9:D14)</f>
         <v>180</v>
       </c>
-      <c r="E15" s="88" t="s"/>
-      <c r="F15" s="89">
+      <c r="E15" s="105" t="s"/>
+      <c r="F15" s="106">
         <f>=SUM(F9:F14)</f>
         <v>180</v>
       </c>
-      <c r="G15" s="88" t="s"/>
-      <c r="H15" s="89">
+      <c r="G15" s="105" t="s"/>
+      <c r="H15" s="106">
         <f>=SUM(H9:H14)</f>
         <v>180</v>
       </c>
-      <c r="I15" s="154" t="s"/>
-      <c r="J15" s="155">
+      <c r="I15" s="128" t="s"/>
+      <c r="J15" s="129">
         <f>=SUM(J9:J14)</f>
         <v>180</v>
       </c>
-      <c r="K15" s="91">
+      <c r="K15" s="108">
         <f>=SUM(A15:J15)</f>
         <v>900</v>
+      </c>
+      <c r="L15" s="195" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -6180,120 +7074,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="110" t="s"/>
-      <c r="B1" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="127" t="s"/>
-      <c r="D1" s="94" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="127" t="s"/>
-      <c r="F1" s="94" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="127" t="s"/>
-      <c r="H1" s="128" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="129" t="s"/>
-      <c r="J1" s="94" t="s">
+      <c r="A1" s="130" t="s"/>
+      <c r="B1" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="127" t="s"/>
-      <c r="L1" s="130" t="s"/>
+      <c r="C1" s="147" t="s"/>
+      <c r="D1" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="147" t="s"/>
+      <c r="F1" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="147" t="s"/>
+      <c r="H1" s="148" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="149" t="s"/>
+      <c r="J1" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="147" t="s"/>
+      <c r="L1" s="150" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="131" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="97" t="s">
-        <v>62</v>
+      <c r="A2" s="151" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>67</v>
       </c>
       <c r="C2" s="44">
         <v>90</v>
       </c>
-      <c r="D2" s="97" t="s">
-        <v>62</v>
+      <c r="D2" s="52" t="s">
+        <v>67</v>
       </c>
       <c r="E2" s="44">
         <v>90</v>
       </c>
-      <c r="F2" s="97" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="98">
-        <v>90</v>
-      </c>
-      <c r="H2" s="97" t="s">
-        <v>62</v>
+      <c r="F2" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="114">
+        <v>90</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>67</v>
       </c>
       <c r="I2" s="44">
         <v>45</v>
       </c>
-      <c r="J2" s="54" t="s"/>
-      <c r="K2" s="54" t="s"/>
-      <c r="L2" s="95" t="s"/>
+      <c r="J2" s="67" t="s"/>
+      <c r="K2" s="67" t="s"/>
+      <c r="L2" s="112" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="119" t="s"/>
-      <c r="B3" s="119" t="s"/>
-      <c r="C3" s="132" t="s"/>
+      <c r="A3" s="139" t="s"/>
+      <c r="B3" s="139" t="s"/>
+      <c r="C3" s="152" t="s"/>
       <c r="D3" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G3" s="10">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I3" s="11">
         <v>45</v>
       </c>
-      <c r="L3" s="99" t="s"/>
+      <c r="L3" s="115" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="119" t="s"/>
-      <c r="B4" s="119" t="s"/>
-      <c r="C4" s="132" t="s"/>
+      <c r="A4" s="139" t="s"/>
+      <c r="B4" s="139" t="s"/>
+      <c r="C4" s="152" t="s"/>
       <c r="D4" s="9" t="s"/>
       <c r="E4" s="11" t="s"/>
-      <c r="F4" s="119" t="s"/>
-      <c r="G4" s="133" t="s"/>
+      <c r="F4" s="139" t="s"/>
+      <c r="G4" s="153" t="s"/>
       <c r="H4" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I4" s="11">
         <v>20</v>
       </c>
-      <c r="L4" s="65" t="s">
-        <v>44</v>
+      <c r="L4" s="78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="121" t="s"/>
-      <c r="B5" s="121" t="s"/>
-      <c r="C5" s="122" t="s"/>
-      <c r="D5" s="121" t="s"/>
-      <c r="E5" s="122" t="s"/>
-      <c r="F5" s="121" t="s"/>
-      <c r="G5" s="123" t="s"/>
-      <c r="H5" s="102" t="s"/>
-      <c r="I5" s="103" t="s"/>
-      <c r="J5" s="134" t="s"/>
-      <c r="K5" s="134" t="s"/>
-      <c r="L5" s="105">
+      <c r="A5" s="141" t="s"/>
+      <c r="B5" s="141" t="s"/>
+      <c r="C5" s="142" t="s"/>
+      <c r="D5" s="141" t="s"/>
+      <c r="E5" s="142" t="s"/>
+      <c r="F5" s="141" t="s"/>
+      <c r="G5" s="143" t="s"/>
+      <c r="H5" s="118" t="s"/>
+      <c r="I5" s="119" t="s"/>
+      <c r="J5" s="154" t="s"/>
+      <c r="K5" s="154" t="s"/>
+      <c r="L5" s="121">
         <f>=SUM(B2:K5)</f>
         <v>560</v>
       </c>
-      <c r="M5" s="71" t="s">
+      <c r="M5" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6313,7 +7207,7 @@
   <sheetPr codeName="和业广场">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K16"/>
+  <dimension ref="L16"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="11" width="10.793" customWidth="1"/>
@@ -6321,136 +7215,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="110" t="s"/>
-      <c r="B1" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="127" t="s"/>
-      <c r="D1" s="94" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="127" t="s"/>
-      <c r="F1" s="94" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="127" t="s"/>
-      <c r="H1" s="94" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="127" t="s"/>
-      <c r="J1" s="94" t="s">
+      <c r="A1" s="130" t="s"/>
+      <c r="B1" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="127" t="s"/>
-      <c r="L1" s="130" t="s"/>
+      <c r="C1" s="147" t="s"/>
+      <c r="D1" s="111" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="147" t="s"/>
+      <c r="F1" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="147" t="s"/>
+      <c r="H1" s="111" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="147" t="s"/>
+      <c r="J1" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="147" t="s"/>
+      <c r="L1" s="150" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="113" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="97" t="s">
-        <v>67</v>
+      <c r="A2" s="133" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>72</v>
       </c>
       <c r="C2" s="44">
         <v>90</v>
       </c>
-      <c r="D2" s="97" t="s">
-        <v>67</v>
+      <c r="D2" s="52" t="s">
+        <v>72</v>
       </c>
       <c r="E2" s="44">
         <v>90</v>
       </c>
-      <c r="F2" s="97" t="s">
-        <v>67</v>
+      <c r="F2" s="52" t="s">
+        <v>72</v>
       </c>
       <c r="G2" s="44">
         <v>90</v>
       </c>
-      <c r="H2" s="97" t="s">
-        <v>67</v>
+      <c r="H2" s="52" t="s">
+        <v>72</v>
       </c>
       <c r="I2" s="44">
         <v>90</v>
       </c>
-      <c r="J2" s="135" t="s"/>
-      <c r="K2" s="136" t="s"/>
-      <c r="L2" s="99" t="s"/>
+      <c r="J2" s="155" t="s"/>
+      <c r="K2" s="156" t="s"/>
+      <c r="L2" s="115" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="119" t="s"/>
+      <c r="A3" s="139" t="s"/>
       <c r="B3" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C3" s="11">
         <v>90</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G3" s="11">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I3" s="11">
         <v>90</v>
       </c>
-      <c r="J3" s="119" t="s"/>
-      <c r="K3" s="133" t="s"/>
-      <c r="L3" s="99" t="s"/>
+      <c r="J3" s="139" t="s"/>
+      <c r="K3" s="153" t="s"/>
+      <c r="L3" s="115" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="119" t="s"/>
-      <c r="B4" s="119" t="s"/>
-      <c r="C4" s="132" t="s"/>
-      <c r="D4" s="119" t="s"/>
-      <c r="E4" s="132" t="s"/>
+      <c r="A4" s="139" t="s"/>
+      <c r="B4" s="139" t="s"/>
+      <c r="C4" s="152" t="s"/>
+      <c r="D4" s="139" t="s"/>
+      <c r="E4" s="152" t="s"/>
       <c r="F4" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G4" s="11">
         <v>90</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I4" s="11">
         <v>90</v>
       </c>
-      <c r="J4" s="119" t="s"/>
-      <c r="K4" s="133" t="s"/>
-      <c r="L4" s="65" t="s">
-        <v>44</v>
+      <c r="J4" s="139" t="s"/>
+      <c r="K4" s="153" t="s"/>
+      <c r="L4" s="78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="121" t="s"/>
-      <c r="B5" s="121" t="s"/>
-      <c r="C5" s="122" t="s"/>
-      <c r="D5" s="121" t="s"/>
-      <c r="E5" s="122" t="s"/>
-      <c r="F5" s="121" t="s"/>
-      <c r="G5" s="122" t="s"/>
-      <c r="H5" s="102" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" s="103">
+      <c r="A5" s="141" t="s"/>
+      <c r="B5" s="141" t="s"/>
+      <c r="C5" s="142" t="s"/>
+      <c r="D5" s="141" t="s"/>
+      <c r="E5" s="142" t="s"/>
+      <c r="F5" s="141" t="s"/>
+      <c r="G5" s="142" t="s"/>
+      <c r="H5" s="118" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="119">
         <v>10</v>
       </c>
-      <c r="J5" s="121" t="s"/>
-      <c r="K5" s="123" t="s"/>
-      <c r="L5" s="105">
+      <c r="J5" s="141" t="s"/>
+      <c r="K5" s="143" t="s"/>
+      <c r="L5" s="121">
         <f>=SUM(B2:K5)</f>
         <v>910</v>
       </c>
-      <c r="M5" s="71" t="s">
+      <c r="M5" s="84" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6488,211 +7382,214 @@
       <c r="K8" s="6" t="s"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="106" t="s">
+      <c r="A9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="107" t="s">
+      <c r="B9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="106" t="s">
+      <c r="C9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="107" t="s">
+      <c r="D9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="107" t="s">
+      <c r="F9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="106" t="s">
+      <c r="G9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="107" t="s">
+      <c r="H9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="106" t="s">
+      <c r="I9" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="108" t="s">
+      <c r="J9" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="108" t="s"/>
+      <c r="K9" s="124" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="137">
-        <v>90</v>
-      </c>
-      <c r="C10" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="137">
-        <v>90</v>
-      </c>
-      <c r="E10" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="137">
-        <v>60</v>
-      </c>
-      <c r="G10" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="137">
-        <v>60</v>
-      </c>
-      <c r="I10" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="137">
-        <v>60</v>
-      </c>
-      <c r="K10" s="86" t="s"/>
+      <c r="A10" s="125" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="157">
+        <v>90</v>
+      </c>
+      <c r="C10" s="125" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="157">
+        <v>90</v>
+      </c>
+      <c r="E10" s="125" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="157">
+        <v>60</v>
+      </c>
+      <c r="G10" s="125" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="157">
+        <v>60</v>
+      </c>
+      <c r="I10" s="125" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="157">
+        <v>60</v>
+      </c>
+      <c r="K10" s="102" t="s"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B11" s="30">
         <v>90</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D11" s="30">
         <v>90</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F11" s="30">
         <v>90</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H11" s="30">
         <v>90</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J11" s="30">
         <v>90</v>
       </c>
-      <c r="K11" s="86" t="s"/>
+      <c r="K11" s="102" t="s"/>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="28" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B12" s="30">
         <v>90</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D12" s="30">
         <v>90</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F12" s="30">
         <v>60</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H12" s="30">
         <v>60</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J12" s="30">
         <v>60</v>
       </c>
-      <c r="K12" s="86" t="s"/>
+      <c r="K12" s="102" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="85" t="s"/>
-      <c r="B13" s="92" t="s"/>
-      <c r="C13" s="85" t="s"/>
-      <c r="D13" s="92" t="s"/>
-      <c r="E13" s="85" t="s"/>
-      <c r="F13" s="92" t="s"/>
-      <c r="G13" s="85" t="s"/>
-      <c r="H13" s="92" t="s"/>
-      <c r="I13" s="85" t="s">
-        <v>87</v>
-      </c>
-      <c r="J13" s="86">
-        <v>60</v>
-      </c>
-      <c r="K13" s="86" t="s"/>
+      <c r="A13" s="103" t="s"/>
+      <c r="B13" s="109" t="s"/>
+      <c r="C13" s="103" t="s"/>
+      <c r="D13" s="109" t="s"/>
+      <c r="E13" s="103" t="s"/>
+      <c r="F13" s="109" t="s"/>
+      <c r="G13" s="103" t="s"/>
+      <c r="H13" s="109" t="s"/>
+      <c r="I13" s="103" t="s">
+        <v>75</v>
+      </c>
+      <c r="J13" s="102">
+        <v>60</v>
+      </c>
+      <c r="K13" s="102" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="85" t="s"/>
-      <c r="B14" s="92" t="s"/>
-      <c r="C14" s="85" t="s"/>
-      <c r="D14" s="92" t="s"/>
-      <c r="E14" s="85" t="s"/>
-      <c r="F14" s="92" t="s"/>
-      <c r="G14" s="85" t="s"/>
-      <c r="H14" s="92" t="s"/>
-      <c r="I14" s="85" t="s"/>
-      <c r="J14" s="86" t="s"/>
-      <c r="K14" s="86" t="s"/>
+      <c r="A14" s="103" t="s"/>
+      <c r="B14" s="109" t="s"/>
+      <c r="C14" s="103" t="s"/>
+      <c r="D14" s="109" t="s"/>
+      <c r="E14" s="103" t="s"/>
+      <c r="F14" s="109" t="s"/>
+      <c r="G14" s="103" t="s"/>
+      <c r="H14" s="109" t="s"/>
+      <c r="I14" s="103" t="s"/>
+      <c r="J14" s="102" t="s"/>
+      <c r="K14" s="102" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="85" t="s"/>
-      <c r="B15" s="92" t="s"/>
-      <c r="C15" s="85" t="s"/>
-      <c r="D15" s="92" t="s"/>
-      <c r="E15" s="85" t="s"/>
-      <c r="F15" s="92" t="s"/>
-      <c r="G15" s="85" t="s"/>
-      <c r="H15" s="92" t="s"/>
-      <c r="I15" s="85" t="s"/>
-      <c r="J15" s="86" t="s"/>
-      <c r="K15" s="87" t="s">
+      <c r="A15" s="103" t="s"/>
+      <c r="B15" s="109" t="s"/>
+      <c r="C15" s="103" t="s"/>
+      <c r="D15" s="109" t="s"/>
+      <c r="E15" s="103" t="s"/>
+      <c r="F15" s="109" t="s"/>
+      <c r="G15" s="103" t="s"/>
+      <c r="H15" s="109" t="s"/>
+      <c r="I15" s="103" t="s"/>
+      <c r="J15" s="102" t="s"/>
+      <c r="K15" s="104" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="88" t="s"/>
-      <c r="B16" s="89">
+    <row r="16" spans="1:12">
+      <c r="A16" s="105" t="s"/>
+      <c r="B16" s="106">
         <f>=SUM(B10:B15)</f>
         <v>270</v>
       </c>
-      <c r="C16" s="88" t="s"/>
-      <c r="D16" s="89">
+      <c r="C16" s="105" t="s"/>
+      <c r="D16" s="106">
         <f>=SUM(D10:D15)</f>
         <v>270</v>
       </c>
-      <c r="E16" s="88" t="s"/>
-      <c r="F16" s="89">
+      <c r="E16" s="105" t="s"/>
+      <c r="F16" s="106">
         <f>=SUM(F10:F15)</f>
         <v>210</v>
       </c>
-      <c r="G16" s="88" t="s"/>
-      <c r="H16" s="89">
+      <c r="G16" s="105" t="s"/>
+      <c r="H16" s="106">
         <f>=SUM(H10:H15)</f>
         <v>210</v>
       </c>
-      <c r="I16" s="88" t="s"/>
-      <c r="J16" s="90">
+      <c r="I16" s="105" t="s"/>
+      <c r="J16" s="107">
         <f>=SUM(J10:J15)</f>
         <v>270</v>
       </c>
-      <c r="K16" s="91">
+      <c r="K16" s="108">
         <f>=SUM(A16:J16)</f>
         <v>1230</v>
+      </c>
+      <c r="L16" s="195" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -329,7 +329,7 @@
     <numFmt numFmtId="300" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="301" formatCode="m&quot;月&quot;d&quot;号&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Microsoft YaHei"/>
     </font>
@@ -368,8 +368,9 @@
     <font>
       <name val="Microsoft YaHei"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,8 +446,9 @@
         <bgColor rgb="FFF4B183"/>
       </patternFill>
     </fill>
+    <fill/>
   </fills>
-  <borders count="34">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -660,13 +662,110 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <top/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+    </border>
+    <border>
+      <left/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <top/>
+    </border>
   </borders>
   <cellStyleXfs>
     <xf fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1293,6 +1392,126 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0">
       <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="16" borderId="2" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="16" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="16" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="34" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="35" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="36" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="37" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="38" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="39" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="40" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="39" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="41" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="42" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="43" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="44" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="45" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="1" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="2" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="46" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="47" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="6" borderId="3" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="5" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="31" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="5" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="7" fillId="6" borderId="31" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="13" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="14" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="48" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="37" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="6" borderId="15" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="7" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="5" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="8" fillId="7" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="7" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="31" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="31" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="7" fillId="7" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -3796,323 +4015,406 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="广州交易广场"/>
-  <dimension ref="K26"/>
+  <dimension ref="K27"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="149" t="s"/>
-      <c r="B1" s="142" t="s"/>
-      <c r="C1" s="166" t="s"/>
-      <c r="D1" s="142" t="s"/>
-      <c r="E1" s="166" t="s"/>
-      <c r="F1" s="142" t="s"/>
-      <c r="G1" s="166" t="s"/>
-      <c r="H1" s="142" t="s"/>
-      <c r="I1" s="166" t="s"/>
-      <c r="J1" s="142" t="s">
-        <v>95</v>
-      </c>
-      <c r="K1" s="166" t="s"/>
-      <c r="L1" s="169" t="s"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="198" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="53" t="s"/>
-      <c r="C2" s="54" t="s"/>
-      <c r="D2" s="53" t="s"/>
-      <c r="E2" s="54" t="s"/>
-      <c r="F2" s="53" t="s"/>
-      <c r="G2" s="54" t="s"/>
-      <c r="H2" s="53" t="s"/>
-      <c r="I2" s="54" t="s"/>
-      <c r="J2" s="149" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B1" s="209" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4">
+        <v>46203</v>
+      </c>
+      <c r="D1" s="209" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4">
+        <v>46204</v>
+      </c>
+      <c r="F1" s="209" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4">
+        <v>46205</v>
+      </c>
+      <c r="H1" s="209" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="4">
+        <v>46206</v>
+      </c>
+      <c r="J1" s="210" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="6" t="s"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="211" t="s"/>
+      <c r="B2" s="212" t="s"/>
+      <c r="C2" s="213" t="s"/>
+      <c r="D2" s="212" t="s"/>
+      <c r="E2" s="213" t="s"/>
+      <c r="F2" s="212" t="s"/>
+      <c r="G2" s="213" t="s"/>
+      <c r="H2" s="212" t="s"/>
+      <c r="I2" s="246" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="199">
-        <v>90</v>
-      </c>
-      <c r="L2" s="200" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="201" t="s"/>
-      <c r="B3" s="39" t="s"/>
-      <c r="C3" s="41" t="s"/>
-      <c r="D3" s="39" t="s"/>
-      <c r="E3" s="41" t="s"/>
-      <c r="F3" s="39" t="s"/>
-      <c r="G3" s="41" t="s"/>
-      <c r="H3" s="39" t="s"/>
-      <c r="I3" s="41" t="s"/>
-      <c r="J3" s="201" t="s"/>
-      <c r="K3" s="202" t="s"/>
-      <c r="L3" s="200" t="s"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="201" t="s"/>
-      <c r="B4" s="201" t="s"/>
-      <c r="C4" s="203" t="s"/>
-      <c r="D4" s="201" t="s"/>
-      <c r="E4" s="203" t="s"/>
-      <c r="F4" s="39" t="s"/>
-      <c r="G4" s="41" t="s"/>
-      <c r="H4" s="39" t="s"/>
-      <c r="I4" s="41" t="s"/>
-      <c r="J4" s="201" t="s"/>
-      <c r="K4" s="202" t="s"/>
-      <c r="L4" s="105" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="204" t="s"/>
-      <c r="B5" s="204" t="s"/>
-      <c r="C5" s="205" t="s"/>
-      <c r="D5" s="204" t="s"/>
-      <c r="E5" s="205" t="s"/>
-      <c r="F5" s="204" t="s"/>
-      <c r="G5" s="205" t="s"/>
-      <c r="H5" s="63" t="s"/>
-      <c r="I5" s="65" t="s"/>
-      <c r="J5" s="204" t="s"/>
-      <c r="K5" s="206" t="s"/>
-      <c r="L5" s="207">
-        <f>=SUM(B2:K5)</f>
-        <v>90</v>
-      </c>
-      <c r="M5" s="135" t="s"/>
+      <c r="J2" s="247">
+        <v>90</v>
+      </c>
+      <c r="K2" s="215" t="s"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="39" t="s"/>
+      <c r="B3" s="216" t="s"/>
+      <c r="C3" s="217" t="s"/>
+      <c r="D3" s="216" t="s"/>
+      <c r="E3" s="217" t="s"/>
+      <c r="F3" s="216" t="s"/>
+      <c r="G3" s="217" t="s"/>
+      <c r="H3" s="216" t="s"/>
+      <c r="I3" s="217" t="s"/>
+      <c r="J3" s="218" t="s"/>
+      <c r="K3" s="219" t="s"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="39" t="s"/>
+      <c r="B4" s="216" t="s"/>
+      <c r="C4" s="217" t="s"/>
+      <c r="D4" s="216" t="s"/>
+      <c r="E4" s="217" t="s"/>
+      <c r="F4" s="216" t="s"/>
+      <c r="G4" s="217" t="s"/>
+      <c r="H4" s="216" t="s"/>
+      <c r="I4" s="220" t="s"/>
+      <c r="J4" s="218" t="s"/>
+      <c r="K4" s="219" t="s"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="221" t="s"/>
+      <c r="B5" s="222" t="s"/>
+      <c r="C5" s="223" t="s"/>
+      <c r="D5" s="222" t="s"/>
+      <c r="E5" s="223" t="s"/>
+      <c r="F5" s="222" t="s"/>
+      <c r="G5" s="223" t="s"/>
+      <c r="H5" s="222" t="s"/>
+      <c r="I5" s="223" t="s"/>
+      <c r="J5" s="224" t="s"/>
+      <c r="K5" s="225" t="s"/>
+      <c r="L5" s="248" t="s"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="129" t="s"/>
+      <c r="B6" s="136" t="s"/>
+      <c r="C6" s="129" t="s"/>
+      <c r="D6" s="136" t="s"/>
+      <c r="E6" s="129" t="s"/>
+      <c r="F6" s="136" t="s"/>
+      <c r="G6" s="129" t="s"/>
+      <c r="H6" s="136" t="s"/>
+      <c r="I6" s="129" t="s"/>
+      <c r="J6" s="128" t="s"/>
+      <c r="K6" s="128" t="s"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="129" t="s"/>
+      <c r="B7" s="136" t="s"/>
+      <c r="C7" s="129" t="s"/>
+      <c r="D7" s="136" t="s"/>
+      <c r="E7" s="129" t="s"/>
+      <c r="F7" s="136" t="s"/>
+      <c r="G7" s="129" t="s"/>
+      <c r="H7" s="136" t="s"/>
+      <c r="I7" s="137" t="s"/>
+      <c r="J7" s="138" t="s"/>
+      <c r="K7" s="130" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="4" t="s"/>
-      <c r="B8" s="5" t="s"/>
-      <c r="C8" s="4" t="s"/>
-      <c r="D8" s="5" t="s"/>
-      <c r="E8" s="4" t="s"/>
-      <c r="F8" s="5" t="s"/>
-      <c r="G8" s="4" t="s"/>
-      <c r="H8" s="5" t="s"/>
-      <c r="I8" s="4" t="s"/>
-      <c r="J8" s="6" t="s"/>
-      <c r="K8" s="6" t="s"/>
+      <c r="A8" s="226" t="s"/>
+      <c r="B8" s="227">
+        <f>=SUM(B2:B7)</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="226" t="s"/>
+      <c r="D8" s="227">
+        <f>=SUM(D2:D7)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="226" t="s"/>
+      <c r="F8" s="227">
+        <f>=SUM(F2:F7)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="226" t="s"/>
+      <c r="H8" s="227">
+        <f>=SUM(H2:H7)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="228" t="s"/>
+      <c r="J8" s="229">
+        <f>=SUM(J2:J7)</f>
+        <v>90</v>
+      </c>
+      <c r="K8" s="230">
+        <f>=SUM(A8:J8)</f>
+        <v>90</v>
+      </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="63" t="s"/>
-      <c r="B9" s="64" t="s"/>
-      <c r="C9" s="63" t="s"/>
-      <c r="D9" s="64" t="s"/>
-      <c r="E9" s="63" t="s"/>
-      <c r="F9" s="64" t="s"/>
-      <c r="G9" s="63" t="s"/>
-      <c r="H9" s="64" t="s"/>
-      <c r="I9" s="63" t="s"/>
-      <c r="J9" s="65" t="s"/>
-      <c r="K9" s="65" t="s"/>
+      <c r="A9" s="240" t="s"/>
+      <c r="B9" s="240" t="s"/>
+      <c r="C9" s="240" t="s"/>
+      <c r="D9" s="240" t="s"/>
+      <c r="E9" s="240" t="s"/>
+      <c r="F9" s="240" t="s"/>
+      <c r="G9" s="240" t="s"/>
+      <c r="H9" s="240" t="s"/>
+      <c r="I9" s="240" t="s"/>
+      <c r="J9" s="240" t="s"/>
+      <c r="K9" s="240" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="53" t="s"/>
-      <c r="B10" s="54" t="s"/>
-      <c r="C10" s="53" t="s"/>
-      <c r="D10" s="54" t="s"/>
-      <c r="E10" s="53" t="s"/>
-      <c r="F10" s="54" t="s"/>
-      <c r="G10" s="53" t="s"/>
-      <c r="H10" s="54" t="s"/>
-      <c r="I10" s="53" t="s"/>
-      <c r="J10" s="54" t="s"/>
-      <c r="K10" s="128" t="s"/>
+      <c r="A10" s="240" t="s"/>
+      <c r="B10" s="240" t="s"/>
+      <c r="C10" s="240" t="s"/>
+      <c r="D10" s="240" t="s"/>
+      <c r="E10" s="240" t="s"/>
+      <c r="F10" s="240" t="s"/>
+      <c r="G10" s="240" t="s"/>
+      <c r="H10" s="240" t="s"/>
+      <c r="I10" s="240" t="s"/>
+      <c r="J10" s="240" t="s"/>
+      <c r="K10" s="241" t="s"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="39" t="s"/>
-      <c r="B11" s="41" t="s"/>
-      <c r="C11" s="39" t="s"/>
-      <c r="D11" s="41" t="s"/>
-      <c r="E11" s="39" t="s"/>
-      <c r="F11" s="41" t="s"/>
-      <c r="G11" s="39" t="s"/>
-      <c r="H11" s="41" t="s"/>
-      <c r="I11" s="39" t="s"/>
-      <c r="J11" s="41" t="s"/>
-      <c r="K11" s="128" t="s"/>
+      <c r="A11" s="240" t="s"/>
+      <c r="B11" s="240" t="s"/>
+      <c r="C11" s="240" t="s"/>
+      <c r="D11" s="240" t="s"/>
+      <c r="E11" s="240" t="s"/>
+      <c r="F11" s="240" t="s"/>
+      <c r="G11" s="240" t="s"/>
+      <c r="H11" s="240" t="s"/>
+      <c r="I11" s="240" t="s"/>
+      <c r="J11" s="240" t="s"/>
+      <c r="K11" s="241" t="s"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="39" t="s"/>
-      <c r="B12" s="41" t="s"/>
-      <c r="C12" s="39" t="s"/>
-      <c r="D12" s="41" t="s"/>
-      <c r="E12" s="39" t="s"/>
-      <c r="F12" s="41" t="s"/>
-      <c r="G12" s="39" t="s"/>
-      <c r="H12" s="41" t="s"/>
-      <c r="I12" s="39" t="s"/>
-      <c r="J12" s="41" t="s"/>
-      <c r="K12" s="128" t="s"/>
+      <c r="A12" s="240" t="s"/>
+      <c r="B12" s="240" t="s"/>
+      <c r="C12" s="240" t="s"/>
+      <c r="D12" s="240" t="s"/>
+      <c r="E12" s="240" t="s"/>
+      <c r="F12" s="240" t="s"/>
+      <c r="G12" s="240" t="s"/>
+      <c r="H12" s="240" t="s"/>
+      <c r="I12" s="240" t="s"/>
+      <c r="J12" s="240" t="s"/>
+      <c r="K12" s="241" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="129" t="s"/>
-      <c r="B13" s="136" t="s"/>
-      <c r="C13" s="129" t="s"/>
-      <c r="D13" s="136" t="s"/>
-      <c r="E13" s="129" t="s"/>
-      <c r="F13" s="136" t="s"/>
-      <c r="G13" s="129" t="s"/>
-      <c r="H13" s="136" t="s"/>
-      <c r="I13" s="129" t="s"/>
-      <c r="J13" s="128" t="s"/>
-      <c r="K13" s="128" t="s"/>
+      <c r="A13" s="241" t="s"/>
+      <c r="B13" s="244" t="s"/>
+      <c r="C13" s="241" t="s"/>
+      <c r="D13" s="244" t="s"/>
+      <c r="E13" s="241" t="s"/>
+      <c r="F13" s="244" t="s"/>
+      <c r="G13" s="241" t="s"/>
+      <c r="H13" s="244" t="s"/>
+      <c r="I13" s="241" t="s"/>
+      <c r="J13" s="241" t="s"/>
+      <c r="K13" s="241" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="129" t="s"/>
-      <c r="B14" s="136" t="s"/>
-      <c r="C14" s="129" t="s"/>
-      <c r="D14" s="136" t="s"/>
-      <c r="E14" s="129" t="s"/>
-      <c r="F14" s="136" t="s"/>
-      <c r="G14" s="129" t="s"/>
-      <c r="H14" s="136" t="s"/>
-      <c r="I14" s="129" t="s"/>
-      <c r="J14" s="128" t="s"/>
-      <c r="K14" s="128" t="s"/>
+      <c r="A14" s="241" t="s"/>
+      <c r="B14" s="244" t="s"/>
+      <c r="C14" s="241" t="s"/>
+      <c r="D14" s="244" t="s"/>
+      <c r="E14" s="241" t="s"/>
+      <c r="F14" s="244" t="s"/>
+      <c r="G14" s="241" t="s"/>
+      <c r="H14" s="244" t="s"/>
+      <c r="I14" s="241" t="s"/>
+      <c r="J14" s="241" t="s"/>
+      <c r="K14" s="241" t="s"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="129" t="s"/>
-      <c r="B15" s="136" t="s"/>
-      <c r="C15" s="129" t="s"/>
-      <c r="D15" s="136" t="s"/>
-      <c r="E15" s="129" t="s"/>
-      <c r="F15" s="136" t="s"/>
-      <c r="G15" s="129" t="s"/>
-      <c r="H15" s="136" t="s"/>
-      <c r="I15" s="129" t="s"/>
-      <c r="J15" s="128" t="s"/>
-      <c r="K15" s="130" t="s"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="131" t="s"/>
-      <c r="B16" s="132" t="s"/>
-      <c r="C16" s="131" t="s"/>
-      <c r="D16" s="132" t="s"/>
-      <c r="E16" s="131" t="s"/>
-      <c r="F16" s="132" t="s"/>
-      <c r="G16" s="131" t="s"/>
-      <c r="H16" s="132" t="s"/>
-      <c r="I16" s="131" t="s"/>
-      <c r="J16" s="133" t="s"/>
-      <c r="K16" s="134" t="s"/>
-      <c r="L16" s="135" t="s"/>
+      <c r="A15" s="241" t="s"/>
+      <c r="B15" s="244" t="s"/>
+      <c r="C15" s="241" t="s"/>
+      <c r="D15" s="244" t="s"/>
+      <c r="E15" s="241" t="s"/>
+      <c r="F15" s="244" t="s"/>
+      <c r="G15" s="241" t="s"/>
+      <c r="H15" s="244" t="s"/>
+      <c r="I15" s="241" t="s"/>
+      <c r="J15" s="241" t="s"/>
+      <c r="K15" s="241" t="s"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="241" t="s"/>
+      <c r="B16" s="241" t="s"/>
+      <c r="C16" s="241" t="s"/>
+      <c r="D16" s="241" t="s"/>
+      <c r="E16" s="241" t="s"/>
+      <c r="F16" s="241" t="s"/>
+      <c r="G16" s="241" t="s"/>
+      <c r="H16" s="241" t="s"/>
+      <c r="I16" s="241" t="s"/>
+      <c r="J16" s="241" t="s"/>
+      <c r="K16" s="241" t="s"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="242" t="s"/>
+      <c r="B17" s="242" t="s"/>
+      <c r="C17" s="242" t="s"/>
+      <c r="D17" s="242" t="s"/>
+      <c r="E17" s="242" t="s"/>
+      <c r="F17" s="242" t="s"/>
+      <c r="G17" s="242" t="s"/>
+      <c r="H17" s="242" t="s"/>
+      <c r="I17" s="242" t="s"/>
+      <c r="J17" s="242" t="s"/>
+      <c r="K17" s="242" t="s"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="242" t="s"/>
+      <c r="B18" s="242" t="s"/>
+      <c r="C18" s="242" t="s"/>
+      <c r="D18" s="242" t="s"/>
+      <c r="E18" s="242" t="s"/>
+      <c r="F18" s="242" t="s"/>
+      <c r="G18" s="242" t="s"/>
+      <c r="H18" s="242" t="s"/>
+      <c r="I18" s="242" t="s"/>
+      <c r="J18" s="242" t="s"/>
+      <c r="K18" s="242" t="s"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="4" t="s"/>
-      <c r="B19" s="5" t="s"/>
-      <c r="C19" s="4" t="s"/>
-      <c r="D19" s="5" t="s"/>
-      <c r="E19" s="4" t="s"/>
-      <c r="F19" s="5" t="s"/>
-      <c r="G19" s="4" t="s"/>
-      <c r="H19" s="5" t="s"/>
-      <c r="I19" s="4" t="s"/>
-      <c r="J19" s="6" t="s"/>
-      <c r="K19" s="6" t="s"/>
+      <c r="A19" s="243" t="s"/>
+      <c r="B19" s="243" t="s"/>
+      <c r="C19" s="243" t="s"/>
+      <c r="D19" s="243" t="s"/>
+      <c r="E19" s="243" t="s"/>
+      <c r="F19" s="243" t="s"/>
+      <c r="G19" s="243" t="s"/>
+      <c r="H19" s="243" t="s"/>
+      <c r="I19" s="243" t="s"/>
+      <c r="J19" s="243" t="s"/>
+      <c r="K19" s="243" t="s"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="63" t="s"/>
-      <c r="B20" s="64" t="s"/>
-      <c r="C20" s="63" t="s"/>
-      <c r="D20" s="64" t="s"/>
-      <c r="E20" s="63" t="s"/>
-      <c r="F20" s="64" t="s"/>
-      <c r="G20" s="63" t="s"/>
-      <c r="H20" s="64" t="s"/>
-      <c r="I20" s="63" t="s"/>
-      <c r="J20" s="65" t="s"/>
-      <c r="K20" s="128" t="s"/>
+      <c r="A20" s="240" t="s"/>
+      <c r="B20" s="240" t="s"/>
+      <c r="C20" s="240" t="s"/>
+      <c r="D20" s="240" t="s"/>
+      <c r="E20" s="240" t="s"/>
+      <c r="F20" s="240" t="s"/>
+      <c r="G20" s="240" t="s"/>
+      <c r="H20" s="240" t="s"/>
+      <c r="I20" s="240" t="s"/>
+      <c r="J20" s="240" t="s"/>
+      <c r="K20" s="241" t="s"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="53" t="s"/>
-      <c r="B21" s="54" t="s"/>
-      <c r="C21" s="53" t="s"/>
-      <c r="D21" s="54" t="s"/>
-      <c r="E21" s="53" t="s"/>
-      <c r="F21" s="54" t="s"/>
-      <c r="G21" s="53" t="s"/>
-      <c r="H21" s="54" t="s"/>
-      <c r="I21" s="53" t="s"/>
-      <c r="J21" s="54" t="s"/>
-      <c r="K21" s="128" t="s"/>
+      <c r="A21" s="240" t="s"/>
+      <c r="B21" s="240" t="s"/>
+      <c r="C21" s="240" t="s"/>
+      <c r="D21" s="240" t="s"/>
+      <c r="E21" s="240" t="s"/>
+      <c r="F21" s="240" t="s"/>
+      <c r="G21" s="240" t="s"/>
+      <c r="H21" s="240" t="s"/>
+      <c r="I21" s="240" t="s"/>
+      <c r="J21" s="240" t="s"/>
+      <c r="K21" s="241" t="s"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="39" t="s"/>
-      <c r="B22" s="41" t="s"/>
-      <c r="C22" s="39" t="s"/>
-      <c r="D22" s="41" t="s"/>
-      <c r="E22" s="39" t="s"/>
-      <c r="F22" s="41" t="s"/>
-      <c r="G22" s="39" t="s"/>
-      <c r="H22" s="41" t="s"/>
-      <c r="I22" s="39" t="s"/>
-      <c r="J22" s="41" t="s"/>
-      <c r="K22" s="128" t="s"/>
+      <c r="A22" s="240" t="s"/>
+      <c r="B22" s="240" t="s"/>
+      <c r="C22" s="240" t="s"/>
+      <c r="D22" s="240" t="s"/>
+      <c r="E22" s="240" t="s"/>
+      <c r="F22" s="240" t="s"/>
+      <c r="G22" s="240" t="s"/>
+      <c r="H22" s="240" t="s"/>
+      <c r="I22" s="240" t="s"/>
+      <c r="J22" s="240" t="s"/>
+      <c r="K22" s="241" t="s"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="39" t="s"/>
-      <c r="B23" s="41" t="s"/>
-      <c r="C23" s="39" t="s"/>
-      <c r="D23" s="41" t="s"/>
-      <c r="E23" s="39" t="s"/>
-      <c r="F23" s="41" t="s"/>
-      <c r="G23" s="39" t="s"/>
-      <c r="H23" s="41" t="s"/>
-      <c r="I23" s="39" t="s"/>
-      <c r="J23" s="41" t="s"/>
-      <c r="K23" s="128" t="s"/>
+      <c r="A23" s="240" t="s"/>
+      <c r="B23" s="240" t="s"/>
+      <c r="C23" s="240" t="s"/>
+      <c r="D23" s="240" t="s"/>
+      <c r="E23" s="240" t="s"/>
+      <c r="F23" s="240" t="s"/>
+      <c r="G23" s="240" t="s"/>
+      <c r="H23" s="240" t="s"/>
+      <c r="I23" s="240" t="s"/>
+      <c r="J23" s="240" t="s"/>
+      <c r="K23" s="241" t="s"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="129" t="s"/>
-      <c r="B24" s="128" t="s"/>
-      <c r="C24" s="129" t="s"/>
-      <c r="D24" s="128" t="s"/>
-      <c r="E24" s="129" t="s"/>
-      <c r="F24" s="128" t="s"/>
-      <c r="G24" s="129" t="s"/>
-      <c r="H24" s="128" t="s"/>
-      <c r="I24" s="129" t="s"/>
-      <c r="J24" s="128" t="s"/>
-      <c r="K24" s="128" t="s"/>
+      <c r="A24" s="241" t="s"/>
+      <c r="B24" s="241" t="s"/>
+      <c r="C24" s="241" t="s"/>
+      <c r="D24" s="241" t="s"/>
+      <c r="E24" s="241" t="s"/>
+      <c r="F24" s="241" t="s"/>
+      <c r="G24" s="241" t="s"/>
+      <c r="H24" s="241" t="s"/>
+      <c r="I24" s="241" t="s"/>
+      <c r="J24" s="241" t="s"/>
+      <c r="K24" s="241" t="s"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="129" t="s"/>
-      <c r="B25" s="136" t="s"/>
-      <c r="C25" s="129" t="s"/>
-      <c r="D25" s="136" t="s"/>
-      <c r="E25" s="129" t="s"/>
-      <c r="F25" s="136" t="s"/>
-      <c r="G25" s="129" t="s"/>
-      <c r="H25" s="136" t="s"/>
-      <c r="I25" s="129" t="s"/>
-      <c r="J25" s="128" t="s"/>
-      <c r="K25" s="130" t="s"/>
+      <c r="A25" s="241" t="s"/>
+      <c r="B25" s="244" t="s"/>
+      <c r="C25" s="241" t="s"/>
+      <c r="D25" s="244" t="s"/>
+      <c r="E25" s="241" t="s"/>
+      <c r="F25" s="244" t="s"/>
+      <c r="G25" s="241" t="s"/>
+      <c r="H25" s="244" t="s"/>
+      <c r="I25" s="241" t="s"/>
+      <c r="J25" s="241" t="s"/>
+      <c r="K25" s="241" t="s"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="131" t="s"/>
-      <c r="B26" s="132" t="s"/>
-      <c r="C26" s="131" t="s"/>
-      <c r="D26" s="132" t="s"/>
-      <c r="E26" s="131" t="s"/>
-      <c r="F26" s="132" t="s"/>
-      <c r="G26" s="131" t="s"/>
-      <c r="H26" s="132" t="s"/>
-      <c r="I26" s="131" t="s"/>
-      <c r="J26" s="133" t="s"/>
-      <c r="K26" s="134" t="s"/>
+      <c r="A26" s="241" t="s"/>
+      <c r="B26" s="241" t="s"/>
+      <c r="C26" s="241" t="s"/>
+      <c r="D26" s="241" t="s"/>
+      <c r="E26" s="241" t="s"/>
+      <c r="F26" s="241" t="s"/>
+      <c r="G26" s="241" t="s"/>
+      <c r="H26" s="241" t="s"/>
+      <c r="I26" s="241" t="s"/>
+      <c r="J26" s="241" t="s"/>
+      <c r="K26" s="241" t="s"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="242" t="s"/>
+      <c r="B27" s="242" t="s"/>
+      <c r="C27" s="242" t="s"/>
+      <c r="D27" s="242" t="s"/>
+      <c r="E27" s="242" t="s"/>
+      <c r="F27" s="242" t="s"/>
+      <c r="G27" s="242" t="s"/>
+      <c r="H27" s="242" t="s"/>
+      <c r="I27" s="242" t="s"/>
+      <c r="J27" s="242" t="s"/>
+      <c r="K27" s="242" t="s"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-  </mergeCells>
 </worksheet>
 </file>
 

--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -765,7 +765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1512,6 +1512,12 @@
     </xf>
     <xf fontId="7" fillId="7" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="48" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="37" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -5797,8 +5803,12 @@
       <c r="L44" s="54">
         <v>60</v>
       </c>
-      <c r="M44" s="55" t="s"/>
-      <c r="N44" s="54" t="s"/>
+      <c r="M44" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="N44" s="54">
+        <v>60</v>
+      </c>
       <c r="O44" s="41" t="s"/>
     </row>
     <row r="45" spans="1:15">
@@ -5838,8 +5848,12 @@
       <c r="L45" s="41">
         <v>75</v>
       </c>
-      <c r="M45" s="58" t="s"/>
-      <c r="N45" s="41" t="s"/>
+      <c r="M45" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="N45" s="41">
+        <v>75</v>
+      </c>
       <c r="O45" s="41" t="s"/>
     </row>
     <row r="46" spans="1:15">
@@ -5879,8 +5893,12 @@
       <c r="L46" s="41">
         <v>75</v>
       </c>
-      <c r="M46" s="40" t="s"/>
-      <c r="N46" s="41" t="s"/>
+      <c r="M46" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="N46" s="41">
+        <v>75</v>
+      </c>
       <c r="O46" s="41" t="s"/>
     </row>
     <row r="47" spans="1:15">
@@ -5916,8 +5934,12 @@
       <c r="L47" s="41">
         <v>60</v>
       </c>
-      <c r="M47" s="58" t="s"/>
-      <c r="N47" s="41" t="s"/>
+      <c r="M47" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="N47" s="41">
+        <v>60</v>
+      </c>
       <c r="O47" s="41" t="s"/>
     </row>
     <row r="48" spans="1:15">
@@ -5955,10 +5977,14 @@
         <v>23</v>
       </c>
       <c r="L48" s="41">
+        <v>60</v>
+      </c>
+      <c r="M48" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="N48" s="41">
         <v>75</v>
       </c>
-      <c r="M48" s="40" t="s"/>
-      <c r="N48" s="41" t="s"/>
       <c r="O48" s="59" t="s"/>
     </row>
     <row r="49" spans="1:15">
@@ -5996,10 +6022,14 @@
         <v>25</v>
       </c>
       <c r="L49" s="41">
-        <v>90</v>
-      </c>
-      <c r="M49" s="40" t="s"/>
-      <c r="N49" s="41" t="s"/>
+        <v>75</v>
+      </c>
+      <c r="M49" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="N49" s="41">
+        <v>60</v>
+      </c>
       <c r="O49" s="60" t="s"/>
     </row>
     <row r="50" spans="1:15">
@@ -6183,10 +6213,14 @@
         <v>25</v>
       </c>
       <c r="L56" s="41">
-        <v>90</v>
-      </c>
-      <c r="M56" s="40" t="s"/>
-      <c r="N56" s="41" t="s"/>
+        <v>75</v>
+      </c>
+      <c r="M56" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="N56" s="70">
+        <v>75</v>
+      </c>
       <c r="O56" s="59" t="s"/>
     </row>
     <row r="57" spans="1:15">
@@ -6220,14 +6254,14 @@
       <c r="J57" s="70">
         <v>75</v>
       </c>
-      <c r="K57" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="L57" s="70">
-        <v>60</v>
-      </c>
-      <c r="M57" s="40" t="s"/>
-      <c r="N57" s="41" t="s"/>
+      <c r="K57" s="39" t="s"/>
+      <c r="L57" s="70" t="s"/>
+      <c r="M57" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="41">
+        <v>75</v>
+      </c>
       <c r="O57" s="60" t="s"/>
     </row>
     <row r="58" spans="1:15">
@@ -6267,8 +6301,12 @@
       <c r="L58" s="41">
         <v>75</v>
       </c>
-      <c r="M58" s="58" t="s"/>
-      <c r="N58" s="41" t="s"/>
+      <c r="M58" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="N58" s="41">
+        <v>60</v>
+      </c>
       <c r="O58" s="60" t="s"/>
     </row>
     <row r="59" spans="1:15">
@@ -6309,7 +6347,7 @@
         <v>60</v>
       </c>
       <c r="M59" s="40" t="s"/>
-      <c r="N59" s="62" t="s"/>
+      <c r="N59" s="70" t="s"/>
       <c r="O59" s="60" t="s"/>
     </row>
     <row r="60" spans="1:15">
@@ -6387,16 +6425,16 @@
       <c r="K62" s="68" t="s"/>
       <c r="L62" s="69">
         <f>=SUM(L44:L61)</f>
-        <v>720</v>
+        <v>615</v>
       </c>
       <c r="M62" s="68" t="s"/>
       <c r="N62" s="68">
         <f>=SUM(N44:N61)</f>
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="O62" s="51">
         <f>=SUM(A62:N62)</f>
-        <v>4730</v>
+        <v>5240</v>
       </c>
       <c r="P62" s="71" t="s"/>
     </row>

--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -17,13 +17,14 @@
     <sheet name="和业广场" sheetId="9" r:id="rId11"/>
     <sheet name="中大附三岭南医院" sheetId="10" r:id="rId12"/>
     <sheet name="广州交易广场" sheetId="11" r:id="rId13"/>
+    <sheet name="公司集采物资表格" sheetId="12" r:id="rId14"/>
   </sheets>
   <calcPr fullCalcOnLoad="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <si>
     <t/>
   </si>
@@ -185,6 +186,9 @@
     <t>许润瑾</t>
   </si>
   <si>
+    <t>物</t>
+  </si>
+  <si>
     <t>北京路广百</t>
   </si>
   <si>
@@ -252,6 +256,15 @@
     <t>伍晓莹</t>
   </si>
   <si>
+    <t>小卖部</t>
+  </si>
+  <si>
+    <t>骆丽君</t>
+  </si>
+  <si>
+    <t>陈慧仪</t>
+  </si>
+  <si>
     <t>和业广场</t>
   </si>
   <si>
@@ -265,6 +278,15 @@
   </si>
   <si>
     <t>蔡建华</t>
+  </si>
+  <si>
+    <t>丘奇</t>
+  </si>
+  <si>
+    <t>李雨柔</t>
+  </si>
+  <si>
+    <t>余佳茹</t>
   </si>
   <si>
     <t>林佳宁</t>
@@ -309,25 +331,79 @@
     <t>卢嘉伟</t>
   </si>
   <si>
-    <t>广州交易广场</t>
+    <t>成义强</t>
   </si>
   <si>
-    <t>2026/7/3星期五</t>
+    <t>采购日期</t>
   </si>
   <si>
-    <t>丘奇</t>
+    <t>物品名称</t>
   </si>
   <si>
-    <t>小卖部</t>
+    <t>采购金额</t>
+  </si>
+  <si>
+    <t>物品数量</t>
+  </si>
+  <si>
+    <t>点位使用数量</t>
+  </si>
+  <si>
+    <t>图例</t>
+  </si>
+  <si>
+    <t>送餐塑料筐</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>点位KT板</t>
+  </si>
+  <si>
+    <t>接力送马甲</t>
+  </si>
+  <si>
+    <t>三轮摩托车</t>
+  </si>
+  <si>
+    <t>万科欧泊</t>
+  </si>
+  <si>
+    <t>四角遮阳棚</t>
+  </si>
+  <si>
+    <t>红色马克笔</t>
+  </si>
+  <si>
+    <t>户外伞</t>
+  </si>
+  <si>
+    <t>送餐四轮拖框</t>
+  </si>
+  <si>
+    <t>万科三轮租电</t>
+  </si>
+  <si>
+    <t>6月</t>
+  </si>
+  <si>
+    <t>7月</t>
+  </si>
+  <si>
+    <t>泽泽</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="300" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="301" formatCode="m&quot;月&quot;d&quot;号&quot;"/>
+    <numFmt numFmtId="302" formatCode="&quot;¥&quot;#,##0.00"/>
+    <numFmt numFmtId="303" formatCode="yyyy-mm-dd;@"/>
+    <numFmt numFmtId="304" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -370,7 +446,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,8 +523,14 @@
       </patternFill>
     </fill>
     <fill/>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="49">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -753,19 +835,13 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <top/>
-    </border>
   </borders>
   <cellStyleXfs>
     <xf fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1177,6 +1253,21 @@
     <xf fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="7" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
@@ -1189,6 +1280,78 @@
     <xf fontId="0" fillId="10" borderId="9" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="2" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
     <xf fontId="3" fillId="11" borderId="13" xfId="0">
       <alignment vertical="bottom" textRotation="0"/>
     </xf>
@@ -1264,6 +1427,75 @@
     <xf fontId="0" fillId="10" borderId="9" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="2" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1294,6 +1526,15 @@
     <xf fontId="3" fillId="0" borderId="14" xfId="0">
       <alignment vertical="bottom" textRotation="0"/>
     </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
     <xf numFmtId="58" fontId="3" fillId="0" borderId="33" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
@@ -1360,39 +1601,6 @@
     <xf fontId="0" fillId="6" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="9" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="14" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="10" borderId="12" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
     <xf numFmtId="58" fontId="3" fillId="16" borderId="2" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
@@ -1408,7 +1616,10 @@
     <xf fontId="3" fillId="0" borderId="35" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="36" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
     <xf fontId="9" fillId="0" borderId="37" xfId="0">
@@ -1444,6 +1655,9 @@
     <xf fontId="9" fillId="0" borderId="45" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
+    <xf fontId="7" fillId="7" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="9" fillId="10" borderId="1" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
@@ -1459,71 +1673,490 @@
     <xf fontId="9" fillId="6" borderId="3" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="0" fillId="10" borderId="5" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="31" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="5" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="7" fillId="6" borderId="31" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="9" fillId="10" borderId="13" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="9" fillId="10" borderId="14" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="9" fillId="10" borderId="48" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="9" fillId="10" borderId="37" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="9" fillId="6" borderId="15" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
     <xf fontId="3" fillId="7" borderId="5" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
     <xf fontId="0" fillId="7" borderId="5" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
+    <xf numFmtId="58" fontId="3" fillId="7" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="31" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
     <xf fontId="8" fillId="7" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="7" borderId="5" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="31" xfId="0">
+    <xf numFmtId="302" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="303" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="303" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="304" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="17" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="6" xfId="0">
       <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="7" fillId="7" borderId="31" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="7" fillId="7" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="48" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="37" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
     </xf>
   </cellXfs>
   <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId0" r:link="rId0"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" r:link="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="3"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="4"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3" r:link="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="5"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4" r:link="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="6"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5" r:link="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="7"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6" r:link="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="8"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7" r:link="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="9"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8" r:link="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="10"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9" r:link="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="11"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10" r:link="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320751</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91923" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="12"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11" r:link="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="13"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12" r:link="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="14"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13" r:link="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320992</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="91440" cy="203200"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="15"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14" r:link="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3117,186 +3750,186 @@
       <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="176">
+      <c r="M1" s="231">
         <v>46194</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="177" t="s"/>
+      <c r="O1" s="232" t="s"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="178" t="s"/>
-      <c r="B2" s="179" t="s"/>
-      <c r="C2" s="180" t="s"/>
-      <c r="D2" s="178" t="s"/>
-      <c r="E2" s="180" t="s"/>
-      <c r="F2" s="180" t="s"/>
-      <c r="G2" s="159" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" s="178">
-        <v>90</v>
-      </c>
-      <c r="I2" s="159" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="178">
-        <v>90</v>
-      </c>
-      <c r="K2" s="159" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" s="178">
-        <v>60</v>
-      </c>
-      <c r="M2" s="159" t="s">
-        <v>82</v>
-      </c>
-      <c r="N2" s="178">
-        <v>60</v>
-      </c>
-      <c r="O2" s="145" t="s"/>
+      <c r="A2" s="233" t="s"/>
+      <c r="B2" s="234" t="s"/>
+      <c r="C2" s="235" t="s"/>
+      <c r="D2" s="233" t="s"/>
+      <c r="E2" s="235" t="s"/>
+      <c r="F2" s="235" t="s"/>
+      <c r="G2" s="188" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="233">
+        <v>90</v>
+      </c>
+      <c r="I2" s="188" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="233">
+        <v>90</v>
+      </c>
+      <c r="K2" s="188" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" s="233">
+        <v>60</v>
+      </c>
+      <c r="M2" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="N2" s="233">
+        <v>60</v>
+      </c>
+      <c r="O2" s="174" t="s"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="178" t="s"/>
-      <c r="B3" s="179" t="s"/>
-      <c r="C3" s="180" t="s"/>
-      <c r="D3" s="178" t="s"/>
-      <c r="E3" s="180" t="s"/>
-      <c r="F3" s="180" t="s"/>
-      <c r="G3" s="159" t="s">
-        <v>82</v>
-      </c>
-      <c r="H3" s="178">
-        <v>60</v>
-      </c>
-      <c r="I3" s="159" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="178">
-        <v>90</v>
-      </c>
-      <c r="K3" s="159" t="s">
-        <v>82</v>
-      </c>
-      <c r="L3" s="178">
-        <v>60</v>
-      </c>
-      <c r="M3" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="N3" s="178">
-        <v>90</v>
-      </c>
-      <c r="O3" s="145" t="s"/>
+      <c r="A3" s="233" t="s"/>
+      <c r="B3" s="234" t="s"/>
+      <c r="C3" s="235" t="s"/>
+      <c r="D3" s="233" t="s"/>
+      <c r="E3" s="235" t="s"/>
+      <c r="F3" s="235" t="s"/>
+      <c r="G3" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="233">
+        <v>60</v>
+      </c>
+      <c r="I3" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="233">
+        <v>90</v>
+      </c>
+      <c r="K3" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="L3" s="233">
+        <v>60</v>
+      </c>
+      <c r="M3" s="188" t="s">
+        <v>90</v>
+      </c>
+      <c r="N3" s="233">
+        <v>90</v>
+      </c>
+      <c r="O3" s="174" t="s"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="178" t="s"/>
-      <c r="B4" s="179" t="s"/>
-      <c r="C4" s="180" t="s"/>
-      <c r="D4" s="178" t="s"/>
-      <c r="E4" s="180" t="s"/>
-      <c r="F4" s="180" t="s"/>
-      <c r="G4" s="159" t="s"/>
-      <c r="H4" s="178" t="s"/>
-      <c r="I4" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="178">
-        <v>60</v>
-      </c>
-      <c r="K4" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="L4" s="178">
-        <v>90</v>
-      </c>
-      <c r="M4" s="159" t="s"/>
-      <c r="N4" s="178" t="s"/>
-      <c r="O4" s="145" t="s"/>
+      <c r="A4" s="233" t="s"/>
+      <c r="B4" s="234" t="s"/>
+      <c r="C4" s="235" t="s"/>
+      <c r="D4" s="233" t="s"/>
+      <c r="E4" s="235" t="s"/>
+      <c r="F4" s="235" t="s"/>
+      <c r="G4" s="188" t="s"/>
+      <c r="H4" s="233" t="s"/>
+      <c r="I4" s="188" t="s">
+        <v>90</v>
+      </c>
+      <c r="J4" s="233">
+        <v>60</v>
+      </c>
+      <c r="K4" s="188" t="s">
+        <v>90</v>
+      </c>
+      <c r="L4" s="233">
+        <v>90</v>
+      </c>
+      <c r="M4" s="188" t="s"/>
+      <c r="N4" s="233" t="s"/>
+      <c r="O4" s="174" t="s"/>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="178" t="s"/>
-      <c r="B5" s="179" t="s"/>
-      <c r="C5" s="180" t="s"/>
-      <c r="D5" s="178" t="s"/>
-      <c r="E5" s="180" t="s"/>
-      <c r="F5" s="180" t="s"/>
-      <c r="G5" s="159" t="s"/>
-      <c r="H5" s="178" t="s"/>
-      <c r="I5" s="159" t="s"/>
-      <c r="J5" s="178" t="s"/>
-      <c r="K5" s="159" t="s"/>
-      <c r="L5" s="178" t="s"/>
-      <c r="M5" s="159" t="s"/>
-      <c r="N5" s="178" t="s"/>
-      <c r="O5" s="145" t="s"/>
+      <c r="A5" s="233" t="s"/>
+      <c r="B5" s="234" t="s"/>
+      <c r="C5" s="235" t="s"/>
+      <c r="D5" s="233" t="s"/>
+      <c r="E5" s="235" t="s"/>
+      <c r="F5" s="235" t="s"/>
+      <c r="G5" s="188" t="s"/>
+      <c r="H5" s="233" t="s"/>
+      <c r="I5" s="188" t="s"/>
+      <c r="J5" s="233" t="s"/>
+      <c r="K5" s="188" t="s"/>
+      <c r="L5" s="233" t="s"/>
+      <c r="M5" s="188" t="s"/>
+      <c r="N5" s="233" t="s"/>
+      <c r="O5" s="174" t="s"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="178" t="s"/>
-      <c r="B6" s="179" t="s"/>
-      <c r="C6" s="180" t="s"/>
-      <c r="D6" s="178" t="s"/>
-      <c r="E6" s="180" t="s"/>
-      <c r="F6" s="180" t="s"/>
-      <c r="G6" s="159" t="s"/>
-      <c r="H6" s="178" t="s"/>
-      <c r="I6" s="159" t="s"/>
-      <c r="J6" s="178" t="s"/>
-      <c r="K6" s="159" t="s"/>
-      <c r="L6" s="178" t="s"/>
-      <c r="M6" s="159" t="s"/>
-      <c r="N6" s="178" t="s"/>
-      <c r="O6" s="145" t="s"/>
+      <c r="A6" s="233" t="s"/>
+      <c r="B6" s="234" t="s"/>
+      <c r="C6" s="235" t="s"/>
+      <c r="D6" s="233" t="s"/>
+      <c r="E6" s="235" t="s"/>
+      <c r="F6" s="235" t="s"/>
+      <c r="G6" s="188" t="s"/>
+      <c r="H6" s="233" t="s"/>
+      <c r="I6" s="188" t="s"/>
+      <c r="J6" s="233" t="s"/>
+      <c r="K6" s="188" t="s"/>
+      <c r="L6" s="233" t="s"/>
+      <c r="M6" s="188" t="s"/>
+      <c r="N6" s="233" t="s"/>
+      <c r="O6" s="174" t="s"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="178" t="s"/>
-      <c r="B7" s="179" t="s"/>
-      <c r="C7" s="180" t="s"/>
-      <c r="D7" s="178" t="s"/>
-      <c r="E7" s="180" t="s"/>
-      <c r="F7" s="180" t="s"/>
-      <c r="G7" s="159" t="s"/>
-      <c r="H7" s="178" t="s"/>
-      <c r="I7" s="159" t="s"/>
-      <c r="J7" s="178" t="s"/>
-      <c r="K7" s="159" t="s"/>
-      <c r="L7" s="178" t="s"/>
-      <c r="M7" s="159" t="s"/>
-      <c r="N7" s="178" t="s"/>
-      <c r="O7" s="181" t="s">
+      <c r="A7" s="233" t="s"/>
+      <c r="B7" s="234" t="s"/>
+      <c r="C7" s="235" t="s"/>
+      <c r="D7" s="233" t="s"/>
+      <c r="E7" s="235" t="s"/>
+      <c r="F7" s="235" t="s"/>
+      <c r="G7" s="188" t="s"/>
+      <c r="H7" s="233" t="s"/>
+      <c r="I7" s="188" t="s"/>
+      <c r="J7" s="233" t="s"/>
+      <c r="K7" s="188" t="s"/>
+      <c r="L7" s="233" t="s"/>
+      <c r="M7" s="188" t="s"/>
+      <c r="N7" s="233" t="s"/>
+      <c r="O7" s="236" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="182" t="s"/>
-      <c r="B8" s="182" t="s"/>
-      <c r="C8" s="182" t="s"/>
-      <c r="D8" s="182" t="s"/>
-      <c r="E8" s="182" t="s"/>
-      <c r="F8" s="182" t="s"/>
-      <c r="G8" s="183" t="s"/>
-      <c r="H8" s="184">
+      <c r="A8" s="237" t="s"/>
+      <c r="B8" s="237" t="s"/>
+      <c r="C8" s="237" t="s"/>
+      <c r="D8" s="237" t="s"/>
+      <c r="E8" s="237" t="s"/>
+      <c r="F8" s="237" t="s"/>
+      <c r="G8" s="238" t="s"/>
+      <c r="H8" s="239">
         <f>=SUM(H2:H7)</f>
         <v>150</v>
       </c>
-      <c r="I8" s="183" t="s"/>
-      <c r="J8" s="184">
+      <c r="I8" s="238" t="s"/>
+      <c r="J8" s="239">
         <f>=SUM(J2:J7)</f>
         <v>240</v>
       </c>
-      <c r="K8" s="183" t="s"/>
-      <c r="L8" s="184">
+      <c r="K8" s="238" t="s"/>
+      <c r="L8" s="239">
         <f>=SUM(L2:L7)</f>
         <v>210</v>
       </c>
-      <c r="M8" s="183" t="s"/>
-      <c r="N8" s="184">
+      <c r="M8" s="238" t="s"/>
+      <c r="N8" s="239">
         <f>=SUM(N2:N7)</f>
         <v>150</v>
       </c>
-      <c r="O8" s="185">
+      <c r="O8" s="240">
         <f>=SUM(A8:N8)</f>
         <v>750</v>
       </c>
@@ -3307,319 +3940,319 @@
     <row r="9" spans="1:28"/>
     <row r="10" spans="1:28"/>
     <row r="11" spans="1:15">
-      <c r="A11" s="186">
+      <c r="A11" s="241">
         <v>46195</v>
       </c>
-      <c r="B11" s="187" t="s">
+      <c r="B11" s="242" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="188">
+      <c r="C11" s="243">
         <v>46196</v>
       </c>
-      <c r="D11" s="156" t="s">
+      <c r="D11" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="189">
+      <c r="E11" s="244">
         <v>46197</v>
       </c>
       <c r="F11" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="188">
+      <c r="G11" s="243">
         <v>46198</v>
       </c>
-      <c r="H11" s="156" t="s">
+      <c r="H11" s="185" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="189">
+      <c r="I11" s="244">
         <v>46199</v>
       </c>
-      <c r="J11" s="156" t="s">
+      <c r="J11" s="185" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="189">
+      <c r="K11" s="244">
         <v>46200</v>
       </c>
-      <c r="L11" s="156" t="s">
+      <c r="L11" s="185" t="s">
         <v>7</v>
       </c>
-      <c r="M11" s="189">
+      <c r="M11" s="244">
         <v>46201</v>
       </c>
-      <c r="N11" s="156" t="s">
+      <c r="N11" s="185" t="s">
         <v>1</v>
       </c>
-      <c r="O11" s="190" t="s"/>
+      <c r="O11" s="245" t="s"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="159" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="178">
+      <c r="A12" s="188" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="233">
         <v>75</v>
       </c>
-      <c r="C12" s="155" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="156">
+      <c r="C12" s="184" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="185">
         <v>75</v>
       </c>
       <c r="E12" s="94" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F12" s="94">
         <v>135</v>
       </c>
-      <c r="G12" s="155" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="156">
+      <c r="G12" s="184" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="185">
         <v>60</v>
       </c>
       <c r="I12" s="94" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="156">
+        <v>87</v>
+      </c>
+      <c r="J12" s="185">
         <v>60</v>
       </c>
       <c r="K12" s="94" t="s">
-        <v>82</v>
-      </c>
-      <c r="L12" s="156">
+        <v>89</v>
+      </c>
+      <c r="L12" s="185">
         <v>120</v>
       </c>
       <c r="M12" s="94" t="s">
-        <v>84</v>
-      </c>
-      <c r="N12" s="156">
-        <v>60</v>
-      </c>
-      <c r="O12" s="156" t="s"/>
+        <v>91</v>
+      </c>
+      <c r="N12" s="185">
+        <v>60</v>
+      </c>
+      <c r="O12" s="185" t="s"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="159" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="178">
-        <v>60</v>
-      </c>
-      <c r="C13" s="159" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="157">
+      <c r="A13" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="233">
+        <v>60</v>
+      </c>
+      <c r="C13" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="186">
         <v>75</v>
       </c>
-      <c r="E13" s="178" t="s">
-        <v>82</v>
+      <c r="E13" s="233" t="s">
+        <v>89</v>
       </c>
       <c r="F13">
         <v>60</v>
       </c>
-      <c r="G13" s="159" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="157">
-        <v>60</v>
-      </c>
-      <c r="I13" s="178" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" s="157">
-        <v>60</v>
-      </c>
-      <c r="K13" s="178" t="s">
-        <v>83</v>
-      </c>
-      <c r="L13" s="157">
-        <v>90</v>
-      </c>
-      <c r="M13" s="178" t="s">
-        <v>85</v>
-      </c>
-      <c r="N13" s="157">
+      <c r="G13" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="186">
+        <v>60</v>
+      </c>
+      <c r="I13" s="233" t="s">
+        <v>89</v>
+      </c>
+      <c r="J13" s="186">
+        <v>60</v>
+      </c>
+      <c r="K13" s="233" t="s">
+        <v>90</v>
+      </c>
+      <c r="L13" s="186">
+        <v>90</v>
+      </c>
+      <c r="M13" s="233" t="s">
+        <v>92</v>
+      </c>
+      <c r="N13" s="186">
         <v>120</v>
       </c>
-      <c r="O13" s="157" t="s"/>
+      <c r="O13" s="186" t="s"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="178">
-        <v>90</v>
-      </c>
-      <c r="C14" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="157">
-        <v>90</v>
-      </c>
-      <c r="E14" s="178" t="s">
-        <v>83</v>
+      <c r="A14" s="188" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="233">
+        <v>90</v>
+      </c>
+      <c r="C14" s="188" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="186">
+        <v>90</v>
+      </c>
+      <c r="E14" s="233" t="s">
+        <v>90</v>
       </c>
       <c r="F14">
         <v>90</v>
       </c>
-      <c r="G14" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="157">
-        <v>90</v>
-      </c>
-      <c r="I14" s="178" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="157">
-        <v>90</v>
-      </c>
-      <c r="K14" s="191" t="s">
-        <v>86</v>
-      </c>
-      <c r="L14" s="157">
-        <v>60</v>
-      </c>
-      <c r="M14" s="178" t="s">
-        <v>87</v>
-      </c>
-      <c r="N14" s="157">
-        <v>90</v>
-      </c>
-      <c r="O14" s="157" t="s"/>
+      <c r="G14" s="188" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="186">
+        <v>90</v>
+      </c>
+      <c r="I14" s="233" t="s">
+        <v>90</v>
+      </c>
+      <c r="J14" s="186">
+        <v>90</v>
+      </c>
+      <c r="K14" s="246" t="s">
+        <v>93</v>
+      </c>
+      <c r="L14" s="186">
+        <v>60</v>
+      </c>
+      <c r="M14" s="233" t="s">
+        <v>94</v>
+      </c>
+      <c r="N14" s="186">
+        <v>90</v>
+      </c>
+      <c r="O14" s="186" t="s"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="159" t="s"/>
-      <c r="B15" s="178" t="s"/>
-      <c r="C15" s="159" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="157">
+      <c r="A15" s="188" t="s"/>
+      <c r="B15" s="233" t="s"/>
+      <c r="C15" s="188" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="186">
         <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F15">
         <v>60</v>
       </c>
-      <c r="G15" s="192" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="157">
+      <c r="G15" s="247" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="186">
         <v>120</v>
       </c>
-      <c r="I15" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="J15" s="157">
-        <v>60</v>
-      </c>
-      <c r="K15" s="178" t="s"/>
-      <c r="L15" s="157" t="s"/>
-      <c r="M15" s="178" t="s"/>
-      <c r="N15" s="157" t="s"/>
-      <c r="O15" s="157" t="s"/>
+      <c r="I15" s="246" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" s="186">
+        <v>60</v>
+      </c>
+      <c r="K15" s="233" t="s"/>
+      <c r="L15" s="186" t="s"/>
+      <c r="M15" s="233" t="s"/>
+      <c r="N15" s="186" t="s"/>
+      <c r="O15" s="186" t="s"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="159" t="s"/>
-      <c r="B16" s="178" t="s"/>
-      <c r="C16" s="159" t="s"/>
-      <c r="D16" s="157" t="s"/>
+      <c r="A16" s="188" t="s"/>
+      <c r="B16" s="233" t="s"/>
+      <c r="C16" s="188" t="s"/>
+      <c r="D16" s="186" t="s"/>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F16">
         <v>75</v>
       </c>
-      <c r="G16" s="192" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="157">
-        <v>60</v>
-      </c>
-      <c r="I16" s="191" t="s">
-        <v>90</v>
-      </c>
-      <c r="J16" s="157">
-        <v>60</v>
-      </c>
-      <c r="K16" s="178" t="s"/>
-      <c r="L16" s="157" t="s"/>
-      <c r="M16" s="178" t="s"/>
-      <c r="N16" s="157" t="s"/>
-      <c r="O16" s="157" t="s"/>
+      <c r="G16" s="247" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="186">
+        <v>60</v>
+      </c>
+      <c r="I16" s="246" t="s">
+        <v>97</v>
+      </c>
+      <c r="J16" s="186">
+        <v>60</v>
+      </c>
+      <c r="K16" s="233" t="s"/>
+      <c r="L16" s="186" t="s"/>
+      <c r="M16" s="233" t="s"/>
+      <c r="N16" s="186" t="s"/>
+      <c r="O16" s="186" t="s"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="159" t="s"/>
-      <c r="B17" s="178" t="s"/>
-      <c r="C17" s="159" t="s"/>
-      <c r="D17" s="157" t="s"/>
+      <c r="A17" s="188" t="s"/>
+      <c r="B17" s="233" t="s"/>
+      <c r="C17" s="188" t="s"/>
+      <c r="D17" s="186" t="s"/>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F17">
         <v>60</v>
       </c>
-      <c r="G17" s="192" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="157">
-        <v>60</v>
-      </c>
-      <c r="I17" s="191" t="s">
-        <v>91</v>
-      </c>
-      <c r="J17" s="157">
-        <v>60</v>
-      </c>
-      <c r="K17" s="178" t="s"/>
-      <c r="L17" s="157" t="s"/>
-      <c r="M17" s="178" t="s"/>
-      <c r="N17" s="157" t="s"/>
-      <c r="O17" s="181" t="s">
+      <c r="G17" s="247" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="186">
+        <v>60</v>
+      </c>
+      <c r="I17" s="246" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" s="186">
+        <v>60</v>
+      </c>
+      <c r="K17" s="233" t="s"/>
+      <c r="L17" s="186" t="s"/>
+      <c r="M17" s="233" t="s"/>
+      <c r="N17" s="186" t="s"/>
+      <c r="O17" s="236" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="193" t="s"/>
-      <c r="B18" s="194">
+      <c r="A18" s="248" t="s"/>
+      <c r="B18" s="249">
         <f>=SUM(B12:B17)</f>
         <v>225</v>
       </c>
-      <c r="C18" s="193" t="s"/>
-      <c r="D18" s="195">
+      <c r="C18" s="248" t="s"/>
+      <c r="D18" s="250">
         <f>=SUM(D12:D17)</f>
         <v>315</v>
       </c>
-      <c r="E18" s="194" t="s"/>
-      <c r="F18" s="194">
+      <c r="E18" s="249" t="s"/>
+      <c r="F18" s="249">
         <f>=SUM(F12:F17)</f>
         <v>480</v>
       </c>
-      <c r="G18" s="193" t="s"/>
-      <c r="H18" s="195">
+      <c r="G18" s="248" t="s"/>
+      <c r="H18" s="250">
         <f>=SUM(H12:H17)</f>
         <v>450</v>
       </c>
-      <c r="I18" s="194" t="s"/>
-      <c r="J18" s="195">
+      <c r="I18" s="249" t="s"/>
+      <c r="J18" s="250">
         <f>=SUM(J12:J17)</f>
         <v>390</v>
       </c>
-      <c r="K18" s="194" t="s"/>
-      <c r="L18" s="195">
+      <c r="K18" s="249" t="s"/>
+      <c r="L18" s="250">
         <f>=SUM(L12:L17)</f>
         <v>270</v>
       </c>
-      <c r="M18" s="194" t="s"/>
-      <c r="N18" s="195">
+      <c r="M18" s="249" t="s"/>
+      <c r="N18" s="250">
         <f>=SUM(N12:N17)</f>
         <v>270</v>
       </c>
-      <c r="O18" s="196">
+      <c r="O18" s="251">
         <f>=SUM(A18:N18)</f>
         <v>2400</v>
       </c>
-      <c r="P18" s="197" t="s">
+      <c r="P18" s="252" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3670,174 +4303,174 @@
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="159" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="178">
+      <c r="A22" s="188" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="233">
         <v>120</v>
       </c>
-      <c r="C22" s="159" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="156">
+      <c r="C22" s="188" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="185">
         <v>90</v>
       </c>
       <c r="E22" s="94" t="s"/>
       <c r="F22" s="94" t="s"/>
-      <c r="G22" s="155" t="s"/>
-      <c r="H22" s="156" t="s"/>
+      <c r="G22" s="184" t="s"/>
+      <c r="H22" s="185" t="s"/>
       <c r="I22" s="94" t="s"/>
-      <c r="J22" s="156" t="s"/>
+      <c r="J22" s="185" t="s"/>
       <c r="K22" s="94" t="s"/>
-      <c r="L22" s="156" t="s"/>
+      <c r="L22" s="185" t="s"/>
       <c r="M22" s="94" t="s"/>
-      <c r="N22" s="156" t="s"/>
-      <c r="O22" s="156" t="s"/>
+      <c r="N22" s="185" t="s"/>
+      <c r="O22" s="185" t="s"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="178">
-        <v>90</v>
-      </c>
-      <c r="C23" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="157">
-        <v>90</v>
-      </c>
-      <c r="E23" s="178" t="s"/>
-      <c r="G23" s="159" t="s"/>
-      <c r="H23" s="157" t="s"/>
-      <c r="I23" s="178" t="s"/>
-      <c r="J23" s="157" t="s"/>
-      <c r="K23" s="178" t="s"/>
-      <c r="L23" s="157" t="s"/>
-      <c r="M23" s="178" t="s"/>
-      <c r="N23" s="157" t="s"/>
-      <c r="O23" s="157" t="s"/>
+      <c r="A23" s="188" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="233">
+        <v>90</v>
+      </c>
+      <c r="C23" s="188" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="186">
+        <v>90</v>
+      </c>
+      <c r="E23" s="233" t="s"/>
+      <c r="G23" s="188" t="s"/>
+      <c r="H23" s="186" t="s"/>
+      <c r="I23" s="233" t="s"/>
+      <c r="J23" s="186" t="s"/>
+      <c r="K23" s="233" t="s"/>
+      <c r="L23" s="186" t="s"/>
+      <c r="M23" s="233" t="s"/>
+      <c r="N23" s="186" t="s"/>
+      <c r="O23" s="186" t="s"/>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="159" t="s">
+      <c r="A24" s="188" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="233">
+        <v>60</v>
+      </c>
+      <c r="C24" s="188" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="186">
+        <v>60</v>
+      </c>
+      <c r="E24" s="233" t="s"/>
+      <c r="G24" s="188" t="s"/>
+      <c r="H24" s="186" t="s"/>
+      <c r="I24" s="233" t="s"/>
+      <c r="J24" s="186" t="s"/>
+      <c r="K24" s="246" t="s"/>
+      <c r="L24" s="186" t="s"/>
+      <c r="M24" s="233" t="s"/>
+      <c r="N24" s="186" t="s"/>
+      <c r="O24" s="186" t="s"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="188" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="233">
+        <v>60</v>
+      </c>
+      <c r="C25" s="188" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="178">
-        <v>60</v>
-      </c>
-      <c r="C24" s="159" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="157">
-        <v>60</v>
-      </c>
-      <c r="E24" s="178" t="s"/>
-      <c r="G24" s="159" t="s"/>
-      <c r="H24" s="157" t="s"/>
-      <c r="I24" s="178" t="s"/>
-      <c r="J24" s="157" t="s"/>
-      <c r="K24" s="191" t="s"/>
-      <c r="L24" s="157" t="s"/>
-      <c r="M24" s="178" t="s"/>
-      <c r="N24" s="157" t="s"/>
-      <c r="O24" s="157" t="s"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="159" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="178">
-        <v>60</v>
-      </c>
-      <c r="C25" s="159" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" s="157">
-        <v>60</v>
-      </c>
-      <c r="G25" s="192" t="s"/>
-      <c r="H25" s="157" t="s"/>
-      <c r="I25" s="191" t="s"/>
-      <c r="J25" s="157" t="s"/>
-      <c r="K25" s="178" t="s"/>
-      <c r="L25" s="157" t="s"/>
-      <c r="M25" s="178" t="s"/>
-      <c r="N25" s="157" t="s"/>
-      <c r="O25" s="157" t="s"/>
+      <c r="D25" s="186">
+        <v>60</v>
+      </c>
+      <c r="G25" s="247" t="s"/>
+      <c r="H25" s="186" t="s"/>
+      <c r="I25" s="246" t="s"/>
+      <c r="J25" s="186" t="s"/>
+      <c r="K25" s="233" t="s"/>
+      <c r="L25" s="186" t="s"/>
+      <c r="M25" s="233" t="s"/>
+      <c r="N25" s="186" t="s"/>
+      <c r="O25" s="186" t="s"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="159" t="s"/>
-      <c r="B26" s="178" t="s"/>
-      <c r="C26" s="159" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="157">
-        <v>60</v>
-      </c>
-      <c r="G26" s="192" t="s"/>
-      <c r="H26" s="157" t="s"/>
-      <c r="I26" s="191" t="s"/>
-      <c r="J26" s="157" t="s"/>
-      <c r="K26" s="178" t="s"/>
-      <c r="L26" s="157" t="s"/>
-      <c r="M26" s="178" t="s"/>
-      <c r="N26" s="157" t="s"/>
-      <c r="O26" s="157" t="s"/>
+      <c r="A26" s="188" t="s"/>
+      <c r="B26" s="233" t="s"/>
+      <c r="C26" s="188" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="186">
+        <v>60</v>
+      </c>
+      <c r="G26" s="247" t="s"/>
+      <c r="H26" s="186" t="s"/>
+      <c r="I26" s="246" t="s"/>
+      <c r="J26" s="186" t="s"/>
+      <c r="K26" s="233" t="s"/>
+      <c r="L26" s="186" t="s"/>
+      <c r="M26" s="233" t="s"/>
+      <c r="N26" s="186" t="s"/>
+      <c r="O26" s="186" t="s"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="159" t="s"/>
-      <c r="B27" s="178" t="s"/>
-      <c r="C27" s="159" t="s"/>
-      <c r="D27" s="157" t="s"/>
-      <c r="G27" s="192" t="s"/>
-      <c r="H27" s="157" t="s"/>
-      <c r="I27" s="191" t="s"/>
-      <c r="J27" s="157" t="s"/>
-      <c r="K27" s="178" t="s"/>
-      <c r="L27" s="157" t="s"/>
-      <c r="M27" s="178" t="s"/>
-      <c r="N27" s="157" t="s"/>
-      <c r="O27" s="181" t="s">
+      <c r="A27" s="188" t="s"/>
+      <c r="B27" s="233" t="s"/>
+      <c r="C27" s="188" t="s"/>
+      <c r="D27" s="186" t="s"/>
+      <c r="G27" s="247" t="s"/>
+      <c r="H27" s="186" t="s"/>
+      <c r="I27" s="246" t="s"/>
+      <c r="J27" s="186" t="s"/>
+      <c r="K27" s="233" t="s"/>
+      <c r="L27" s="186" t="s"/>
+      <c r="M27" s="233" t="s"/>
+      <c r="N27" s="186" t="s"/>
+      <c r="O27" s="236" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="193" t="s"/>
-      <c r="B28" s="194">
+      <c r="A28" s="248" t="s"/>
+      <c r="B28" s="249">
         <f>=SUM(B22:B27)</f>
         <v>330</v>
       </c>
-      <c r="C28" s="193" t="s"/>
-      <c r="D28" s="195">
+      <c r="C28" s="248" t="s"/>
+      <c r="D28" s="250">
         <f>=SUM(D22:D27)</f>
         <v>360</v>
       </c>
-      <c r="E28" s="194" t="s"/>
-      <c r="F28" s="194">
+      <c r="E28" s="249" t="s"/>
+      <c r="F28" s="249">
         <f>=SUM(F22:F27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="193" t="s"/>
-      <c r="H28" s="195">
+      <c r="G28" s="248" t="s"/>
+      <c r="H28" s="250">
         <f>=SUM(H22:H27)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="194" t="s"/>
-      <c r="J28" s="195">
+      <c r="I28" s="249" t="s"/>
+      <c r="J28" s="250">
         <f>=SUM(J22:J27)</f>
         <v>0</v>
       </c>
-      <c r="K28" s="194" t="s"/>
-      <c r="L28" s="195">
+      <c r="K28" s="249" t="s"/>
+      <c r="L28" s="250">
         <f>=SUM(L22:L27)</f>
         <v>0</v>
       </c>
-      <c r="M28" s="194" t="s"/>
-      <c r="N28" s="195">
+      <c r="M28" s="249" t="s"/>
+      <c r="N28" s="250">
         <f>=SUM(N22:N27)</f>
         <v>0</v>
       </c>
-      <c r="O28" s="196">
+      <c r="O28" s="251">
         <f>=SUM(A28:N28)</f>
         <v>690</v>
       </c>
@@ -4028,91 +4661,91 @@
       <c r="A1" s="4">
         <v>46202</v>
       </c>
-      <c r="B1" s="209" t="s">
+      <c r="B1" s="253" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="4">
         <v>46203</v>
       </c>
-      <c r="D1" s="209" t="s">
+      <c r="D1" s="253" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4">
         <v>46204</v>
       </c>
-      <c r="F1" s="209" t="s">
+      <c r="F1" s="253" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="4">
         <v>46205</v>
       </c>
-      <c r="H1" s="209" t="s">
+      <c r="H1" s="253" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="4">
         <v>46206</v>
       </c>
-      <c r="J1" s="210" t="s">
+      <c r="J1" s="254" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="6" t="s"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="211" t="s"/>
-      <c r="B2" s="212" t="s"/>
-      <c r="C2" s="213" t="s"/>
-      <c r="D2" s="212" t="s"/>
-      <c r="E2" s="213" t="s"/>
-      <c r="F2" s="212" t="s"/>
-      <c r="G2" s="213" t="s"/>
-      <c r="H2" s="212" t="s"/>
-      <c r="I2" s="246" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="247">
-        <v>90</v>
-      </c>
-      <c r="K2" s="215" t="s"/>
+      <c r="A2" s="255" t="s"/>
+      <c r="B2" s="256" t="s"/>
+      <c r="C2" s="257" t="s"/>
+      <c r="D2" s="256" t="s"/>
+      <c r="E2" s="257" t="s"/>
+      <c r="F2" s="256" t="s"/>
+      <c r="G2" s="257" t="s"/>
+      <c r="H2" s="256" t="s"/>
+      <c r="I2" s="258" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="259">
+        <v>90</v>
+      </c>
+      <c r="K2" s="260" t="s"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="39" t="s"/>
-      <c r="B3" s="216" t="s"/>
-      <c r="C3" s="217" t="s"/>
-      <c r="D3" s="216" t="s"/>
-      <c r="E3" s="217" t="s"/>
-      <c r="F3" s="216" t="s"/>
-      <c r="G3" s="217" t="s"/>
-      <c r="H3" s="216" t="s"/>
-      <c r="I3" s="217" t="s"/>
-      <c r="J3" s="218" t="s"/>
-      <c r="K3" s="219" t="s"/>
+      <c r="B3" s="261" t="s"/>
+      <c r="C3" s="262" t="s"/>
+      <c r="D3" s="261" t="s"/>
+      <c r="E3" s="262" t="s"/>
+      <c r="F3" s="261" t="s"/>
+      <c r="G3" s="262" t="s"/>
+      <c r="H3" s="261" t="s"/>
+      <c r="I3" s="262" t="s"/>
+      <c r="J3" s="263" t="s"/>
+      <c r="K3" s="264" t="s"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="39" t="s"/>
-      <c r="B4" s="216" t="s"/>
-      <c r="C4" s="217" t="s"/>
-      <c r="D4" s="216" t="s"/>
-      <c r="E4" s="217" t="s"/>
-      <c r="F4" s="216" t="s"/>
-      <c r="G4" s="217" t="s"/>
-      <c r="H4" s="216" t="s"/>
-      <c r="I4" s="220" t="s"/>
-      <c r="J4" s="218" t="s"/>
-      <c r="K4" s="219" t="s"/>
+      <c r="B4" s="261" t="s"/>
+      <c r="C4" s="262" t="s"/>
+      <c r="D4" s="261" t="s"/>
+      <c r="E4" s="262" t="s"/>
+      <c r="F4" s="261" t="s"/>
+      <c r="G4" s="262" t="s"/>
+      <c r="H4" s="261" t="s"/>
+      <c r="I4" s="265" t="s"/>
+      <c r="J4" s="263" t="s"/>
+      <c r="K4" s="264" t="s"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="221" t="s"/>
-      <c r="B5" s="222" t="s"/>
-      <c r="C5" s="223" t="s"/>
-      <c r="D5" s="222" t="s"/>
-      <c r="E5" s="223" t="s"/>
-      <c r="F5" s="222" t="s"/>
-      <c r="G5" s="223" t="s"/>
-      <c r="H5" s="222" t="s"/>
-      <c r="I5" s="223" t="s"/>
-      <c r="J5" s="224" t="s"/>
-      <c r="K5" s="225" t="s"/>
-      <c r="L5" s="248" t="s"/>
+      <c r="A5" s="266" t="s"/>
+      <c r="B5" s="267" t="s"/>
+      <c r="C5" s="268" t="s"/>
+      <c r="D5" s="267" t="s"/>
+      <c r="E5" s="268" t="s"/>
+      <c r="F5" s="267" t="s"/>
+      <c r="G5" s="268" t="s"/>
+      <c r="H5" s="267" t="s"/>
+      <c r="I5" s="268" t="s"/>
+      <c r="J5" s="269" t="s"/>
+      <c r="K5" s="270" t="s"/>
+      <c r="L5" s="271" t="s"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="129" t="s"/>
@@ -4136,291 +4769,600 @@
       <c r="F7" s="136" t="s"/>
       <c r="G7" s="129" t="s"/>
       <c r="H7" s="136" t="s"/>
-      <c r="I7" s="137" t="s"/>
-      <c r="J7" s="138" t="s"/>
+      <c r="I7" s="142" t="s"/>
+      <c r="J7" s="143" t="s"/>
       <c r="K7" s="130" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="226" t="s"/>
-      <c r="B8" s="227">
+      <c r="A8" s="272" t="s"/>
+      <c r="B8" s="273">
         <f>=SUM(B2:B7)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="226" t="s"/>
-      <c r="D8" s="227">
+      <c r="C8" s="272" t="s"/>
+      <c r="D8" s="273">
         <f>=SUM(D2:D7)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="226" t="s"/>
-      <c r="F8" s="227">
+      <c r="E8" s="272" t="s"/>
+      <c r="F8" s="273">
         <f>=SUM(F2:F7)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="226" t="s"/>
-      <c r="H8" s="227">
+      <c r="G8" s="272" t="s"/>
+      <c r="H8" s="273">
         <f>=SUM(H2:H7)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="228" t="s"/>
-      <c r="J8" s="229">
+      <c r="I8" s="274" t="s"/>
+      <c r="J8" s="275">
         <f>=SUM(J2:J7)</f>
         <v>90</v>
       </c>
-      <c r="K8" s="230">
+      <c r="K8" s="276">
         <f>=SUM(A8:J8)</f>
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="240" t="s"/>
-      <c r="B9" s="240" t="s"/>
-      <c r="C9" s="240" t="s"/>
-      <c r="D9" s="240" t="s"/>
-      <c r="E9" s="240" t="s"/>
-      <c r="F9" s="240" t="s"/>
-      <c r="G9" s="240" t="s"/>
-      <c r="H9" s="240" t="s"/>
-      <c r="I9" s="240" t="s"/>
-      <c r="J9" s="240" t="s"/>
-      <c r="K9" s="240" t="s"/>
+      <c r="A9" s="277" t="s"/>
+      <c r="B9" s="277" t="s"/>
+      <c r="C9" s="277" t="s"/>
+      <c r="D9" s="277" t="s"/>
+      <c r="E9" s="277" t="s"/>
+      <c r="F9" s="277" t="s"/>
+      <c r="G9" s="277" t="s"/>
+      <c r="H9" s="277" t="s"/>
+      <c r="I9" s="277" t="s"/>
+      <c r="J9" s="277" t="s"/>
+      <c r="K9" s="277" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="240" t="s"/>
-      <c r="B10" s="240" t="s"/>
-      <c r="C10" s="240" t="s"/>
-      <c r="D10" s="240" t="s"/>
-      <c r="E10" s="240" t="s"/>
-      <c r="F10" s="240" t="s"/>
-      <c r="G10" s="240" t="s"/>
-      <c r="H10" s="240" t="s"/>
-      <c r="I10" s="240" t="s"/>
-      <c r="J10" s="240" t="s"/>
-      <c r="K10" s="241" t="s"/>
+      <c r="A10" s="277" t="s"/>
+      <c r="B10" s="277" t="s"/>
+      <c r="C10" s="277" t="s"/>
+      <c r="D10" s="277" t="s"/>
+      <c r="E10" s="277" t="s"/>
+      <c r="F10" s="277" t="s"/>
+      <c r="G10" s="277" t="s"/>
+      <c r="H10" s="277" t="s"/>
+      <c r="I10" s="277" t="s"/>
+      <c r="J10" s="277" t="s"/>
+      <c r="K10" s="278" t="s"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="240" t="s"/>
-      <c r="B11" s="240" t="s"/>
-      <c r="C11" s="240" t="s"/>
-      <c r="D11" s="240" t="s"/>
-      <c r="E11" s="240" t="s"/>
-      <c r="F11" s="240" t="s"/>
-      <c r="G11" s="240" t="s"/>
-      <c r="H11" s="240" t="s"/>
-      <c r="I11" s="240" t="s"/>
-      <c r="J11" s="240" t="s"/>
-      <c r="K11" s="241" t="s"/>
+      <c r="A11" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B11" s="253" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>46210</v>
+      </c>
+      <c r="D11" s="253" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46211</v>
+      </c>
+      <c r="F11" s="253" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46212</v>
+      </c>
+      <c r="H11" s="253" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="4">
+        <v>46213</v>
+      </c>
+      <c r="J11" s="254" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="6" t="s"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="240" t="s"/>
-      <c r="B12" s="240" t="s"/>
-      <c r="C12" s="240" t="s"/>
-      <c r="D12" s="240" t="s"/>
-      <c r="E12" s="240" t="s"/>
-      <c r="F12" s="240" t="s"/>
-      <c r="G12" s="240" t="s"/>
-      <c r="H12" s="240" t="s"/>
-      <c r="I12" s="240" t="s"/>
-      <c r="J12" s="240" t="s"/>
-      <c r="K12" s="241" t="s"/>
+      <c r="A12" s="255" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="256">
+        <v>90</v>
+      </c>
+      <c r="C12" s="257" t="s"/>
+      <c r="D12" s="256" t="s"/>
+      <c r="E12" s="257" t="s"/>
+      <c r="F12" s="256" t="s"/>
+      <c r="G12" s="257" t="s"/>
+      <c r="H12" s="256" t="s"/>
+      <c r="I12" s="258" t="s"/>
+      <c r="J12" s="259" t="s"/>
+      <c r="K12" s="260" t="s"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="241" t="s"/>
-      <c r="B13" s="244" t="s"/>
-      <c r="C13" s="241" t="s"/>
-      <c r="D13" s="244" t="s"/>
-      <c r="E13" s="241" t="s"/>
-      <c r="F13" s="244" t="s"/>
-      <c r="G13" s="241" t="s"/>
-      <c r="H13" s="244" t="s"/>
-      <c r="I13" s="241" t="s"/>
-      <c r="J13" s="241" t="s"/>
-      <c r="K13" s="241" t="s"/>
+      <c r="A13" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="261">
+        <v>60</v>
+      </c>
+      <c r="C13" s="262" t="s"/>
+      <c r="D13" s="261" t="s"/>
+      <c r="E13" s="262" t="s"/>
+      <c r="F13" s="261" t="s"/>
+      <c r="G13" s="262" t="s"/>
+      <c r="H13" s="261" t="s"/>
+      <c r="I13" s="262" t="s"/>
+      <c r="J13" s="263" t="s"/>
+      <c r="K13" s="264" t="s"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="241" t="s"/>
-      <c r="B14" s="244" t="s"/>
-      <c r="C14" s="241" t="s"/>
-      <c r="D14" s="244" t="s"/>
-      <c r="E14" s="241" t="s"/>
-      <c r="F14" s="244" t="s"/>
-      <c r="G14" s="241" t="s"/>
-      <c r="H14" s="244" t="s"/>
-      <c r="I14" s="241" t="s"/>
-      <c r="J14" s="241" t="s"/>
-      <c r="K14" s="241" t="s"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="241" t="s"/>
-      <c r="B15" s="244" t="s"/>
-      <c r="C15" s="241" t="s"/>
-      <c r="D15" s="244" t="s"/>
-      <c r="E15" s="241" t="s"/>
-      <c r="F15" s="244" t="s"/>
-      <c r="G15" s="241" t="s"/>
-      <c r="H15" s="244" t="s"/>
-      <c r="I15" s="241" t="s"/>
-      <c r="J15" s="241" t="s"/>
-      <c r="K15" s="241" t="s"/>
+      <c r="A14" s="39" t="s"/>
+      <c r="B14" s="261" t="s"/>
+      <c r="C14" s="262" t="s"/>
+      <c r="D14" s="261" t="s"/>
+      <c r="E14" s="262" t="s"/>
+      <c r="F14" s="261" t="s"/>
+      <c r="G14" s="262" t="s"/>
+      <c r="H14" s="261" t="s"/>
+      <c r="I14" s="265" t="s"/>
+      <c r="J14" s="263" t="s"/>
+      <c r="K14" s="264" t="s"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="266" t="s"/>
+      <c r="B15" s="267" t="s"/>
+      <c r="C15" s="268" t="s"/>
+      <c r="D15" s="267" t="s"/>
+      <c r="E15" s="268" t="s"/>
+      <c r="F15" s="267" t="s"/>
+      <c r="G15" s="268" t="s"/>
+      <c r="H15" s="267" t="s"/>
+      <c r="I15" s="268" t="s"/>
+      <c r="J15" s="269" t="s"/>
+      <c r="K15" s="270" t="s"/>
+      <c r="L15" s="271" t="s"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="241" t="s"/>
-      <c r="B16" s="241" t="s"/>
-      <c r="C16" s="241" t="s"/>
-      <c r="D16" s="241" t="s"/>
-      <c r="E16" s="241" t="s"/>
-      <c r="F16" s="241" t="s"/>
-      <c r="G16" s="241" t="s"/>
-      <c r="H16" s="241" t="s"/>
-      <c r="I16" s="241" t="s"/>
-      <c r="J16" s="241" t="s"/>
-      <c r="K16" s="241" t="s"/>
+      <c r="A16" s="129" t="s"/>
+      <c r="B16" s="136" t="s"/>
+      <c r="C16" s="129" t="s"/>
+      <c r="D16" s="136" t="s"/>
+      <c r="E16" s="129" t="s"/>
+      <c r="F16" s="136" t="s"/>
+      <c r="G16" s="129" t="s"/>
+      <c r="H16" s="136" t="s"/>
+      <c r="I16" s="129" t="s"/>
+      <c r="J16" s="128" t="s"/>
+      <c r="K16" s="128" t="s"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="242" t="s"/>
-      <c r="B17" s="242" t="s"/>
-      <c r="C17" s="242" t="s"/>
-      <c r="D17" s="242" t="s"/>
-      <c r="E17" s="242" t="s"/>
-      <c r="F17" s="242" t="s"/>
-      <c r="G17" s="242" t="s"/>
-      <c r="H17" s="242" t="s"/>
-      <c r="I17" s="242" t="s"/>
-      <c r="J17" s="242" t="s"/>
-      <c r="K17" s="242" t="s"/>
+      <c r="A17" s="129" t="s"/>
+      <c r="B17" s="136" t="s"/>
+      <c r="C17" s="129" t="s"/>
+      <c r="D17" s="136" t="s"/>
+      <c r="E17" s="129" t="s"/>
+      <c r="F17" s="136" t="s"/>
+      <c r="G17" s="129" t="s"/>
+      <c r="H17" s="136" t="s"/>
+      <c r="I17" s="142" t="s"/>
+      <c r="J17" s="143" t="s"/>
+      <c r="K17" s="130" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="242" t="s"/>
-      <c r="B18" s="242" t="s"/>
-      <c r="C18" s="242" t="s"/>
-      <c r="D18" s="242" t="s"/>
-      <c r="E18" s="242" t="s"/>
-      <c r="F18" s="242" t="s"/>
-      <c r="G18" s="242" t="s"/>
-      <c r="H18" s="242" t="s"/>
-      <c r="I18" s="242" t="s"/>
-      <c r="J18" s="242" t="s"/>
-      <c r="K18" s="242" t="s"/>
+      <c r="A18" s="272" t="s"/>
+      <c r="B18" s="273">
+        <f>=SUM(B12:B17)</f>
+        <v>150</v>
+      </c>
+      <c r="C18" s="272" t="s"/>
+      <c r="D18" s="273">
+        <f>=SUM(D12:D17)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="272" t="s"/>
+      <c r="F18" s="273">
+        <f>=SUM(F12:F17)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="272" t="s"/>
+      <c r="H18" s="273">
+        <f>=SUM(H12:H17)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="274" t="s"/>
+      <c r="J18" s="275">
+        <f>=SUM(J12:J17)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="276">
+        <f>=SUM(A18:J18)</f>
+        <v>150</v>
+      </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="243" t="s"/>
-      <c r="B19" s="243" t="s"/>
-      <c r="C19" s="243" t="s"/>
-      <c r="D19" s="243" t="s"/>
-      <c r="E19" s="243" t="s"/>
-      <c r="F19" s="243" t="s"/>
-      <c r="G19" s="243" t="s"/>
-      <c r="H19" s="243" t="s"/>
-      <c r="I19" s="243" t="s"/>
-      <c r="J19" s="243" t="s"/>
-      <c r="K19" s="243" t="s"/>
+      <c r="A19" s="279" t="s"/>
+      <c r="B19" s="279" t="s"/>
+      <c r="C19" s="279" t="s"/>
+      <c r="D19" s="279" t="s"/>
+      <c r="E19" s="279" t="s"/>
+      <c r="F19" s="279" t="s"/>
+      <c r="G19" s="279" t="s"/>
+      <c r="H19" s="279" t="s"/>
+      <c r="I19" s="279" t="s"/>
+      <c r="J19" s="279" t="s"/>
+      <c r="K19" s="279" t="s"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="240" t="s"/>
-      <c r="B20" s="240" t="s"/>
-      <c r="C20" s="240" t="s"/>
-      <c r="D20" s="240" t="s"/>
-      <c r="E20" s="240" t="s"/>
-      <c r="F20" s="240" t="s"/>
-      <c r="G20" s="240" t="s"/>
-      <c r="H20" s="240" t="s"/>
-      <c r="I20" s="240" t="s"/>
-      <c r="J20" s="240" t="s"/>
-      <c r="K20" s="241" t="s"/>
+      <c r="A20" s="277" t="s"/>
+      <c r="B20" s="277" t="s"/>
+      <c r="C20" s="277" t="s"/>
+      <c r="D20" s="277" t="s"/>
+      <c r="E20" s="277" t="s"/>
+      <c r="F20" s="277" t="s"/>
+      <c r="G20" s="277" t="s"/>
+      <c r="H20" s="277" t="s"/>
+      <c r="I20" s="277" t="s"/>
+      <c r="J20" s="277" t="s"/>
+      <c r="K20" s="278" t="s"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="240" t="s"/>
-      <c r="B21" s="240" t="s"/>
-      <c r="C21" s="240" t="s"/>
-      <c r="D21" s="240" t="s"/>
-      <c r="E21" s="240" t="s"/>
-      <c r="F21" s="240" t="s"/>
-      <c r="G21" s="240" t="s"/>
-      <c r="H21" s="240" t="s"/>
-      <c r="I21" s="240" t="s"/>
-      <c r="J21" s="240" t="s"/>
-      <c r="K21" s="241" t="s"/>
+      <c r="A21" s="277" t="s"/>
+      <c r="B21" s="277" t="s"/>
+      <c r="C21" s="277" t="s"/>
+      <c r="D21" s="277" t="s"/>
+      <c r="E21" s="277" t="s"/>
+      <c r="F21" s="277" t="s"/>
+      <c r="G21" s="277" t="s"/>
+      <c r="H21" s="277" t="s"/>
+      <c r="I21" s="277" t="s"/>
+      <c r="J21" s="277" t="s"/>
+      <c r="K21" s="278" t="s"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="240" t="s"/>
-      <c r="B22" s="240" t="s"/>
-      <c r="C22" s="240" t="s"/>
-      <c r="D22" s="240" t="s"/>
-      <c r="E22" s="240" t="s"/>
-      <c r="F22" s="240" t="s"/>
-      <c r="G22" s="240" t="s"/>
-      <c r="H22" s="240" t="s"/>
-      <c r="I22" s="240" t="s"/>
-      <c r="J22" s="240" t="s"/>
-      <c r="K22" s="241" t="s"/>
+      <c r="A22" s="277" t="s"/>
+      <c r="B22" s="277" t="s"/>
+      <c r="C22" s="277" t="s"/>
+      <c r="D22" s="277" t="s"/>
+      <c r="E22" s="277" t="s"/>
+      <c r="F22" s="277" t="s"/>
+      <c r="G22" s="277" t="s"/>
+      <c r="H22" s="277" t="s"/>
+      <c r="I22" s="277" t="s"/>
+      <c r="J22" s="277" t="s"/>
+      <c r="K22" s="278" t="s"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="240" t="s"/>
-      <c r="B23" s="240" t="s"/>
-      <c r="C23" s="240" t="s"/>
-      <c r="D23" s="240" t="s"/>
-      <c r="E23" s="240" t="s"/>
-      <c r="F23" s="240" t="s"/>
-      <c r="G23" s="240" t="s"/>
-      <c r="H23" s="240" t="s"/>
-      <c r="I23" s="240" t="s"/>
-      <c r="J23" s="240" t="s"/>
-      <c r="K23" s="241" t="s"/>
+      <c r="A23" s="277" t="s"/>
+      <c r="B23" s="277" t="s"/>
+      <c r="C23" s="277" t="s"/>
+      <c r="D23" s="277" t="s"/>
+      <c r="E23" s="277" t="s"/>
+      <c r="F23" s="277" t="s"/>
+      <c r="G23" s="277" t="s"/>
+      <c r="H23" s="277" t="s"/>
+      <c r="I23" s="277" t="s"/>
+      <c r="J23" s="277" t="s"/>
+      <c r="K23" s="278" t="s"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="241" t="s"/>
-      <c r="B24" s="241" t="s"/>
-      <c r="C24" s="241" t="s"/>
-      <c r="D24" s="241" t="s"/>
-      <c r="E24" s="241" t="s"/>
-      <c r="F24" s="241" t="s"/>
-      <c r="G24" s="241" t="s"/>
-      <c r="H24" s="241" t="s"/>
-      <c r="I24" s="241" t="s"/>
-      <c r="J24" s="241" t="s"/>
-      <c r="K24" s="241" t="s"/>
+      <c r="A24" s="278" t="s"/>
+      <c r="B24" s="278" t="s"/>
+      <c r="C24" s="278" t="s"/>
+      <c r="D24" s="278" t="s"/>
+      <c r="E24" s="278" t="s"/>
+      <c r="F24" s="278" t="s"/>
+      <c r="G24" s="278" t="s"/>
+      <c r="H24" s="278" t="s"/>
+      <c r="I24" s="278" t="s"/>
+      <c r="J24" s="278" t="s"/>
+      <c r="K24" s="278" t="s"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="241" t="s"/>
-      <c r="B25" s="244" t="s"/>
-      <c r="C25" s="241" t="s"/>
-      <c r="D25" s="244" t="s"/>
-      <c r="E25" s="241" t="s"/>
-      <c r="F25" s="244" t="s"/>
-      <c r="G25" s="241" t="s"/>
-      <c r="H25" s="244" t="s"/>
-      <c r="I25" s="241" t="s"/>
-      <c r="J25" s="241" t="s"/>
-      <c r="K25" s="241" t="s"/>
+      <c r="A25" s="278" t="s"/>
+      <c r="B25" s="280" t="s"/>
+      <c r="C25" s="278" t="s"/>
+      <c r="D25" s="280" t="s"/>
+      <c r="E25" s="278" t="s"/>
+      <c r="F25" s="280" t="s"/>
+      <c r="G25" s="278" t="s"/>
+      <c r="H25" s="280" t="s"/>
+      <c r="I25" s="278" t="s"/>
+      <c r="J25" s="278" t="s"/>
+      <c r="K25" s="278" t="s"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="241" t="s"/>
-      <c r="B26" s="241" t="s"/>
-      <c r="C26" s="241" t="s"/>
-      <c r="D26" s="241" t="s"/>
-      <c r="E26" s="241" t="s"/>
-      <c r="F26" s="241" t="s"/>
-      <c r="G26" s="241" t="s"/>
-      <c r="H26" s="241" t="s"/>
-      <c r="I26" s="241" t="s"/>
-      <c r="J26" s="241" t="s"/>
-      <c r="K26" s="241" t="s"/>
+      <c r="A26" s="278" t="s"/>
+      <c r="B26" s="278" t="s"/>
+      <c r="C26" s="278" t="s"/>
+      <c r="D26" s="278" t="s"/>
+      <c r="E26" s="278" t="s"/>
+      <c r="F26" s="278" t="s"/>
+      <c r="G26" s="278" t="s"/>
+      <c r="H26" s="278" t="s"/>
+      <c r="I26" s="278" t="s"/>
+      <c r="J26" s="278" t="s"/>
+      <c r="K26" s="278" t="s"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="242" t="s"/>
-      <c r="B27" s="242" t="s"/>
-      <c r="C27" s="242" t="s"/>
-      <c r="D27" s="242" t="s"/>
-      <c r="E27" s="242" t="s"/>
-      <c r="F27" s="242" t="s"/>
-      <c r="G27" s="242" t="s"/>
-      <c r="H27" s="242" t="s"/>
-      <c r="I27" s="242" t="s"/>
-      <c r="J27" s="242" t="s"/>
-      <c r="K27" s="242" t="s"/>
+      <c r="A27" s="281" t="s"/>
+      <c r="B27" s="281" t="s"/>
+      <c r="C27" s="281" t="s"/>
+      <c r="D27" s="281" t="s"/>
+      <c r="E27" s="281" t="s"/>
+      <c r="F27" s="281" t="s"/>
+      <c r="G27" s="281" t="s"/>
+      <c r="H27" s="281" t="s"/>
+      <c r="I27" s="281" t="s"/>
+      <c r="J27" s="281" t="s"/>
+      <c r="K27" s="281" t="s"/>
     </row>
   </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="公司集采物资表格">
+    <tabColor/>
+  </sheetPr>
+  <dimension ref="F15"/>
+  <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="3" max="3" width="13.6719" style="282"/>
+    <col min="4" max="4" width="13.6719" style="286"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="282" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="286" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="283">
+        <v>46184</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="282">
+        <v>359</v>
+      </c>
+      <c r="D2" s="286">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="283">
+        <v>46179</v>
+      </c>
+      <c r="B3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="282">
+        <v>48</v>
+      </c>
+      <c r="D3" s="286">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="284">
+        <v>46179</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="282">
+        <v>380</v>
+      </c>
+      <c r="D4" s="286">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="284">
+        <v>46180</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="282">
+        <v>1400</v>
+      </c>
+      <c r="D5" s="286">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" t="s"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="284">
+        <v>46180</v>
+      </c>
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="282">
+        <v>135</v>
+      </c>
+      <c r="D6" s="286">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" t="s"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="283">
+        <v>46183</v>
+      </c>
+      <c r="B7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="282">
+        <v>120</v>
+      </c>
+      <c r="D7" s="286">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="284">
+        <v>46185</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="282">
+        <v>110.79</v>
+      </c>
+      <c r="D8" s="286">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="284">
+        <v>46206</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="282">
+        <v>359</v>
+      </c>
+      <c r="D9" s="286">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="284">
+        <v>46206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="282">
+        <v>900</v>
+      </c>
+      <c r="D10" s="286">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="284">
+        <v>46206</v>
+      </c>
+      <c r="B11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="282">
+        <v>96.8</v>
+      </c>
+      <c r="D11" s="286">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="283">
+        <v>46209</v>
+      </c>
+      <c r="B12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="282">
+        <v>200</v>
+      </c>
+      <c r="D12" s="286">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="283">
+        <v>46196</v>
+      </c>
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="282">
+        <v>592.78</v>
+      </c>
+      <c r="D13" s="286">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s"/>
+      <c r="G13" t="s"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="284">
+        <v>46180</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="282">
+        <v>259</v>
+      </c>
+      <c r="D14" s="286" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" t="s"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="285">
+        <v>46210</v>
+      </c>
+      <c r="B15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="282">
+        <v>249</v>
+      </c>
+      <c r="D15" s="286" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" t="s"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId0"/>
 </worksheet>
 </file>
 
@@ -4429,13 +5371,13 @@
   <sheetPr codeName="中大附属第六医院">
     <tabColor/>
   </sheetPr>
-  <dimension ref="P62"/>
+  <dimension ref="O85"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="15" width="10.6523" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" hidden="1">
       <c r="A1" s="4">
         <v>46188</v>
       </c>
@@ -4480,7 +5422,7 @@
       </c>
       <c r="O1" s="21" t="s"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" hidden="1">
       <c r="A2" s="39" t="s">
         <v>8</v>
       </c>
@@ -4525,7 +5467,7 @@
       </c>
       <c r="O2" s="42" t="s"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" hidden="1">
       <c r="A3" s="43" t="s"/>
       <c r="B3" s="40" t="s"/>
       <c r="C3" s="39" t="s"/>
@@ -4562,7 +5504,7 @@
       </c>
       <c r="O3" s="42" t="s"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" hidden="1">
       <c r="A4" s="39" t="s"/>
       <c r="B4" s="40" t="s"/>
       <c r="C4" s="43" t="s"/>
@@ -4599,7 +5541,7 @@
       </c>
       <c r="O4" s="42" t="s"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" hidden="1">
       <c r="A5" s="39" t="s"/>
       <c r="B5" s="40" t="s"/>
       <c r="C5" s="39" t="s"/>
@@ -4636,7 +5578,7 @@
       </c>
       <c r="O5" s="42" t="s"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" hidden="1">
       <c r="A6" s="39" t="s"/>
       <c r="B6" s="40" t="s"/>
       <c r="C6" s="39" t="s"/>
@@ -4669,7 +5611,7 @@
       </c>
       <c r="O6" s="42" t="s"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" hidden="1">
       <c r="A7" s="39" t="s"/>
       <c r="B7" s="40" t="s"/>
       <c r="C7" s="39" t="s"/>
@@ -4704,7 +5646,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" hidden="1">
       <c r="A8" s="39" t="s"/>
       <c r="B8" s="40" t="s"/>
       <c r="C8" s="39" t="s"/>
@@ -4733,7 +5675,7 @@
       </c>
       <c r="O8" s="46" t="s"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" hidden="1">
       <c r="A9" s="39" t="s"/>
       <c r="B9" s="40" t="s"/>
       <c r="C9" s="39" t="s"/>
@@ -4750,7 +5692,7 @@
       <c r="N9" s="8" t="s"/>
       <c r="O9" s="46" t="s"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" hidden="1">
       <c r="A10" s="39" t="s"/>
       <c r="B10" s="40" t="s"/>
       <c r="C10" s="39" t="s"/>
@@ -4767,7 +5709,7 @@
       <c r="N10" s="8" t="s"/>
       <c r="O10" s="46" t="s"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" hidden="1">
       <c r="A11" s="39" t="s"/>
       <c r="B11" s="40" t="s"/>
       <c r="C11" s="39" t="s"/>
@@ -4784,7 +5726,7 @@
       <c r="N11" s="8" t="s"/>
       <c r="O11" s="46" t="s"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" hidden="1">
       <c r="A12" s="39" t="s"/>
       <c r="B12" s="40" t="s"/>
       <c r="C12" s="39" t="s"/>
@@ -4801,7 +5743,7 @@
       <c r="N12" s="8" t="s"/>
       <c r="O12" s="46" t="s"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" hidden="1">
       <c r="A13" s="39" t="s"/>
       <c r="B13" s="40" t="s"/>
       <c r="C13" s="39" t="s"/>
@@ -4818,7 +5760,7 @@
       <c r="N13" s="8" t="s"/>
       <c r="O13" s="46" t="s"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" hidden="1">
       <c r="A14" s="39" t="s"/>
       <c r="B14" s="40" t="s"/>
       <c r="C14" s="39" t="s"/>
@@ -4835,7 +5777,7 @@
       <c r="N14" s="8" t="s"/>
       <c r="O14" s="46" t="s"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" hidden="1">
       <c r="A15" s="39" t="s"/>
       <c r="B15" s="40" t="s"/>
       <c r="C15" s="39" t="s"/>
@@ -4854,7 +5796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" hidden="1">
       <c r="A16" s="48" t="s"/>
       <c r="B16" s="49">
         <f>=SUM(B3:B7)</f>
@@ -4900,7 +5842,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="17" spans="1:24" hidden="1"/>
+    <row r="18" spans="1:24" hidden="1"/>
+    <row r="19" spans="1:15" hidden="1">
       <c r="A19" s="4">
         <v>46195</v>
       </c>
@@ -4945,7 +5889,7 @@
       </c>
       <c r="O19" s="21" t="s"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" hidden="1">
       <c r="A20" s="39" t="s">
         <v>8</v>
       </c>
@@ -4990,7 +5934,7 @@
       </c>
       <c r="O20" s="42" t="s"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" hidden="1">
       <c r="A21" s="53" t="s">
         <v>17</v>
       </c>
@@ -5035,7 +5979,7 @@
       </c>
       <c r="O21" s="41" t="s"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" hidden="1">
       <c r="A22" s="43" t="s">
         <v>18</v>
       </c>
@@ -5080,7 +6024,7 @@
       </c>
       <c r="O22" s="41" t="s"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" hidden="1">
       <c r="A23" s="39" t="s">
         <v>19</v>
       </c>
@@ -5125,7 +6069,7 @@
       </c>
       <c r="O23" s="41" t="s"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" hidden="1">
       <c r="A24" s="44" t="s">
         <v>20</v>
       </c>
@@ -5170,7 +6114,7 @@
       </c>
       <c r="O24" s="41" t="s"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" hidden="1">
       <c r="A25" s="39" t="s">
         <v>21</v>
       </c>
@@ -5215,7 +6159,7 @@
       </c>
       <c r="O25" s="59" t="s"/>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" hidden="1">
       <c r="A26" s="44" t="s">
         <v>22</v>
       </c>
@@ -5260,7 +6204,7 @@
       </c>
       <c r="O26" s="60" t="s"/>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" hidden="1">
       <c r="A27" s="39" t="s"/>
       <c r="B27" s="40" t="s"/>
       <c r="C27" s="39" t="s">
@@ -5301,7 +6245,7 @@
       </c>
       <c r="O27" s="60" t="s"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" hidden="1">
       <c r="A28" s="39" t="s"/>
       <c r="B28" s="40" t="s"/>
       <c r="C28" s="39" t="s">
@@ -5332,7 +6276,7 @@
       <c r="N28" s="41" t="s"/>
       <c r="O28" s="60" t="s"/>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" hidden="1">
       <c r="A29" s="39" t="s"/>
       <c r="B29" s="40" t="s"/>
       <c r="C29" s="43" t="s">
@@ -5361,7 +6305,7 @@
       <c r="N29" s="41" t="s"/>
       <c r="O29" s="60" t="s"/>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" hidden="1">
       <c r="A30" s="39" t="s"/>
       <c r="B30" s="40" t="s"/>
       <c r="C30" s="39" t="s">
@@ -5382,7 +6326,7 @@
       <c r="N30" s="41" t="s"/>
       <c r="O30" s="60" t="s"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" hidden="1">
       <c r="A31" s="39" t="s"/>
       <c r="B31" s="40" t="s"/>
       <c r="C31" s="39" t="s">
@@ -5413,7 +6357,7 @@
       <c r="N31" s="41" t="s"/>
       <c r="O31" s="60" t="s"/>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" hidden="1">
       <c r="A32" s="39" t="s"/>
       <c r="B32" s="40" t="s"/>
       <c r="C32" s="44" t="s">
@@ -5454,7 +6398,7 @@
       </c>
       <c r="O32" s="60" t="s"/>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" hidden="1">
       <c r="A33" s="39" t="s"/>
       <c r="B33" s="40" t="s"/>
       <c r="C33" s="39" t="s"/>
@@ -5491,7 +6435,7 @@
       </c>
       <c r="O33" s="59" t="s"/>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" hidden="1">
       <c r="A34" s="39" t="s"/>
       <c r="B34" s="40" t="s"/>
       <c r="C34" s="39" t="s"/>
@@ -5528,7 +6472,7 @@
       </c>
       <c r="O34" s="60" t="s"/>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" hidden="1">
       <c r="A35" s="39" t="s"/>
       <c r="B35" s="40" t="s"/>
       <c r="C35" s="39" t="s"/>
@@ -5565,7 +6509,7 @@
       </c>
       <c r="O35" s="60" t="s"/>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" hidden="1">
       <c r="A36" s="39" t="s"/>
       <c r="B36" s="40" t="s"/>
       <c r="C36" s="39" t="s"/>
@@ -5594,7 +6538,7 @@
       </c>
       <c r="O36" s="60" t="s"/>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" hidden="1">
       <c r="A37" s="39" t="s"/>
       <c r="B37" s="40" t="s"/>
       <c r="C37" s="39" t="s"/>
@@ -5611,7 +6555,7 @@
       <c r="N37" s="41" t="s"/>
       <c r="O37" s="60" t="s"/>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" hidden="1">
       <c r="A38" s="63" t="s"/>
       <c r="B38" s="64" t="s"/>
       <c r="C38" s="63" t="s"/>
@@ -5630,7 +6574,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" hidden="1">
       <c r="A39" s="67" t="s"/>
       <c r="B39" s="68">
         <f>=SUM(B21:B38)</f>
@@ -6219,7 +7163,7 @@
         <v>19</v>
       </c>
       <c r="N56" s="70">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O56" s="59" t="s"/>
     </row>
@@ -6260,7 +7204,7 @@
         <v>21</v>
       </c>
       <c r="N57" s="41">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O57" s="60" t="s"/>
     </row>
@@ -6305,7 +7249,7 @@
         <v>22</v>
       </c>
       <c r="N58" s="41">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O58" s="60" t="s"/>
     </row>
@@ -6430,13 +7374,466 @@
       <c r="M62" s="68" t="s"/>
       <c r="N62" s="68">
         <f>=SUM(N44:N61)</f>
-        <v>615</v>
+        <v>660</v>
       </c>
       <c r="O62" s="51">
         <f>=SUM(A62:N62)</f>
-        <v>5240</v>
+        <v>5285</v>
       </c>
       <c r="P62" s="71" t="s"/>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="4">
+        <v>46210</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E65" s="4">
+        <v>46211</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46212</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I65" s="4">
+        <v>46213</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K65" s="4">
+        <v>46214</v>
+      </c>
+      <c r="L65" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="M65" s="4">
+        <v>46215</v>
+      </c>
+      <c r="N65" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O65" s="21" t="s"/>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G66" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I66" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K66" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="M66" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O66" s="42" t="s"/>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="56" t="s"/>
+      <c r="B67" s="55" t="s"/>
+      <c r="C67" s="56" t="s"/>
+      <c r="D67" s="55" t="s"/>
+      <c r="E67" s="56" t="s"/>
+      <c r="F67" s="55" t="s"/>
+      <c r="G67" s="53" t="s"/>
+      <c r="H67" s="54" t="s"/>
+      <c r="I67" s="53" t="s"/>
+      <c r="J67" s="54" t="s"/>
+      <c r="K67" s="53" t="s"/>
+      <c r="L67" s="55" t="s"/>
+      <c r="M67" s="53" t="s"/>
+      <c r="N67" s="54" t="s"/>
+      <c r="O67" s="41" t="s"/>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" s="39" t="s"/>
+      <c r="B68" s="8" t="s"/>
+      <c r="C68" s="39" t="s"/>
+      <c r="D68" s="8" t="s"/>
+      <c r="E68" s="39" t="s"/>
+      <c r="F68" s="8" t="s"/>
+      <c r="G68" s="44" t="s"/>
+      <c r="H68" s="41" t="s"/>
+      <c r="I68" s="44" t="s"/>
+      <c r="J68" s="41" t="s"/>
+      <c r="K68" s="44" t="s"/>
+      <c r="L68" s="40" t="s"/>
+      <c r="M68" s="44" t="s"/>
+      <c r="N68" s="41" t="s"/>
+      <c r="O68" s="41" t="s"/>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" s="44" t="s"/>
+      <c r="B69" s="8" t="s"/>
+      <c r="C69" s="44" t="s"/>
+      <c r="D69" s="8" t="s"/>
+      <c r="E69" s="44" t="s"/>
+      <c r="F69" s="8" t="s"/>
+      <c r="G69" s="39" t="s"/>
+      <c r="H69" s="41" t="s"/>
+      <c r="I69" s="39" t="s"/>
+      <c r="J69" s="41" t="s"/>
+      <c r="K69" s="39" t="s"/>
+      <c r="L69" s="40" t="s"/>
+      <c r="M69" s="39" t="s"/>
+      <c r="N69" s="41" t="s"/>
+      <c r="O69" s="41" t="s"/>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" s="39" t="s"/>
+      <c r="B70" s="8" t="s"/>
+      <c r="C70" s="39" t="s"/>
+      <c r="D70" s="8" t="s"/>
+      <c r="E70" s="39" t="s"/>
+      <c r="F70" s="8" t="s"/>
+      <c r="G70" s="44" t="s"/>
+      <c r="H70" s="41" t="s"/>
+      <c r="I70" s="44" t="s"/>
+      <c r="J70" s="41" t="s"/>
+      <c r="K70" s="44" t="s"/>
+      <c r="L70" s="40" t="s"/>
+      <c r="M70" s="44" t="s"/>
+      <c r="N70" s="41" t="s"/>
+      <c r="O70" s="41" t="s"/>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="44" t="s"/>
+      <c r="B71" s="8" t="s"/>
+      <c r="C71" s="44" t="s"/>
+      <c r="D71" s="8" t="s"/>
+      <c r="E71" s="44" t="s"/>
+      <c r="F71" s="8" t="s"/>
+      <c r="G71" s="39" t="s"/>
+      <c r="H71" s="41" t="s"/>
+      <c r="I71" s="39" t="s"/>
+      <c r="J71" s="41" t="s"/>
+      <c r="K71" s="39" t="s"/>
+      <c r="L71" s="40" t="s"/>
+      <c r="M71" s="39" t="s"/>
+      <c r="N71" s="41" t="s"/>
+      <c r="O71" s="59" t="s"/>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" s="39" t="s"/>
+      <c r="B72" s="8" t="s"/>
+      <c r="C72" s="39" t="s"/>
+      <c r="D72" s="8" t="s"/>
+      <c r="E72" s="39" t="s"/>
+      <c r="F72" s="8" t="s"/>
+      <c r="G72" s="39" t="s"/>
+      <c r="H72" s="41" t="s"/>
+      <c r="I72" s="39" t="s"/>
+      <c r="J72" s="41" t="s"/>
+      <c r="K72" s="39" t="s"/>
+      <c r="L72" s="40" t="s"/>
+      <c r="M72" s="39" t="s"/>
+      <c r="N72" s="41" t="s"/>
+      <c r="O72" s="59" t="s"/>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="39" t="s"/>
+      <c r="B73" s="8" t="s"/>
+      <c r="C73" s="39" t="s"/>
+      <c r="D73" s="8" t="s"/>
+      <c r="E73" s="39" t="s"/>
+      <c r="F73" s="8" t="s"/>
+      <c r="G73" s="39" t="s"/>
+      <c r="H73" s="41" t="s"/>
+      <c r="I73" s="39" t="s"/>
+      <c r="J73" s="41" t="s"/>
+      <c r="K73" s="39" t="s"/>
+      <c r="L73" s="40" t="s"/>
+      <c r="M73" s="39" t="s"/>
+      <c r="N73" s="41" t="s"/>
+      <c r="O73" s="59" t="s"/>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="39" t="s"/>
+      <c r="B74" s="8" t="s"/>
+      <c r="C74" s="39" t="s"/>
+      <c r="D74" s="8" t="s"/>
+      <c r="E74" s="39" t="s"/>
+      <c r="F74" s="8" t="s"/>
+      <c r="G74" s="39" t="s"/>
+      <c r="H74" s="41" t="s"/>
+      <c r="I74" s="8" t="s"/>
+      <c r="J74" s="8" t="s"/>
+      <c r="K74" s="39" t="s"/>
+      <c r="L74" s="40" t="s"/>
+      <c r="M74" s="39" t="s"/>
+      <c r="N74" s="41" t="s"/>
+      <c r="O74" s="59" t="s"/>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="39" t="s"/>
+      <c r="B75" s="8" t="s"/>
+      <c r="C75" s="43" t="s"/>
+      <c r="D75" s="8" t="s"/>
+      <c r="E75" s="39" t="s"/>
+      <c r="F75" s="8" t="s"/>
+      <c r="G75" s="39" t="s"/>
+      <c r="H75" s="41" t="s"/>
+      <c r="I75" s="8" t="s"/>
+      <c r="J75" s="8" t="s"/>
+      <c r="K75" s="39" t="s"/>
+      <c r="L75" s="40" t="s"/>
+      <c r="M75" s="39" t="s"/>
+      <c r="N75" s="41" t="s"/>
+      <c r="O75" s="59" t="s"/>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="39" t="s"/>
+      <c r="B76" s="8" t="s"/>
+      <c r="C76" s="39" t="s"/>
+      <c r="D76" s="8" t="s"/>
+      <c r="E76" s="39" t="s"/>
+      <c r="F76" s="8" t="s"/>
+      <c r="G76" s="39" t="s"/>
+      <c r="H76" s="41" t="s"/>
+      <c r="I76" s="8" t="s"/>
+      <c r="J76" s="8" t="s"/>
+      <c r="K76" s="39" t="s"/>
+      <c r="L76" s="40" t="s"/>
+      <c r="M76" s="39" t="s"/>
+      <c r="N76" s="41" t="s"/>
+      <c r="O76" s="59" t="s"/>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="39" t="s"/>
+      <c r="B77" s="8" t="s"/>
+      <c r="C77" s="39" t="s"/>
+      <c r="D77" s="8" t="s"/>
+      <c r="E77" s="39" t="s"/>
+      <c r="F77" s="8" t="s"/>
+      <c r="G77" s="39" t="s"/>
+      <c r="H77" s="41" t="s"/>
+      <c r="I77" s="8" t="s"/>
+      <c r="J77" s="8" t="s"/>
+      <c r="K77" s="39" t="s"/>
+      <c r="L77" s="40" t="s"/>
+      <c r="M77" s="39" t="s"/>
+      <c r="N77" s="41" t="s"/>
+      <c r="O77" s="59" t="s"/>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="B78" s="8" t="s"/>
+      <c r="C78" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="D78" s="8" t="s"/>
+      <c r="E78" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" s="8" t="s"/>
+      <c r="G78" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="H78" s="41" t="s"/>
+      <c r="I78" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78" s="41" t="s"/>
+      <c r="K78" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="L78" s="40" t="s"/>
+      <c r="M78" s="43" t="s"/>
+      <c r="N78" s="41" t="s"/>
+      <c r="O78" s="59" t="s"/>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="43" t="s"/>
+      <c r="B79" s="8" t="s"/>
+      <c r="C79" s="43" t="s"/>
+      <c r="D79" s="8" t="s"/>
+      <c r="E79" s="43" t="s"/>
+      <c r="F79" s="8" t="s"/>
+      <c r="G79" s="43" t="s"/>
+      <c r="H79" s="41" t="s"/>
+      <c r="I79" s="43" t="s"/>
+      <c r="J79" s="41" t="s"/>
+      <c r="K79" s="43" t="s"/>
+      <c r="L79" s="40" t="s"/>
+      <c r="M79" s="39" t="s"/>
+      <c r="N79" s="41" t="s"/>
+      <c r="O79" s="59" t="s"/>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="39" t="s"/>
+      <c r="B80" s="8" t="s"/>
+      <c r="C80" s="39" t="s"/>
+      <c r="D80" s="8" t="s"/>
+      <c r="E80" s="39" t="s"/>
+      <c r="F80" s="8" t="s"/>
+      <c r="G80" s="39" t="s"/>
+      <c r="H80" s="70" t="s"/>
+      <c r="I80" s="39" t="s"/>
+      <c r="J80" s="70" t="s"/>
+      <c r="K80" s="39" t="s"/>
+      <c r="L80" s="40" t="s"/>
+      <c r="M80" s="39" t="s"/>
+      <c r="N80" s="41" t="s"/>
+      <c r="O80" s="59" t="s"/>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" s="39" t="s"/>
+      <c r="B81" s="8" t="s"/>
+      <c r="C81" s="39" t="s"/>
+      <c r="D81" s="8" t="s"/>
+      <c r="E81" s="39" t="s"/>
+      <c r="F81" s="8" t="s"/>
+      <c r="G81" s="39" t="s"/>
+      <c r="H81" s="41" t="s"/>
+      <c r="I81" s="39" t="s"/>
+      <c r="J81" s="41" t="s"/>
+      <c r="K81" s="39" t="s"/>
+      <c r="L81" s="40" t="s"/>
+      <c r="M81" s="44" t="s"/>
+      <c r="N81" s="41" t="s"/>
+      <c r="O81" s="59" t="s"/>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" s="44" t="s"/>
+      <c r="B82" s="8" t="s"/>
+      <c r="C82" s="44" t="s"/>
+      <c r="D82" s="8" t="s"/>
+      <c r="E82" s="44" t="s"/>
+      <c r="F82" s="8" t="s"/>
+      <c r="G82" s="44" t="s"/>
+      <c r="H82" s="41" t="s"/>
+      <c r="I82" s="44" t="s"/>
+      <c r="J82" s="41" t="s"/>
+      <c r="K82" s="44" t="s"/>
+      <c r="L82" s="40" t="s"/>
+      <c r="M82" s="39" t="s"/>
+      <c r="N82" s="41" t="s"/>
+      <c r="O82" s="59" t="s"/>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="39" t="s"/>
+      <c r="B83" s="8" t="s"/>
+      <c r="C83" s="39" t="s"/>
+      <c r="D83" s="8" t="s"/>
+      <c r="E83" s="39" t="s"/>
+      <c r="F83" s="8" t="s"/>
+      <c r="G83" s="39" t="s"/>
+      <c r="H83" s="41" t="s"/>
+      <c r="I83" s="8" t="s"/>
+      <c r="J83" s="8" t="s"/>
+      <c r="K83" s="39" t="s"/>
+      <c r="L83" s="40" t="s"/>
+      <c r="M83" s="39" t="s"/>
+      <c r="N83" s="41" t="s"/>
+      <c r="O83" s="59" t="s"/>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" s="63" t="s"/>
+      <c r="B84" s="64" t="s"/>
+      <c r="C84" s="63" t="s"/>
+      <c r="D84" s="64" t="s"/>
+      <c r="E84" s="63" t="s"/>
+      <c r="F84" s="64" t="s"/>
+      <c r="G84" s="63" t="s"/>
+      <c r="H84" s="65" t="s"/>
+      <c r="I84" s="64" t="s"/>
+      <c r="J84" s="64" t="s"/>
+      <c r="K84" s="63" t="s"/>
+      <c r="L84" s="64" t="s"/>
+      <c r="M84" s="63" t="s"/>
+      <c r="N84" s="65" t="s"/>
+      <c r="O84" s="66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" s="67" t="s"/>
+      <c r="B85" s="68">
+        <f>=SUM(B67:B84)</f>
+        <v>0</v>
+      </c>
+      <c r="C85" s="67" t="s"/>
+      <c r="D85" s="68">
+        <f>=SUM(D67:D84)</f>
+        <v>0</v>
+      </c>
+      <c r="E85" s="67" t="s"/>
+      <c r="F85" s="68">
+        <f>=SUM(F67:F84)</f>
+        <v>0</v>
+      </c>
+      <c r="G85" s="67">
+        <v>0</v>
+      </c>
+      <c r="H85" s="68">
+        <f>=SUM(H67:H84)</f>
+        <v>0</v>
+      </c>
+      <c r="I85" s="67" t="s"/>
+      <c r="J85" s="69">
+        <f>=SUM(J67:J84)</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="68" t="s"/>
+      <c r="L85" s="69">
+        <f>=SUM(L67:L84)</f>
+        <v>0</v>
+      </c>
+      <c r="M85" s="68" t="s"/>
+      <c r="N85" s="68">
+        <f>=SUM(N67:N84)</f>
+        <v>0</v>
+      </c>
+      <c r="O85" s="51">
+        <f>=SUM(A85:N85)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A19:N36">
@@ -7642,7 +9039,7 @@
   <sheetPr codeName="汇德国际">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K26"/>
+  <dimension ref="K35"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="11" width="12.1406" style="136" customWidth="1"/>
@@ -8069,10 +9466,10 @@
       <c r="H19" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="112">
+      <c r="I19" s="137">
         <v>46206</v>
       </c>
-      <c r="J19" s="114" t="s">
+      <c r="J19" s="138" t="s">
         <v>6</v>
       </c>
       <c r="K19" s="114" t="s"/>
@@ -8102,10 +9499,10 @@
       <c r="H20" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="118" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="119" t="s">
+      <c r="I20" s="139" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="140" t="s">
         <v>9</v>
       </c>
       <c r="K20" s="128" t="s"/>
@@ -8138,7 +9535,7 @@
       <c r="I21" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="124">
+      <c r="J21" s="128">
         <v>90</v>
       </c>
       <c r="K21" s="128" t="s"/>
@@ -8171,7 +9568,7 @@
       <c r="I22" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="J22" s="124">
+      <c r="J22" s="128">
         <v>60</v>
       </c>
       <c r="K22" s="128" t="s"/>
@@ -8204,7 +9601,7 @@
       <c r="I23" s="123" t="s">
         <v>52</v>
       </c>
-      <c r="J23" s="124">
+      <c r="J23" s="128">
         <v>60</v>
       </c>
       <c r="K23" s="128" t="s"/>
@@ -8224,7 +9621,7 @@
       <c r="J24" s="128">
         <v>10</v>
       </c>
-      <c r="K24" s="208" t="s">
+      <c r="K24" s="141" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8237,8 +9634,8 @@
       <c r="F25" s="124" t="s"/>
       <c r="G25" s="129" t="s"/>
       <c r="H25" s="124" t="s"/>
-      <c r="I25" s="137" t="s"/>
-      <c r="J25" s="138" t="s"/>
+      <c r="I25" s="142" t="s"/>
+      <c r="J25" s="143" t="s"/>
       <c r="K25" s="130" t="s">
         <v>15</v>
       </c>
@@ -8264,14 +9661,192 @@
         <f>=SUM(H20:H25)</f>
         <v>210</v>
       </c>
-      <c r="I26" s="139" t="s"/>
-      <c r="J26" s="140">
+      <c r="I26" s="144" t="s"/>
+      <c r="J26" s="145">
         <f>=SUM(J20:J25)</f>
         <v>220</v>
       </c>
       <c r="K26" s="134">
         <f>=SUM(A26:J26)</f>
         <v>1060</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="287">
+        <v>46209</v>
+      </c>
+      <c r="B28" s="288" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="287">
+        <v>46210</v>
+      </c>
+      <c r="D28" s="288" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="287">
+        <v>46211</v>
+      </c>
+      <c r="F28" s="288" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" s="287">
+        <v>46212</v>
+      </c>
+      <c r="H28" s="288" t="s">
+        <v>5</v>
+      </c>
+      <c r="I28" s="289">
+        <v>46213</v>
+      </c>
+      <c r="J28" s="290" t="s">
+        <v>6</v>
+      </c>
+      <c r="K28" s="150" t="s"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="151" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="152" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="151" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="152" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="151" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="152" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="151" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="152" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="153" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="154" t="s">
+        <v>9</v>
+      </c>
+      <c r="K29" s="155" t="s"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="156" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="157">
+        <v>120</v>
+      </c>
+      <c r="C30" s="156" t="s"/>
+      <c r="D30" s="157" t="s"/>
+      <c r="E30" s="156" t="s"/>
+      <c r="F30" s="157" t="s"/>
+      <c r="G30" s="156" t="s"/>
+      <c r="H30" s="157" t="s"/>
+      <c r="I30" s="156" t="s"/>
+      <c r="J30" s="158" t="s"/>
+      <c r="K30" s="159" t="s"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="156" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="157">
+        <v>60</v>
+      </c>
+      <c r="C31" s="156" t="s"/>
+      <c r="D31" s="157" t="s"/>
+      <c r="E31" s="156" t="s"/>
+      <c r="F31" s="157" t="s"/>
+      <c r="G31" s="156" t="s"/>
+      <c r="H31" s="157" t="s"/>
+      <c r="I31" s="156" t="s"/>
+      <c r="J31" s="158" t="s"/>
+      <c r="K31" s="159" t="s"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="156" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="157">
+        <v>60</v>
+      </c>
+      <c r="C32" s="156" t="s"/>
+      <c r="D32" s="157" t="s"/>
+      <c r="E32" s="156" t="s"/>
+      <c r="F32" s="157" t="s"/>
+      <c r="G32" s="156" t="s"/>
+      <c r="H32" s="157" t="s"/>
+      <c r="I32" s="156" t="s"/>
+      <c r="J32" s="158" t="s"/>
+      <c r="K32" s="159" t="s"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="160" t="s"/>
+      <c r="B33" s="161" t="s"/>
+      <c r="C33" s="160" t="s"/>
+      <c r="D33" s="161" t="s"/>
+      <c r="E33" s="160" t="s"/>
+      <c r="F33" s="161" t="s"/>
+      <c r="G33" s="160" t="s"/>
+      <c r="H33" s="161" t="s"/>
+      <c r="I33" s="160" t="s"/>
+      <c r="J33" s="158" t="s"/>
+      <c r="K33" s="158" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="160" t="s"/>
+      <c r="B34" s="161" t="s"/>
+      <c r="C34" s="160" t="s"/>
+      <c r="D34" s="161" t="s"/>
+      <c r="E34" s="160" t="s"/>
+      <c r="F34" s="161" t="s"/>
+      <c r="G34" s="160" t="s"/>
+      <c r="H34" s="161" t="s"/>
+      <c r="I34" s="162" t="s"/>
+      <c r="J34" s="163" t="s"/>
+      <c r="K34" s="164" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="165" t="s"/>
+      <c r="B35" s="166">
+        <f>=SUM(B29:B34)</f>
+        <v>240</v>
+      </c>
+      <c r="C35" s="165" t="s"/>
+      <c r="D35" s="166">
+        <f>=SUM(D29:D34)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="165" t="s"/>
+      <c r="F35" s="166">
+        <f>=SUM(F29:F34)</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="165" t="s"/>
+      <c r="H35" s="166">
+        <f>=SUM(H29:H34)</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="167" t="s"/>
+      <c r="J35" s="168">
+        <f>=SUM(J29:J34)</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="169">
+        <f>=SUM(A35:J35)</f>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -8290,7 +9865,7 @@
   <sheetPr codeName="北京路广百">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K27"/>
+  <dimension ref="K38"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="11" width="12.6836" customWidth="1"/>
@@ -8298,113 +9873,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="141" t="s"/>
-      <c r="B1" s="142" t="s">
+      <c r="A1" s="170" t="s"/>
+      <c r="B1" s="171" t="s">
         <v>40</v>
       </c>
       <c r="C1" s="94" t="s"/>
-      <c r="D1" s="142" t="s">
+      <c r="D1" s="171" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="94" t="s"/>
-      <c r="F1" s="142" t="s">
+      <c r="F1" s="171" t="s">
         <v>42</v>
       </c>
       <c r="G1" s="94" t="s"/>
-      <c r="H1" s="142" t="s">
+      <c r="H1" s="171" t="s">
         <v>43</v>
       </c>
       <c r="I1" s="94" t="s"/>
-      <c r="J1" s="142" t="s">
+      <c r="J1" s="171" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="94" t="s"/>
-      <c r="L1" s="143" t="s"/>
+      <c r="L1" s="172" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="144" t="s">
-        <v>53</v>
+      <c r="A2" s="173" t="s">
+        <v>54</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" s="30">
         <v>60</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" s="30">
         <v>60</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2" s="30">
         <v>60</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I2" s="30">
         <v>60</v>
       </c>
       <c r="J2" s="28" t="s"/>
       <c r="K2" s="29" t="s"/>
-      <c r="L2" s="145" t="s"/>
+      <c r="L2" s="174" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="146" t="s"/>
+      <c r="A3" s="175" t="s"/>
       <c r="B3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" s="11">
         <v>60</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="11">
         <v>60</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" s="11">
         <v>60</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3" s="11">
         <v>60</v>
       </c>
       <c r="J3" s="9" t="s"/>
       <c r="K3" s="10" t="s"/>
-      <c r="L3" s="145" t="s"/>
+      <c r="L3" s="174" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="146" t="s"/>
+      <c r="A4" s="175" t="s"/>
       <c r="B4" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="11">
         <v>60</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" s="11">
         <v>60</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" s="11">
         <v>60</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I4" s="11">
         <v>60</v>
@@ -8416,7 +9991,7 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="147" t="s"/>
+      <c r="A5" s="176" t="s"/>
       <c r="B5" s="32" t="s"/>
       <c r="C5" s="34" t="s"/>
       <c r="D5" s="32" t="s"/>
@@ -8424,14 +9999,14 @@
       <c r="F5" s="32" t="s"/>
       <c r="G5" s="34" t="s"/>
       <c r="H5" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I5" s="34">
         <v>10</v>
       </c>
       <c r="J5" s="32" t="s"/>
       <c r="K5" s="33" t="s"/>
-      <c r="L5" s="148">
+      <c r="L5" s="177">
         <f>=SUM(B2:K5)</f>
         <v>730</v>
       </c>
@@ -8507,31 +10082,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="136">
         <v>60</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="136">
         <v>60</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" s="136">
         <v>60</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H10" s="136">
         <v>60</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J10" s="127">
         <v>60</v>
@@ -8540,31 +10115,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B11" s="136">
         <v>60</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" s="136">
         <v>60</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="136">
         <v>60</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="136">
         <v>60</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J11" s="128">
         <v>60</v>
@@ -8573,25 +10148,25 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B12" s="136">
         <v>60</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" s="136">
         <v>60</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="136">
         <v>60</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" s="136">
         <v>60</v>
@@ -8635,8 +10210,8 @@
       <c r="F15" s="136" t="s"/>
       <c r="G15" s="129" t="s"/>
       <c r="H15" s="136" t="s"/>
-      <c r="I15" s="137" t="s"/>
-      <c r="J15" s="138" t="s"/>
+      <c r="I15" s="142" t="s"/>
+      <c r="J15" s="143" t="s"/>
       <c r="K15" s="130" t="s">
         <v>15</v>
       </c>
@@ -8662,8 +10237,8 @@
         <f>=SUM(H10:H15)</f>
         <v>180</v>
       </c>
-      <c r="I16" s="139" t="s"/>
-      <c r="J16" s="140">
+      <c r="I16" s="144" t="s"/>
+      <c r="J16" s="145">
         <f>=SUM(J10:J15)</f>
         <v>120</v>
       </c>
@@ -8743,31 +10318,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="136">
         <v>60</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D21" s="136">
         <v>60</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F21" s="136">
         <v>60</v>
       </c>
       <c r="G21" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H21" s="136">
         <v>60</v>
       </c>
       <c r="I21" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J21" s="127">
         <v>60</v>
@@ -8776,31 +10351,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="136">
         <v>60</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="136">
         <v>60</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F22" s="136">
         <v>60</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H22" s="136">
         <v>60</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J22" s="128">
         <v>60</v>
@@ -8809,31 +10384,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="136">
         <v>60</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D23" s="136">
         <v>60</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" s="136">
         <v>60</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H23" s="136">
         <v>60</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J23" s="128">
         <v>60</v>
@@ -8850,7 +10425,7 @@
       <c r="G24" s="129" t="s"/>
       <c r="H24" s="136" t="s"/>
       <c r="I24" s="53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J24" s="127">
         <v>60</v>
@@ -8881,8 +10456,8 @@
       <c r="F26" s="136" t="s"/>
       <c r="G26" s="129" t="s"/>
       <c r="H26" s="136" t="s"/>
-      <c r="I26" s="137" t="s"/>
-      <c r="J26" s="138" t="s"/>
+      <c r="I26" s="142" t="s"/>
+      <c r="J26" s="143" t="s"/>
       <c r="K26" s="130" t="s">
         <v>15</v>
       </c>
@@ -8908,14 +10483,217 @@
         <f>=SUM(H21:H26)</f>
         <v>180</v>
       </c>
-      <c r="I27" s="139" t="s"/>
-      <c r="J27" s="140">
+      <c r="I27" s="144" t="s"/>
+      <c r="J27" s="145">
         <f>=SUM(J21:J26)</f>
         <v>240</v>
       </c>
       <c r="K27" s="134">
         <f>=SUM(A27:J27)</f>
         <v>960</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4">
+        <v>46210</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
+        <v>46211</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="4">
+        <v>46212</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I30" s="4">
+        <v>46213</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K30" s="6" t="s"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="H31" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="I31" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="K31" s="65" t="s"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="136">
+        <v>60</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="136">
+        <v>60</v>
+      </c>
+      <c r="E32" s="53" t="s"/>
+      <c r="F32" s="136" t="s"/>
+      <c r="G32" s="53" t="s"/>
+      <c r="H32" s="136" t="s"/>
+      <c r="I32" s="53" t="s"/>
+      <c r="J32" s="127" t="s"/>
+      <c r="K32" s="128" t="s"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="136">
+        <v>60</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="136">
+        <v>60</v>
+      </c>
+      <c r="E33" s="39" t="s"/>
+      <c r="F33" s="136" t="s"/>
+      <c r="G33" s="39" t="s"/>
+      <c r="H33" s="136" t="s"/>
+      <c r="I33" s="39" t="s"/>
+      <c r="J33" s="128" t="s"/>
+      <c r="K33" s="128" t="s"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="136">
+        <v>60</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="136">
+        <v>60</v>
+      </c>
+      <c r="E34" s="39" t="s"/>
+      <c r="F34" s="136" t="s"/>
+      <c r="G34" s="39" t="s"/>
+      <c r="H34" s="136" t="s"/>
+      <c r="I34" s="39" t="s"/>
+      <c r="J34" s="128" t="s"/>
+      <c r="K34" s="128" t="s"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="129" t="s"/>
+      <c r="B35" s="136" t="s"/>
+      <c r="C35" s="129" t="s"/>
+      <c r="D35" s="136" t="s"/>
+      <c r="E35" s="129" t="s"/>
+      <c r="F35" s="136" t="s"/>
+      <c r="G35" s="129" t="s"/>
+      <c r="H35" s="136" t="s"/>
+      <c r="I35" s="39" t="s"/>
+      <c r="J35" s="128" t="s"/>
+      <c r="K35" s="128" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="129" t="s"/>
+      <c r="B36" s="136" t="s"/>
+      <c r="C36" s="129" t="s"/>
+      <c r="D36" s="136" t="s"/>
+      <c r="E36" s="129" t="s"/>
+      <c r="F36" s="136" t="s"/>
+      <c r="G36" s="129" t="s"/>
+      <c r="H36" s="136" t="s"/>
+      <c r="I36" s="129" t="s"/>
+      <c r="J36" s="128" t="s"/>
+      <c r="K36" s="128" t="s"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="129" t="s"/>
+      <c r="B37" s="136" t="s"/>
+      <c r="C37" s="129" t="s"/>
+      <c r="D37" s="136" t="s"/>
+      <c r="E37" s="129" t="s"/>
+      <c r="F37" s="136" t="s"/>
+      <c r="G37" s="129" t="s"/>
+      <c r="H37" s="136" t="s"/>
+      <c r="I37" s="142" t="s"/>
+      <c r="J37" s="143" t="s"/>
+      <c r="K37" s="130" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="131" t="s"/>
+      <c r="B38" s="132">
+        <f>=SUM(B32:B37)</f>
+        <v>180</v>
+      </c>
+      <c r="C38" s="131" t="s"/>
+      <c r="D38" s="132">
+        <f>=SUM(D32:D37)</f>
+        <v>180</v>
+      </c>
+      <c r="E38" s="131" t="s"/>
+      <c r="F38" s="132">
+        <f>=SUM(F32:F37)</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="131" t="s"/>
+      <c r="H38" s="132">
+        <f>=SUM(H32:H37)</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="144" t="s"/>
+      <c r="J38" s="145">
+        <f>=SUM(J32:J37)</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="134">
+        <f>=SUM(A38:J38)</f>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -8942,123 +10720,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A1" s="149" t="s"/>
-      <c r="B1" s="142">
+      <c r="A1" s="178" t="s"/>
+      <c r="B1" s="171">
         <v>46188</v>
       </c>
-      <c r="C1" s="150" t="s">
+      <c r="C1" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="142">
+      <c r="D1" s="171">
         <v>46189</v>
       </c>
-      <c r="E1" s="150" t="s">
+      <c r="E1" s="179" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="142">
+      <c r="F1" s="171">
         <v>46190</v>
       </c>
-      <c r="G1" s="150" t="s">
+      <c r="G1" s="179" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="142">
+      <c r="H1" s="171">
         <v>46191</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="179" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="93">
         <v>46192</v>
       </c>
-      <c r="K1" s="151" t="s">
-        <v>58</v>
-      </c>
-      <c r="L1" s="143" t="s"/>
+      <c r="K1" s="180" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="172" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="152" t="s">
-        <v>59</v>
+      <c r="A2" s="181" t="s">
+        <v>60</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" s="30">
         <v>90</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" s="30">
         <v>90</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2" s="30">
         <v>90</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I2" s="30">
         <v>90</v>
       </c>
       <c r="J2" s="28" t="s"/>
       <c r="K2" s="29" t="s"/>
-      <c r="L2" s="145" t="s"/>
+      <c r="L2" s="174" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="153" t="s"/>
+      <c r="A3" s="182" t="s"/>
       <c r="B3" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" s="11">
         <v>90</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" s="11">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I3" s="11">
         <v>90</v>
       </c>
       <c r="J3" s="9" t="s"/>
       <c r="K3" s="10" t="s"/>
-      <c r="L3" s="145" t="s"/>
+      <c r="L3" s="174" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="153" t="s"/>
+      <c r="A4" s="182" t="s"/>
       <c r="B4" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" s="11">
         <v>60</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="11">
         <v>60</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4" s="11">
         <v>60</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4" s="11">
         <v>60</v>
@@ -9078,14 +10856,14 @@
       <c r="F5" s="32" t="s"/>
       <c r="G5" s="34" t="s"/>
       <c r="H5" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I5" s="34">
         <v>10</v>
       </c>
       <c r="J5" s="32" t="s"/>
       <c r="K5" s="33" t="s"/>
-      <c r="L5" s="148">
+      <c r="L5" s="177">
         <f>=SUM(B2:K5)</f>
         <v>970</v>
       </c>
@@ -9161,31 +10939,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" s="136">
         <v>90</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" s="136">
         <v>90</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F10" s="136">
         <v>90</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H10" s="136">
         <v>90</v>
       </c>
       <c r="I10" s="129" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J10" s="128">
         <v>10</v>
@@ -9196,25 +10974,25 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="136">
         <v>90</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="136">
         <v>90</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" s="136">
         <v>60</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H11" s="136">
         <v>60</v>
@@ -9225,19 +11003,19 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" s="136">
         <v>60</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" s="136">
         <v>60</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F12" s="136">
         <v>60</v>
@@ -9332,7 +11110,7 @@
   <sheetPr codeName="万菱广场">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K26"/>
+  <dimension ref="K36"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="9" width="10.6523" customWidth="1"/>
@@ -9340,110 +11118,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="149" t="s"/>
-      <c r="B1" s="142" t="s">
+      <c r="A1" s="178" t="s"/>
+      <c r="B1" s="171" t="s">
         <v>40</v>
       </c>
       <c r="C1" s="94" t="s"/>
-      <c r="D1" s="142" t="s">
+      <c r="D1" s="171" t="s">
         <v>41</v>
       </c>
       <c r="E1" s="94" t="s"/>
-      <c r="F1" s="142" t="s">
+      <c r="F1" s="171" t="s">
         <v>42</v>
       </c>
       <c r="G1" s="94" t="s"/>
-      <c r="H1" s="142" t="s">
+      <c r="H1" s="171" t="s">
         <v>43</v>
       </c>
       <c r="I1" s="94" t="s"/>
-      <c r="J1" s="142" t="s">
+      <c r="J1" s="171" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="94" t="s"/>
-      <c r="L1" s="143" t="s"/>
+      <c r="L1" s="172" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="154" t="s">
-        <v>64</v>
+      <c r="A2" s="183" t="s">
+        <v>65</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="30">
         <v>90</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" s="30">
         <v>90</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="30">
         <v>90</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I2" s="29">
         <v>90</v>
       </c>
-      <c r="J2" s="155" t="s"/>
-      <c r="K2" s="156" t="s"/>
-      <c r="L2" s="157" t="s"/>
+      <c r="J2" s="184" t="s"/>
+      <c r="K2" s="185" t="s"/>
+      <c r="L2" s="186" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="158" t="s"/>
+      <c r="A3" s="187" t="s"/>
       <c r="B3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="11">
         <v>90</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" s="11">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" s="10">
         <v>90</v>
       </c>
-      <c r="J3" s="159" t="s"/>
-      <c r="K3" s="157" t="s"/>
+      <c r="J3" s="188" t="s"/>
+      <c r="K3" s="186" t="s"/>
       <c r="L3" s="105" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="160" t="s"/>
-      <c r="B4" s="160" t="s"/>
-      <c r="C4" s="161" t="s"/>
+      <c r="A4" s="189" t="s"/>
+      <c r="B4" s="189" t="s"/>
+      <c r="C4" s="190" t="s"/>
       <c r="D4" s="32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" s="34">
         <v>90</v>
       </c>
-      <c r="F4" s="160" t="s"/>
-      <c r="G4" s="161" t="s"/>
-      <c r="H4" s="160" t="s"/>
-      <c r="I4" s="162" t="s"/>
-      <c r="J4" s="163" t="s"/>
-      <c r="K4" s="164" t="s"/>
-      <c r="L4" s="165">
+      <c r="F4" s="189" t="s"/>
+      <c r="G4" s="190" t="s"/>
+      <c r="H4" s="189" t="s"/>
+      <c r="I4" s="191" t="s"/>
+      <c r="J4" s="192" t="s"/>
+      <c r="K4" s="193" t="s"/>
+      <c r="L4" s="194">
         <f>=SUM(B2:K4)</f>
         <v>810</v>
       </c>
@@ -9519,31 +11297,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="136">
         <v>90</v>
       </c>
       <c r="C9" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" s="136">
         <v>90</v>
       </c>
       <c r="E9" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" s="136">
         <v>90</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H9" s="136">
         <v>90</v>
       </c>
       <c r="I9" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J9" s="127">
         <v>90</v>
@@ -9552,31 +11330,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" s="136">
         <v>90</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" s="136">
         <v>90</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10" s="136">
         <v>90</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H10" s="136">
         <v>90</v>
       </c>
       <c r="I10" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J10" s="128">
         <v>90</v>
@@ -9631,8 +11409,8 @@
       <c r="F14" s="136" t="s"/>
       <c r="G14" s="129" t="s"/>
       <c r="H14" s="136" t="s"/>
-      <c r="I14" s="137" t="s"/>
-      <c r="J14" s="138" t="s"/>
+      <c r="I14" s="142" t="s"/>
+      <c r="J14" s="143" t="s"/>
       <c r="K14" s="130" t="s">
         <v>15</v>
       </c>
@@ -9658,8 +11436,8 @@
         <f>=SUM(H9:H14)</f>
         <v>180</v>
       </c>
-      <c r="I15" s="139" t="s"/>
-      <c r="J15" s="140">
+      <c r="I15" s="144" t="s"/>
+      <c r="J15" s="145">
         <f>=SUM(J9:J14)</f>
         <v>180</v>
       </c>
@@ -9739,31 +11517,31 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="136">
         <v>90</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" s="136">
         <v>90</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F20" s="136">
         <v>60</v>
       </c>
       <c r="G20" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H20" s="136">
         <v>60</v>
       </c>
       <c r="I20" s="53" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J20" s="127">
         <v>60</v>
@@ -9772,31 +11550,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" s="136">
         <v>90</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D21" s="136">
         <v>90</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21" s="136">
         <v>100</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="136">
         <v>90</v>
       </c>
       <c r="I21" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J21" s="128">
         <v>90</v>
@@ -9851,8 +11629,8 @@
       <c r="F25" s="136" t="s"/>
       <c r="G25" s="129" t="s"/>
       <c r="H25" s="136" t="s"/>
-      <c r="I25" s="137" t="s"/>
-      <c r="J25" s="138" t="s"/>
+      <c r="I25" s="142" t="s"/>
+      <c r="J25" s="143" t="s"/>
       <c r="K25" s="130" t="s">
         <v>15</v>
       </c>
@@ -9878,14 +11656,186 @@
         <f>=SUM(H20:H25)</f>
         <v>150</v>
       </c>
-      <c r="I26" s="139" t="s"/>
-      <c r="J26" s="140">
+      <c r="I26" s="144" t="s"/>
+      <c r="J26" s="145">
         <f>=SUM(J20:J25)</f>
         <v>150</v>
       </c>
       <c r="K26" s="134">
         <f>=SUM(A26:J26)</f>
         <v>820</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="195">
+        <v>46209</v>
+      </c>
+      <c r="B29" s="196" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="195">
+        <v>46210</v>
+      </c>
+      <c r="D29" s="196" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="195">
+        <v>46211</v>
+      </c>
+      <c r="F29" s="196" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="195">
+        <v>46212</v>
+      </c>
+      <c r="H29" s="196" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="197">
+        <v>46213</v>
+      </c>
+      <c r="J29" s="198" t="s">
+        <v>6</v>
+      </c>
+      <c r="K29" s="7" t="s"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="199" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="200" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="199" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="200" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="199" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="200" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="199" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="200" t="s">
+        <v>9</v>
+      </c>
+      <c r="I30" s="201" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" s="202" t="s">
+        <v>9</v>
+      </c>
+      <c r="K30" s="203" t="s"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="204" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="205">
+        <v>90</v>
+      </c>
+      <c r="C31" s="204" t="s"/>
+      <c r="D31" s="205" t="s"/>
+      <c r="E31" s="204" t="s"/>
+      <c r="F31" s="205" t="s"/>
+      <c r="G31" s="204" t="s"/>
+      <c r="H31" s="205" t="s"/>
+      <c r="I31" s="204" t="s"/>
+      <c r="J31" s="206" t="s"/>
+      <c r="K31" s="207" t="s"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="204" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="205">
+        <v>60</v>
+      </c>
+      <c r="C32" s="204" t="s"/>
+      <c r="D32" s="205" t="s"/>
+      <c r="E32" s="204" t="s"/>
+      <c r="F32" s="205" t="s"/>
+      <c r="G32" s="204" t="s"/>
+      <c r="H32" s="205" t="s"/>
+      <c r="I32" s="204" t="s"/>
+      <c r="J32" s="206" t="s"/>
+      <c r="K32" s="207" t="s"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="204" t="s"/>
+      <c r="B33" s="205" t="s"/>
+      <c r="C33" s="204" t="s"/>
+      <c r="D33" s="205" t="s"/>
+      <c r="E33" s="204" t="s"/>
+      <c r="F33" s="205" t="s"/>
+      <c r="G33" s="204" t="s"/>
+      <c r="H33" s="205" t="s"/>
+      <c r="I33" s="204" t="s"/>
+      <c r="J33" s="206" t="s"/>
+      <c r="K33" s="207" t="s"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="208" t="s"/>
+      <c r="B34" s="209" t="s"/>
+      <c r="C34" s="208" t="s"/>
+      <c r="D34" s="209" t="s"/>
+      <c r="E34" s="208" t="s"/>
+      <c r="F34" s="209" t="s"/>
+      <c r="G34" s="208" t="s"/>
+      <c r="H34" s="209" t="s"/>
+      <c r="I34" s="208" t="s"/>
+      <c r="J34" s="206" t="s"/>
+      <c r="K34" s="206" t="s"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="208" t="s"/>
+      <c r="B35" s="209" t="s"/>
+      <c r="C35" s="208" t="s"/>
+      <c r="D35" s="209" t="s"/>
+      <c r="E35" s="208" t="s"/>
+      <c r="F35" s="209" t="s"/>
+      <c r="G35" s="208" t="s"/>
+      <c r="H35" s="209" t="s"/>
+      <c r="I35" s="210" t="s"/>
+      <c r="J35" s="211" t="s"/>
+      <c r="K35" s="212" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="213" t="s"/>
+      <c r="B36" s="214">
+        <f>=SUM(B30:B35)</f>
+        <v>150</v>
+      </c>
+      <c r="C36" s="213" t="s"/>
+      <c r="D36" s="214">
+        <f>=SUM(D30:D35)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="213" t="s"/>
+      <c r="F36" s="214">
+        <f>=SUM(F30:F35)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="213" t="s"/>
+      <c r="H36" s="214">
+        <f>=SUM(H30:H35)</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="215" t="s"/>
+      <c r="J36" s="216">
+        <f>=SUM(J30:J35)</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="217">
+        <f>=SUM(A36:J36)</f>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -9904,7 +11854,7 @@
   <sheetPr codeName="华林国际C馆">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K16"/>
+  <dimension ref="K27"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="9" width="10.793" customWidth="1"/>
@@ -9912,95 +11862,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="149" t="s"/>
-      <c r="B1" s="142" t="s">
+      <c r="A1" s="178" t="s"/>
+      <c r="B1" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="166" t="s"/>
-      <c r="D1" s="142" t="s">
+      <c r="C1" s="218" t="s"/>
+      <c r="D1" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="166" t="s"/>
-      <c r="F1" s="142" t="s">
+      <c r="E1" s="218" t="s"/>
+      <c r="F1" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="166" t="s"/>
-      <c r="H1" s="167" t="s">
+      <c r="G1" s="218" t="s"/>
+      <c r="H1" s="219" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="168" t="s"/>
-      <c r="J1" s="142" t="s">
+      <c r="I1" s="220" t="s"/>
+      <c r="J1" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="166" t="s"/>
-      <c r="L1" s="169" t="s"/>
+      <c r="K1" s="218" t="s"/>
+      <c r="L1" s="221" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="170" t="s">
-        <v>68</v>
+      <c r="A2" s="222" t="s">
+        <v>69</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="30">
         <v>90</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" s="30">
         <v>90</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="29">
         <v>90</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I2" s="30">
         <v>45</v>
       </c>
       <c r="J2" s="94" t="s"/>
       <c r="K2" s="94" t="s"/>
-      <c r="L2" s="143" t="s"/>
+      <c r="L2" s="172" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="158" t="s"/>
-      <c r="B3" s="158" t="s"/>
-      <c r="C3" s="171" t="s"/>
+      <c r="A3" s="187" t="s"/>
+      <c r="B3" s="187" t="s"/>
+      <c r="C3" s="223" t="s"/>
       <c r="D3" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" s="10">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" s="11">
         <v>45</v>
       </c>
-      <c r="L3" s="145" t="s"/>
+      <c r="L3" s="174" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="158" t="s"/>
-      <c r="B4" s="158" t="s"/>
-      <c r="C4" s="171" t="s"/>
+      <c r="A4" s="187" t="s"/>
+      <c r="B4" s="187" t="s"/>
+      <c r="C4" s="223" t="s"/>
       <c r="D4" s="9" t="s"/>
       <c r="E4" s="11" t="s"/>
-      <c r="F4" s="158" t="s"/>
-      <c r="G4" s="172" t="s"/>
+      <c r="F4" s="187" t="s"/>
+      <c r="G4" s="224" t="s"/>
       <c r="H4" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" s="11">
         <v>20</v>
@@ -10010,18 +11960,18 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="160" t="s"/>
-      <c r="B5" s="160" t="s"/>
-      <c r="C5" s="161" t="s"/>
-      <c r="D5" s="160" t="s"/>
-      <c r="E5" s="161" t="s"/>
-      <c r="F5" s="160" t="s"/>
-      <c r="G5" s="162" t="s"/>
+      <c r="A5" s="189" t="s"/>
+      <c r="B5" s="189" t="s"/>
+      <c r="C5" s="190" t="s"/>
+      <c r="D5" s="189" t="s"/>
+      <c r="E5" s="190" t="s"/>
+      <c r="F5" s="189" t="s"/>
+      <c r="G5" s="191" t="s"/>
       <c r="H5" s="32" t="s"/>
       <c r="I5" s="34" t="s"/>
-      <c r="J5" s="173" t="s"/>
-      <c r="K5" s="173" t="s"/>
-      <c r="L5" s="148">
+      <c r="J5" s="225" t="s"/>
+      <c r="K5" s="225" t="s"/>
+      <c r="L5" s="177">
         <f>=SUM(B2:K5)</f>
         <v>560</v>
       </c>
@@ -10083,13 +12033,13 @@
       <c r="E10" s="53" t="s"/>
       <c r="F10" s="136" t="s"/>
       <c r="G10" s="53" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H10" s="136">
         <v>90</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J10" s="127">
         <v>90</v>
@@ -10104,13 +12054,13 @@
       <c r="E11" s="39" t="s"/>
       <c r="F11" s="136" t="s"/>
       <c r="G11" s="39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H11" s="136">
         <v>90</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J11" s="128">
         <v>60</v>
@@ -10127,7 +12077,7 @@
       <c r="G12" s="39" t="s"/>
       <c r="H12" s="136" t="s"/>
       <c r="I12" s="129" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="J12" s="128">
         <v>5</v>
@@ -10171,8 +12121,8 @@
       <c r="F15" s="136" t="s"/>
       <c r="G15" s="129" t="s"/>
       <c r="H15" s="136" t="s"/>
-      <c r="I15" s="137" t="s"/>
-      <c r="J15" s="138" t="s"/>
+      <c r="I15" s="142" t="s"/>
+      <c r="J15" s="143" t="s"/>
       <c r="K15" s="130" t="s"/>
     </row>
     <row r="16" spans="1:11">
@@ -10196,14 +12146,181 @@
         <f>=SUM(H10:H15)</f>
         <v>180</v>
       </c>
-      <c r="I16" s="139" t="s"/>
-      <c r="J16" s="140">
+      <c r="I16" s="144" t="s"/>
+      <c r="J16" s="145">
         <f>=SUM(J10:J15)</f>
         <v>155</v>
       </c>
       <c r="K16" s="134">
         <f>=SUM(A16:J16)</f>
         <v>335</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="4">
+        <v>46210</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="4">
+        <v>46211</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46212</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I19" s="4">
+        <v>46213</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="6" t="s"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="63" t="s"/>
+      <c r="B20" s="64" t="s"/>
+      <c r="C20" s="63" t="s"/>
+      <c r="D20" s="64" t="s"/>
+      <c r="E20" s="63" t="s"/>
+      <c r="F20" s="64" t="s"/>
+      <c r="G20" s="63" t="s"/>
+      <c r="H20" s="64" t="s"/>
+      <c r="I20" s="39" t="s"/>
+      <c r="J20" s="41" t="s"/>
+      <c r="K20" s="65" t="s"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="136">
+        <v>120</v>
+      </c>
+      <c r="C21" s="53" t="s"/>
+      <c r="D21" s="136" t="s"/>
+      <c r="E21" s="53" t="s"/>
+      <c r="F21" s="136" t="s"/>
+      <c r="G21" s="53" t="s"/>
+      <c r="H21" s="136" t="s"/>
+      <c r="I21" s="53" t="s"/>
+      <c r="J21" s="127" t="s"/>
+      <c r="K21" s="128" t="s"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="136">
+        <v>60</v>
+      </c>
+      <c r="C22" s="39" t="s"/>
+      <c r="D22" s="136" t="s"/>
+      <c r="E22" s="39" t="s"/>
+      <c r="F22" s="136" t="s"/>
+      <c r="G22" s="39" t="s"/>
+      <c r="H22" s="136" t="s"/>
+      <c r="I22" s="39" t="s"/>
+      <c r="J22" s="128" t="s"/>
+      <c r="K22" s="128" t="s"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="136">
+        <v>60</v>
+      </c>
+      <c r="C23" s="39" t="s"/>
+      <c r="D23" s="136" t="s"/>
+      <c r="E23" s="39" t="s"/>
+      <c r="F23" s="136" t="s"/>
+      <c r="G23" s="39" t="s"/>
+      <c r="H23" s="136" t="s"/>
+      <c r="I23" s="129" t="s"/>
+      <c r="J23" s="128" t="s"/>
+      <c r="K23" s="128" t="s"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="129" t="s"/>
+      <c r="B24" s="136" t="s"/>
+      <c r="C24" s="129" t="s"/>
+      <c r="D24" s="136" t="s"/>
+      <c r="E24" s="129" t="s"/>
+      <c r="F24" s="136" t="s"/>
+      <c r="G24" s="129" t="s"/>
+      <c r="H24" s="136" t="s"/>
+      <c r="I24" s="129" t="s"/>
+      <c r="J24" s="128" t="s"/>
+      <c r="K24" s="128" t="s"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="129" t="s"/>
+      <c r="B25" s="136" t="s"/>
+      <c r="C25" s="129" t="s"/>
+      <c r="D25" s="136" t="s"/>
+      <c r="E25" s="129" t="s"/>
+      <c r="F25" s="136" t="s"/>
+      <c r="G25" s="129" t="s"/>
+      <c r="H25" s="136" t="s"/>
+      <c r="I25" s="129" t="s"/>
+      <c r="J25" s="128" t="s"/>
+      <c r="K25" s="128" t="s"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="129" t="s"/>
+      <c r="B26" s="136" t="s"/>
+      <c r="C26" s="129" t="s"/>
+      <c r="D26" s="136" t="s"/>
+      <c r="E26" s="129" t="s"/>
+      <c r="F26" s="136" t="s"/>
+      <c r="G26" s="129" t="s"/>
+      <c r="H26" s="136" t="s"/>
+      <c r="I26" s="142" t="s"/>
+      <c r="J26" s="143" t="s"/>
+      <c r="K26" s="130" t="s"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="131" t="s"/>
+      <c r="B27" s="132">
+        <f>=SUM(B21:B26)</f>
+        <v>240</v>
+      </c>
+      <c r="C27" s="131" t="s"/>
+      <c r="D27" s="132">
+        <f>=SUM(D21:D26)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="131" t="s"/>
+      <c r="F27" s="132">
+        <f>=SUM(F21:F26)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="131" t="s"/>
+      <c r="H27" s="132">
+        <f>=SUM(H21:H26)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="144" t="s"/>
+      <c r="J27" s="145">
+        <f>=SUM(J21:J26)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="134">
+        <f>=SUM(A27:J27)</f>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -10222,7 +12339,7 @@
   <sheetPr codeName="和业广场">
     <tabColor/>
   </sheetPr>
-  <dimension ref="K27"/>
+  <dimension ref="K37"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="11" width="10.793" customWidth="1"/>
@@ -10230,132 +12347,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="149" t="s"/>
-      <c r="B1" s="142" t="s">
+      <c r="A1" s="178" t="s"/>
+      <c r="B1" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="166" t="s"/>
-      <c r="D1" s="142" t="s">
+      <c r="C1" s="218" t="s"/>
+      <c r="D1" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="166" t="s"/>
-      <c r="F1" s="142" t="s">
+      <c r="E1" s="218" t="s"/>
+      <c r="F1" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="166" t="s"/>
-      <c r="H1" s="142" t="s">
+      <c r="G1" s="218" t="s"/>
+      <c r="H1" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="166" t="s"/>
-      <c r="J1" s="142" t="s">
+      <c r="I1" s="218" t="s"/>
+      <c r="J1" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="166" t="s"/>
-      <c r="L1" s="169" t="s"/>
+      <c r="K1" s="218" t="s"/>
+      <c r="L1" s="221" t="s"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="152" t="s">
-        <v>75</v>
+      <c r="A2" s="181" t="s">
+        <v>79</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C2" s="30">
         <v>90</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E2" s="30">
         <v>90</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G2" s="30">
         <v>90</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I2" s="30">
         <v>90</v>
       </c>
-      <c r="J2" s="174" t="s"/>
-      <c r="K2" s="175" t="s"/>
-      <c r="L2" s="145" t="s"/>
+      <c r="J2" s="226" t="s"/>
+      <c r="K2" s="227" t="s"/>
+      <c r="L2" s="174" t="s"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="158" t="s"/>
+      <c r="A3" s="187" t="s"/>
       <c r="B3" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C3" s="11">
         <v>90</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E3" s="11">
         <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G3" s="11">
         <v>90</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I3" s="11">
         <v>90</v>
       </c>
-      <c r="J3" s="158" t="s"/>
-      <c r="K3" s="172" t="s"/>
-      <c r="L3" s="145" t="s"/>
+      <c r="J3" s="187" t="s"/>
+      <c r="K3" s="224" t="s"/>
+      <c r="L3" s="174" t="s"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="158" t="s"/>
-      <c r="B4" s="158" t="s"/>
-      <c r="C4" s="171" t="s"/>
-      <c r="D4" s="158" t="s"/>
-      <c r="E4" s="171" t="s"/>
+      <c r="A4" s="187" t="s"/>
+      <c r="B4" s="187" t="s"/>
+      <c r="C4" s="223" t="s"/>
+      <c r="D4" s="187" t="s"/>
+      <c r="E4" s="223" t="s"/>
       <c r="F4" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G4" s="11">
         <v>90</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I4" s="11">
         <v>90</v>
       </c>
-      <c r="J4" s="158" t="s"/>
-      <c r="K4" s="172" t="s"/>
+      <c r="J4" s="187" t="s"/>
+      <c r="K4" s="224" t="s"/>
       <c r="L4" s="105" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="160" t="s"/>
-      <c r="B5" s="160" t="s"/>
-      <c r="C5" s="161" t="s"/>
-      <c r="D5" s="160" t="s"/>
-      <c r="E5" s="161" t="s"/>
-      <c r="F5" s="160" t="s"/>
-      <c r="G5" s="161" t="s"/>
+      <c r="A5" s="189" t="s"/>
+      <c r="B5" s="189" t="s"/>
+      <c r="C5" s="190" t="s"/>
+      <c r="D5" s="189" t="s"/>
+      <c r="E5" s="190" t="s"/>
+      <c r="F5" s="189" t="s"/>
+      <c r="G5" s="190" t="s"/>
       <c r="H5" s="32" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I5" s="34">
         <v>10</v>
       </c>
-      <c r="J5" s="160" t="s"/>
-      <c r="K5" s="162" t="s"/>
-      <c r="L5" s="148">
+      <c r="J5" s="189" t="s"/>
+      <c r="K5" s="191" t="s"/>
+      <c r="L5" s="177">
         <f>=SUM(B2:K5)</f>
         <v>910</v>
       </c>
@@ -10431,31 +12548,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B10" s="54">
         <v>90</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D10" s="54">
         <v>90</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F10" s="54">
         <v>60</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H10" s="54">
         <v>60</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J10" s="54">
         <v>60</v>
@@ -10464,31 +12581,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B11" s="41">
         <v>90</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D11" s="41">
         <v>90</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F11" s="41">
         <v>90</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H11" s="41">
         <v>90</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J11" s="41">
         <v>90</v>
@@ -10497,31 +12614,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B12" s="41">
         <v>90</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D12" s="41">
         <v>90</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F12" s="41">
         <v>60</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H12" s="41">
         <v>60</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J12" s="41">
         <v>60</v>
@@ -10538,7 +12655,7 @@
       <c r="G13" s="129" t="s"/>
       <c r="H13" s="136" t="s"/>
       <c r="I13" s="129" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J13" s="128">
         <v>60</v>
@@ -10675,31 +12792,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B21" s="54">
         <v>60</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D21" s="54">
         <v>60</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F21" s="54">
         <v>60</v>
       </c>
       <c r="G21" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H21" s="54">
         <v>60</v>
       </c>
       <c r="I21" s="53" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J21" s="54">
         <v>60</v>
@@ -10708,31 +12825,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B22" s="41">
         <v>90</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D22" s="41">
         <v>90</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F22" s="41">
         <v>90</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H22" s="41">
         <v>90</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J22" s="41">
         <v>90</v>
@@ -10741,31 +12858,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B23" s="41">
         <v>60</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D23" s="41">
         <v>60</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F23" s="41">
         <v>60</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H23" s="41">
         <v>60</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J23" s="41">
         <v>60</v>
@@ -10774,31 +12891,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="129" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B24" s="128">
         <v>60</v>
       </c>
       <c r="C24" s="129" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D24" s="128">
         <v>60</v>
       </c>
       <c r="E24" s="129" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F24" s="128">
         <v>60</v>
       </c>
       <c r="G24" s="129" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H24" s="128">
         <v>60</v>
       </c>
       <c r="I24" s="129" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J24" s="128">
         <v>60</v>
@@ -10815,12 +12932,12 @@
       <c r="G25" s="129" t="s"/>
       <c r="H25" s="136" t="s"/>
       <c r="I25" s="129" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J25" s="128">
         <v>60</v>
       </c>
-      <c r="K25" s="130" t="s"/>
+      <c r="K25" s="299" t="s"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="129" t="s"/>
@@ -10832,7 +12949,7 @@
       <c r="G26" s="129" t="s"/>
       <c r="H26" s="136" t="s"/>
       <c r="I26" s="39" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J26" s="128">
         <v>10</v>
@@ -10868,6 +12985,187 @@
       <c r="K27" s="134">
         <f>=SUM(A27:J27)</f>
         <v>1420</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="195">
+        <v>46209</v>
+      </c>
+      <c r="B29" s="196" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="195">
+        <v>46210</v>
+      </c>
+      <c r="D29" s="196" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="195">
+        <v>46211</v>
+      </c>
+      <c r="F29" s="196" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="195">
+        <v>46212</v>
+      </c>
+      <c r="H29" s="196" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="197">
+        <v>46213</v>
+      </c>
+      <c r="J29" s="198" t="s">
+        <v>6</v>
+      </c>
+      <c r="K29" s="7" t="s"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="209">
+        <v>120</v>
+      </c>
+      <c r="C30" s="28" t="s"/>
+      <c r="D30" s="209" t="s"/>
+      <c r="E30" s="28" t="s"/>
+      <c r="F30" s="209" t="s"/>
+      <c r="G30" s="28" t="s"/>
+      <c r="H30" s="209" t="s"/>
+      <c r="I30" s="229" t="s"/>
+      <c r="J30" s="230" t="s"/>
+      <c r="K30" s="203" t="s"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="209">
+        <v>60</v>
+      </c>
+      <c r="C31" s="9" t="s"/>
+      <c r="D31" s="209" t="s"/>
+      <c r="E31" s="9" t="s"/>
+      <c r="F31" s="209" t="s"/>
+      <c r="G31" s="9" t="s"/>
+      <c r="H31" s="209" t="s"/>
+      <c r="I31" s="9" t="s"/>
+      <c r="J31" s="203" t="s"/>
+      <c r="K31" s="203" t="s"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="209">
+        <v>60</v>
+      </c>
+      <c r="C32" s="9" t="s"/>
+      <c r="D32" s="209" t="s"/>
+      <c r="E32" s="9" t="s"/>
+      <c r="F32" s="209" t="s"/>
+      <c r="G32" s="9" t="s"/>
+      <c r="H32" s="209" t="s"/>
+      <c r="I32" s="208" t="s"/>
+      <c r="J32" s="203" t="s"/>
+      <c r="K32" s="203" t="s"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="208" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="209">
+        <v>60</v>
+      </c>
+      <c r="C33" s="208" t="s"/>
+      <c r="D33" s="209" t="s"/>
+      <c r="E33" s="208" t="s"/>
+      <c r="F33" s="209" t="s"/>
+      <c r="G33" s="208" t="s"/>
+      <c r="H33" s="209" t="s"/>
+      <c r="I33" s="208" t="s"/>
+      <c r="J33" s="203" t="s"/>
+      <c r="K33" s="203" t="s"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="208" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="209">
+        <v>60</v>
+      </c>
+      <c r="C34" s="208" t="s"/>
+      <c r="D34" s="209" t="s"/>
+      <c r="E34" s="208" t="s"/>
+      <c r="F34" s="209" t="s"/>
+      <c r="G34" s="208" t="s"/>
+      <c r="H34" s="209" t="s"/>
+      <c r="I34" s="208" t="s"/>
+      <c r="J34" s="203" t="s"/>
+      <c r="K34" s="203" t="s"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="208" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="209">
+        <v>60</v>
+      </c>
+      <c r="C35" s="208" t="s"/>
+      <c r="D35" s="209" t="s"/>
+      <c r="E35" s="208" t="s"/>
+      <c r="F35" s="209" t="s"/>
+      <c r="G35" s="208" t="s"/>
+      <c r="H35" s="209" t="s"/>
+      <c r="I35" s="208" t="s"/>
+      <c r="J35" s="203" t="s"/>
+      <c r="K35" s="298" t="s"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="291" t="s"/>
+      <c r="B36" s="292" t="s"/>
+      <c r="C36" s="291" t="s"/>
+      <c r="D36" s="292" t="s"/>
+      <c r="E36" s="291" t="s"/>
+      <c r="F36" s="292" t="s"/>
+      <c r="G36" s="291" t="s"/>
+      <c r="H36" s="292" t="s"/>
+      <c r="I36" s="293" t="s"/>
+      <c r="J36" s="294" t="s"/>
+      <c r="K36" s="297" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="213" t="s"/>
+      <c r="B37" s="214">
+        <f>=SUM(B30:B36)</f>
+        <v>420</v>
+      </c>
+      <c r="C37" s="213" t="s"/>
+      <c r="D37" s="214">
+        <f>=SUM(D30:D36)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="213" t="s"/>
+      <c r="F37" s="214">
+        <f>=SUM(F30:F36)</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="213" t="s"/>
+      <c r="H37" s="214">
+        <f>=SUM(H30:H36)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="215" t="s"/>
+      <c r="J37" s="216">
+        <f>=SUM(J30:J36)</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="217">
+        <f>=SUM(A37:J37)</f>
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <si>
     <t/>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>已结清</t>
+  </si>
+  <si>
+    <t>卢倚群</t>
   </si>
   <si>
     <t>陈贤乡</t>
@@ -143,9 +146,6 @@
     <t>黄晓琳</t>
   </si>
   <si>
-    <t>申请中</t>
-  </si>
-  <si>
     <t>星期五
 (端午假期)</t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>黄沐芸</t>
-  </si>
-  <si>
-    <t>合</t>
   </si>
   <si>
     <t>蔡文（物料保管）</t>
@@ -189,9 +186,6 @@
     <t>泽泽</t>
   </si>
   <si>
-    <t>金鹰大厦</t>
-  </si>
-  <si>
     <t>蔡嘉成</t>
   </si>
   <si>
@@ -202,6 +196,15 @@
   </si>
   <si>
     <t>蔡嘉成（物料保管）</t>
+  </si>
+  <si>
+    <t>廖燕锋</t>
+  </si>
+  <si>
+    <t>胡文轩</t>
+  </si>
+  <si>
+    <t>吴恒志</t>
   </si>
   <si>
     <t>2026/6/15星期一</t>
@@ -220,21 +223,6 @@
 (端午假期)</t>
   </si>
   <si>
-    <t>万菱广场</t>
-  </si>
-  <si>
-    <t>廖燕锋</t>
-  </si>
-  <si>
-    <t>胡文轩</t>
-  </si>
-  <si>
-    <t>吴恒志</t>
-  </si>
-  <si>
-    <t>华林国际C馆</t>
-  </si>
-  <si>
     <t>黄丹</t>
   </si>
   <si>
@@ -245,6 +233,9 @@
   </si>
   <si>
     <t>黄丹（物料保管-小卖部代交）</t>
+  </si>
+  <si>
+    <t>合</t>
   </si>
   <si>
     <t>曹文杰</t>
@@ -260,9 +251,6 @@
   </si>
   <si>
     <t>陈慧仪</t>
-  </si>
-  <si>
-    <t>和业广场</t>
   </si>
   <si>
     <t>张子慧</t>
@@ -322,7 +310,16 @@
     <t>温凯瀚</t>
   </si>
   <si>
+    <t>童瑞锋</t>
+  </si>
+  <si>
+    <t>李学文</t>
+  </si>
+  <si>
     <t>王艺勋</t>
+  </si>
+  <si>
+    <t>黄国邦</t>
   </si>
   <si>
     <t>卢嘉伟</t>
@@ -387,6 +384,15 @@
   <si>
     <t>7月</t>
   </si>
+  <si>
+    <t>支出</t>
+  </si>
+  <si>
+    <t>手续费</t>
+  </si>
+  <si>
+    <t>侯源</t>
+  </si>
 </sst>
 </file>
 
@@ -438,12 +444,12 @@
     <font>
       <color rgb="FF000000"/>
     </font>
+    <font/>
     <font>
       <name val="Microsoft YaHei"/>
     </font>
-    <font/>
   </fonts>
-  <fills count="17">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,11 +486,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
@@ -501,26 +502,9 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFBDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4B183"/>
-        <bgColor rgb="FFF4B183"/>
-      </patternFill>
-    </fill>
     <fill/>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="50">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -723,6 +707,17 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
     <border diagonalUp="1" diagonalDown="1">
       <left/>
       <right/>
@@ -732,6 +727,15 @@
     </border>
     <border/>
     <border/>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
     <border>
       <left/>
       <top style="medium">
@@ -832,22 +836,13 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs>
-    <xf fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="328">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1115,31 +1110,34 @@
     <xf fontId="3" fillId="0" borderId="30" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="0" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
     <xf numFmtId="58" fontId="3" fillId="0" borderId="10" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
     <xf numFmtId="58" fontId="3" fillId="0" borderId="5" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="9" borderId="14" xfId="0">
+    <xf fontId="3" fillId="0" borderId="31" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="32" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="8" borderId="14" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="9" borderId="14" xfId="0">
+    <xf numFmtId="300" fontId="3" fillId="8" borderId="14" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="9" borderId="14" xfId="0">
+    <xf numFmtId="300" fontId="3" fillId="8" borderId="14" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0"/>
     </xf>
-    <xf numFmtId="300" fontId="3" fillId="9" borderId="14" xfId="0">
+    <xf numFmtId="300" fontId="3" fillId="8" borderId="14" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="16" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="7" fillId="10" borderId="31" xfId="0">
+    <xf fontId="7" fillId="9" borderId="33" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="13" xfId="0">
@@ -1163,469 +1161,502 @@
     <xf fontId="3" fillId="0" borderId="5" xfId="0">
       <alignment vertical="center" textRotation="0" wrapText="0"/>
     </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="11" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="1" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="2" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="7" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="8" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="10" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="34" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="35" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="1" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="2" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="3" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="3" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="7" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="9" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="2" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="11" borderId="14" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="11" borderId="14" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="11" borderId="14" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="11" borderId="14" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="1" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="2" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="7" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="8" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="5" borderId="10" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="8" fillId="5" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="14" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="11" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="8" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="8" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" xfId="0">
+      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="2" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="4" borderId="9" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="3" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="8" borderId="13" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="16" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="14" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="6" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="11" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="6" xfId="0">
+    <xf fontId="9" fillId="10" borderId="1" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
+    <xf fontId="9" fillId="10" borderId="36" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="9" fillId="10" borderId="2" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="10" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="14" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="16" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="11" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="12" xfId="0">
+      <alignment vertical="bottom" textRotation="0"/>
+    </xf>
+    <xf fontId="9" fillId="6" borderId="10" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="6" xfId="0">
+      <alignment vertical="center" wrapText="0"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="7" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="1" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="2" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="7" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="9" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="3" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
+    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="2" borderId="6" xfId="0">
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="0" borderId="37" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="3" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="32" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="33" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
+    <xf fontId="0" fillId="0" borderId="10" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="10" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="10" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="6" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="1" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="2" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="3" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="3" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="3" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="7" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="9" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
-      <alignment horizontal="left" vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
-      <alignment horizontal="left" vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="3" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="3" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    <xf fontId="0" fillId="6" borderId="11" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="10" borderId="8" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="6" borderId="12" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="2" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="14" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="15" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="6" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    <xf fontId="0" fillId="0" borderId="5" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="4" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf fontId="0" fillId="10" borderId="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="7" xfId="0">
+    <xf fontId="0" fillId="10" borderId="2" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="6" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="2" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="9" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="3" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="12" borderId="14" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="12" borderId="14" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="12" borderId="14" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="12" borderId="14" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="9" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="4" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="12" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="14" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="13" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="9" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="1" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="2" xfId="0">
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="15" xfId="0">
-      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="3" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="6" xfId="0">
-      <alignment horizontal="right" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="6" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="2" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="4" borderId="9" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="3" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="14" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="300" fontId="3" fillId="9" borderId="13" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="16" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="14" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="6" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="14" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="6" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="7" borderId="6" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="2" borderId="6" xfId="0">
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </xf>
-    <xf numFmtId="58" fontId="3" fillId="0" borderId="34" xfId="0">
-      <alignment vertical="center" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="10" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="11" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="5" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="8" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="12" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="301" fontId="0" fillId="0" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="2" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="301" fontId="0" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="301" fontId="0" fillId="0" borderId="14" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="301" fontId="0" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="5" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="2" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="3" xfId="0">
+    <xf fontId="0" fillId="10" borderId="3" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="6" borderId="9" xfId="0">
@@ -1634,76 +1665,76 @@
     <xf fontId="0" fillId="6" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="15" borderId="2" xfId="0">
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="12" borderId="2" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf numFmtId="58" fontId="3" fillId="15" borderId="3" xfId="0">
+    <xf numFmtId="58" fontId="3" fillId="12" borderId="3" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="3" fillId="15" borderId="13" xfId="0">
+    <xf fontId="3" fillId="12" borderId="13" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="35" xfId="0">
+    <xf fontId="9" fillId="0" borderId="38" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="36" xfId="0">
+    <xf fontId="3" fillId="0" borderId="39" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="38" xfId="0">
+    <xf fontId="9" fillId="0" borderId="41" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="39" xfId="0">
+    <xf fontId="9" fillId="0" borderId="42" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="40" xfId="0">
+    <xf fontId="3" fillId="0" borderId="43" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="41" xfId="0">
+    <xf fontId="9" fillId="0" borderId="44" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="6" xfId="0">
+    <xf fontId="9" fillId="0" borderId="6" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="40" xfId="0">
+    <xf fontId="9" fillId="0" borderId="43" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="42" xfId="0">
+    <xf fontId="9" fillId="0" borderId="45" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="43" xfId="0">
+    <xf fontId="9" fillId="0" borderId="46" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="44" xfId="0">
+    <xf fontId="9" fillId="0" borderId="47" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="45" xfId="0">
+    <xf fontId="9" fillId="0" borderId="48" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="0" borderId="46" xfId="0">
+    <xf fontId="9" fillId="0" borderId="49" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
     <xf fontId="8" fillId="7" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="10" fillId="11" borderId="1" xfId="0">
+    <xf fontId="9" fillId="10" borderId="50" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="11" borderId="2" xfId="0">
+    <xf fontId="9" fillId="10" borderId="51" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="10" fillId="11" borderId="47" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="10" fillId="11" borderId="48" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="10" fillId="6" borderId="3" xfId="0">
+    <xf fontId="9" fillId="6" borderId="3" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
     <xf fontId="3" fillId="7" borderId="5" xfId="0">
@@ -1715,10 +1746,10 @@
     <xf numFmtId="58" fontId="3" fillId="7" borderId="5" xfId="0">
       <alignment vertical="center" textRotation="0"/>
     </xf>
-    <xf fontId="0" fillId="7" borderId="32" xfId="0">
+    <xf fontId="0" fillId="7" borderId="34" xfId="0">
       <alignment vertical="center" wrapText="0"/>
     </xf>
-    <xf fontId="9" fillId="7" borderId="0" xfId="0">
+    <xf fontId="10" fillId="7" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="302" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1735,102 +1766,6 @@
     </xf>
     <xf numFmtId="304" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="11" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="10" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="8" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="12" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="16" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="5" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="10" fillId="11" borderId="7" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="10" fillId="11" borderId="9" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="3" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="5" borderId="10" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="10" fillId="11" borderId="8" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="13" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="4" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="7" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="0" fillId="11" borderId="8" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="11" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="14" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="8" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="10" fillId="11" borderId="1" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="10" fillId="11" borderId="49" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="10" fillId="11" borderId="2" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="0" fillId="6" borderId="10" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="10" fillId="6" borderId="10" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="15" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="10" fillId="6" borderId="3" xfId="0">
-      <alignment vertical="center" wrapText="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="16" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="11" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="12" xfId="0">
-      <alignment vertical="bottom" textRotation="0"/>
     </xf>
   </cellXfs>
   <cellStyles>
@@ -3673,7 +3608,9 @@
       <c r="R36" s="38" t="s"/>
     </row>
     <row r="37" spans="1:15">
-      <c r="A37" s="28" t="s"/>
+      <c r="A37" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="B37" s="29" t="s"/>
       <c r="C37" s="28" t="s"/>
       <c r="D37" s="29" t="s"/>
@@ -3690,7 +3627,9 @@
       <c r="O37" s="31" t="s"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="12" t="s"/>
+      <c r="A38" s="12" t="s">
+        <v>11</v>
+      </c>
       <c r="B38" s="10" t="s"/>
       <c r="C38" s="12" t="s"/>
       <c r="D38" s="10" t="s"/>
@@ -3707,7 +3646,9 @@
       <c r="O38" s="22" t="s"/>
     </row>
     <row r="39" spans="1:15">
-      <c r="A39" s="9" t="s"/>
+      <c r="A39" s="9" t="s">
+        <v>10</v>
+      </c>
       <c r="B39" s="10" t="s"/>
       <c r="C39" s="9" t="s"/>
       <c r="D39" s="10" t="s"/>
@@ -3724,7 +3665,9 @@
       <c r="O39" s="22" t="s"/>
     </row>
     <row r="40" spans="1:15">
-      <c r="A40" s="9" t="s"/>
+      <c r="A40" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="B40" s="10" t="s"/>
       <c r="C40" s="9" t="s"/>
       <c r="D40" s="10" t="s"/>
@@ -3811,19 +3754,19 @@
   <sheetPr codeName="中大附三岭南医院">
     <tabColor/>
   </sheetPr>
-  <dimension ref="O200"/>
+  <dimension ref="D200"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="15" width="11.0625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="91" t="s"/>
-      <c r="B1" s="91" t="s"/>
-      <c r="C1" s="91" t="s"/>
-      <c r="D1" s="91" t="s"/>
-      <c r="E1" s="91" t="s"/>
-      <c r="F1" s="91" t="s"/>
+      <c r="A1" s="90" t="s"/>
+      <c r="B1" s="90" t="s"/>
+      <c r="C1" s="90" t="s"/>
+      <c r="D1" s="90" t="s"/>
+      <c r="E1" s="90" t="s"/>
+      <c r="F1" s="90" t="s"/>
       <c r="G1" s="4">
         <v>46191</v>
       </c>
@@ -3842,186 +3785,186 @@
       <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="240">
+      <c r="M1" s="250">
         <v>46194</v>
       </c>
       <c r="N1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="O1" s="241" t="s"/>
+      <c r="O1" s="251" t="s"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="242" t="s"/>
-      <c r="B2" s="243" t="s"/>
-      <c r="C2" s="244" t="s"/>
-      <c r="D2" s="242" t="s"/>
-      <c r="E2" s="244" t="s"/>
-      <c r="F2" s="244" t="s"/>
-      <c r="G2" s="191" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="242">
-        <v>90</v>
-      </c>
-      <c r="I2" s="191" t="s">
-        <v>87</v>
-      </c>
-      <c r="J2" s="242">
-        <v>90</v>
-      </c>
-      <c r="K2" s="191" t="s">
-        <v>87</v>
-      </c>
-      <c r="L2" s="242">
-        <v>60</v>
-      </c>
-      <c r="M2" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="N2" s="242">
-        <v>60</v>
-      </c>
-      <c r="O2" s="181" t="s"/>
+      <c r="A2" s="190" t="s"/>
+      <c r="B2" s="252" t="s"/>
+      <c r="C2" s="253" t="s"/>
+      <c r="D2" s="190" t="s"/>
+      <c r="E2" s="253" t="s"/>
+      <c r="F2" s="253" t="s"/>
+      <c r="G2" s="254" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="190">
+        <v>90</v>
+      </c>
+      <c r="I2" s="254" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" s="190">
+        <v>90</v>
+      </c>
+      <c r="K2" s="254" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" s="190">
+        <v>60</v>
+      </c>
+      <c r="M2" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="N2" s="190">
+        <v>60</v>
+      </c>
+      <c r="O2" s="188" t="s"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="242" t="s"/>
-      <c r="B3" s="243" t="s"/>
-      <c r="C3" s="244" t="s"/>
-      <c r="D3" s="242" t="s"/>
-      <c r="E3" s="244" t="s"/>
-      <c r="F3" s="244" t="s"/>
-      <c r="G3" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="242">
-        <v>60</v>
-      </c>
-      <c r="I3" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="J3" s="242">
-        <v>90</v>
-      </c>
-      <c r="K3" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="L3" s="242">
-        <v>60</v>
-      </c>
-      <c r="M3" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="N3" s="242">
-        <v>90</v>
-      </c>
-      <c r="O3" s="181" t="s"/>
+      <c r="A3" s="190" t="s"/>
+      <c r="B3" s="252" t="s"/>
+      <c r="C3" s="253" t="s"/>
+      <c r="D3" s="190" t="s"/>
+      <c r="E3" s="253" t="s"/>
+      <c r="F3" s="253" t="s"/>
+      <c r="G3" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="190">
+        <v>60</v>
+      </c>
+      <c r="I3" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" s="190">
+        <v>90</v>
+      </c>
+      <c r="K3" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" s="190">
+        <v>60</v>
+      </c>
+      <c r="M3" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="N3" s="190">
+        <v>90</v>
+      </c>
+      <c r="O3" s="188" t="s"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="242" t="s"/>
-      <c r="B4" s="243" t="s"/>
-      <c r="C4" s="244" t="s"/>
-      <c r="D4" s="242" t="s"/>
-      <c r="E4" s="244" t="s"/>
-      <c r="F4" s="244" t="s"/>
-      <c r="G4" s="191" t="s"/>
-      <c r="H4" s="242" t="s"/>
-      <c r="I4" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="J4" s="242">
-        <v>60</v>
-      </c>
-      <c r="K4" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="L4" s="242">
-        <v>90</v>
-      </c>
-      <c r="M4" s="191" t="s"/>
-      <c r="N4" s="242" t="s"/>
-      <c r="O4" s="181" t="s"/>
+      <c r="A4" s="190" t="s"/>
+      <c r="B4" s="252" t="s"/>
+      <c r="C4" s="253" t="s"/>
+      <c r="D4" s="190" t="s"/>
+      <c r="E4" s="253" t="s"/>
+      <c r="F4" s="253" t="s"/>
+      <c r="G4" s="254" t="s"/>
+      <c r="H4" s="190" t="s"/>
+      <c r="I4" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="190">
+        <v>60</v>
+      </c>
+      <c r="K4" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="L4" s="190">
+        <v>90</v>
+      </c>
+      <c r="M4" s="254" t="s"/>
+      <c r="N4" s="190" t="s"/>
+      <c r="O4" s="188" t="s"/>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="242" t="s"/>
-      <c r="B5" s="243" t="s"/>
-      <c r="C5" s="244" t="s"/>
-      <c r="D5" s="242" t="s"/>
-      <c r="E5" s="244" t="s"/>
-      <c r="F5" s="244" t="s"/>
-      <c r="G5" s="191" t="s"/>
-      <c r="H5" s="242" t="s"/>
-      <c r="I5" s="191" t="s"/>
-      <c r="J5" s="242" t="s"/>
-      <c r="K5" s="191" t="s"/>
-      <c r="L5" s="242" t="s"/>
-      <c r="M5" s="191" t="s"/>
-      <c r="N5" s="242" t="s"/>
-      <c r="O5" s="181" t="s"/>
+      <c r="A5" s="190" t="s"/>
+      <c r="B5" s="252" t="s"/>
+      <c r="C5" s="253" t="s"/>
+      <c r="D5" s="190" t="s"/>
+      <c r="E5" s="253" t="s"/>
+      <c r="F5" s="253" t="s"/>
+      <c r="G5" s="254" t="s"/>
+      <c r="H5" s="190" t="s"/>
+      <c r="I5" s="254" t="s"/>
+      <c r="J5" s="190" t="s"/>
+      <c r="K5" s="254" t="s"/>
+      <c r="L5" s="190" t="s"/>
+      <c r="M5" s="254" t="s"/>
+      <c r="N5" s="190" t="s"/>
+      <c r="O5" s="188" t="s"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="242" t="s"/>
-      <c r="B6" s="243" t="s"/>
-      <c r="C6" s="244" t="s"/>
-      <c r="D6" s="242" t="s"/>
-      <c r="E6" s="244" t="s"/>
-      <c r="F6" s="244" t="s"/>
-      <c r="G6" s="191" t="s"/>
-      <c r="H6" s="242" t="s"/>
-      <c r="I6" s="191" t="s"/>
-      <c r="J6" s="242" t="s"/>
-      <c r="K6" s="191" t="s"/>
-      <c r="L6" s="242" t="s"/>
-      <c r="M6" s="191" t="s"/>
-      <c r="N6" s="242" t="s"/>
-      <c r="O6" s="181" t="s"/>
+      <c r="A6" s="190" t="s"/>
+      <c r="B6" s="252" t="s"/>
+      <c r="C6" s="253" t="s"/>
+      <c r="D6" s="190" t="s"/>
+      <c r="E6" s="253" t="s"/>
+      <c r="F6" s="253" t="s"/>
+      <c r="G6" s="254" t="s"/>
+      <c r="H6" s="190" t="s"/>
+      <c r="I6" s="254" t="s"/>
+      <c r="J6" s="190" t="s"/>
+      <c r="K6" s="254" t="s"/>
+      <c r="L6" s="190" t="s"/>
+      <c r="M6" s="254" t="s"/>
+      <c r="N6" s="190" t="s"/>
+      <c r="O6" s="188" t="s"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="242" t="s"/>
-      <c r="B7" s="243" t="s"/>
-      <c r="C7" s="244" t="s"/>
-      <c r="D7" s="242" t="s"/>
-      <c r="E7" s="244" t="s"/>
-      <c r="F7" s="244" t="s"/>
-      <c r="G7" s="191" t="s"/>
-      <c r="H7" s="242" t="s"/>
-      <c r="I7" s="191" t="s"/>
-      <c r="J7" s="242" t="s"/>
-      <c r="K7" s="191" t="s"/>
-      <c r="L7" s="242" t="s"/>
-      <c r="M7" s="191" t="s"/>
-      <c r="N7" s="242" t="s"/>
-      <c r="O7" s="245" t="s">
+      <c r="A7" s="190" t="s"/>
+      <c r="B7" s="252" t="s"/>
+      <c r="C7" s="253" t="s"/>
+      <c r="D7" s="190" t="s"/>
+      <c r="E7" s="253" t="s"/>
+      <c r="F7" s="253" t="s"/>
+      <c r="G7" s="254" t="s"/>
+      <c r="H7" s="190" t="s"/>
+      <c r="I7" s="254" t="s"/>
+      <c r="J7" s="190" t="s"/>
+      <c r="K7" s="254" t="s"/>
+      <c r="L7" s="190" t="s"/>
+      <c r="M7" s="254" t="s"/>
+      <c r="N7" s="190" t="s"/>
+      <c r="O7" s="255" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="246" t="s"/>
-      <c r="B8" s="246" t="s"/>
-      <c r="C8" s="246" t="s"/>
-      <c r="D8" s="246" t="s"/>
-      <c r="E8" s="246" t="s"/>
-      <c r="F8" s="246" t="s"/>
-      <c r="G8" s="247" t="s"/>
-      <c r="H8" s="248">
+      <c r="A8" s="256" t="s"/>
+      <c r="B8" s="256" t="s"/>
+      <c r="C8" s="256" t="s"/>
+      <c r="D8" s="256" t="s"/>
+      <c r="E8" s="256" t="s"/>
+      <c r="F8" s="256" t="s"/>
+      <c r="G8" s="257" t="s"/>
+      <c r="H8" s="258">
         <f>=SUM(H2:H7)</f>
         <v>150</v>
       </c>
-      <c r="I8" s="247" t="s"/>
-      <c r="J8" s="248">
+      <c r="I8" s="257" t="s"/>
+      <c r="J8" s="258">
         <f>=SUM(J2:J7)</f>
         <v>240</v>
       </c>
-      <c r="K8" s="247" t="s"/>
-      <c r="L8" s="248">
+      <c r="K8" s="257" t="s"/>
+      <c r="L8" s="258">
         <f>=SUM(L2:L7)</f>
         <v>210</v>
       </c>
-      <c r="M8" s="247" t="s"/>
-      <c r="N8" s="248">
+      <c r="M8" s="257" t="s"/>
+      <c r="N8" s="258">
         <f>=SUM(N2:N7)</f>
         <v>150</v>
       </c>
-      <c r="O8" s="249">
+      <c r="O8" s="259">
         <f>=SUM(A8:N8)</f>
         <v>750</v>
       </c>
@@ -4032,319 +3975,319 @@
     <row r="9" spans="1:28"/>
     <row r="10" spans="1:28"/>
     <row r="11" spans="1:15">
-      <c r="A11" s="250">
+      <c r="A11" s="260">
         <v>46195</v>
       </c>
-      <c r="B11" s="251" t="s">
+      <c r="B11" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="252">
+      <c r="C11" s="262">
         <v>46196</v>
       </c>
-      <c r="D11" s="188" t="s">
+      <c r="D11" s="222" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="253">
+      <c r="E11" s="263">
         <v>46197</v>
       </c>
-      <c r="F11" s="185" t="s">
+      <c r="F11" s="187" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="252">
+      <c r="G11" s="262">
         <v>46198</v>
       </c>
-      <c r="H11" s="188" t="s">
+      <c r="H11" s="222" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="253">
+      <c r="I11" s="263">
         <v>46199</v>
       </c>
-      <c r="J11" s="188" t="s">
+      <c r="J11" s="222" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="253">
+      <c r="K11" s="263">
         <v>46200</v>
       </c>
-      <c r="L11" s="188" t="s">
+      <c r="L11" s="222" t="s">
         <v>7</v>
       </c>
-      <c r="M11" s="253">
+      <c r="M11" s="263">
         <v>46201</v>
       </c>
-      <c r="N11" s="188" t="s">
+      <c r="N11" s="222" t="s">
         <v>1</v>
       </c>
-      <c r="O11" s="254" t="s"/>
+      <c r="O11" s="264" t="s"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="191" t="s">
+      <c r="A12" s="254" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="190">
+        <v>75</v>
+      </c>
+      <c r="C12" s="265" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="222">
+        <v>75</v>
+      </c>
+      <c r="E12" s="187" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="187">
+        <v>135</v>
+      </c>
+      <c r="G12" s="265" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="222">
+        <v>60</v>
+      </c>
+      <c r="I12" s="187" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" s="222">
+        <v>60</v>
+      </c>
+      <c r="K12" s="187" t="s">
+        <v>84</v>
+      </c>
+      <c r="L12" s="222">
+        <v>120</v>
+      </c>
+      <c r="M12" s="187" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="242">
+      <c r="N12" s="222">
+        <v>60</v>
+      </c>
+      <c r="O12" s="222" t="s"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="190">
+        <v>60</v>
+      </c>
+      <c r="C13" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="266">
         <v>75</v>
       </c>
-      <c r="C12" s="187" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="188">
+      <c r="E13" s="190" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13">
+        <v>60</v>
+      </c>
+      <c r="G13" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="266">
+        <v>60</v>
+      </c>
+      <c r="I13" s="190" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" s="266">
+        <v>60</v>
+      </c>
+      <c r="K13" s="190" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="266">
+        <v>90</v>
+      </c>
+      <c r="M13" s="190" t="s">
+        <v>87</v>
+      </c>
+      <c r="N13" s="266">
+        <v>120</v>
+      </c>
+      <c r="O13" s="266" t="s"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="190">
+        <v>90</v>
+      </c>
+      <c r="C14" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="266">
+        <v>90</v>
+      </c>
+      <c r="E14" s="190" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14">
+        <v>90</v>
+      </c>
+      <c r="G14" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="266">
+        <v>90</v>
+      </c>
+      <c r="I14" s="190" t="s">
+        <v>85</v>
+      </c>
+      <c r="J14" s="266">
+        <v>90</v>
+      </c>
+      <c r="K14" s="267" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="266">
+        <v>60</v>
+      </c>
+      <c r="M14" s="190" t="s">
+        <v>89</v>
+      </c>
+      <c r="N14" s="266">
+        <v>90</v>
+      </c>
+      <c r="O14" s="266" t="s"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="254" t="s"/>
+      <c r="B15" s="190" t="s"/>
+      <c r="C15" s="254" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="266">
         <v>75</v>
       </c>
-      <c r="E12" s="185" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="185">
-        <v>135</v>
-      </c>
-      <c r="G12" s="187" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="188">
-        <v>60</v>
-      </c>
-      <c r="I12" s="185" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="188">
-        <v>60</v>
-      </c>
-      <c r="K12" s="185" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" s="188">
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15">
+        <v>60</v>
+      </c>
+      <c r="G15" s="268" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="266">
         <v>120</v>
       </c>
-      <c r="M12" s="185" t="s">
-        <v>90</v>
-      </c>
-      <c r="N12" s="188">
-        <v>60</v>
-      </c>
-      <c r="O12" s="188" t="s"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="242">
-        <v>60</v>
-      </c>
-      <c r="C13" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="189">
-        <v>75</v>
-      </c>
-      <c r="E13" s="242" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13">
-        <v>60</v>
-      </c>
-      <c r="G13" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="189">
-        <v>60</v>
-      </c>
-      <c r="I13" s="242" t="s">
-        <v>88</v>
-      </c>
-      <c r="J13" s="189">
-        <v>60</v>
-      </c>
-      <c r="K13" s="242" t="s">
-        <v>89</v>
-      </c>
-      <c r="L13" s="189">
-        <v>90</v>
-      </c>
-      <c r="M13" s="242" t="s">
+      <c r="I15" s="267" t="s">
         <v>91</v>
       </c>
-      <c r="N13" s="189">
-        <v>120</v>
-      </c>
-      <c r="O13" s="189" t="s"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="242">
-        <v>90</v>
-      </c>
-      <c r="C14" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="189">
-        <v>90</v>
-      </c>
-      <c r="E14" s="242" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14">
-        <v>90</v>
-      </c>
-      <c r="G14" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="189">
-        <v>90</v>
-      </c>
-      <c r="I14" s="242" t="s">
-        <v>89</v>
-      </c>
-      <c r="J14" s="189">
-        <v>90</v>
-      </c>
-      <c r="K14" s="255" t="s">
+      <c r="J15" s="266">
+        <v>60</v>
+      </c>
+      <c r="K15" s="190" t="s"/>
+      <c r="L15" s="266" t="s"/>
+      <c r="M15" s="190" t="s"/>
+      <c r="N15" s="266" t="s"/>
+      <c r="O15" s="266" t="s"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="254" t="s"/>
+      <c r="B16" s="190" t="s"/>
+      <c r="C16" s="254" t="s"/>
+      <c r="D16" s="266" t="s"/>
+      <c r="E16" t="s">
         <v>92</v>
-      </c>
-      <c r="L14" s="189">
-        <v>60</v>
-      </c>
-      <c r="M14" s="242" t="s">
-        <v>93</v>
-      </c>
-      <c r="N14" s="189">
-        <v>90</v>
-      </c>
-      <c r="O14" s="189" t="s"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="191" t="s"/>
-      <c r="B15" s="242" t="s"/>
-      <c r="C15" s="191" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="189">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15">
-        <v>60</v>
-      </c>
-      <c r="G15" s="256" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="189">
-        <v>120</v>
-      </c>
-      <c r="I15" s="255" t="s">
-        <v>95</v>
-      </c>
-      <c r="J15" s="189">
-        <v>60</v>
-      </c>
-      <c r="K15" s="242" t="s"/>
-      <c r="L15" s="189" t="s"/>
-      <c r="M15" s="242" t="s"/>
-      <c r="N15" s="189" t="s"/>
-      <c r="O15" s="189" t="s"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="191" t="s"/>
-      <c r="B16" s="242" t="s"/>
-      <c r="C16" s="191" t="s"/>
-      <c r="D16" s="189" t="s"/>
-      <c r="E16" t="s">
-        <v>96</v>
       </c>
       <c r="F16">
         <v>75</v>
       </c>
-      <c r="G16" s="256" t="s">
-        <v>96</v>
-      </c>
-      <c r="H16" s="189">
-        <v>60</v>
-      </c>
-      <c r="I16" s="255" t="s">
-        <v>96</v>
-      </c>
-      <c r="J16" s="189">
-        <v>60</v>
-      </c>
-      <c r="K16" s="242" t="s"/>
-      <c r="L16" s="189" t="s"/>
-      <c r="M16" s="242" t="s"/>
-      <c r="N16" s="189" t="s"/>
-      <c r="O16" s="189" t="s"/>
+      <c r="G16" s="268" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="266">
+        <v>60</v>
+      </c>
+      <c r="I16" s="267" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" s="266">
+        <v>60</v>
+      </c>
+      <c r="K16" s="190" t="s"/>
+      <c r="L16" s="266" t="s"/>
+      <c r="M16" s="190" t="s"/>
+      <c r="N16" s="266" t="s"/>
+      <c r="O16" s="266" t="s"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="191" t="s"/>
-      <c r="B17" s="242" t="s"/>
-      <c r="C17" s="191" t="s"/>
-      <c r="D17" s="189" t="s"/>
+      <c r="A17" s="254" t="s"/>
+      <c r="B17" s="190" t="s"/>
+      <c r="C17" s="254" t="s"/>
+      <c r="D17" s="266" t="s"/>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F17">
         <v>60</v>
       </c>
-      <c r="G17" s="256" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="189">
-        <v>60</v>
-      </c>
-      <c r="I17" s="255" t="s">
-        <v>97</v>
-      </c>
-      <c r="J17" s="189">
-        <v>60</v>
-      </c>
-      <c r="K17" s="242" t="s"/>
-      <c r="L17" s="189" t="s"/>
-      <c r="M17" s="242" t="s"/>
-      <c r="N17" s="189" t="s"/>
-      <c r="O17" s="245" t="s">
+      <c r="G17" s="268" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="266">
+        <v>60</v>
+      </c>
+      <c r="I17" s="267" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" s="266">
+        <v>60</v>
+      </c>
+      <c r="K17" s="190" t="s"/>
+      <c r="L17" s="266" t="s"/>
+      <c r="M17" s="190" t="s"/>
+      <c r="N17" s="266" t="s"/>
+      <c r="O17" s="255" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="257" t="s"/>
-      <c r="B18" s="258">
+      <c r="A18" s="269" t="s"/>
+      <c r="B18" s="270">
         <f>=SUM(B12:B17)</f>
         <v>225</v>
       </c>
-      <c r="C18" s="257" t="s"/>
-      <c r="D18" s="259">
+      <c r="C18" s="269" t="s"/>
+      <c r="D18" s="271">
         <f>=SUM(D12:D17)</f>
         <v>315</v>
       </c>
-      <c r="E18" s="258" t="s"/>
-      <c r="F18" s="258">
+      <c r="E18" s="270" t="s"/>
+      <c r="F18" s="270">
         <f>=SUM(F12:F17)</f>
         <v>480</v>
       </c>
-      <c r="G18" s="257" t="s"/>
-      <c r="H18" s="259">
+      <c r="G18" s="269" t="s"/>
+      <c r="H18" s="271">
         <f>=SUM(H12:H17)</f>
         <v>450</v>
       </c>
-      <c r="I18" s="258" t="s"/>
-      <c r="J18" s="259">
+      <c r="I18" s="270" t="s"/>
+      <c r="J18" s="271">
         <f>=SUM(J12:J17)</f>
         <v>390</v>
       </c>
-      <c r="K18" s="258" t="s"/>
-      <c r="L18" s="259">
+      <c r="K18" s="270" t="s"/>
+      <c r="L18" s="271">
         <f>=SUM(L12:L17)</f>
         <v>270</v>
       </c>
-      <c r="M18" s="258" t="s"/>
-      <c r="N18" s="259">
+      <c r="M18" s="270" t="s"/>
+      <c r="N18" s="271">
         <f>=SUM(N12:N17)</f>
         <v>270</v>
       </c>
-      <c r="O18" s="260">
+      <c r="O18" s="272">
         <f>=SUM(A18:N18)</f>
         <v>2400</v>
       </c>
-      <c r="P18" s="261" t="s">
+      <c r="P18" s="273" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4395,185 +4338,360 @@
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="191" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="242">
+      <c r="A22" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="190">
         <v>120</v>
       </c>
-      <c r="C22" s="191" t="s">
+      <c r="C22" s="254" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="222">
+        <v>90</v>
+      </c>
+      <c r="E22" s="187" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="187">
+        <v>60</v>
+      </c>
+      <c r="G22" s="265" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="222">
+        <v>90</v>
+      </c>
+      <c r="I22" s="187" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22" s="222">
+        <v>135</v>
+      </c>
+      <c r="K22" s="187" t="s">
+        <v>84</v>
+      </c>
+      <c r="L22" s="222">
+        <v>60</v>
+      </c>
+      <c r="M22" s="187" t="s">
+        <v>93</v>
+      </c>
+      <c r="N22" s="222">
+        <v>60</v>
+      </c>
+      <c r="O22" s="222" t="s"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="190">
+        <v>90</v>
+      </c>
+      <c r="C23" s="254" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="266">
+        <v>90</v>
+      </c>
+      <c r="E23" s="190" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23">
+        <v>120</v>
+      </c>
+      <c r="G23" s="254" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="266">
+        <v>120</v>
+      </c>
+      <c r="I23" s="190" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" s="266">
+        <v>60</v>
+      </c>
+      <c r="K23" s="190" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="188">
-        <v>90</v>
-      </c>
-      <c r="E22" s="185" t="s"/>
-      <c r="F22" s="185" t="s"/>
-      <c r="G22" s="187" t="s"/>
-      <c r="H22" s="188" t="s"/>
-      <c r="I22" s="185" t="s"/>
-      <c r="J22" s="188" t="s"/>
-      <c r="K22" s="185" t="s"/>
-      <c r="L22" s="188" t="s"/>
-      <c r="M22" s="185" t="s"/>
-      <c r="N22" s="188" t="s"/>
-      <c r="O22" s="188" t="s"/>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="242">
-        <v>90</v>
-      </c>
-      <c r="C23" s="191" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="189">
-        <v>90</v>
-      </c>
-      <c r="E23" s="242" t="s"/>
-      <c r="G23" s="191" t="s"/>
-      <c r="H23" s="189" t="s"/>
-      <c r="I23" s="242" t="s"/>
-      <c r="J23" s="189" t="s"/>
-      <c r="K23" s="242" t="s"/>
-      <c r="L23" s="189" t="s"/>
-      <c r="M23" s="242" t="s"/>
-      <c r="N23" s="189" t="s"/>
-      <c r="O23" s="189" t="s"/>
+      <c r="L23" s="266">
+        <v>135</v>
+      </c>
+      <c r="M23" s="190" t="s">
+        <v>96</v>
+      </c>
+      <c r="N23" s="266">
+        <v>60</v>
+      </c>
+      <c r="O23" s="266" t="s"/>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="191" t="s">
+      <c r="A24" s="254" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="190">
+        <v>60</v>
+      </c>
+      <c r="C24" s="254" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="266">
+        <v>60</v>
+      </c>
+      <c r="E24" s="190" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24">
+        <v>120</v>
+      </c>
+      <c r="G24" s="254" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" s="266">
+        <v>60</v>
+      </c>
+      <c r="I24" s="190" t="s">
+        <v>96</v>
+      </c>
+      <c r="J24" s="266">
+        <v>60</v>
+      </c>
+      <c r="K24" s="267" t="s">
+        <v>85</v>
+      </c>
+      <c r="L24" s="266">
+        <v>90</v>
+      </c>
+      <c r="M24" s="190" t="s">
+        <v>85</v>
+      </c>
+      <c r="N24" s="266">
+        <v>90</v>
+      </c>
+      <c r="O24" s="266" t="s"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="254" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="242">
-        <v>60</v>
-      </c>
-      <c r="C24" s="191" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="189">
-        <v>60</v>
-      </c>
-      <c r="E24" s="242" t="s"/>
-      <c r="G24" s="191" t="s"/>
-      <c r="H24" s="189" t="s"/>
-      <c r="I24" s="242" t="s"/>
-      <c r="J24" s="189" t="s"/>
-      <c r="K24" s="255" t="s"/>
-      <c r="L24" s="189" t="s"/>
-      <c r="M24" s="242" t="s"/>
-      <c r="N24" s="189" t="s"/>
-      <c r="O24" s="189" t="s"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="191" t="s">
-        <v>99</v>
-      </c>
-      <c r="B25" s="242">
-        <v>60</v>
-      </c>
-      <c r="C25" s="191" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="189">
-        <v>60</v>
-      </c>
-      <c r="G25" s="256" t="s"/>
-      <c r="H25" s="189" t="s"/>
-      <c r="I25" s="255" t="s"/>
-      <c r="J25" s="189" t="s"/>
-      <c r="K25" s="242" t="s"/>
-      <c r="L25" s="189" t="s"/>
-      <c r="M25" s="242" t="s"/>
-      <c r="N25" s="189" t="s"/>
-      <c r="O25" s="189" t="s"/>
+      <c r="B25" s="190">
+        <v>60</v>
+      </c>
+      <c r="C25" s="254" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="266">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25">
+        <v>90</v>
+      </c>
+      <c r="G25" s="268" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="266">
+        <v>60</v>
+      </c>
+      <c r="I25" s="267" t="s">
+        <v>85</v>
+      </c>
+      <c r="J25" s="266">
+        <v>90</v>
+      </c>
+      <c r="K25" s="190" t="s"/>
+      <c r="L25" s="266" t="s"/>
+      <c r="M25" s="190" t="s">
+        <v>95</v>
+      </c>
+      <c r="N25" s="266">
+        <v>60</v>
+      </c>
+      <c r="O25" s="266" t="s"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="191" t="s"/>
-      <c r="B26" s="242" t="s"/>
-      <c r="C26" s="191" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="189">
-        <v>60</v>
-      </c>
-      <c r="G26" s="256" t="s"/>
-      <c r="H26" s="189" t="s"/>
-      <c r="I26" s="255" t="s"/>
-      <c r="J26" s="189" t="s"/>
-      <c r="K26" s="242" t="s"/>
-      <c r="L26" s="189" t="s"/>
-      <c r="M26" s="242" t="s"/>
-      <c r="N26" s="189" t="s"/>
-      <c r="O26" s="189" t="s"/>
+      <c r="A26" s="254" t="s"/>
+      <c r="B26" s="190" t="s"/>
+      <c r="C26" s="254" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="266">
+        <v>60</v>
+      </c>
+      <c r="G26" s="268" t="s"/>
+      <c r="H26" s="266" t="s"/>
+      <c r="I26" s="267" t="s"/>
+      <c r="J26" s="266" t="s"/>
+      <c r="K26" s="190" t="s"/>
+      <c r="L26" s="266" t="s"/>
+      <c r="M26" s="190" t="s"/>
+      <c r="N26" s="266" t="s"/>
+      <c r="O26" s="266" t="s"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="191" t="s"/>
-      <c r="B27" s="242" t="s"/>
-      <c r="C27" s="191" t="s"/>
-      <c r="D27" s="189" t="s"/>
-      <c r="G27" s="256" t="s"/>
-      <c r="H27" s="189" t="s"/>
-      <c r="I27" s="255" t="s"/>
-      <c r="J27" s="189" t="s"/>
-      <c r="K27" s="242" t="s"/>
-      <c r="L27" s="189" t="s"/>
-      <c r="M27" s="242" t="s"/>
-      <c r="N27" s="189" t="s"/>
-      <c r="O27" s="245" t="s">
+      <c r="A27" s="254" t="s"/>
+      <c r="B27" s="190" t="s"/>
+      <c r="C27" s="254" t="s"/>
+      <c r="D27" s="266" t="s"/>
+      <c r="G27" s="268" t="s"/>
+      <c r="H27" s="266" t="s"/>
+      <c r="I27" s="267" t="s"/>
+      <c r="J27" s="266" t="s"/>
+      <c r="K27" s="190" t="s"/>
+      <c r="L27" s="266" t="s"/>
+      <c r="M27" s="190" t="s"/>
+      <c r="N27" s="266" t="s"/>
+      <c r="O27" s="255" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="257" t="s"/>
-      <c r="B28" s="258">
+      <c r="A28" s="269" t="s"/>
+      <c r="B28" s="270">
         <f>=SUM(B22:B27)</f>
         <v>330</v>
       </c>
-      <c r="C28" s="257" t="s"/>
-      <c r="D28" s="259">
+      <c r="C28" s="269" t="s"/>
+      <c r="D28" s="271">
         <f>=SUM(D22:D27)</f>
         <v>360</v>
       </c>
-      <c r="E28" s="258" t="s"/>
-      <c r="F28" s="258">
+      <c r="E28" s="270" t="s"/>
+      <c r="F28" s="270">
         <f>=SUM(F22:F27)</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="257" t="s"/>
-      <c r="H28" s="259">
+        <v>390</v>
+      </c>
+      <c r="G28" s="269" t="s"/>
+      <c r="H28" s="271">
         <f>=SUM(H22:H27)</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="258" t="s"/>
-      <c r="J28" s="259">
+        <v>330</v>
+      </c>
+      <c r="I28" s="270" t="s"/>
+      <c r="J28" s="271">
         <f>=SUM(J22:J27)</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="258" t="s"/>
-      <c r="L28" s="259">
+        <v>345</v>
+      </c>
+      <c r="K28" s="270" t="s"/>
+      <c r="L28" s="271">
         <f>=SUM(L22:L27)</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="258" t="s"/>
-      <c r="N28" s="259">
+        <v>285</v>
+      </c>
+      <c r="M28" s="270" t="s"/>
+      <c r="N28" s="271">
         <f>=SUM(N22:N27)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="260">
+        <v>270</v>
+      </c>
+      <c r="O28" s="272">
         <f>=SUM(A28:N28)</f>
-        <v>690</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="29" spans="1:28"/>
     <row r="30" spans="1:28"/>
-    <row r="31" spans="1:28"/>
-    <row r="32" spans="1:28"/>
-    <row r="33" spans="1:28"/>
-    <row r="34" spans="1:28"/>
-    <row r="35" spans="1:28"/>
+    <row r="31" spans="1:14">
+      <c r="A31" s="274">
+        <v>46209</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="275">
+        <v>46210</v>
+      </c>
+      <c r="D31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="275">
+        <v>46211</v>
+      </c>
+      <c r="F31" t="s">
+        <v>4</v>
+      </c>
+      <c r="G31" s="275">
+        <v>46212</v>
+      </c>
+      <c r="H31" t="s">
+        <v>5</v>
+      </c>
+      <c r="I31" s="275">
+        <v>46213</v>
+      </c>
+      <c r="J31" t="s">
+        <v>6</v>
+      </c>
+      <c r="K31" s="275">
+        <v>46214</v>
+      </c>
+      <c r="L31" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="275">
+        <v>46215</v>
+      </c>
+      <c r="N31" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32">
+        <v>60</v>
+      </c>
+      <c r="E32" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33">
+        <v>120</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33">
+        <v>60</v>
+      </c>
+      <c r="E33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35">
+        <v>60</v>
+      </c>
+    </row>
     <row r="36" spans="1:28"/>
     <row r="37" spans="1:28"/>
     <row r="38" spans="1:28"/>
@@ -4753,91 +4871,91 @@
       <c r="A1" s="4">
         <v>46202</v>
       </c>
-      <c r="B1" s="262" t="s">
+      <c r="B1" s="276" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="4">
         <v>46203</v>
       </c>
-      <c r="D1" s="262" t="s">
+      <c r="D1" s="276" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4">
         <v>46204</v>
       </c>
-      <c r="F1" s="262" t="s">
+      <c r="F1" s="276" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="4">
         <v>46205</v>
       </c>
-      <c r="H1" s="262" t="s">
+      <c r="H1" s="276" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="4">
         <v>46206</v>
       </c>
-      <c r="J1" s="263" t="s">
+      <c r="J1" s="277" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="6" t="s"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="264" t="s"/>
-      <c r="B2" s="265" t="s"/>
-      <c r="C2" s="266" t="s"/>
-      <c r="D2" s="265" t="s"/>
-      <c r="E2" s="266" t="s"/>
-      <c r="F2" s="265" t="s"/>
-      <c r="G2" s="266" t="s"/>
-      <c r="H2" s="265" t="s"/>
-      <c r="I2" s="267" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="268">
-        <v>90</v>
-      </c>
-      <c r="K2" s="269" t="s"/>
+      <c r="A2" s="278" t="s"/>
+      <c r="B2" s="279" t="s"/>
+      <c r="C2" s="280" t="s"/>
+      <c r="D2" s="279" t="s"/>
+      <c r="E2" s="280" t="s"/>
+      <c r="F2" s="279" t="s"/>
+      <c r="G2" s="280" t="s"/>
+      <c r="H2" s="279" t="s"/>
+      <c r="I2" s="281" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="282">
+        <v>90</v>
+      </c>
+      <c r="K2" s="283" t="s"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="39" t="s"/>
-      <c r="B3" s="270" t="s"/>
-      <c r="C3" s="271" t="s"/>
-      <c r="D3" s="270" t="s"/>
-      <c r="E3" s="271" t="s"/>
-      <c r="F3" s="270" t="s"/>
-      <c r="G3" s="271" t="s"/>
-      <c r="H3" s="270" t="s"/>
-      <c r="I3" s="271" t="s"/>
-      <c r="J3" s="272" t="s"/>
-      <c r="K3" s="273" t="s"/>
+      <c r="B3" s="284" t="s"/>
+      <c r="C3" s="285" t="s"/>
+      <c r="D3" s="284" t="s"/>
+      <c r="E3" s="285" t="s"/>
+      <c r="F3" s="284" t="s"/>
+      <c r="G3" s="285" t="s"/>
+      <c r="H3" s="284" t="s"/>
+      <c r="I3" s="285" t="s"/>
+      <c r="J3" s="286" t="s"/>
+      <c r="K3" s="287" t="s"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="39" t="s"/>
-      <c r="B4" s="270" t="s"/>
-      <c r="C4" s="271" t="s"/>
-      <c r="D4" s="270" t="s"/>
-      <c r="E4" s="271" t="s"/>
-      <c r="F4" s="270" t="s"/>
-      <c r="G4" s="271" t="s"/>
-      <c r="H4" s="270" t="s"/>
-      <c r="I4" s="274" t="s"/>
-      <c r="J4" s="272" t="s"/>
-      <c r="K4" s="273" t="s"/>
+      <c r="B4" s="284" t="s"/>
+      <c r="C4" s="285" t="s"/>
+      <c r="D4" s="284" t="s"/>
+      <c r="E4" s="285" t="s"/>
+      <c r="F4" s="284" t="s"/>
+      <c r="G4" s="285" t="s"/>
+      <c r="H4" s="284" t="s"/>
+      <c r="I4" s="288" t="s"/>
+      <c r="J4" s="286" t="s"/>
+      <c r="K4" s="287" t="s"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="275" t="s"/>
-      <c r="B5" s="276" t="s"/>
-      <c r="C5" s="277" t="s"/>
-      <c r="D5" s="276" t="s"/>
-      <c r="E5" s="277" t="s"/>
-      <c r="F5" s="276" t="s"/>
-      <c r="G5" s="277" t="s"/>
-      <c r="H5" s="276" t="s"/>
-      <c r="I5" s="277" t="s"/>
-      <c r="J5" s="278" t="s"/>
-      <c r="K5" s="279" t="s"/>
-      <c r="L5" s="280" t="s"/>
+      <c r="A5" s="289" t="s"/>
+      <c r="B5" s="290" t="s"/>
+      <c r="C5" s="291" t="s"/>
+      <c r="D5" s="290" t="s"/>
+      <c r="E5" s="291" t="s"/>
+      <c r="F5" s="290" t="s"/>
+      <c r="G5" s="291" t="s"/>
+      <c r="H5" s="290" t="s"/>
+      <c r="I5" s="291" t="s"/>
+      <c r="J5" s="292" t="s"/>
+      <c r="K5" s="293" t="s"/>
+      <c r="L5" s="294" t="s"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="134" t="s"/>
@@ -4868,155 +4986,171 @@
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="281" t="s"/>
-      <c r="B8" s="282">
+      <c r="A8" s="180" t="s"/>
+      <c r="B8" s="181">
         <f>=SUM(B2:B7)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="281" t="s"/>
-      <c r="D8" s="282">
+      <c r="C8" s="180" t="s"/>
+      <c r="D8" s="181">
         <f>=SUM(D2:D7)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="281" t="s"/>
-      <c r="F8" s="282">
+      <c r="E8" s="180" t="s"/>
+      <c r="F8" s="181">
         <f>=SUM(F2:F7)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="281" t="s"/>
-      <c r="H8" s="282">
+      <c r="G8" s="180" t="s"/>
+      <c r="H8" s="181">
         <f>=SUM(H2:H7)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="283" t="s"/>
-      <c r="J8" s="284">
+      <c r="I8" s="295" t="s"/>
+      <c r="J8" s="296">
         <f>=SUM(J2:J7)</f>
         <v>90</v>
       </c>
-      <c r="K8" s="285">
+      <c r="K8" s="297">
         <f>=SUM(A8:J8)</f>
         <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="286" t="s"/>
-      <c r="B9" s="286" t="s"/>
-      <c r="C9" s="286" t="s"/>
-      <c r="D9" s="286" t="s"/>
-      <c r="E9" s="286" t="s"/>
-      <c r="F9" s="286" t="s"/>
-      <c r="G9" s="286" t="s"/>
-      <c r="H9" s="286" t="s"/>
-      <c r="I9" s="286" t="s"/>
-      <c r="J9" s="286" t="s"/>
-      <c r="K9" s="286" t="s"/>
+      <c r="A9" s="298" t="s"/>
+      <c r="B9" s="298" t="s"/>
+      <c r="C9" s="298" t="s"/>
+      <c r="D9" s="298" t="s"/>
+      <c r="E9" s="298" t="s"/>
+      <c r="F9" s="298" t="s"/>
+      <c r="G9" s="298" t="s"/>
+      <c r="H9" s="298" t="s"/>
+      <c r="I9" s="298" t="s"/>
+      <c r="J9" s="298" t="s"/>
+      <c r="K9" s="298" t="s"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="286" t="s"/>
-      <c r="B10" s="286" t="s"/>
-      <c r="C10" s="286" t="s"/>
-      <c r="D10" s="286" t="s"/>
-      <c r="E10" s="286" t="s"/>
-      <c r="F10" s="286" t="s"/>
-      <c r="G10" s="286" t="s"/>
-      <c r="H10" s="286" t="s"/>
-      <c r="I10" s="286" t="s"/>
-      <c r="J10" s="286" t="s"/>
-      <c r="K10" s="287" t="s"/>
+      <c r="A10" s="298" t="s"/>
+      <c r="B10" s="298" t="s"/>
+      <c r="C10" s="298" t="s"/>
+      <c r="D10" s="298" t="s"/>
+      <c r="E10" s="298" t="s"/>
+      <c r="F10" s="298" t="s"/>
+      <c r="G10" s="298" t="s"/>
+      <c r="H10" s="298" t="s"/>
+      <c r="I10" s="298" t="s"/>
+      <c r="J10" s="298" t="s"/>
+      <c r="K10" s="299" t="s"/>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="4">
         <v>46209</v>
       </c>
-      <c r="B11" s="262" t="s">
+      <c r="B11" s="276" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="4">
         <v>46210</v>
       </c>
-      <c r="D11" s="262" t="s">
+      <c r="D11" s="276" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="4">
         <v>46211</v>
       </c>
-      <c r="F11" s="262" t="s">
+      <c r="F11" s="276" t="s">
         <v>4</v>
       </c>
       <c r="G11" s="4">
         <v>46212</v>
       </c>
-      <c r="H11" s="262" t="s">
+      <c r="H11" s="276" t="s">
         <v>5</v>
       </c>
       <c r="I11" s="4">
         <v>46213</v>
       </c>
-      <c r="J11" s="263" t="s">
+      <c r="J11" s="277" t="s">
         <v>6</v>
       </c>
       <c r="K11" s="6" t="s"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="264" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="265">
-        <v>90</v>
-      </c>
-      <c r="C12" s="266" t="s"/>
-      <c r="D12" s="265" t="s"/>
-      <c r="E12" s="266" t="s"/>
-      <c r="F12" s="265" t="s"/>
-      <c r="G12" s="266" t="s"/>
-      <c r="H12" s="265" t="s"/>
-      <c r="I12" s="267" t="s"/>
-      <c r="J12" s="268" t="s"/>
-      <c r="K12" s="269" t="s"/>
+      <c r="A12" s="278" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="279">
+        <v>90</v>
+      </c>
+      <c r="C12" s="280" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="279">
+        <v>90</v>
+      </c>
+      <c r="E12" s="280" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="279">
+        <v>90</v>
+      </c>
+      <c r="G12" s="280" t="s"/>
+      <c r="H12" s="279" t="s"/>
+      <c r="I12" s="281" t="s"/>
+      <c r="J12" s="282" t="s"/>
+      <c r="K12" s="283" t="s"/>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="270">
-        <v>60</v>
-      </c>
-      <c r="C13" s="271" t="s"/>
-      <c r="D13" s="270" t="s"/>
-      <c r="E13" s="271" t="s"/>
-      <c r="F13" s="270" t="s"/>
-      <c r="G13" s="271" t="s"/>
-      <c r="H13" s="270" t="s"/>
-      <c r="I13" s="271" t="s"/>
-      <c r="J13" s="272" t="s"/>
-      <c r="K13" s="273" t="s"/>
+        <v>99</v>
+      </c>
+      <c r="B13" s="284">
+        <v>60</v>
+      </c>
+      <c r="C13" s="285" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="284">
+        <v>60</v>
+      </c>
+      <c r="E13" s="285" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="284">
+        <v>60</v>
+      </c>
+      <c r="G13" s="285" t="s"/>
+      <c r="H13" s="284" t="s"/>
+      <c r="I13" s="285" t="s"/>
+      <c r="J13" s="286" t="s"/>
+      <c r="K13" s="287" t="s"/>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="39" t="s"/>
-      <c r="B14" s="270" t="s"/>
-      <c r="C14" s="271" t="s"/>
-      <c r="D14" s="270" t="s"/>
-      <c r="E14" s="271" t="s"/>
-      <c r="F14" s="270" t="s"/>
-      <c r="G14" s="271" t="s"/>
-      <c r="H14" s="270" t="s"/>
-      <c r="I14" s="274" t="s"/>
-      <c r="J14" s="272" t="s"/>
-      <c r="K14" s="273" t="s"/>
+      <c r="B14" s="284" t="s"/>
+      <c r="C14" s="285" t="s"/>
+      <c r="D14" s="284" t="s"/>
+      <c r="E14" s="285" t="s"/>
+      <c r="F14" s="284" t="s"/>
+      <c r="G14" s="285" t="s"/>
+      <c r="H14" s="284" t="s"/>
+      <c r="I14" s="288" t="s"/>
+      <c r="J14" s="286" t="s"/>
+      <c r="K14" s="287" t="s"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="275" t="s"/>
-      <c r="B15" s="276" t="s"/>
-      <c r="C15" s="277" t="s"/>
-      <c r="D15" s="276" t="s"/>
-      <c r="E15" s="277" t="s"/>
-      <c r="F15" s="276" t="s"/>
-      <c r="G15" s="277" t="s"/>
-      <c r="H15" s="276" t="s"/>
-      <c r="I15" s="277" t="s"/>
-      <c r="J15" s="278" t="s"/>
-      <c r="K15" s="279" t="s"/>
-      <c r="L15" s="280" t="s"/>
+      <c r="A15" s="289" t="s"/>
+      <c r="B15" s="290" t="s"/>
+      <c r="C15" s="291" t="s"/>
+      <c r="D15" s="290" t="s"/>
+      <c r="E15" s="291" t="s"/>
+      <c r="F15" s="290" t="s"/>
+      <c r="G15" s="291" t="s"/>
+      <c r="H15" s="290" t="s"/>
+      <c r="I15" s="291" t="s"/>
+      <c r="J15" s="292" t="s"/>
+      <c r="K15" s="293" t="s"/>
+      <c r="L15" s="294" t="s"/>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="134" t="s"/>
@@ -5047,152 +5181,152 @@
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="281" t="s"/>
-      <c r="B18" s="282">
+      <c r="A18" s="180" t="s"/>
+      <c r="B18" s="181">
         <f>=SUM(B12:B17)</f>
         <v>150</v>
       </c>
-      <c r="C18" s="281" t="s"/>
-      <c r="D18" s="282">
+      <c r="C18" s="180" t="s"/>
+      <c r="D18" s="181">
         <f>=SUM(D12:D17)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="281" t="s"/>
-      <c r="F18" s="282">
+        <v>150</v>
+      </c>
+      <c r="E18" s="180" t="s"/>
+      <c r="F18" s="181">
         <f>=SUM(F12:F17)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="281" t="s"/>
-      <c r="H18" s="282">
+        <v>150</v>
+      </c>
+      <c r="G18" s="180" t="s"/>
+      <c r="H18" s="181">
         <f>=SUM(H12:H17)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="283" t="s"/>
-      <c r="J18" s="284">
+      <c r="I18" s="295" t="s"/>
+      <c r="J18" s="296">
         <f>=SUM(J12:J17)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="285">
+      <c r="K18" s="297">
         <f>=SUM(A18:J18)</f>
-        <v>150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="288" t="s"/>
-      <c r="B19" s="288" t="s"/>
-      <c r="C19" s="288" t="s"/>
-      <c r="D19" s="288" t="s"/>
-      <c r="E19" s="288" t="s"/>
-      <c r="F19" s="288" t="s"/>
-      <c r="G19" s="288" t="s"/>
-      <c r="H19" s="288" t="s"/>
-      <c r="I19" s="288" t="s"/>
-      <c r="J19" s="288" t="s"/>
-      <c r="K19" s="288" t="s"/>
+      <c r="A19" s="300" t="s"/>
+      <c r="B19" s="300" t="s"/>
+      <c r="C19" s="300" t="s"/>
+      <c r="D19" s="300" t="s"/>
+      <c r="E19" s="300" t="s"/>
+      <c r="F19" s="300" t="s"/>
+      <c r="G19" s="300" t="s"/>
+      <c r="H19" s="300" t="s"/>
+      <c r="I19" s="300" t="s"/>
+      <c r="J19" s="300" t="s"/>
+      <c r="K19" s="300" t="s"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="286" t="s"/>
-      <c r="B20" s="286" t="s"/>
-      <c r="C20" s="286" t="s"/>
-      <c r="D20" s="286" t="s"/>
-      <c r="E20" s="286" t="s"/>
-      <c r="F20" s="286" t="s"/>
-      <c r="G20" s="286" t="s"/>
-      <c r="H20" s="286" t="s"/>
-      <c r="I20" s="286" t="s"/>
-      <c r="J20" s="286" t="s"/>
-      <c r="K20" s="287" t="s"/>
+      <c r="A20" s="298" t="s"/>
+      <c r="B20" s="298" t="s"/>
+      <c r="C20" s="298" t="s"/>
+      <c r="D20" s="298" t="s"/>
+      <c r="E20" s="298" t="s"/>
+      <c r="F20" s="298" t="s"/>
+      <c r="G20" s="298" t="s"/>
+      <c r="H20" s="298" t="s"/>
+      <c r="I20" s="298" t="s"/>
+      <c r="J20" s="298" t="s"/>
+      <c r="K20" s="299" t="s"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="286" t="s"/>
-      <c r="B21" s="286" t="s"/>
-      <c r="C21" s="286" t="s"/>
-      <c r="D21" s="286" t="s"/>
-      <c r="E21" s="286" t="s"/>
-      <c r="F21" s="286" t="s"/>
-      <c r="G21" s="286" t="s"/>
-      <c r="H21" s="286" t="s"/>
-      <c r="I21" s="286" t="s"/>
-      <c r="J21" s="286" t="s"/>
-      <c r="K21" s="287" t="s"/>
+      <c r="A21" s="298" t="s"/>
+      <c r="B21" s="298" t="s"/>
+      <c r="C21" s="298" t="s"/>
+      <c r="D21" s="298" t="s"/>
+      <c r="E21" s="298" t="s"/>
+      <c r="F21" s="298" t="s"/>
+      <c r="G21" s="298" t="s"/>
+      <c r="H21" s="298" t="s"/>
+      <c r="I21" s="298" t="s"/>
+      <c r="J21" s="298" t="s"/>
+      <c r="K21" s="299" t="s"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="286" t="s"/>
-      <c r="B22" s="286" t="s"/>
-      <c r="C22" s="286" t="s"/>
-      <c r="D22" s="286" t="s"/>
-      <c r="E22" s="286" t="s"/>
-      <c r="F22" s="286" t="s"/>
-      <c r="G22" s="286" t="s"/>
-      <c r="H22" s="286" t="s"/>
-      <c r="I22" s="286" t="s"/>
-      <c r="J22" s="286" t="s"/>
-      <c r="K22" s="287" t="s"/>
+      <c r="A22" s="298" t="s"/>
+      <c r="B22" s="298" t="s"/>
+      <c r="C22" s="298" t="s"/>
+      <c r="D22" s="298" t="s"/>
+      <c r="E22" s="298" t="s"/>
+      <c r="F22" s="298" t="s"/>
+      <c r="G22" s="298" t="s"/>
+      <c r="H22" s="298" t="s"/>
+      <c r="I22" s="298" t="s"/>
+      <c r="J22" s="298" t="s"/>
+      <c r="K22" s="299" t="s"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="286" t="s"/>
-      <c r="B23" s="286" t="s"/>
-      <c r="C23" s="286" t="s"/>
-      <c r="D23" s="286" t="s"/>
-      <c r="E23" s="286" t="s"/>
-      <c r="F23" s="286" t="s"/>
-      <c r="G23" s="286" t="s"/>
-      <c r="H23" s="286" t="s"/>
-      <c r="I23" s="286" t="s"/>
-      <c r="J23" s="286" t="s"/>
-      <c r="K23" s="287" t="s"/>
+      <c r="A23" s="298" t="s"/>
+      <c r="B23" s="298" t="s"/>
+      <c r="C23" s="298" t="s"/>
+      <c r="D23" s="298" t="s"/>
+      <c r="E23" s="298" t="s"/>
+      <c r="F23" s="298" t="s"/>
+      <c r="G23" s="298" t="s"/>
+      <c r="H23" s="298" t="s"/>
+      <c r="I23" s="298" t="s"/>
+      <c r="J23" s="298" t="s"/>
+      <c r="K23" s="299" t="s"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="287" t="s"/>
-      <c r="B24" s="287" t="s"/>
-      <c r="C24" s="287" t="s"/>
-      <c r="D24" s="287" t="s"/>
-      <c r="E24" s="287" t="s"/>
-      <c r="F24" s="287" t="s"/>
-      <c r="G24" s="287" t="s"/>
-      <c r="H24" s="287" t="s"/>
-      <c r="I24" s="287" t="s"/>
-      <c r="J24" s="287" t="s"/>
-      <c r="K24" s="287" t="s"/>
+      <c r="A24" s="299" t="s"/>
+      <c r="B24" s="299" t="s"/>
+      <c r="C24" s="299" t="s"/>
+      <c r="D24" s="299" t="s"/>
+      <c r="E24" s="299" t="s"/>
+      <c r="F24" s="299" t="s"/>
+      <c r="G24" s="299" t="s"/>
+      <c r="H24" s="299" t="s"/>
+      <c r="I24" s="299" t="s"/>
+      <c r="J24" s="299" t="s"/>
+      <c r="K24" s="299" t="s"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="287" t="s"/>
-      <c r="B25" s="289" t="s"/>
-      <c r="C25" s="287" t="s"/>
-      <c r="D25" s="289" t="s"/>
-      <c r="E25" s="287" t="s"/>
-      <c r="F25" s="289" t="s"/>
-      <c r="G25" s="287" t="s"/>
-      <c r="H25" s="289" t="s"/>
-      <c r="I25" s="287" t="s"/>
-      <c r="J25" s="287" t="s"/>
-      <c r="K25" s="287" t="s"/>
+      <c r="A25" s="299" t="s"/>
+      <c r="B25" s="301" t="s"/>
+      <c r="C25" s="299" t="s"/>
+      <c r="D25" s="301" t="s"/>
+      <c r="E25" s="299" t="s"/>
+      <c r="F25" s="301" t="s"/>
+      <c r="G25" s="299" t="s"/>
+      <c r="H25" s="301" t="s"/>
+      <c r="I25" s="299" t="s"/>
+      <c r="J25" s="299" t="s"/>
+      <c r="K25" s="299" t="s"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="287" t="s"/>
-      <c r="B26" s="287" t="s"/>
-      <c r="C26" s="287" t="s"/>
-      <c r="D26" s="287" t="s"/>
-      <c r="E26" s="287" t="s"/>
-      <c r="F26" s="287" t="s"/>
-      <c r="G26" s="287" t="s"/>
-      <c r="H26" s="287" t="s"/>
-      <c r="I26" s="287" t="s"/>
-      <c r="J26" s="287" t="s"/>
-      <c r="K26" s="287" t="s"/>
+      <c r="A26" s="299" t="s"/>
+      <c r="B26" s="299" t="s"/>
+      <c r="C26" s="299" t="s"/>
+      <c r="D26" s="299" t="s"/>
+      <c r="E26" s="299" t="s"/>
+      <c r="F26" s="299" t="s"/>
+      <c r="G26" s="299" t="s"/>
+      <c r="H26" s="299" t="s"/>
+      <c r="I26" s="299" t="s"/>
+      <c r="J26" s="299" t="s"/>
+      <c r="K26" s="299" t="s"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="290" t="s"/>
-      <c r="B27" s="290" t="s"/>
-      <c r="C27" s="290" t="s"/>
-      <c r="D27" s="290" t="s"/>
-      <c r="E27" s="290" t="s"/>
-      <c r="F27" s="290" t="s"/>
-      <c r="G27" s="290" t="s"/>
-      <c r="H27" s="290" t="s"/>
-      <c r="I27" s="290" t="s"/>
-      <c r="J27" s="290" t="s"/>
-      <c r="K27" s="290" t="s"/>
+      <c r="A27" s="302" t="s"/>
+      <c r="B27" s="302" t="s"/>
+      <c r="C27" s="302" t="s"/>
+      <c r="D27" s="302" t="s"/>
+      <c r="E27" s="302" t="s"/>
+      <c r="F27" s="302" t="s"/>
+      <c r="G27" s="302" t="s"/>
+      <c r="H27" s="302" t="s"/>
+      <c r="I27" s="302" t="s"/>
+      <c r="J27" s="302" t="s"/>
+      <c r="K27" s="302" t="s"/>
     </row>
   </sheetData>
 </worksheet>
@@ -5206,250 +5340,250 @@
   <dimension ref="F15"/>
   <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="13.6719" style="291"/>
-    <col min="4" max="4" width="13.6719" style="292"/>
+    <col min="3" max="3" width="13.6719" style="303"/>
+    <col min="4" max="4" width="13.6719" style="304"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" t="s">
         <v>101</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="303" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="291" t="s">
+      <c r="D1" s="304" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="292" t="s">
+      <c r="E1" t="s">
         <v>104</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>105</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="305">
+        <v>46184</v>
+      </c>
+      <c r="B2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="293">
-        <v>46184</v>
-      </c>
-      <c r="B2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="291">
+      <c r="C2" s="303">
         <v>359</v>
       </c>
-      <c r="D2" s="292">
+      <c r="D2" s="304">
         <v>30</v>
       </c>
       <c r="F2" t="s"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="293">
+      <c r="A3" s="305">
         <v>46179</v>
       </c>
       <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="303">
+        <v>48</v>
+      </c>
+      <c r="D3" s="304">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="306">
+        <v>46179</v>
+      </c>
+      <c r="B4" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="291">
-        <v>48</v>
-      </c>
-      <c r="D3" s="292">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="294">
-        <v>46179</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" s="303">
+        <v>380</v>
+      </c>
+      <c r="D4" s="304">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="306">
+        <v>46180</v>
+      </c>
+      <c r="B5" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="291">
-        <v>380</v>
-      </c>
-      <c r="D4" s="292">
+      <c r="C5" s="303">
+        <v>1400</v>
+      </c>
+      <c r="D5" s="304">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" t="s"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="306">
+        <v>46180</v>
+      </c>
+      <c r="B6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="303">
+        <v>135</v>
+      </c>
+      <c r="D6" s="304">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" t="s"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="305">
+        <v>46183</v>
+      </c>
+      <c r="B7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="303">
+        <v>120</v>
+      </c>
+      <c r="D7" s="304">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="306">
+        <v>46185</v>
+      </c>
+      <c r="B8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="303">
+        <v>110.79</v>
+      </c>
+      <c r="D8" s="304">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="306">
+        <v>46206</v>
+      </c>
+      <c r="B9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="303">
+        <v>359</v>
+      </c>
+      <c r="D9" s="304">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="306">
+        <v>46206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="303">
+        <v>900</v>
+      </c>
+      <c r="D10" s="304">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="306">
+        <v>46206</v>
+      </c>
+      <c r="B11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="303">
+        <v>96.8</v>
+      </c>
+      <c r="D11" s="304">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="305">
+        <v>46209</v>
+      </c>
+      <c r="B12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="303">
+        <v>200</v>
+      </c>
+      <c r="D12" s="304">
         <v>20</v>
       </c>
-      <c r="F4" t="s"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="294">
-        <v>46180</v>
-      </c>
-      <c r="B5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="291">
-        <v>1400</v>
-      </c>
-      <c r="D5" s="292">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" t="s"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="294">
-        <v>46180</v>
-      </c>
-      <c r="B6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="291">
-        <v>135</v>
-      </c>
-      <c r="D6" s="292">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" t="s"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="293">
-        <v>46183</v>
-      </c>
-      <c r="B7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" s="291">
-        <v>120</v>
-      </c>
-      <c r="D7" s="292">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="294">
-        <v>46185</v>
-      </c>
-      <c r="B8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="291">
-        <v>110.79</v>
-      </c>
-      <c r="D8" s="292">
-        <v>100</v>
-      </c>
-      <c r="F8" t="s"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="294">
-        <v>46206</v>
-      </c>
-      <c r="B9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="291">
-        <v>359</v>
-      </c>
-      <c r="D9" s="292">
-        <v>30</v>
-      </c>
-      <c r="F9" t="s"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="294">
-        <v>46206</v>
-      </c>
-      <c r="B10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="291">
-        <v>900</v>
-      </c>
-      <c r="D10" s="292">
-        <v>50</v>
-      </c>
-      <c r="F10" t="s"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="294">
-        <v>46206</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="F12" t="s"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="305">
+        <v>46196</v>
+      </c>
+      <c r="B13" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="291">
-        <v>96.8</v>
-      </c>
-      <c r="D11" s="292">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="293">
-        <v>46209</v>
-      </c>
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" s="291">
-        <v>200</v>
-      </c>
-      <c r="D12" s="292">
-        <v>20</v>
-      </c>
-      <c r="F12" t="s"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="293">
-        <v>46196</v>
-      </c>
-      <c r="B13" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="291">
+      <c r="C13" s="303">
         <v>592.78</v>
       </c>
-      <c r="D13" s="292">
+      <c r="D13" s="304">
         <v>30</v>
       </c>
       <c r="F13" t="s"/>
       <c r="G13" t="s"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="294">
+      <c r="A14" s="306">
         <v>46180</v>
       </c>
       <c r="B14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="303">
+        <v>259</v>
+      </c>
+      <c r="D14" s="304" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="291">
-        <v>259</v>
-      </c>
-      <c r="D14" s="292" t="s">
+      <c r="E14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" t="s"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="307">
+        <v>46210</v>
+      </c>
+      <c r="B15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="303">
+        <v>249</v>
+      </c>
+      <c r="D15" s="304" t="s">
         <v>118</v>
       </c>
-      <c r="E14" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" t="s"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="295">
-        <v>46210</v>
-      </c>
-      <c r="B15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="291">
-        <v>249</v>
-      </c>
-      <c r="D15" s="292" t="s">
-        <v>119</v>
-      </c>
       <c r="E15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F15" t="s"/>
     </row>
@@ -5565,31 +5699,31 @@
       <c r="C3" s="39" t="s"/>
       <c r="D3" s="40" t="s"/>
       <c r="E3" s="39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="40">
         <v>90</v>
       </c>
       <c r="G3" s="39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="40">
         <v>90</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="40">
         <v>90</v>
       </c>
       <c r="K3" s="39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L3" s="40">
         <v>90</v>
       </c>
       <c r="M3" s="39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N3" s="40">
         <v>90</v>
@@ -5602,31 +5736,31 @@
       <c r="C4" s="43" t="s"/>
       <c r="D4" s="40" t="s"/>
       <c r="E4" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="40">
         <v>90</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="40">
         <v>90</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="40">
         <v>90</v>
       </c>
       <c r="K4" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L4" s="40">
         <v>90</v>
       </c>
       <c r="M4" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" s="40">
         <v>90</v>
@@ -5639,31 +5773,31 @@
       <c r="C5" s="39" t="s"/>
       <c r="D5" s="40" t="s"/>
       <c r="E5" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="40">
         <v>90</v>
       </c>
       <c r="G5" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="40">
         <v>90</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" s="40">
         <v>90</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" s="40">
         <v>90</v>
       </c>
       <c r="M5" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N5" s="40">
         <v>90</v>
@@ -5678,25 +5812,25 @@
       <c r="E6" s="39" t="s"/>
       <c r="F6" s="40" t="s"/>
       <c r="G6" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="40">
         <v>60</v>
       </c>
       <c r="I6" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" s="40">
         <v>60</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="40">
         <v>60</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="40">
         <v>60</v>
@@ -5711,25 +5845,25 @@
       <c r="E7" s="39" t="s"/>
       <c r="F7" s="40" t="s"/>
       <c r="G7" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="40">
         <v>60</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7" s="40">
         <v>60</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7" s="40">
         <v>60</v>
       </c>
       <c r="M7" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N7" s="40">
         <v>60</v>
@@ -5748,19 +5882,19 @@
       <c r="G8" s="39" t="s"/>
       <c r="H8" s="40" t="s"/>
       <c r="I8" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="40">
         <v>60</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L8" s="40">
         <v>60</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N8" s="40">
         <v>60</v>
@@ -6028,43 +6162,43 @@
     </row>
     <row r="21" spans="1:15" hidden="1">
       <c r="A21" s="53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" s="55">
         <v>90</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D21" s="55">
         <v>90</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" s="55">
         <v>90</v>
       </c>
       <c r="G21" s="53" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" s="55">
         <v>90</v>
       </c>
       <c r="I21" s="56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" s="55">
         <v>90</v>
       </c>
       <c r="K21" s="56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L21" s="54">
         <v>90</v>
       </c>
       <c r="M21" s="55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N21" s="54">
         <v>90</v>
@@ -6073,43 +6207,43 @@
     </row>
     <row r="22" spans="1:15" hidden="1">
       <c r="A22" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" s="40">
         <v>90</v>
       </c>
       <c r="C22" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" s="40">
         <v>90</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" s="40">
         <v>90</v>
       </c>
       <c r="G22" s="57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="40">
         <v>90</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" s="40">
         <v>90</v>
       </c>
       <c r="K22" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L22" s="41">
         <v>90</v>
       </c>
       <c r="M22" s="58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N22" s="41">
         <v>60</v>
@@ -6118,43 +6252,43 @@
     </row>
     <row r="23" spans="1:15" hidden="1">
       <c r="A23" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="40">
         <v>90</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" s="40">
         <v>90</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F23" s="40">
         <v>90</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H23" s="40">
         <v>90</v>
       </c>
       <c r="I23" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J23" s="40">
         <v>60</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L23" s="41">
         <v>60</v>
       </c>
       <c r="M23" s="40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N23" s="41">
         <v>60</v>
@@ -6163,43 +6297,43 @@
     </row>
     <row r="24" spans="1:15" hidden="1">
       <c r="A24" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="40">
         <v>60</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" s="40">
         <v>60</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F24" s="40">
         <v>60</v>
       </c>
       <c r="G24" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H24" s="40">
         <v>60</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J24" s="40">
         <v>60</v>
       </c>
       <c r="K24" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L24" s="41">
         <v>60</v>
       </c>
       <c r="M24" s="58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N24" s="41">
         <v>60</v>
@@ -6208,43 +6342,43 @@
     </row>
     <row r="25" spans="1:15" hidden="1">
       <c r="A25" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="40">
         <v>60</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" s="40">
         <v>60</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="40">
         <v>60</v>
       </c>
       <c r="G25" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" s="40">
         <v>60</v>
       </c>
       <c r="I25" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J25" s="40">
         <v>60</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L25" s="41">
         <v>60</v>
       </c>
       <c r="M25" s="40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N25" s="41">
         <v>90</v>
@@ -6253,43 +6387,43 @@
     </row>
     <row r="26" spans="1:15" hidden="1">
       <c r="A26" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="40">
         <v>60</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" s="40">
         <v>60</v>
       </c>
       <c r="E26" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F26" s="40">
         <v>60</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H26" s="40">
         <v>60</v>
       </c>
       <c r="I26" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="40">
+        <v>60</v>
+      </c>
+      <c r="K26" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="J26" s="40">
-        <v>60</v>
-      </c>
-      <c r="K26" s="39" t="s">
-        <v>23</v>
-      </c>
       <c r="L26" s="41">
         <v>60</v>
       </c>
       <c r="M26" s="40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N26" s="41">
         <v>60</v>
@@ -6300,37 +6434,37 @@
       <c r="A27" s="39" t="s"/>
       <c r="B27" s="40" t="s"/>
       <c r="C27" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="40">
+        <v>60</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="40">
+        <v>60</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="40">
+        <v>60</v>
+      </c>
+      <c r="I27" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="40">
-        <v>60</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="40">
-        <v>60</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="40">
-        <v>60</v>
-      </c>
-      <c r="I27" s="39" t="s">
-        <v>23</v>
-      </c>
       <c r="J27" s="40">
         <v>90</v>
       </c>
       <c r="K27" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L27" s="41">
         <v>60</v>
       </c>
       <c r="M27" s="40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N27" s="41">
         <v>90</v>
@@ -6341,23 +6475,23 @@
       <c r="A28" s="39" t="s"/>
       <c r="B28" s="40" t="s"/>
       <c r="C28" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D28" s="40" t="s"/>
       <c r="E28" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="40">
         <v>60</v>
       </c>
       <c r="G28" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="40">
         <v>90</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" s="40">
         <v>60</v>
@@ -6372,19 +6506,19 @@
       <c r="A29" s="39" t="s"/>
       <c r="B29" s="40" t="s"/>
       <c r="C29" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" s="40">
         <v>60</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F29" s="40">
         <v>60</v>
       </c>
       <c r="G29" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H29" s="40">
         <v>60</v>
@@ -6401,7 +6535,7 @@
       <c r="A30" s="39" t="s"/>
       <c r="B30" s="40" t="s"/>
       <c r="C30" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" s="40">
         <v>60</v>
@@ -6422,29 +6556,29 @@
       <c r="A31" s="39" t="s"/>
       <c r="B31" s="40" t="s"/>
       <c r="C31" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D31" s="40">
         <v>60</v>
       </c>
       <c r="E31" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F31" s="40" t="s"/>
       <c r="G31" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H31" s="40" t="s"/>
       <c r="I31" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J31" s="40" t="s"/>
       <c r="K31" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L31" s="41" t="s"/>
       <c r="M31" s="40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N31" s="41" t="s"/>
       <c r="O31" s="60" t="s"/>
@@ -6453,37 +6587,37 @@
       <c r="A32" s="39" t="s"/>
       <c r="B32" s="40" t="s"/>
       <c r="C32" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D32" s="40">
         <v>60</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F32" s="40">
         <v>60</v>
       </c>
       <c r="G32" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H32" s="40">
         <v>60</v>
       </c>
       <c r="I32" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J32" s="40">
         <v>60</v>
       </c>
       <c r="K32" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L32" s="41">
         <v>60</v>
       </c>
       <c r="M32" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N32" s="41">
         <v>60</v>
@@ -6496,31 +6630,31 @@
       <c r="C33" s="39" t="s"/>
       <c r="D33" s="40" t="s"/>
       <c r="E33" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F33" s="40">
         <v>60</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H33" s="40">
         <v>60</v>
       </c>
       <c r="I33" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J33" s="40">
         <v>60</v>
       </c>
       <c r="K33" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L33" s="41">
         <v>30</v>
       </c>
       <c r="M33" s="40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N33" s="41">
         <v>105</v>
@@ -6533,31 +6667,31 @@
       <c r="C34" s="39" t="s"/>
       <c r="D34" s="40" t="s"/>
       <c r="E34" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F34" s="40">
         <v>60</v>
       </c>
       <c r="G34" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H34" s="40">
         <v>60</v>
       </c>
       <c r="I34" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J34" s="40">
         <v>60</v>
       </c>
       <c r="K34" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L34" s="41">
         <v>60</v>
       </c>
       <c r="M34" s="40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N34" s="41">
         <v>60</v>
@@ -6570,31 +6704,31 @@
       <c r="C35" s="39" t="s"/>
       <c r="D35" s="40" t="s"/>
       <c r="E35" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F35" s="40">
         <v>60</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H35" s="40">
         <v>60</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J35" s="40">
         <v>60</v>
       </c>
       <c r="K35" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L35" s="41">
         <v>60</v>
       </c>
       <c r="M35" s="58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N35" s="41">
         <v>60</v>
@@ -6609,13 +6743,13 @@
       <c r="E36" s="39" t="s"/>
       <c r="F36" s="40" t="s"/>
       <c r="G36" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H36" s="40">
         <v>60</v>
       </c>
       <c r="I36" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" s="40">
         <v>60</v>
@@ -6623,7 +6757,7 @@
       <c r="K36" s="39" t="s"/>
       <c r="L36" s="41" t="s"/>
       <c r="M36" s="40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N36" s="62">
         <v>45</v>
@@ -6804,43 +6938,43 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B44" s="55">
         <v>90</v>
       </c>
       <c r="C44" s="56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D44" s="55">
         <v>90</v>
       </c>
       <c r="E44" s="56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F44" s="55">
         <v>60</v>
       </c>
       <c r="G44" s="53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H44" s="54">
         <v>60</v>
       </c>
       <c r="I44" s="53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J44" s="54">
         <v>60</v>
       </c>
       <c r="K44" s="53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L44" s="54">
         <v>60</v>
       </c>
       <c r="M44" s="53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N44" s="54">
         <v>60</v>
@@ -6849,43 +6983,43 @@
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" s="40">
         <v>90</v>
       </c>
       <c r="C45" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D45" s="40">
         <v>90</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F45" s="40">
         <v>75</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H45" s="41">
         <v>60</v>
       </c>
       <c r="I45" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J45" s="41">
         <v>60</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L45" s="41">
         <v>75</v>
       </c>
       <c r="M45" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N45" s="41">
         <v>75</v>
@@ -6894,43 +7028,43 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B46" s="40">
         <v>60</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D46" s="40">
         <v>60</v>
       </c>
       <c r="E46" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F46" s="40">
         <v>60</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H46" s="41">
         <v>60</v>
       </c>
       <c r="I46" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J46" s="41">
         <v>60</v>
       </c>
       <c r="K46" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L46" s="41">
         <v>75</v>
       </c>
       <c r="M46" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N46" s="41">
         <v>75</v>
@@ -6939,7 +7073,7 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B47" s="40">
         <v>60</v>
@@ -6947,31 +7081,31 @@
       <c r="C47" s="39" t="s"/>
       <c r="D47" s="40" t="s"/>
       <c r="E47" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F47" s="40">
         <v>60</v>
       </c>
       <c r="G47" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H47" s="41">
         <v>60</v>
       </c>
       <c r="I47" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J47" s="41">
         <v>60</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L47" s="41">
         <v>60</v>
       </c>
       <c r="M47" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N47" s="41">
         <v>60</v>
@@ -6980,43 +7114,43 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48" s="40">
         <v>60</v>
       </c>
       <c r="C48" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D48" s="40">
         <v>60</v>
       </c>
       <c r="E48" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F48" s="40">
         <v>60</v>
       </c>
       <c r="G48" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" s="41">
+        <v>60</v>
+      </c>
+      <c r="I48" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="41">
+        <v>60</v>
+      </c>
+      <c r="K48" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="H48" s="41">
-        <v>60</v>
-      </c>
-      <c r="I48" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="J48" s="41">
-        <v>60</v>
-      </c>
-      <c r="K48" s="39" t="s">
-        <v>23</v>
-      </c>
       <c r="L48" s="41">
         <v>60</v>
       </c>
       <c r="M48" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N48" s="41">
         <v>75</v>
@@ -7025,43 +7159,43 @@
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="40">
+        <v>60</v>
+      </c>
+      <c r="C49" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="40">
+        <v>60</v>
+      </c>
+      <c r="E49" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="40">
+        <v>60</v>
+      </c>
+      <c r="G49" s="39" t="s">
         <v>24</v>
-      </c>
-      <c r="B49" s="40">
-        <v>60</v>
-      </c>
-      <c r="C49" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="40">
-        <v>60</v>
-      </c>
-      <c r="E49" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="F49" s="40">
-        <v>60</v>
-      </c>
-      <c r="G49" s="39" t="s">
-        <v>23</v>
       </c>
       <c r="H49" s="41">
         <v>75</v>
       </c>
       <c r="I49" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J49" s="41">
         <v>75</v>
       </c>
       <c r="K49" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L49" s="41">
         <v>75</v>
       </c>
       <c r="M49" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N49" s="41">
         <v>60</v>
@@ -7070,31 +7204,31 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50" s="40">
         <v>90</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D50" s="40">
         <v>90</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F50" s="40">
         <v>75</v>
       </c>
       <c r="G50" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H50" s="41">
         <v>90</v>
       </c>
       <c r="I50" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J50" s="41">
         <v>90</v>
@@ -7107,19 +7241,19 @@
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B51" s="40">
         <v>60</v>
       </c>
       <c r="C51" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D51" s="40">
         <v>60</v>
       </c>
       <c r="E51" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F51" s="40">
         <v>90</v>
@@ -7187,27 +7321,27 @@
     </row>
     <row r="55" spans="1:15">
       <c r="A55" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B55" s="40" t="s"/>
       <c r="C55" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D55" s="40" t="s"/>
       <c r="E55" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F55" s="40" t="s"/>
       <c r="G55" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H55" s="41" t="s"/>
       <c r="I55" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J55" s="41" t="s"/>
       <c r="K55" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L55" s="41" t="s"/>
       <c r="M55" s="61" t="s"/>
@@ -7216,43 +7350,43 @@
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B56" s="40">
         <v>110</v>
       </c>
       <c r="C56" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D56" s="40">
         <v>60</v>
       </c>
       <c r="E56" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F56" s="40">
         <v>90</v>
       </c>
       <c r="G56" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H56" s="41">
         <v>90</v>
       </c>
       <c r="I56" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J56" s="41">
         <v>90</v>
       </c>
       <c r="K56" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L56" s="41">
         <v>75</v>
       </c>
       <c r="M56" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N56" s="70">
         <v>90</v>
@@ -7261,31 +7395,31 @@
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B57" s="40">
         <v>60</v>
       </c>
       <c r="C57" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D57" s="40">
         <v>30</v>
       </c>
       <c r="E57" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F57" s="40">
         <v>75</v>
       </c>
       <c r="G57" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H57" s="70">
         <v>60</v>
       </c>
       <c r="I57" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J57" s="70">
         <v>75</v>
@@ -7293,7 +7427,7 @@
       <c r="K57" s="39" t="s"/>
       <c r="L57" s="70" t="s"/>
       <c r="M57" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N57" s="41">
         <v>90</v>
@@ -7302,43 +7436,43 @@
     </row>
     <row r="58" spans="1:15">
       <c r="A58" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B58" s="40">
         <v>60</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D58" s="40">
         <v>60</v>
       </c>
       <c r="E58" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F58" s="40">
         <v>60</v>
       </c>
       <c r="G58" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H58" s="41">
         <v>60</v>
       </c>
       <c r="I58" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J58" s="41">
         <v>60</v>
       </c>
       <c r="K58" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L58" s="41">
         <v>75</v>
       </c>
       <c r="M58" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N58" s="41">
         <v>75</v>
@@ -7347,54 +7481,58 @@
     </row>
     <row r="59" spans="1:15">
       <c r="A59" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B59" s="40">
         <v>60</v>
       </c>
       <c r="C59" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D59" s="40">
         <v>60</v>
       </c>
       <c r="E59" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F59" s="40">
         <v>60</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H59" s="41">
         <v>60</v>
       </c>
       <c r="I59" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J59" s="41">
         <v>60</v>
       </c>
       <c r="K59" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L59" s="41">
         <v>60</v>
       </c>
-      <c r="M59" s="40" t="s"/>
-      <c r="N59" s="70" t="s"/>
+      <c r="M59" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="N59" s="70">
+        <v>300</v>
+      </c>
       <c r="O59" s="60" t="s"/>
     </row>
     <row r="60" spans="1:15">
       <c r="A60" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B60" s="40">
         <v>60</v>
       </c>
       <c r="C60" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D60" s="40">
         <v>60</v>
@@ -7407,8 +7545,12 @@
       <c r="J60" s="40" t="s"/>
       <c r="K60" s="39" t="s"/>
       <c r="L60" s="41" t="s"/>
-      <c r="M60" s="40" t="s"/>
-      <c r="N60" s="41" t="s"/>
+      <c r="M60" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="N60" s="41">
+        <v>50</v>
+      </c>
       <c r="O60" s="60" t="s"/>
     </row>
     <row r="61" spans="1:15">
@@ -7466,11 +7608,11 @@
       <c r="M62" s="68" t="s"/>
       <c r="N62" s="68">
         <f>=SUM(N44:N61)</f>
-        <v>660</v>
+        <v>1010</v>
       </c>
       <c r="O62" s="51">
         <f>=SUM(A62:N62)</f>
-        <v>5285</v>
+        <v>5635</v>
       </c>
       <c r="P62" s="71" t="s"/>
     </row>
@@ -7566,19 +7708,23 @@
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B67" s="54">
+        <v>60</v>
+      </c>
+      <c r="C67" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B67" s="54">
-        <v>60</v>
-      </c>
-      <c r="C67" s="56" t="s">
-        <v>18</v>
-      </c>
       <c r="D67" s="55">
         <v>90</v>
       </c>
-      <c r="E67" s="56" t="s"/>
-      <c r="F67" s="55" t="s"/>
+      <c r="E67" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" s="55">
+        <v>90</v>
+      </c>
       <c r="G67" s="53" t="s"/>
       <c r="H67" s="54" t="s"/>
       <c r="I67" s="53" t="s"/>
@@ -7591,7 +7737,7 @@
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B68" s="41">
         <v>75</v>
@@ -7612,19 +7758,23 @@
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B69" s="41">
         <v>75</v>
       </c>
       <c r="C69" s="44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D69" s="8">
         <v>90</v>
       </c>
-      <c r="E69" s="44" t="s"/>
-      <c r="F69" s="8" t="s"/>
+      <c r="E69" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" s="8">
+        <v>90</v>
+      </c>
       <c r="G69" s="39" t="s"/>
       <c r="H69" s="41" t="s"/>
       <c r="I69" s="39" t="s"/>
@@ -7637,19 +7787,23 @@
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" s="41">
+        <v>60</v>
+      </c>
+      <c r="C70" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B70" s="41">
-        <v>60</v>
-      </c>
-      <c r="C70" s="39" t="s">
-        <v>21</v>
-      </c>
       <c r="D70" s="8">
         <v>90</v>
       </c>
-      <c r="E70" s="39" t="s"/>
-      <c r="F70" s="8" t="s"/>
+      <c r="E70" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F70" s="8">
+        <v>90</v>
+      </c>
       <c r="G70" s="44" t="s"/>
       <c r="H70" s="41" t="s"/>
       <c r="I70" s="44" t="s"/>
@@ -7662,19 +7816,23 @@
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" s="41">
+        <v>60</v>
+      </c>
+      <c r="C71" s="44" t="s">
         <v>23</v>
-      </c>
-      <c r="B71" s="41">
-        <v>60</v>
-      </c>
-      <c r="C71" s="44" t="s">
-        <v>22</v>
       </c>
       <c r="D71" s="8">
         <v>75</v>
       </c>
-      <c r="E71" s="44" t="s"/>
-      <c r="F71" s="8" t="s"/>
+      <c r="E71" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71" s="8">
+        <v>75</v>
+      </c>
       <c r="G71" s="39" t="s"/>
       <c r="H71" s="41" t="s"/>
       <c r="I71" s="39" t="s"/>
@@ -7687,19 +7845,23 @@
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B72" s="41">
         <v>75</v>
       </c>
       <c r="C72" s="39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D72" s="8">
         <v>75</v>
       </c>
-      <c r="E72" s="39" t="s"/>
-      <c r="F72" s="8" t="s"/>
+      <c r="E72" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="8">
+        <v>75</v>
+      </c>
       <c r="G72" s="39" t="s"/>
       <c r="H72" s="41" t="s"/>
       <c r="I72" s="39" t="s"/>
@@ -7712,19 +7874,23 @@
     </row>
     <row r="73" spans="1:15">
       <c r="A73" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" s="8">
+        <v>60</v>
+      </c>
+      <c r="C73" s="39" t="s">
         <v>24</v>
-      </c>
-      <c r="B73" s="8">
-        <v>60</v>
-      </c>
-      <c r="C73" s="39" t="s">
-        <v>23</v>
       </c>
       <c r="D73" s="8">
         <v>75</v>
       </c>
-      <c r="E73" s="39" t="s"/>
-      <c r="F73" s="8" t="s"/>
+      <c r="E73" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="8">
+        <v>75</v>
+      </c>
       <c r="G73" s="39" t="s"/>
       <c r="H73" s="41" t="s"/>
       <c r="I73" s="39" t="s"/>
@@ -7739,13 +7905,17 @@
       <c r="A74" s="39" t="s"/>
       <c r="B74" s="8" t="s"/>
       <c r="C74" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D74" s="8">
         <v>90</v>
       </c>
-      <c r="E74" s="39" t="s"/>
-      <c r="F74" s="8" t="s"/>
+      <c r="E74" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="F74" s="8">
+        <v>90</v>
+      </c>
       <c r="G74" s="39" t="s"/>
       <c r="H74" s="41" t="s"/>
       <c r="I74" s="8" t="s"/>
@@ -7809,27 +7979,27 @@
     </row>
     <row r="78" spans="1:15">
       <c r="A78" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B78" s="8" t="s"/>
       <c r="C78" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D78" s="8" t="s"/>
       <c r="E78" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F78" s="8" t="s"/>
       <c r="G78" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H78" s="41" t="s"/>
       <c r="I78" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J78" s="41" t="s"/>
       <c r="K78" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L78" s="40" t="s"/>
       <c r="M78" s="43" t="s"/>
@@ -7838,19 +8008,23 @@
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B79" s="41">
         <v>105</v>
       </c>
       <c r="C79" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D79" s="8">
+        <v>90</v>
+      </c>
+      <c r="E79" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="8">
         <v>75</v>
       </c>
-      <c r="E79" s="43" t="s"/>
-      <c r="F79" s="8" t="s"/>
       <c r="G79" s="43" t="s"/>
       <c r="H79" s="41" t="s"/>
       <c r="I79" s="43" t="s"/>
@@ -7863,19 +8037,23 @@
     </row>
     <row r="80" spans="1:15">
       <c r="A80" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B80" s="70">
         <v>60</v>
       </c>
       <c r="C80" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D80" s="8">
         <v>60</v>
       </c>
-      <c r="E80" s="39" t="s"/>
-      <c r="F80" s="8" t="s"/>
+      <c r="E80" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="8">
+        <v>60</v>
+      </c>
       <c r="G80" s="39" t="s"/>
       <c r="H80" s="70" t="s"/>
       <c r="I80" s="39" t="s"/>
@@ -7888,19 +8066,23 @@
     </row>
     <row r="81" spans="1:15">
       <c r="A81" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B81" s="41">
         <v>75</v>
       </c>
       <c r="C81" s="43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D81" s="8">
         <v>90</v>
       </c>
-      <c r="E81" s="39" t="s"/>
-      <c r="F81" s="8" t="s"/>
+      <c r="E81" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F81" s="8">
+        <v>75</v>
+      </c>
       <c r="G81" s="39" t="s"/>
       <c r="H81" s="41" t="s"/>
       <c r="I81" s="39" t="s"/>
@@ -7913,19 +8095,23 @@
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B82" s="41">
         <v>60</v>
       </c>
       <c r="C82" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D82" s="8">
-        <v>60</v>
-      </c>
-      <c r="E82" s="44" t="s"/>
-      <c r="F82" s="8" t="s"/>
+        <v>75</v>
+      </c>
+      <c r="E82" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" s="8">
+        <v>60</v>
+      </c>
       <c r="G82" s="44" t="s"/>
       <c r="H82" s="41" t="s"/>
       <c r="I82" s="44" t="s"/>
@@ -7981,12 +8167,12 @@
       <c r="C85" s="67" t="s"/>
       <c r="D85" s="68">
         <f>=SUM(D67:D84)</f>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="E85" s="67" t="s"/>
       <c r="F85" s="68">
         <f>=SUM(F67:F84)</f>
-        <v>0</v>
+        <v>855</v>
       </c>
       <c r="G85" s="67">
         <v>0</v>
@@ -8012,7 +8198,7 @@
       </c>
       <c r="O85" s="51">
         <f>=SUM(A85:N85)</f>
-        <v>1635</v>
+        <v>2520</v>
       </c>
     </row>
   </sheetData>
@@ -8090,25 +8276,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="72">
         <v>60</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" s="72">
         <v>60</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="72">
         <v>60</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="74">
         <v>60</v>
@@ -8117,25 +8303,25 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="72">
         <v>60</v>
       </c>
       <c r="C4" s="75" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="72">
         <v>60</v>
       </c>
       <c r="E4" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="72">
+        <v>60</v>
+      </c>
+      <c r="G4" s="73" t="s">
         <v>29</v>
-      </c>
-      <c r="F4" s="72">
-        <v>60</v>
-      </c>
-      <c r="G4" s="73" t="s">
-        <v>28</v>
       </c>
       <c r="H4" s="74">
         <v>60</v>
@@ -8144,25 +8330,25 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="72">
+        <v>60</v>
+      </c>
+      <c r="C5" s="75" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="72">
+        <v>60</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="72">
-        <v>60</v>
-      </c>
-      <c r="C5" s="75" t="s">
+      <c r="F5" s="72">
+        <v>60</v>
+      </c>
+      <c r="G5" s="77" t="s">
         <v>30</v>
-      </c>
-      <c r="D5" s="72">
-        <v>60</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="72">
-        <v>60</v>
-      </c>
-      <c r="G5" s="77" t="s">
-        <v>29</v>
       </c>
       <c r="H5" s="74">
         <v>60</v>
@@ -8171,25 +8357,25 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="72">
+        <v>60</v>
+      </c>
+      <c r="C6" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="72">
-        <v>60</v>
-      </c>
-      <c r="C6" s="76" t="s">
-        <v>29</v>
-      </c>
       <c r="D6" s="72">
         <v>60</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="72">
         <v>60</v>
       </c>
       <c r="G6" s="73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" s="74">
         <v>60</v>
@@ -8198,7 +8384,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="72">
         <v>60</v>
@@ -8231,13 +8417,13 @@
         <v>60</v>
       </c>
       <c r="C8" s="73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="72">
         <v>60</v>
       </c>
       <c r="E8" s="75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="72">
         <v>60</v>
@@ -8252,13 +8438,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="72">
         <v>60</v>
       </c>
       <c r="C9" s="75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="72">
         <v>60</v>
@@ -8293,7 +8479,7 @@
         <v>60</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10" s="74">
         <v>60</v>
@@ -8308,19 +8494,19 @@
         <v>60</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" s="72">
         <v>60</v>
       </c>
       <c r="E11" s="73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="72">
         <v>60</v>
       </c>
       <c r="G11" s="73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" s="74">
         <v>60</v>
@@ -8485,31 +8671,31 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="80">
         <v>60</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="80">
         <v>60</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="80">
         <v>60</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" s="80">
         <v>60</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18" s="80">
         <v>60</v>
@@ -8525,37 +8711,37 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="72">
         <v>60</v>
       </c>
       <c r="C19" s="73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D19" s="72">
         <v>60</v>
       </c>
       <c r="E19" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="72">
+        <v>60</v>
+      </c>
+      <c r="G19" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="72">
-        <v>60</v>
-      </c>
-      <c r="G19" s="73" t="s">
-        <v>28</v>
-      </c>
       <c r="H19" s="72">
         <v>60</v>
       </c>
       <c r="I19" s="73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J19" s="72">
         <v>60</v>
       </c>
       <c r="K19" s="73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L19" s="74">
         <v>60</v>
@@ -8565,31 +8751,31 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="72">
+        <v>60</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="72">
+        <v>60</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="72">
-        <v>60</v>
-      </c>
-      <c r="C20" s="75" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="72">
-        <v>60</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>28</v>
-      </c>
       <c r="F20" s="72">
         <v>60</v>
       </c>
       <c r="G20" s="77" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H20" s="72">
         <v>60</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J20" s="72">
         <v>60</v>
@@ -8605,31 +8791,31 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="72">
+        <v>60</v>
+      </c>
+      <c r="C21" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="72">
-        <v>60</v>
-      </c>
-      <c r="C21" s="76" t="s">
-        <v>29</v>
-      </c>
       <c r="D21" s="72">
         <v>60</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F21" s="72">
         <v>60</v>
       </c>
       <c r="G21" s="76" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="72">
+        <v>60</v>
+      </c>
+      <c r="I21" s="73" t="s">
         <v>35</v>
-      </c>
-      <c r="H21" s="72">
-        <v>60</v>
-      </c>
-      <c r="I21" s="73" t="s">
-        <v>34</v>
       </c>
       <c r="J21" s="72">
         <v>60</v>
@@ -8657,19 +8843,19 @@
         <v>60</v>
       </c>
       <c r="E22" s="73" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F22" s="72">
         <v>60</v>
       </c>
       <c r="G22" s="73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H22" s="72">
         <v>60</v>
       </c>
       <c r="I22" s="75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J22" s="72">
         <v>60</v>
@@ -8723,13 +8909,13 @@
         <v>60</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" s="72">
         <v>60</v>
       </c>
       <c r="E24" s="75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" s="72">
         <v>60</v>
@@ -8765,7 +8951,7 @@
         <v>60</v>
       </c>
       <c r="E25" s="76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25" s="72">
         <v>60</v>
@@ -8789,13 +8975,13 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="73" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="72">
         <v>60</v>
       </c>
       <c r="C26" s="73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D26" s="72">
         <v>60</v>
@@ -8807,7 +8993,7 @@
         <v>60</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="72">
         <v>60</v>
@@ -8831,25 +9017,25 @@
         <v>60</v>
       </c>
       <c r="C27" s="73" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" s="72">
         <v>60</v>
       </c>
       <c r="E27" s="73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F27" s="72">
         <v>60</v>
       </c>
       <c r="G27" s="73" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H27" s="72">
         <v>60</v>
       </c>
       <c r="I27" s="76" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J27" s="72">
         <v>60</v>
@@ -8863,7 +9049,7 @@
       <c r="A28" s="32" t="s"/>
       <c r="B28" s="86" t="s"/>
       <c r="C28" s="87" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="86">
         <v>60</v>
@@ -8965,8 +9151,8 @@
       <c r="L32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="M32" s="90" t="s"/>
-      <c r="N32" s="91" t="s"/>
+      <c r="M32" s="89" t="s"/>
+      <c r="N32" s="90" t="s"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="28" t="s">
@@ -9008,166 +9194,381 @@
       <c r="M33" s="11" t="s"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="28" t="s"/>
-      <c r="B34" s="80" t="s"/>
-      <c r="C34" s="81" t="s"/>
-      <c r="D34" s="80" t="s"/>
-      <c r="E34" s="28" t="s"/>
-      <c r="F34" s="80" t="s"/>
-      <c r="G34" s="28" t="s"/>
-      <c r="H34" s="80" t="s"/>
+      <c r="A34" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="80">
+        <v>60</v>
+      </c>
+      <c r="C34" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="80">
+        <v>60</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" s="80">
+        <v>60</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="80">
+        <v>60</v>
+      </c>
       <c r="I34" s="28" t="s"/>
-      <c r="J34" s="80" t="s"/>
       <c r="K34" s="28" t="s"/>
       <c r="L34" s="78" t="s"/>
       <c r="M34" s="11" t="s"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="73" t="s"/>
-      <c r="B35" s="72" t="s"/>
-      <c r="C35" s="73" t="s"/>
-      <c r="D35" s="72" t="s"/>
-      <c r="E35" s="76" t="s"/>
-      <c r="F35" s="72" t="s"/>
-      <c r="G35" s="73" t="s"/>
-      <c r="H35" s="72" t="s"/>
-      <c r="I35" s="73" t="s"/>
-      <c r="J35" s="72" t="s"/>
+      <c r="A35" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="72">
+        <v>60</v>
+      </c>
+      <c r="C35" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="80">
+        <v>60</v>
+      </c>
+      <c r="E35" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="80">
+        <v>60</v>
+      </c>
+      <c r="G35" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" s="80">
+        <v>60</v>
+      </c>
+      <c r="I35" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="J35" s="80">
+        <v>60</v>
+      </c>
       <c r="K35" s="73" t="s"/>
       <c r="L35" s="74" t="s"/>
       <c r="M35" s="11" t="s"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="75" t="s"/>
-      <c r="B36" s="72" t="s"/>
-      <c r="C36" s="75" t="s"/>
-      <c r="D36" s="72" t="s"/>
-      <c r="E36" s="9" t="s"/>
-      <c r="F36" s="72" t="s"/>
-      <c r="G36" s="77" t="s"/>
-      <c r="H36" s="72" t="s"/>
-      <c r="I36" s="12" t="s"/>
-      <c r="J36" s="72" t="s"/>
+      <c r="A36" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="72">
+        <v>60</v>
+      </c>
+      <c r="C36" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="80">
+        <v>60</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="80">
+        <v>60</v>
+      </c>
+      <c r="G36" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="H36" s="80">
+        <v>60</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="80">
+        <v>60</v>
+      </c>
       <c r="K36" s="9" t="s"/>
       <c r="L36" s="74" t="s"/>
       <c r="M36" s="11" t="s"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="12" t="s"/>
-      <c r="B37" s="72" t="s"/>
-      <c r="C37" s="76" t="s"/>
-      <c r="D37" s="72" t="s"/>
-      <c r="E37" s="9" t="s"/>
-      <c r="F37" s="72" t="s"/>
-      <c r="G37" s="76" t="s"/>
-      <c r="H37" s="72" t="s"/>
-      <c r="I37" s="73" t="s"/>
-      <c r="J37" s="72" t="s"/>
+      <c r="A37" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="72">
+        <v>60</v>
+      </c>
+      <c r="C37" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="80">
+        <v>60</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="80">
+        <v>60</v>
+      </c>
+      <c r="G37" s="76" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="80">
+        <v>60</v>
+      </c>
+      <c r="I37" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="J37" s="80">
+        <v>60</v>
+      </c>
       <c r="K37" s="73" t="s"/>
       <c r="L37" s="74" t="s"/>
       <c r="M37" s="11" t="s"/>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="73" t="s"/>
-      <c r="B38" s="72" t="s"/>
-      <c r="C38" s="75" t="s"/>
-      <c r="D38" s="72" t="s"/>
-      <c r="E38" s="73" t="s"/>
-      <c r="F38" s="72" t="s"/>
-      <c r="G38" s="73" t="s"/>
-      <c r="H38" s="72" t="s"/>
-      <c r="I38" s="75" t="s"/>
-      <c r="J38" s="72" t="s"/>
+      <c r="A38" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="72">
+        <v>60</v>
+      </c>
+      <c r="C38" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="80">
+        <v>60</v>
+      </c>
+      <c r="E38" s="73" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" s="80">
+        <v>60</v>
+      </c>
+      <c r="G38" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="H38" s="80">
+        <v>60</v>
+      </c>
+      <c r="I38" s="75" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="80">
+        <v>60</v>
+      </c>
       <c r="K38" s="73" t="s"/>
       <c r="L38" s="74" t="s"/>
       <c r="M38" s="11" t="s"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="82" t="s"/>
-      <c r="B39" s="83" t="s"/>
-      <c r="C39" s="84" t="s"/>
-      <c r="D39" s="83" t="s"/>
-      <c r="E39" s="84" t="s"/>
-      <c r="F39" s="83" t="s"/>
-      <c r="G39" s="84" t="s"/>
-      <c r="H39" s="83" t="s"/>
-      <c r="I39" s="84" t="s"/>
-      <c r="J39" s="83" t="s"/>
+      <c r="A39" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="83">
+        <v>60</v>
+      </c>
+      <c r="C39" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="91">
+        <v>60</v>
+      </c>
+      <c r="E39" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="91">
+        <v>60</v>
+      </c>
+      <c r="G39" s="84" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="91">
+        <v>60</v>
+      </c>
+      <c r="I39" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="J39" s="91">
+        <v>60</v>
+      </c>
       <c r="K39" s="84" t="s"/>
       <c r="L39" s="85" t="s"/>
       <c r="M39" s="11" t="s"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="75" t="s"/>
-      <c r="B40" s="72" t="s"/>
-      <c r="C40" s="76" t="s"/>
-      <c r="D40" s="72" t="s"/>
-      <c r="E40" s="75" t="s"/>
-      <c r="F40" s="72" t="s"/>
-      <c r="G40" s="73" t="s"/>
-      <c r="H40" s="72" t="s"/>
-      <c r="I40" s="75" t="s"/>
-      <c r="J40" s="72" t="s"/>
+      <c r="A40" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="72">
+        <v>60</v>
+      </c>
+      <c r="C40" s="76" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="80">
+        <v>60</v>
+      </c>
+      <c r="E40" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="80">
+        <v>60</v>
+      </c>
+      <c r="G40" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" s="80">
+        <v>60</v>
+      </c>
+      <c r="I40" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="80">
+        <v>60</v>
+      </c>
       <c r="K40" s="73" t="s"/>
       <c r="L40" s="74" t="s"/>
       <c r="M40" s="11" t="s"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="75" t="s"/>
-      <c r="B41" s="72" t="s"/>
-      <c r="C41" s="75" t="s"/>
-      <c r="D41" s="72" t="s"/>
-      <c r="E41" s="76" t="s"/>
-      <c r="F41" s="72" t="s"/>
-      <c r="G41" s="73" t="s"/>
-      <c r="H41" s="72" t="s"/>
-      <c r="I41" s="73" t="s"/>
-      <c r="J41" s="72" t="s"/>
+      <c r="A41" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="72">
+        <v>60</v>
+      </c>
+      <c r="C41" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="80">
+        <v>60</v>
+      </c>
+      <c r="E41" s="76" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="80">
+        <v>60</v>
+      </c>
+      <c r="G41" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="80">
+        <v>60</v>
+      </c>
+      <c r="I41" s="73" t="s">
+        <v>10</v>
+      </c>
+      <c r="J41" s="80">
+        <v>60</v>
+      </c>
       <c r="K41" s="73" t="s"/>
       <c r="L41" s="74" t="s"/>
       <c r="M41" s="11" t="s"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="73" t="s"/>
-      <c r="B42" s="72" t="s"/>
-      <c r="C42" s="73" t="s"/>
-      <c r="D42" s="72" t="s"/>
-      <c r="E42" s="75" t="s"/>
-      <c r="F42" s="72" t="s"/>
-      <c r="G42" s="12" t="s"/>
-      <c r="H42" s="72" t="s"/>
-      <c r="I42" s="9" t="s"/>
-      <c r="J42" s="72" t="s"/>
+      <c r="A42" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="72">
+        <v>60</v>
+      </c>
+      <c r="C42" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="80">
+        <v>60</v>
+      </c>
+      <c r="E42" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" s="80">
+        <v>60</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="80">
+        <v>60</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J42" s="80">
+        <v>60</v>
+      </c>
       <c r="K42" s="12" t="s"/>
       <c r="L42" s="74" t="s"/>
       <c r="M42" s="11" t="s"/>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="75" t="s"/>
-      <c r="B43" s="72" t="s"/>
-      <c r="C43" s="73" t="s"/>
-      <c r="D43" s="72" t="s"/>
-      <c r="E43" s="73" t="s"/>
-      <c r="F43" s="72" t="s"/>
-      <c r="G43" s="73" t="s"/>
-      <c r="H43" s="72" t="s"/>
-      <c r="I43" s="76" t="s"/>
-      <c r="J43" s="72" t="s"/>
+      <c r="A43" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="72">
+        <v>60</v>
+      </c>
+      <c r="C43" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="80">
+        <v>60</v>
+      </c>
+      <c r="E43" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="80">
+        <v>60</v>
+      </c>
+      <c r="G43" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="80">
+        <v>60</v>
+      </c>
+      <c r="I43" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="J43" s="80">
+        <v>60</v>
+      </c>
       <c r="K43" s="73" t="s"/>
       <c r="L43" s="74" t="s"/>
       <c r="M43" s="11" t="s"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="32" t="s"/>
-      <c r="B44" s="86" t="s"/>
-      <c r="C44" s="87" t="s"/>
-      <c r="D44" s="86" t="s"/>
-      <c r="E44" s="87" t="s"/>
-      <c r="F44" s="86" t="s"/>
-      <c r="G44" s="87" t="s"/>
-      <c r="H44" s="86" t="s"/>
-      <c r="I44" s="87" t="s"/>
-      <c r="J44" s="86" t="s"/>
+      <c r="A44" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="72">
+        <v>60</v>
+      </c>
+      <c r="C44" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="92">
+        <v>60</v>
+      </c>
+      <c r="E44" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="92">
+        <v>60</v>
+      </c>
+      <c r="G44" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="92">
+        <v>60</v>
+      </c>
+      <c r="I44" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="J44" s="92">
+        <v>60</v>
+      </c>
       <c r="K44" s="87" t="s"/>
       <c r="L44" s="88" t="s"/>
       <c r="M44" s="13" t="s">
@@ -9178,27 +9579,27 @@
       <c r="A45" s="15" t="s"/>
       <c r="B45" s="16">
         <f>=SUM(B34:B44)</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="C45" s="15" t="s"/>
       <c r="D45" s="16">
         <f>=SUM(D34:D44)</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="E45" s="15" t="s"/>
       <c r="F45" s="16">
         <f>=SUM(F34:F44)</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="G45" s="15" t="s"/>
       <c r="H45" s="16">
         <f>=SUM(H34:H44)</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="I45" s="15" t="s"/>
       <c r="J45" s="16">
-        <f>=SUM(J34:J44)</f>
-        <v>0</v>
+        <f>=SUM(J35:J44)</f>
+        <v>600</v>
       </c>
       <c r="K45" s="15" t="s"/>
       <c r="L45" s="17">
@@ -9207,7 +9608,7 @@
       </c>
       <c r="M45" s="18">
         <f>=SUM(A45:L45)</f>
-        <v>0</v>
+        <v>3240</v>
       </c>
     </row>
   </sheetData>
@@ -9227,125 +9628,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="92">
+      <c r="A1" s="93">
         <v>46188</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="92">
+      <c r="C1" s="93">
         <v>46189</v>
       </c>
-      <c r="D1" s="93" t="s">
+      <c r="D1" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="92">
+      <c r="E1" s="93">
         <v>46190</v>
       </c>
-      <c r="F1" s="93" t="s">
+      <c r="F1" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="92">
+      <c r="G1" s="93">
         <v>46191</v>
       </c>
-      <c r="H1" s="93" t="s">
+      <c r="H1" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="94">
+      <c r="I1" s="95">
         <v>46192</v>
       </c>
-      <c r="J1" s="95" t="s">
+      <c r="J1" s="96" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="96" t="s"/>
-      <c r="L1" s="97" t="s"/>
+      <c r="K1" s="97" t="s"/>
+      <c r="L1" s="98" t="s"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="98" t="s">
+      <c r="A2" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="99">
-        <v>60</v>
-      </c>
-      <c r="C2" s="98" t="s">
+      <c r="B2" s="100">
+        <v>60</v>
+      </c>
+      <c r="C2" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="99">
-        <v>60</v>
-      </c>
-      <c r="E2" s="98" t="s">
+      <c r="D2" s="100">
+        <v>60</v>
+      </c>
+      <c r="E2" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="99">
-        <v>60</v>
-      </c>
-      <c r="G2" s="98" t="s">
+      <c r="F2" s="100">
+        <v>60</v>
+      </c>
+      <c r="G2" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="99">
+      <c r="H2" s="100">
         <v>65</v>
       </c>
-      <c r="I2" s="98" t="s"/>
-      <c r="J2" s="100" t="s"/>
-      <c r="K2" s="101" t="s"/>
+      <c r="I2" s="99" t="s"/>
+      <c r="J2" s="101" t="s"/>
+      <c r="K2" s="102" t="s"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="103">
-        <v>60</v>
-      </c>
-      <c r="C3" s="102" t="s">
+      <c r="B3" s="104">
+        <v>60</v>
+      </c>
+      <c r="C3" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="103">
-        <v>60</v>
-      </c>
-      <c r="E3" s="102" t="s">
+      <c r="D3" s="104">
+        <v>60</v>
+      </c>
+      <c r="E3" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="103">
-        <v>60</v>
-      </c>
-      <c r="G3" s="102" t="s">
+      <c r="F3" s="104">
+        <v>60</v>
+      </c>
+      <c r="G3" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="103">
+      <c r="H3" s="104">
         <v>65</v>
       </c>
-      <c r="I3" s="102" t="s"/>
-      <c r="J3" s="104" t="s"/>
-      <c r="K3" s="101" t="s"/>
+      <c r="I3" s="103" t="s"/>
+      <c r="J3" s="105" t="s"/>
+      <c r="K3" s="102" t="s"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="103">
-        <v>60</v>
-      </c>
-      <c r="C4" s="102" t="s">
+      <c r="B4" s="104">
+        <v>60</v>
+      </c>
+      <c r="C4" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="103">
-        <v>60</v>
-      </c>
-      <c r="E4" s="102" t="s">
+      <c r="D4" s="104">
+        <v>60</v>
+      </c>
+      <c r="E4" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="103">
-        <v>60</v>
-      </c>
-      <c r="G4" s="102" t="s">
+      <c r="F4" s="104">
+        <v>60</v>
+      </c>
+      <c r="G4" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="103">
+      <c r="H4" s="104">
         <v>65</v>
       </c>
-      <c r="I4" s="102" t="s"/>
-      <c r="J4" s="104" t="s"/>
-      <c r="K4" s="101" t="s"/>
+      <c r="I4" s="103" t="s"/>
+      <c r="J4" s="105" t="s"/>
+      <c r="K4" s="102" t="s"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="106" t="s"/>
@@ -9355,14 +9756,14 @@
       <c r="E5" s="106" t="s"/>
       <c r="F5" s="107" t="s"/>
       <c r="G5" s="106" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H5" s="107">
         <v>10</v>
       </c>
       <c r="I5" s="106" t="s"/>
       <c r="J5" s="108" t="s"/>
-      <c r="K5" s="297" t="s">
+      <c r="K5" s="109" t="s">
         <v>15</v>
       </c>
       <c r="L5" s="110" t="s"/>
@@ -9389,11 +9790,11 @@
         <v>205</v>
       </c>
       <c r="I6" s="113" t="s"/>
-      <c r="J6" s="299">
+      <c r="J6" s="114">
         <f>=SUM(J2:J5)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="298">
+      <c r="K6" s="115">
         <f>=SUM(A6:J6)</f>
         <v>745</v>
       </c>
@@ -9434,8 +9835,8 @@
       </c>
       <c r="K9" s="119" t="s"/>
       <c r="L9" s="120" t="s"/>
-      <c r="M9" s="91" t="s"/>
-      <c r="N9" s="91" t="s"/>
+      <c r="M9" s="90" t="s"/>
+      <c r="N9" s="90" t="s"/>
       <c r="O9" s="40" t="s"/>
     </row>
     <row r="10" spans="1:15">
@@ -9586,7 +9987,7 @@
         <v>10</v>
       </c>
       <c r="K14" s="133" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -9788,31 +10189,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" s="129">
         <v>60</v>
       </c>
       <c r="C24" s="128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" s="129">
         <v>60</v>
       </c>
       <c r="E24" s="128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F24" s="129">
         <v>60</v>
       </c>
       <c r="G24" s="128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H24" s="129">
         <v>60</v>
       </c>
       <c r="I24" s="128" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J24" s="133">
         <v>60</v>
@@ -9835,7 +10236,7 @@
         <v>10</v>
       </c>
       <c r="K25" s="145" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -9957,10 +10358,18 @@
       <c r="B31" s="161">
         <v>120</v>
       </c>
-      <c r="C31" s="160" t="s"/>
-      <c r="D31" s="161" t="s"/>
-      <c r="E31" s="160" t="s"/>
-      <c r="F31" s="161" t="s"/>
+      <c r="C31" s="160" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="161">
+        <v>120</v>
+      </c>
+      <c r="E31" s="160" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" s="161">
+        <v>120</v>
+      </c>
       <c r="G31" s="160" t="s"/>
       <c r="H31" s="161" t="s"/>
       <c r="I31" s="160" t="s"/>
@@ -9974,10 +10383,18 @@
       <c r="B32" s="161">
         <v>60</v>
       </c>
-      <c r="C32" s="160" t="s"/>
-      <c r="D32" s="161" t="s"/>
-      <c r="E32" s="160" t="s"/>
-      <c r="F32" s="161" t="s"/>
+      <c r="C32" s="160" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="161">
+        <v>60</v>
+      </c>
+      <c r="E32" s="160" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="161">
+        <v>60</v>
+      </c>
       <c r="G32" s="160" t="s"/>
       <c r="H32" s="161" t="s"/>
       <c r="I32" s="160" t="s"/>
@@ -9986,13 +10403,17 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="160" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" s="161">
         <v>60</v>
       </c>
-      <c r="C33" s="160" t="s"/>
-      <c r="D33" s="161" t="s"/>
+      <c r="C33" s="160" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="161">
+        <v>60</v>
+      </c>
       <c r="E33" s="160" t="s"/>
       <c r="F33" s="161" t="s"/>
       <c r="G33" s="160" t="s"/>
@@ -10013,7 +10434,7 @@
       <c r="I34" s="164" t="s"/>
       <c r="J34" s="162" t="s"/>
       <c r="K34" s="162" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -10040,12 +10461,12 @@
       <c r="C36" s="169" t="s"/>
       <c r="D36" s="170">
         <f>=SUM(D30:D35)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E36" s="169" t="s"/>
       <c r="F36" s="170">
         <f>=SUM(F30:F35)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G36" s="169" t="s"/>
       <c r="H36" s="170">
@@ -10059,7 +10480,7 @@
       </c>
       <c r="K36" s="173">
         <f>=SUM(A36:J36)</f>
-        <v>240</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -10109,29 +10530,29 @@
       <c r="J1" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="96" t="s"/>
+      <c r="K1" s="97" t="s"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="30">
         <v>60</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" s="30">
         <v>60</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2" s="30">
         <v>60</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H2" s="30">
         <v>60</v>
@@ -10142,25 +10563,25 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="11">
         <v>60</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="11">
         <v>60</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" s="11">
         <v>60</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H3" s="11">
         <v>60</v>
@@ -10171,25 +10592,25 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="11">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="11">
         <v>60</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F4" s="11">
         <v>60</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H4" s="11">
         <v>60</v>
@@ -10206,14 +10627,14 @@
       <c r="E5" s="32" t="s"/>
       <c r="F5" s="34" t="s"/>
       <c r="G5" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H5" s="34">
         <v>10</v>
       </c>
       <c r="I5" s="32" t="s"/>
       <c r="J5" s="33" t="s"/>
-      <c r="K5" s="109" t="s">
+      <c r="K5" s="179" t="s">
         <v>15</v>
       </c>
     </row>
@@ -10319,31 +10740,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="110">
+        <v>60</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="110">
+        <v>60</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="110">
+        <v>60</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="110">
+        <v>60</v>
+      </c>
+      <c r="I11" s="53" t="s">
         <v>49</v>
-      </c>
-      <c r="B11" s="110">
-        <v>60</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="110">
-        <v>60</v>
-      </c>
-      <c r="E11" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="110">
-        <v>60</v>
-      </c>
-      <c r="G11" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="110">
-        <v>60</v>
-      </c>
-      <c r="I11" s="53" t="s">
-        <v>50</v>
       </c>
       <c r="J11" s="132">
         <v>60</v>
@@ -10352,31 +10773,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="110">
+        <v>60</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="110">
+        <v>60</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="110">
+        <v>60</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="110">
+        <v>60</v>
+      </c>
+      <c r="I12" s="39" t="s">
         <v>50</v>
-      </c>
-      <c r="B12" s="110">
-        <v>60</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="110">
-        <v>60</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="110">
-        <v>60</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="110">
-        <v>60</v>
-      </c>
-      <c r="I12" s="39" t="s">
-        <v>51</v>
       </c>
       <c r="J12" s="133">
         <v>60</v>
@@ -10385,25 +10806,25 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="110">
         <v>60</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="110">
         <v>60</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13" s="110">
         <v>60</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H13" s="110">
         <v>60</v>
@@ -10555,31 +10976,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="110">
         <v>60</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22" s="110">
         <v>60</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F22" s="110">
         <v>60</v>
       </c>
       <c r="G22" s="53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H22" s="110">
         <v>60</v>
       </c>
       <c r="I22" s="53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J22" s="132">
         <v>60</v>
@@ -10588,31 +11009,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="110">
         <v>60</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D23" s="110">
         <v>60</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F23" s="110">
         <v>60</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H23" s="110">
         <v>60</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J23" s="133">
         <v>60</v>
@@ -10621,31 +11042,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="110">
         <v>60</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="110">
         <v>60</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F24" s="110">
         <v>60</v>
       </c>
       <c r="G24" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H24" s="110">
         <v>60</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J24" s="133">
         <v>60</v>
@@ -10662,13 +11083,13 @@
       <c r="G25" s="134" t="s"/>
       <c r="H25" s="110" t="s"/>
       <c r="I25" s="53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J25" s="132">
         <v>60</v>
       </c>
       <c r="K25" s="133" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -10798,63 +11219,87 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" s="110">
         <v>60</v>
       </c>
       <c r="C33" s="53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33" s="110">
         <v>60</v>
       </c>
-      <c r="E33" s="53" t="s"/>
-      <c r="F33" s="110" t="s"/>
-      <c r="G33" s="53" t="s"/>
-      <c r="H33" s="110" t="s"/>
+      <c r="E33" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="110">
+        <v>60</v>
+      </c>
+      <c r="G33" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" s="110">
+        <v>60</v>
+      </c>
       <c r="I33" s="53" t="s"/>
       <c r="J33" s="132" t="s"/>
       <c r="K33" s="133" t="s"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" s="110">
         <v>60</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" s="110">
         <v>60</v>
       </c>
-      <c r="E34" s="39" t="s"/>
-      <c r="F34" s="110" t="s"/>
-      <c r="G34" s="39" t="s"/>
-      <c r="H34" s="110" t="s"/>
+      <c r="E34" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" s="110">
+        <v>60</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" s="110">
+        <v>60</v>
+      </c>
       <c r="I34" s="39" t="s"/>
       <c r="J34" s="133" t="s"/>
       <c r="K34" s="133" t="s"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" s="110">
         <v>60</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D35" s="110">
         <v>60</v>
       </c>
-      <c r="E35" s="39" t="s"/>
-      <c r="F35" s="110" t="s"/>
-      <c r="G35" s="39" t="s"/>
-      <c r="H35" s="110" t="s"/>
+      <c r="E35" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" s="110">
+        <v>60</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="110">
+        <v>60</v>
+      </c>
       <c r="I35" s="39" t="s"/>
       <c r="J35" s="133" t="s"/>
       <c r="K35" s="133" t="s"/>
@@ -10871,7 +11316,7 @@
       <c r="I36" s="39" t="s"/>
       <c r="J36" s="133" t="s"/>
       <c r="K36" s="133" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -10916,12 +11361,12 @@
       <c r="E39" s="136" t="s"/>
       <c r="F39" s="137">
         <f>=SUM(F33:F38)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G39" s="136" t="s"/>
       <c r="H39" s="137">
         <f>=SUM(H33:H38)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I39" s="148" t="s"/>
       <c r="J39" s="149">
@@ -10930,7 +11375,7 @@
       </c>
       <c r="K39" s="139">
         <f>=SUM(A39:J39)</f>
-        <v>360</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>
@@ -10949,61 +11394,60 @@
     <col min="12" max="12" width="10.9219" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A1" s="92">
+    <row r="1" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A1" s="93">
         <v>46188</v>
       </c>
       <c r="B1" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="92">
+      <c r="C1" s="93">
         <v>46189</v>
       </c>
       <c r="D1" s="175" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="92">
+      <c r="E1" s="93">
         <v>46190</v>
       </c>
       <c r="F1" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="92">
+      <c r="G1" s="93">
         <v>46191</v>
       </c>
       <c r="H1" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="94">
+      <c r="I1" s="95">
         <v>46192</v>
       </c>
       <c r="J1" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="96" t="s"/>
-      <c r="L1" t="s"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="K1" s="97" t="s"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B2" s="30">
         <v>90</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" s="30">
         <v>90</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F2" s="30">
         <v>90</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H2" s="30">
         <v>90</v>
@@ -11011,29 +11455,28 @@
       <c r="I2" s="28" t="s"/>
       <c r="J2" s="29" t="s"/>
       <c r="K2" s="178" t="s"/>
-      <c r="L2" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" s="11">
         <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D3" s="11">
         <v>90</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F3" s="11">
         <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H3" s="11">
         <v>90</v>
@@ -11041,29 +11484,28 @@
       <c r="I3" s="9" t="s"/>
       <c r="J3" s="10" t="s"/>
       <c r="K3" s="178" t="s"/>
-      <c r="L3" t="s"/>
-    </row>
-    <row r="4" spans="1:12">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" s="11">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4" s="11">
         <v>60</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4" s="11">
         <v>60</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H4" s="11">
         <v>60</v>
@@ -11071,9 +11513,8 @@
       <c r="I4" s="9" t="s"/>
       <c r="J4" s="10" t="s"/>
       <c r="K4" s="178" t="s"/>
-      <c r="L4" t="s"/>
-    </row>
-    <row r="5" spans="1:13">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="32" t="s"/>
       <c r="B5" s="34" t="s"/>
       <c r="C5" s="32" t="s"/>
@@ -11081,53 +11522,50 @@
       <c r="E5" s="32" t="s"/>
       <c r="F5" s="34" t="s"/>
       <c r="G5" s="32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H5" s="34">
         <v>10</v>
       </c>
       <c r="I5" s="32" t="s"/>
       <c r="J5" s="33" t="s"/>
-      <c r="K5" s="109" t="s">
+      <c r="K5" s="179" t="s">
         <v>15</v>
       </c>
-      <c r="L5" t="s"/>
-      <c r="M5" t="s"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="281" t="s"/>
-      <c r="B6" s="282">
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="180" t="s"/>
+      <c r="B6" s="181">
         <f>=SUM(B2:B5)</f>
         <v>240</v>
       </c>
-      <c r="C6" s="281" t="s"/>
-      <c r="D6" s="282">
+      <c r="C6" s="180" t="s"/>
+      <c r="D6" s="181">
         <f>=SUM(D2:D5)</f>
         <v>240</v>
       </c>
-      <c r="E6" s="281" t="s"/>
-      <c r="F6" s="282">
+      <c r="E6" s="180" t="s"/>
+      <c r="F6" s="181">
         <f>=SUM(F2:F5)</f>
         <v>240</v>
       </c>
-      <c r="G6" s="281" t="s"/>
-      <c r="H6" s="282">
+      <c r="G6" s="180" t="s"/>
+      <c r="H6" s="181">
         <f>=SUM(H2:H5)</f>
         <v>250</v>
       </c>
-      <c r="I6" s="303" t="s"/>
-      <c r="J6" s="307">
+      <c r="I6" s="182" t="s"/>
+      <c r="J6" s="183">
         <f>=SUM(J2:J5)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="306">
+      <c r="K6" s="184">
         <f>=SUM(A6:J6)</f>
         <v>970</v>
       </c>
-      <c r="L6" s="302" t="s">
+      <c r="L6" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="M6" t="s"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4">
@@ -11197,60 +11635,60 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="53" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B11" s="110">
         <v>90</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D11" s="110">
         <v>90</v>
       </c>
       <c r="E11" s="53" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F11" s="110">
         <v>90</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H11" s="110">
         <v>90</v>
       </c>
       <c r="I11" s="134" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J11" s="133">
         <v>10</v>
       </c>
       <c r="K11" s="133" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12" s="110">
         <v>90</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D12" s="110">
         <v>90</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F12" s="110">
         <v>60</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H12" s="110">
         <v>60</v>
@@ -11261,19 +11699,19 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B13" s="110">
         <v>60</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" s="110">
         <v>60</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F13" s="110">
         <v>60</v>
@@ -11375,153 +11813,147 @@
     <col min="10" max="12" width="10.6523" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A1" s="92">
+    <row r="1" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A1" s="93">
         <v>46188</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="92">
+      <c r="C1" s="93">
         <v>46189</v>
       </c>
-      <c r="D1" s="93" t="s">
+      <c r="D1" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="92">
+      <c r="E1" s="93">
         <v>46190</v>
       </c>
-      <c r="F1" s="93" t="s">
+      <c r="F1" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="92">
+      <c r="G1" s="93">
         <v>46191</v>
       </c>
-      <c r="H1" s="93" t="s">
+      <c r="H1" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="94">
+      <c r="I1" s="95">
         <v>46192</v>
       </c>
-      <c r="J1" s="95" t="s">
+      <c r="J1" s="96" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="96" t="s"/>
-      <c r="L1" t="s"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="K1" s="97" t="s"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="28" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B2" s="30">
         <v>90</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D2" s="30">
         <v>90</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F2" s="30">
         <v>90</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H2" s="29">
         <v>90</v>
       </c>
-      <c r="I2" s="308" t="s"/>
-      <c r="J2" s="185" t="s"/>
-      <c r="K2" s="181" t="s"/>
-      <c r="L2" t="s"/>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="I2" s="186" t="s"/>
+      <c r="J2" s="187" t="s"/>
+      <c r="K2" s="188" t="s"/>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B3" s="11">
         <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D3" s="11">
         <v>90</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F3" s="11">
         <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H3" s="10">
         <v>90</v>
       </c>
-      <c r="I3" s="309" t="s"/>
-      <c r="J3" s="242" t="s"/>
-      <c r="K3" s="181" t="s"/>
-      <c r="L3" t="s"/>
-      <c r="M3" t="s"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="192" t="s"/>
-      <c r="B4" s="193" t="s"/>
+      <c r="I3" s="189" t="s"/>
+      <c r="J3" s="190" t="s"/>
+      <c r="K3" s="188" t="s"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="191" t="s"/>
+      <c r="B4" s="192" t="s"/>
       <c r="C4" s="32" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D4" s="34">
         <v>90</v>
       </c>
-      <c r="E4" s="192" t="s"/>
-      <c r="F4" s="193" t="s"/>
-      <c r="G4" s="192" t="s"/>
-      <c r="H4" s="194" t="s"/>
-      <c r="I4" s="310" t="s"/>
-      <c r="J4" s="228" t="s"/>
-      <c r="K4" s="313" t="s">
+      <c r="E4" s="191" t="s"/>
+      <c r="F4" s="192" t="s"/>
+      <c r="G4" s="191" t="s"/>
+      <c r="H4" s="193" t="s"/>
+      <c r="I4" s="194" t="s"/>
+      <c r="J4" s="195" t="s"/>
+      <c r="K4" s="196" t="s">
         <v>15</v>
       </c>
-      <c r="L4" t="s"/>
-      <c r="M4" t="s"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="281" t="s"/>
-      <c r="B5" s="282">
+      <c r="A5" s="180" t="s"/>
+      <c r="B5" s="181">
         <f>=SUM(B1:B4)</f>
         <v>180</v>
       </c>
-      <c r="C5" s="281" t="s"/>
-      <c r="D5" s="282">
+      <c r="C5" s="180" t="s"/>
+      <c r="D5" s="181">
         <f>=SUM(D1:D4)</f>
         <v>270</v>
       </c>
-      <c r="E5" s="281" t="s"/>
-      <c r="F5" s="282">
+      <c r="E5" s="180" t="s"/>
+      <c r="F5" s="181">
         <f>=SUM(F1:F4)</f>
         <v>180</v>
       </c>
-      <c r="G5" s="281" t="s"/>
-      <c r="H5" s="282">
+      <c r="G5" s="180" t="s"/>
+      <c r="H5" s="181">
         <f>=SUM(H1:H4)</f>
         <v>180</v>
       </c>
       <c r="I5" s="148" t="s"/>
-      <c r="J5" s="312">
+      <c r="J5" s="197">
         <f>=SUM(J1:J4)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="306">
+      <c r="K5" s="184">
         <f>=SUM(A5:J5)</f>
         <v>810</v>
       </c>
-      <c r="L5" s="302" t="s">
+      <c r="L5" s="185" t="s">
         <v>16</v>
       </c>
     </row>
@@ -11593,31 +12025,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B10" s="110">
         <v>90</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D10" s="110">
         <v>90</v>
       </c>
       <c r="E10" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F10" s="110">
         <v>90</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H10" s="110">
         <v>90</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="J10" s="132">
         <v>90</v>
@@ -11626,31 +12058,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B11" s="110">
         <v>90</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D11" s="110">
         <v>90</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F11" s="110">
         <v>90</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H11" s="110">
         <v>90</v>
       </c>
       <c r="I11" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J11" s="133">
         <v>90</v>
@@ -11813,31 +12245,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B21" s="110">
         <v>90</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D21" s="110">
         <v>90</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F21" s="110">
         <v>60</v>
       </c>
       <c r="G21" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H21" s="110">
         <v>60</v>
       </c>
       <c r="I21" s="53" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="J21" s="132">
         <v>60</v>
@@ -11846,31 +12278,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B22" s="110">
         <v>90</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D22" s="110">
         <v>90</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F22" s="110">
         <v>100</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H22" s="110">
         <v>90</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J22" s="133">
         <v>90</v>
@@ -12030,15 +12462,23 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="207" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B32" s="208">
         <v>90</v>
       </c>
-      <c r="C32" s="207" t="s"/>
-      <c r="D32" s="208" t="s"/>
-      <c r="E32" s="207" t="s"/>
-      <c r="F32" s="208" t="s"/>
+      <c r="C32" s="207" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="208">
+        <v>90</v>
+      </c>
+      <c r="E32" s="207" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="208">
+        <v>90</v>
+      </c>
       <c r="G32" s="207" t="s"/>
       <c r="H32" s="208" t="s"/>
       <c r="I32" s="207" t="s"/>
@@ -12047,15 +12487,23 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="207" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B33" s="208">
         <v>60</v>
       </c>
-      <c r="C33" s="207" t="s"/>
-      <c r="D33" s="208" t="s"/>
-      <c r="E33" s="207" t="s"/>
-      <c r="F33" s="208" t="s"/>
+      <c r="C33" s="207" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="208">
+        <v>60</v>
+      </c>
+      <c r="E33" s="207" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="208">
+        <v>60</v>
+      </c>
       <c r="G33" s="207" t="s"/>
       <c r="H33" s="208" t="s"/>
       <c r="I33" s="207" t="s"/>
@@ -12112,12 +12560,12 @@
       <c r="C37" s="216" t="s"/>
       <c r="D37" s="217">
         <f>=SUM(D31:D36)</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E37" s="216" t="s"/>
       <c r="F37" s="217">
         <f>=SUM(F31:F36)</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G37" s="216" t="s"/>
       <c r="H37" s="217">
@@ -12131,7 +12579,7 @@
       </c>
       <c r="K37" s="220">
         <f>=SUM(A37:J37)</f>
-        <v>150</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -12151,151 +12599,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="92" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="185" t="s"/>
-      <c r="C1" s="92" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="185" t="s"/>
-      <c r="E1" s="92" t="s">
+      <c r="A1" s="93" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="187" t="s"/>
+      <c r="C1" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="185" t="s"/>
-      <c r="G1" s="222" t="s">
+      <c r="D1" s="187" t="s"/>
+      <c r="E1" s="93" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="188" t="s"/>
-      <c r="I1" s="92" t="s">
+      <c r="F1" s="187" t="s"/>
+      <c r="G1" s="221" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="185" t="s"/>
-      <c r="K1" s="224" t="s"/>
-      <c r="L1" s="316" t="s"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="H1" s="222" t="s"/>
+      <c r="I1" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="187" t="s"/>
+      <c r="K1" s="223" t="s"/>
+      <c r="L1" s="224" t="s"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B2" s="30">
         <v>90</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D2" s="30">
         <v>90</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F2" s="29">
         <v>90</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H2" s="30">
         <v>45</v>
       </c>
-      <c r="I2" s="314" t="s"/>
-      <c r="J2" s="185" t="s"/>
-      <c r="K2" s="96" t="s"/>
-      <c r="L2" t="s"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="190" t="s"/>
-      <c r="B3" s="226" t="s"/>
+      <c r="I2" s="225" t="s"/>
+      <c r="J2" s="187" t="s"/>
+      <c r="K2" s="97" t="s"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="226" t="s"/>
+      <c r="B3" s="227" t="s"/>
       <c r="C3" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D3" s="11">
         <v>90</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F3" s="10">
         <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H3" s="11">
         <v>45</v>
       </c>
       <c r="I3" s="23" t="s"/>
-      <c r="J3" t="s"/>
-      <c r="K3" s="181" t="s"/>
-      <c r="L3" t="s"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="190" t="s"/>
-      <c r="B4" s="226" t="s"/>
+      <c r="K3" s="188" t="s"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="226" t="s"/>
+      <c r="B4" s="227" t="s"/>
       <c r="C4" s="9" t="s"/>
       <c r="D4" s="11" t="s"/>
-      <c r="E4" s="190" t="s"/>
-      <c r="F4" s="227" t="s"/>
+      <c r="E4" s="226" t="s"/>
+      <c r="F4" s="228" t="s"/>
       <c r="G4" s="9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H4" s="11">
         <v>20</v>
       </c>
       <c r="I4" s="23" t="s"/>
-      <c r="J4" t="s"/>
-      <c r="K4" s="183" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" t="s"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="317" t="s"/>
-      <c r="B5" s="318">
+      <c r="K4" s="229" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="230" t="s"/>
+      <c r="B5" s="231">
         <f>=SUM(B1:B4)</f>
         <v>90</v>
       </c>
-      <c r="C5" s="317" t="s"/>
-      <c r="D5" s="318">
+      <c r="C5" s="230" t="s"/>
+      <c r="D5" s="231">
         <f>=SUM(D1:D4)</f>
         <v>180</v>
       </c>
-      <c r="E5" s="317" t="s"/>
-      <c r="F5" s="319">
+      <c r="E5" s="230" t="s"/>
+      <c r="F5" s="232">
         <f>=SUM(F1:F4)</f>
         <v>180</v>
       </c>
-      <c r="G5" s="317" t="s"/>
-      <c r="H5" s="318">
+      <c r="G5" s="230" t="s"/>
+      <c r="H5" s="231">
         <f>=SUM(H1:H4)</f>
         <v>110</v>
       </c>
       <c r="I5" s="113" t="s"/>
-      <c r="J5" s="312">
+      <c r="J5" s="197">
         <f>=SUM(J1:J4)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="320">
+      <c r="K5" s="233">
         <f>=SUM(A5:J5)</f>
         <v>560</v>
       </c>
       <c r="L5" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="M5" t="s"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="311" t="s"/>
-      <c r="B6" s="311" t="s"/>
-      <c r="C6" s="311" t="s"/>
-      <c r="D6" s="311" t="s"/>
-      <c r="E6" s="311" t="s"/>
-      <c r="F6" s="311" t="s"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="234" t="s"/>
+      <c r="B6" s="234" t="s"/>
+      <c r="C6" s="234" t="s"/>
+      <c r="D6" s="234" t="s"/>
+      <c r="E6" s="234" t="s"/>
+      <c r="F6" s="234" t="s"/>
       <c r="G6" s="8" t="s"/>
       <c r="H6" s="8" t="s"/>
-      <c r="K6" t="s"/>
-      <c r="L6" t="s"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4">
@@ -12351,13 +12791,13 @@
       <c r="E11" s="53" t="s"/>
       <c r="F11" s="110" t="s"/>
       <c r="G11" s="53" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H11" s="110">
         <v>90</v>
       </c>
       <c r="I11" s="53" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J11" s="132">
         <v>90</v>
@@ -12372,13 +12812,13 @@
       <c r="E12" s="39" t="s"/>
       <c r="F12" s="110" t="s"/>
       <c r="G12" s="39" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H12" s="110">
         <v>90</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="J12" s="133">
         <v>60</v>
@@ -12395,13 +12835,13 @@
       <c r="G13" s="39" t="s"/>
       <c r="H13" s="110" t="s"/>
       <c r="I13" s="134" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J13" s="133">
         <v>5</v>
       </c>
       <c r="K13" s="133" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -12522,15 +12962,23 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="53" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B22" s="110">
         <v>120</v>
       </c>
-      <c r="C22" s="53" t="s"/>
-      <c r="D22" s="110" t="s"/>
-      <c r="E22" s="53" t="s"/>
-      <c r="F22" s="110" t="s"/>
+      <c r="C22" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="110">
+        <v>120</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="110">
+        <v>160</v>
+      </c>
       <c r="G22" s="53" t="s"/>
       <c r="H22" s="110" t="s"/>
       <c r="I22" s="53" t="s"/>
@@ -12539,15 +12987,23 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B23" s="110">
         <v>60</v>
       </c>
-      <c r="C23" s="39" t="s"/>
-      <c r="D23" s="110" t="s"/>
-      <c r="E23" s="39" t="s"/>
-      <c r="F23" s="110" t="s"/>
+      <c r="C23" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="110">
+        <v>60</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="110">
+        <v>90</v>
+      </c>
       <c r="G23" s="39" t="s"/>
       <c r="H23" s="110" t="s"/>
       <c r="I23" s="39" t="s"/>
@@ -12556,15 +13012,23 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B24" s="110">
         <v>60</v>
       </c>
-      <c r="C24" s="39" t="s"/>
-      <c r="D24" s="110" t="s"/>
-      <c r="E24" s="39" t="s"/>
-      <c r="F24" s="110" t="s"/>
+      <c r="C24" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="110">
+        <v>80</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="110">
+        <v>80</v>
+      </c>
       <c r="G24" s="39" t="s"/>
       <c r="H24" s="110" t="s"/>
       <c r="I24" s="134" t="s"/>
@@ -12619,12 +13083,12 @@
       <c r="C28" s="136" t="s"/>
       <c r="D28" s="137">
         <f>=SUM(D22:D27)</f>
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="E28" s="136" t="s"/>
       <c r="F28" s="137">
         <f>=SUM(F22:F27)</f>
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="G28" s="136" t="s"/>
       <c r="H28" s="137">
@@ -12638,7 +13102,7 @@
       </c>
       <c r="K28" s="139">
         <f>=SUM(A28:J28)</f>
-        <v>240</v>
+        <v>830</v>
       </c>
     </row>
   </sheetData>
@@ -12664,172 +13128,159 @@
     <col min="12" max="12" width="10.793" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="92" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="185" t="s"/>
-      <c r="C1" s="92" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="185" t="s"/>
-      <c r="E1" s="92" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="93" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="187" t="s"/>
+      <c r="C1" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="185" t="s"/>
-      <c r="G1" s="92" t="s">
+      <c r="D1" s="187" t="s"/>
+      <c r="E1" s="93" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="185" t="s"/>
-      <c r="I1" s="222" t="s">
+      <c r="F1" s="187" t="s"/>
+      <c r="G1" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="185" t="s"/>
-      <c r="K1" s="224" t="s"/>
-      <c r="L1" s="316" t="s"/>
-      <c r="M1" t="s"/>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="H1" s="187" t="s"/>
+      <c r="I1" s="221" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="187" t="s"/>
+      <c r="K1" s="223" t="s"/>
+      <c r="L1" s="224" t="s"/>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B2" s="30">
         <v>90</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D2" s="30">
         <v>90</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F2" s="30">
         <v>90</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H2" s="29">
         <v>90</v>
       </c>
-      <c r="I2" s="229" t="s"/>
-      <c r="J2" s="230" t="s"/>
-      <c r="K2" s="325" t="s"/>
-      <c r="L2" t="s"/>
-      <c r="M2" t="s"/>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="I2" s="235" t="s"/>
+      <c r="J2" s="236" t="s"/>
+      <c r="K2" s="237" t="s"/>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B3" s="11">
         <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D3" s="11">
         <v>90</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F3" s="11">
         <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H3" s="10">
         <v>90</v>
       </c>
-      <c r="I3" s="190" t="s"/>
-      <c r="J3" s="227" t="s"/>
-      <c r="K3" s="326" t="s"/>
-      <c r="L3" t="s"/>
-      <c r="M3" t="s"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="190" t="s"/>
-      <c r="B4" s="226" t="s"/>
-      <c r="C4" s="190" t="s"/>
-      <c r="D4" s="226" t="s"/>
+      <c r="I3" s="226" t="s"/>
+      <c r="J3" s="228" t="s"/>
+      <c r="K3" s="238" t="s"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="226" t="s"/>
+      <c r="B4" s="227" t="s"/>
+      <c r="C4" s="226" t="s"/>
+      <c r="D4" s="227" t="s"/>
       <c r="E4" s="9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F4" s="11">
         <v>90</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H4" s="10">
         <v>90</v>
       </c>
-      <c r="I4" s="190" t="s"/>
-      <c r="J4" s="227" t="s"/>
-      <c r="K4" s="326" t="s"/>
-      <c r="L4" t="s"/>
-      <c r="M4" t="s"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="192" t="s"/>
-      <c r="B5" s="193" t="s"/>
-      <c r="C5" s="192" t="s"/>
-      <c r="D5" s="193" t="s"/>
-      <c r="E5" s="192" t="s"/>
-      <c r="F5" s="193" t="s"/>
+      <c r="I4" s="226" t="s"/>
+      <c r="J4" s="228" t="s"/>
+      <c r="K4" s="238" t="s"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="191" t="s"/>
+      <c r="B5" s="192" t="s"/>
+      <c r="C5" s="191" t="s"/>
+      <c r="D5" s="192" t="s"/>
+      <c r="E5" s="191" t="s"/>
+      <c r="F5" s="192" t="s"/>
       <c r="G5" s="32" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H5" s="33">
         <v>10</v>
       </c>
-      <c r="I5" s="192" t="s"/>
-      <c r="J5" s="194" t="s"/>
-      <c r="K5" s="327" t="s"/>
-      <c r="L5" t="s"/>
-      <c r="M5" t="s"/>
+      <c r="I5" s="191" t="s"/>
+      <c r="J5" s="193" t="s"/>
+      <c r="K5" s="239" t="s"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="281" t="s"/>
-      <c r="B6" s="282">
+      <c r="A6" s="180" t="s"/>
+      <c r="B6" s="181">
         <f>=SUM(B2:B5)</f>
         <v>180</v>
       </c>
-      <c r="C6" s="281" t="s"/>
-      <c r="D6" s="282">
+      <c r="C6" s="180" t="s"/>
+      <c r="D6" s="181">
         <f>=SUM(D2:D5)</f>
         <v>180</v>
       </c>
-      <c r="E6" s="281" t="s"/>
-      <c r="F6" s="282">
+      <c r="E6" s="180" t="s"/>
+      <c r="F6" s="181">
         <f>=SUM(F2:F5)</f>
         <v>270</v>
       </c>
-      <c r="G6" s="281" t="s"/>
-      <c r="H6" s="282">
+      <c r="G6" s="180" t="s"/>
+      <c r="H6" s="181">
         <f>=SUM(H2:H5)</f>
         <v>280</v>
       </c>
-      <c r="I6" s="303" t="s"/>
-      <c r="J6" s="307">
+      <c r="I6" s="182" t="s"/>
+      <c r="J6" s="183">
         <f>=SUM(J2:J5)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="322">
+      <c r="K6" s="240">
         <f>=SUM(A6:J6)</f>
         <v>910</v>
       </c>
       <c r="L6" s="140" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="12:13">
-      <c r="L7" t="s"/>
-      <c r="M7" t="s"/>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4">
@@ -12899,31 +13350,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B11" s="54">
         <v>90</v>
       </c>
       <c r="C11" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D11" s="54">
         <v>90</v>
       </c>
       <c r="E11" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F11" s="54">
         <v>60</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" s="54">
         <v>60</v>
       </c>
       <c r="I11" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J11" s="54">
         <v>60</v>
@@ -12932,31 +13383,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B12" s="41">
         <v>90</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D12" s="41">
         <v>90</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F12" s="41">
         <v>90</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H12" s="41">
         <v>90</v>
       </c>
       <c r="I12" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J12" s="41">
         <v>90</v>
@@ -12965,31 +13416,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B13" s="41">
         <v>90</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D13" s="41">
         <v>90</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F13" s="41">
         <v>60</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H13" s="41">
         <v>60</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J13" s="41">
         <v>60</v>
@@ -13006,7 +13457,7 @@
       <c r="G14" s="134" t="s"/>
       <c r="H14" s="110" t="s"/>
       <c r="I14" s="134" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J14" s="133">
         <v>60</v>
@@ -13143,31 +13594,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B22" s="54">
         <v>60</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D22" s="54">
         <v>60</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F22" s="54">
         <v>60</v>
       </c>
       <c r="G22" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H22" s="54">
         <v>60</v>
       </c>
       <c r="I22" s="53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J22" s="54">
         <v>60</v>
@@ -13176,31 +13627,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B23" s="41">
         <v>90</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D23" s="41">
         <v>90</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F23" s="41">
         <v>90</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H23" s="41">
         <v>90</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J23" s="41">
         <v>90</v>
@@ -13209,31 +13660,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B24" s="41">
         <v>60</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D24" s="41">
         <v>60</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F24" s="41">
         <v>60</v>
       </c>
       <c r="G24" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H24" s="41">
         <v>60</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J24" s="41">
         <v>60</v>
@@ -13242,31 +13693,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="134" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B25" s="133">
         <v>60</v>
       </c>
       <c r="C25" s="134" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D25" s="133">
         <v>60</v>
       </c>
       <c r="E25" s="134" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F25" s="133">
         <v>60</v>
       </c>
       <c r="G25" s="134" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H25" s="133">
         <v>60</v>
       </c>
       <c r="I25" s="134" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="J25" s="133">
         <v>60</v>
@@ -13283,12 +13734,12 @@
       <c r="G26" s="134" t="s"/>
       <c r="H26" s="110" t="s"/>
       <c r="I26" s="134" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J26" s="133">
         <v>60</v>
       </c>
-      <c r="K26" s="231" t="s"/>
+      <c r="K26" s="241" t="s"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="134" t="s"/>
@@ -13300,7 +13751,7 @@
       <c r="G27" s="134" t="s"/>
       <c r="H27" s="110" t="s"/>
       <c r="I27" s="39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J27" s="133">
         <v>10</v>
@@ -13373,32 +13824,48 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="28" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B31" s="212">
         <v>120</v>
       </c>
-      <c r="C31" s="28" t="s"/>
-      <c r="D31" s="212" t="s"/>
-      <c r="E31" s="28" t="s"/>
-      <c r="F31" s="212" t="s"/>
+      <c r="C31" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="212">
+        <v>120</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="212">
+        <v>120</v>
+      </c>
       <c r="G31" s="28" t="s"/>
       <c r="H31" s="212" t="s"/>
-      <c r="I31" s="232" t="s"/>
-      <c r="J31" s="233" t="s"/>
+      <c r="I31" s="242" t="s"/>
+      <c r="J31" s="243" t="s"/>
       <c r="K31" s="206" t="s"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B32" s="212">
         <v>60</v>
       </c>
-      <c r="C32" s="9" t="s"/>
-      <c r="D32" s="212" t="s"/>
-      <c r="E32" s="9" t="s"/>
-      <c r="F32" s="212" t="s"/>
+      <c r="C32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="212">
+        <v>60</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="212">
+        <v>75</v>
+      </c>
       <c r="G32" s="9" t="s"/>
       <c r="H32" s="212" t="s"/>
       <c r="I32" s="9" t="s"/>
@@ -13407,15 +13874,23 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B33" s="212">
         <v>60</v>
       </c>
-      <c r="C33" s="9" t="s"/>
-      <c r="D33" s="212" t="s"/>
-      <c r="E33" s="9" t="s"/>
-      <c r="F33" s="212" t="s"/>
+      <c r="C33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="212">
+        <v>60</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="212">
+        <v>75</v>
+      </c>
       <c r="G33" s="9" t="s"/>
       <c r="H33" s="212" t="s"/>
       <c r="I33" s="211" t="s"/>
@@ -13424,15 +13899,23 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="211" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B34" s="212">
         <v>60</v>
       </c>
-      <c r="C34" s="211" t="s"/>
-      <c r="D34" s="212" t="s"/>
-      <c r="E34" s="211" t="s"/>
-      <c r="F34" s="212" t="s"/>
+      <c r="C34" s="211" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="212">
+        <v>60</v>
+      </c>
+      <c r="E34" s="211" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" s="212">
+        <v>75</v>
+      </c>
       <c r="G34" s="211" t="s"/>
       <c r="H34" s="212" t="s"/>
       <c r="I34" s="211" t="s"/>
@@ -13441,13 +13924,17 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="211" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B35" s="212">
         <v>60</v>
       </c>
-      <c r="C35" s="211" t="s"/>
-      <c r="D35" s="212" t="s"/>
+      <c r="C35" s="211" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="212">
+        <v>60</v>
+      </c>
       <c r="E35" s="211" t="s"/>
       <c r="F35" s="212" t="s"/>
       <c r="G35" s="211" t="s"/>
@@ -13458,33 +13945,37 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="211" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B36" s="212">
         <v>60</v>
       </c>
-      <c r="C36" s="211" t="s"/>
-      <c r="D36" s="212" t="s"/>
+      <c r="C36" s="211" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="212">
+        <v>60</v>
+      </c>
       <c r="E36" s="211" t="s"/>
       <c r="F36" s="212" t="s"/>
       <c r="G36" s="211" t="s"/>
       <c r="H36" s="212" t="s"/>
       <c r="I36" s="211" t="s"/>
       <c r="J36" s="206" t="s"/>
-      <c r="K36" s="234" t="s"/>
+      <c r="K36" s="244" t="s"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="235" t="s"/>
-      <c r="B37" s="236" t="s"/>
-      <c r="C37" s="235" t="s"/>
-      <c r="D37" s="236" t="s"/>
-      <c r="E37" s="235" t="s"/>
-      <c r="F37" s="236" t="s"/>
-      <c r="G37" s="235" t="s"/>
-      <c r="H37" s="236" t="s"/>
-      <c r="I37" s="237" t="s"/>
-      <c r="J37" s="238" t="s"/>
-      <c r="K37" s="239" t="s">
+      <c r="A37" s="245" t="s"/>
+      <c r="B37" s="246" t="s"/>
+      <c r="C37" s="245" t="s"/>
+      <c r="D37" s="246" t="s"/>
+      <c r="E37" s="245" t="s"/>
+      <c r="F37" s="246" t="s"/>
+      <c r="G37" s="245" t="s"/>
+      <c r="H37" s="246" t="s"/>
+      <c r="I37" s="247" t="s"/>
+      <c r="J37" s="248" t="s"/>
+      <c r="K37" s="249" t="s">
         <v>15</v>
       </c>
     </row>
@@ -13497,12 +13988,12 @@
       <c r="C38" s="216" t="s"/>
       <c r="D38" s="217">
         <f>=SUM(D31:D37)</f>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="E38" s="216" t="s"/>
       <c r="F38" s="217">
         <f>=SUM(F31:F37)</f>
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="G38" s="216" t="s"/>
       <c r="H38" s="217">
@@ -13516,7 +14007,7 @@
       </c>
       <c r="K38" s="220">
         <f>=SUM(A38:J38)</f>
-        <v>420</v>
+        <v>1185</v>
       </c>
     </row>
   </sheetData>

--- a/接力送真实人力计薪/接力送计薪表格.xlsx
+++ b/接力送真实人力计薪/接力送计薪表格.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="番禺万科欧泊" sheetId="1" r:id="rId3"/>
-    <sheet name="中大附属第三医院" sheetId="2" r:id="rId4"/>
-    <sheet name="中大附属第六医院" sheetId="3" r:id="rId5"/>
+    <sheet name="中大附属第六医院" sheetId="2" r:id="rId4"/>
+    <sheet name="中大附属第三医院" sheetId="3" r:id="rId5"/>
     <sheet name="番禺万达" sheetId="4" r:id="rId6"/>
     <sheet name="汇德国际" sheetId="5" r:id="rId7"/>
     <sheet name="北京路广百" sheetId="6" r:id="rId8"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
   <si>
     <t/>
   </si>
@@ -165,6 +165,63 @@
   </si>
   <si>
     <t>闲时</t>
+  </si>
+  <si>
+    <t>郑峰</t>
+  </si>
+  <si>
+    <t>点位费</t>
+  </si>
+  <si>
+    <t>邱泳超</t>
+  </si>
+  <si>
+    <t>沈佳仪</t>
+  </si>
+  <si>
+    <t>韩冰</t>
+  </si>
+  <si>
+    <t>李轩勇</t>
+  </si>
+  <si>
+    <t>隋国宏</t>
+  </si>
+  <si>
+    <t>马云庆</t>
+  </si>
+  <si>
+    <t>李爱兰</t>
+  </si>
+  <si>
+    <t>颜佳民</t>
+  </si>
+  <si>
+    <t>林宇涛</t>
+  </si>
+  <si>
+    <t>欧正武</t>
+  </si>
+  <si>
+    <t>点位费30</t>
+  </si>
+  <si>
+    <t>葛润之</t>
+  </si>
+  <si>
+    <t>卿慧</t>
+  </si>
+  <si>
+    <t>李宇涛</t>
+  </si>
+  <si>
+    <t>葛子晶</t>
+  </si>
+  <si>
+    <t>蔡思怡</t>
+  </si>
+  <si>
+    <t>隋国红</t>
   </si>
   <si>
     <t>苏伟峰</t>
@@ -4633,23 +4690,23 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="68" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B1" s="122" t="s"/>
       <c r="C1" s="68" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="D1" s="122" t="s"/>
       <c r="E1" s="68" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="F1" s="122" t="s"/>
       <c r="G1" s="68" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="H1" s="122" t="s"/>
       <c r="I1" s="131" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="J1" s="122" t="s"/>
       <c r="K1" s="72" t="s"/>
@@ -4657,25 +4714,25 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B2" s="29">
         <v>90</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D2" s="29">
         <v>90</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F2" s="29">
         <v>90</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H2" s="28">
         <v>90</v>
@@ -4686,25 +4743,25 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B3" s="11">
         <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D3" s="11">
         <v>90</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="F3" s="11">
         <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H3" s="10">
         <v>90</v>
@@ -4719,13 +4776,13 @@
       <c r="C4" s="132" t="s"/>
       <c r="D4" s="133" t="s"/>
       <c r="E4" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F4" s="11">
         <v>90</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="H4" s="10">
         <v>90</v>
@@ -4742,7 +4799,7 @@
       <c r="E5" s="123" t="s"/>
       <c r="F5" s="124" t="s"/>
       <c r="G5" s="31" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H5" s="32">
         <v>10</v>
@@ -4853,31 +4910,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B11" s="29">
         <v>90</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D11" s="29">
         <v>90</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F11" s="29">
         <v>60</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H11" s="29">
         <v>60</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="J11" s="29">
         <v>60</v>
@@ -4886,31 +4943,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B12" s="11">
         <v>90</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D12" s="11">
         <v>90</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="F12" s="11">
         <v>90</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H12" s="11">
         <v>90</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J12" s="11">
         <v>90</v>
@@ -4919,31 +4976,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B13" s="11">
         <v>90</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D13" s="11">
         <v>90</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F13" s="11">
         <v>60</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="H13" s="11">
         <v>60</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="J13" s="11">
         <v>60</v>
@@ -4960,7 +5017,7 @@
       <c r="G14" s="51" t="s"/>
       <c r="H14" s="22" t="s"/>
       <c r="I14" s="51" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J14" s="49">
         <v>60</v>
@@ -5097,31 +5154,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B22" s="29">
         <v>60</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D22" s="29">
         <v>60</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F22" s="29">
         <v>60</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H22" s="29">
         <v>60</v>
       </c>
       <c r="I22" s="27" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="J22" s="29">
         <v>60</v>
@@ -5130,31 +5187,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B23" s="11">
         <v>90</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D23" s="11">
         <v>90</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="F23" s="11">
         <v>90</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H23" s="11">
         <v>90</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J23" s="11">
         <v>90</v>
@@ -5163,31 +5220,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B24" s="11">
         <v>60</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D24" s="11">
         <v>60</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F24" s="11">
         <v>60</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="H24" s="11">
         <v>60</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="J24" s="11">
         <v>60</v>
@@ -5196,31 +5253,31 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="51" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="B25" s="49">
         <v>60</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D25" s="49">
         <v>60</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="F25" s="49">
         <v>60</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="H25" s="49">
         <v>60</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J25" s="49">
         <v>60</v>
@@ -5237,7 +5294,7 @@
       <c r="G26" s="51" t="s"/>
       <c r="H26" s="22" t="s"/>
       <c r="I26" s="51" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="J26" s="49">
         <v>60</v>
@@ -5254,7 +5311,7 @@
       <c r="G27" s="51" t="s"/>
       <c r="H27" s="22" t="s"/>
       <c r="I27" s="9" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J27" s="49">
         <v>10</v>
@@ -5292,7 +5349,7 @@
         <v>1420</v>
       </c>
       <c r="L28" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -5330,31 +5387,31 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B31" s="22">
         <v>120</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D31" s="22">
         <v>120</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="F31" s="22">
         <v>120</v>
       </c>
       <c r="G31" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H31" s="22">
         <v>120</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J31" s="48">
         <v>120</v>
@@ -5363,31 +5420,31 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B32" s="22">
         <v>60</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D32" s="22">
         <v>60</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F32" s="22">
         <v>75</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H32" s="22">
         <v>60</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="J32" s="49">
         <v>60</v>
@@ -5396,31 +5453,31 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="B33" s="22">
         <v>60</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D33" s="22">
         <v>60</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="F33" s="22">
         <v>75</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="H33" s="22">
         <v>60</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J33" s="49">
         <v>60</v>
@@ -5429,31 +5486,31 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="51" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B34" s="22">
         <v>60</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="D34" s="22">
         <v>60</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="F34" s="22">
         <v>75</v>
       </c>
       <c r="G34" s="51" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="H34" s="22">
         <v>60</v>
       </c>
       <c r="I34" s="51" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="J34" s="49">
         <v>60</v>
@@ -5462,13 +5519,13 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="51" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="B35" s="22">
         <v>60</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D35" s="22">
         <v>60</v>
@@ -5476,13 +5533,13 @@
       <c r="E35" s="51" t="s"/>
       <c r="F35" s="22" t="s"/>
       <c r="G35" s="51" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="H35" s="22">
         <v>60</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="J35" s="49">
         <v>60</v>
@@ -5491,13 +5548,13 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="51" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B36" s="22">
         <v>60</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D36" s="22">
         <v>60</v>
@@ -5505,13 +5562,13 @@
       <c r="E36" s="51" t="s"/>
       <c r="F36" s="22" t="s"/>
       <c r="G36" s="51" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="H36" s="22">
         <v>60</v>
       </c>
       <c r="I36" s="51" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J36" s="49">
         <v>10</v>
@@ -5564,7 +5621,7 @@
         <v>1975</v>
       </c>
       <c r="L38" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5602,31 +5659,31 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B42" s="22">
         <v>120</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="D42" s="22">
         <v>120</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="F42" s="22">
         <v>120</v>
       </c>
       <c r="G42" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H42" s="22">
         <v>120</v>
       </c>
       <c r="I42" s="27" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J42" s="48">
         <v>120</v>
@@ -5635,31 +5692,31 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B43" s="22">
         <v>60</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="D43" s="22">
         <v>60</v>
       </c>
       <c r="E43" s="57" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F43" s="22">
         <v>60</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="H43" s="22">
         <v>60</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="J43" s="49">
         <v>60</v>
@@ -5668,31 +5725,31 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="B44" s="22">
         <v>60</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="D44" s="22">
         <v>60</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="F44" s="22">
         <v>60</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="H44" s="22">
         <v>60</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J44" s="49">
         <v>60</v>
@@ -5701,31 +5758,31 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="51" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="B45" s="22">
         <v>60</v>
       </c>
       <c r="C45" s="51" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D45" s="22">
         <v>60</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="F45" s="22">
         <v>60</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="H45" s="22">
         <v>60</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="J45" s="49">
         <v>60</v>
@@ -5736,19 +5793,19 @@
       <c r="A46" s="51" t="s"/>
       <c r="B46" s="22" t="s"/>
       <c r="C46" s="51" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D46" s="22">
         <v>60</v>
       </c>
       <c r="G46" s="51" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="H46" s="22">
         <v>60</v>
       </c>
       <c r="I46" s="51" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="J46" s="49">
         <v>60</v>
@@ -5765,7 +5822,7 @@
       <c r="G47" s="51" t="s"/>
       <c r="H47" s="22" t="s"/>
       <c r="I47" s="51" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J47" s="49">
         <v>10</v>
@@ -5818,7 +5875,7 @@
         <v>1690</v>
       </c>
       <c r="L49" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -5884,25 +5941,25 @@
       <c r="E2" s="52" t="s"/>
       <c r="F2" s="52" t="s"/>
       <c r="G2" s="51" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="H2" s="50">
         <v>90</v>
       </c>
       <c r="I2" s="51" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="J2" s="50">
         <v>90</v>
       </c>
       <c r="K2" s="51" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="L2" s="50">
         <v>60</v>
       </c>
       <c r="M2" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="N2" s="50">
         <v>60</v>
@@ -5917,25 +5974,25 @@
       <c r="E3" s="52" t="s"/>
       <c r="F3" s="52" t="s"/>
       <c r="G3" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="H3" s="50">
         <v>60</v>
       </c>
       <c r="I3" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="J3" s="50">
         <v>90</v>
       </c>
       <c r="K3" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="L3" s="50">
         <v>60</v>
       </c>
       <c r="M3" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="N3" s="50">
         <v>90</v>
@@ -5952,13 +6009,13 @@
       <c r="G4" s="51" t="s"/>
       <c r="H4" s="50" t="s"/>
       <c r="I4" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="J4" s="50">
         <v>60</v>
       </c>
       <c r="K4" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="L4" s="50">
         <v>90</v>
@@ -6102,43 +6159,43 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="51" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B12" s="50">
         <v>75</v>
       </c>
       <c r="C12" s="121" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D12" s="48">
         <v>75</v>
       </c>
       <c r="E12" s="122" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F12" s="122">
         <v>135</v>
       </c>
       <c r="G12" s="121" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="H12" s="48">
         <v>60</v>
       </c>
       <c r="I12" s="122" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="J12" s="48">
         <v>60</v>
       </c>
       <c r="K12" s="122" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="L12" s="48">
         <v>120</v>
       </c>
       <c r="M12" s="122" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="N12" s="48">
         <v>60</v>
@@ -6147,43 +6204,43 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B13" s="50">
         <v>60</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="D13" s="49">
         <v>75</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="F13" s="22">
         <v>60</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="H13" s="49">
         <v>60</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="J13" s="49">
         <v>60</v>
       </c>
       <c r="K13" s="50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="L13" s="49">
         <v>90</v>
       </c>
       <c r="M13" s="50" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="N13" s="49">
         <v>120</v>
@@ -6192,43 +6249,43 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B14" s="50">
         <v>90</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="D14" s="49">
         <v>90</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="F14" s="22">
         <v>90</v>
       </c>
       <c r="G14" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="H14" s="49">
         <v>90</v>
       </c>
       <c r="I14" s="50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="J14" s="49">
         <v>90</v>
       </c>
       <c r="K14" s="50" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="L14" s="49">
         <v>60</v>
       </c>
       <c r="M14" s="50" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="N14" s="49">
         <v>90</v>
@@ -6239,25 +6296,25 @@
       <c r="A15" s="51" t="s"/>
       <c r="B15" s="50" t="s"/>
       <c r="C15" s="51" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="D15" s="49">
         <v>75</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="F15" s="22">
         <v>60</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="H15" s="49">
         <v>120</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="J15" s="49">
         <v>60</v>
@@ -6274,19 +6331,19 @@
       <c r="C16" s="51" t="s"/>
       <c r="D16" s="49" t="s"/>
       <c r="E16" s="22" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F16" s="22">
         <v>75</v>
       </c>
       <c r="G16" s="51" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="H16" s="49">
         <v>60</v>
       </c>
       <c r="I16" s="50" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="J16" s="49">
         <v>60</v>
@@ -6303,19 +6360,19 @@
       <c r="C17" s="51" t="s"/>
       <c r="D17" s="49" t="s"/>
       <c r="E17" s="22" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="F17" s="22">
         <v>60</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="H17" s="49">
         <v>60</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="J17" s="49">
         <v>60</v>
@@ -6418,43 +6475,43 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B22" s="50">
         <v>120</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D22" s="48">
         <v>90</v>
       </c>
       <c r="E22" s="122" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="F22" s="122">
         <v>60</v>
       </c>
       <c r="G22" s="121" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="H22" s="48">
         <v>90</v>
       </c>
       <c r="I22" s="122" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="J22" s="48">
         <v>135</v>
       </c>
       <c r="K22" s="122" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="L22" s="48">
         <v>60</v>
       </c>
       <c r="M22" s="122" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="N22" s="48">
         <v>60</v>
@@ -6463,43 +6520,43 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B23" s="50">
         <v>90</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="D23" s="49">
         <v>90</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="F23" s="22">
         <v>120</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="H23" s="49">
         <v>120</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="J23" s="49">
         <v>60</v>
       </c>
       <c r="K23" s="50" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="L23" s="49">
         <v>135</v>
       </c>
       <c r="M23" s="50" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="N23" s="49">
         <v>60</v>
@@ -6508,43 +6565,43 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="51" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B24" s="50">
         <v>60</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D24" s="49">
         <v>60</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="F24" s="22">
         <v>120</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="H24" s="49">
         <v>60</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="J24" s="49">
         <v>60</v>
       </c>
       <c r="K24" s="50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="L24" s="49">
         <v>90</v>
       </c>
       <c r="M24" s="50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="N24" s="49">
         <v>90</v>
@@ -6553,31 +6610,31 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="51" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B25" s="50">
         <v>60</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D25" s="49">
         <v>60</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="F25" s="22">
         <v>90</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="H25" s="49">
         <v>60</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="J25" s="49">
         <v>90</v>
@@ -6585,7 +6642,7 @@
       <c r="K25" s="50" t="s"/>
       <c r="L25" s="49" t="s"/>
       <c r="M25" s="50" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="N25" s="49">
         <v>60</v>
@@ -6596,7 +6653,7 @@
       <c r="A26" s="51" t="s"/>
       <c r="B26" s="50" t="s"/>
       <c r="C26" s="51" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D26" s="49">
         <v>60</v>
@@ -6716,37 +6773,37 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="121" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B32" s="122">
         <v>90</v>
       </c>
       <c r="C32" s="121" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="D32" s="122">
         <v>60</v>
       </c>
       <c r="E32" s="121" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="F32" s="48">
         <v>120</v>
       </c>
       <c r="G32" s="122" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="H32" s="48">
         <v>135</v>
       </c>
       <c r="I32" s="122" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="J32" s="48">
         <v>120</v>
       </c>
       <c r="K32" s="122" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="L32" s="48">
         <v>90</v>
@@ -6757,37 +6814,37 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="51" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="B33" s="50">
         <v>120</v>
       </c>
       <c r="C33" s="51" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="D33" s="22">
         <v>60</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="F33" s="49">
         <v>90</v>
       </c>
       <c r="G33" s="50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="H33" s="49">
         <v>90</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="J33" s="49">
         <v>90</v>
       </c>
       <c r="K33" s="50" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="L33" s="49">
         <v>60</v>
@@ -6800,13 +6857,13 @@
       <c r="A34" s="51" t="s"/>
       <c r="B34" s="50" t="s"/>
       <c r="C34" s="51" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="D34" s="22">
         <v>60</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="F34" s="49">
         <v>30</v>
@@ -6825,7 +6882,7 @@
       <c r="A35" s="51" t="s"/>
       <c r="B35" s="50" t="s"/>
       <c r="C35" s="51" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D35" s="22">
         <v>60</v>
@@ -6987,7 +7044,7 @@
       <c r="G2" s="160" t="s"/>
       <c r="H2" s="159" t="s"/>
       <c r="I2" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="J2" s="161">
         <v>90</v>
@@ -7093,7 +7150,7 @@
         <v>90</v>
       </c>
       <c r="L8" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -7157,31 +7214,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="158" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B12" s="159">
         <v>90</v>
       </c>
       <c r="C12" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D12" s="159">
         <v>90</v>
       </c>
       <c r="E12" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F12" s="159">
         <v>90</v>
       </c>
       <c r="G12" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="H12" s="159">
         <v>90</v>
       </c>
       <c r="I12" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="J12" s="161">
         <v>90</v>
@@ -7190,31 +7247,31 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="9" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="B13" s="163">
         <v>60</v>
       </c>
       <c r="C13" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="D13" s="163">
         <v>60</v>
       </c>
       <c r="E13" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F13" s="163">
         <v>60</v>
       </c>
       <c r="G13" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H13" s="163">
         <v>60</v>
       </c>
       <c r="I13" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="J13" s="165">
         <v>60</v>
@@ -7231,13 +7288,13 @@
       <c r="G14" s="164" t="s"/>
       <c r="H14" s="163" t="s"/>
       <c r="I14" s="166" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="J14" s="165">
         <v>20</v>
       </c>
       <c r="K14" s="65" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -7313,7 +7370,7 @@
         <v>770</v>
       </c>
       <c r="L18" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -7377,31 +7434,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B22" s="159">
         <v>90</v>
       </c>
       <c r="C22" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D22" s="159">
         <v>90</v>
       </c>
       <c r="E22" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="F22" s="159">
         <v>90</v>
       </c>
       <c r="G22" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="H22" s="159">
         <v>90</v>
       </c>
       <c r="I22" s="160" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="J22" s="161">
         <v>90</v>
@@ -7410,31 +7467,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="B23" s="163">
         <v>60</v>
       </c>
       <c r="C23" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="D23" s="163">
         <v>60</v>
       </c>
       <c r="E23" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F23" s="163">
         <v>60</v>
       </c>
       <c r="G23" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="H23" s="163">
         <v>60</v>
       </c>
       <c r="I23" s="164" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="J23" s="165">
         <v>60</v>
@@ -7451,13 +7508,13 @@
       <c r="G24" s="164" t="s"/>
       <c r="H24" s="163" t="s"/>
       <c r="I24" s="166" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="J24" s="165">
         <v>20</v>
       </c>
       <c r="K24" s="65" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -7532,7 +7589,7 @@
         <v>770</v>
       </c>
       <c r="L28" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -7597,7 +7654,7 @@
       <c r="A2" s="185" t="s"/>
       <c r="B2" s="186" t="s"/>
       <c r="C2" s="187" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="D2" s="188">
         <v>60</v>
@@ -7605,13 +7662,13 @@
       <c r="E2" s="187" t="s"/>
       <c r="F2" s="184" t="s"/>
       <c r="G2" s="185" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="H2" s="188">
         <v>90</v>
       </c>
       <c r="I2" s="187" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="J2" s="189">
         <v>90</v>
@@ -7623,7 +7680,7 @@
       <c r="A3" s="191" t="s"/>
       <c r="B3" s="190" t="s"/>
       <c r="C3" s="192" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="D3" s="188">
         <v>60</v>
@@ -7631,13 +7688,13 @@
       <c r="E3" s="193" t="s"/>
       <c r="F3" s="184" t="s"/>
       <c r="G3" s="191" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="H3" s="188">
         <v>60</v>
       </c>
       <c r="I3" s="193" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="J3" s="188">
         <v>60</v>
@@ -7784,7 +7841,7 @@
       <c r="E2" s="160" t="s"/>
       <c r="F2" s="205" t="s"/>
       <c r="G2" s="160" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="H2" s="205">
         <v>60</v>
@@ -7801,7 +7858,7 @@
       <c r="E3" s="164" t="s"/>
       <c r="F3" s="208" t="s"/>
       <c r="G3" s="164" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="H3" s="208">
         <v>60</v>
@@ -7895,7 +7952,7 @@
         <v>120</v>
       </c>
       <c r="L8" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -7916,22 +7973,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="22" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C1" s="218" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="D1" s="219" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7939,7 +7996,7 @@
         <v>46184</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C2" s="218">
         <v>359</v>
@@ -7953,7 +8010,7 @@
         <v>46179</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C3" s="218">
         <v>48</v>
@@ -7967,7 +8024,7 @@
         <v>46179</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C4" s="218">
         <v>380</v>
@@ -7981,7 +8038,7 @@
         <v>46180</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="C5" s="218">
         <v>1400</v>
@@ -7990,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7998,7 +8055,7 @@
         <v>46180</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C6" s="218">
         <v>135</v>
@@ -8007,7 +8064,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -8015,7 +8072,7 @@
         <v>46183</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C7" s="218">
         <v>120</v>
@@ -8029,7 +8086,7 @@
         <v>46185</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="C8" s="218">
         <v>110.79</v>
@@ -8043,7 +8100,7 @@
         <v>46206</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C9" s="218">
         <v>359</v>
@@ -8057,7 +8114,7 @@
         <v>46206</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C10" s="218">
         <v>900</v>
@@ -8071,7 +8128,7 @@
         <v>46206</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="C11" s="218">
         <v>96.8</v>
@@ -8085,7 +8142,7 @@
         <v>46209</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C12" s="218">
         <v>200</v>
@@ -8099,7 +8156,7 @@
         <v>46196</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C13" s="218">
         <v>592.78</v>
@@ -8113,16 +8170,16 @@
         <v>46180</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="C14" s="218">
         <v>259</v>
       </c>
       <c r="D14" s="219" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8130,16 +8187,16 @@
         <v>46210</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="C15" s="218">
         <v>249</v>
       </c>
       <c r="D15" s="219" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -8148,17 +8205,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="中大附属第三医院">
-    <tabColor/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
-  <sheetData/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="中大附属第六医院">
     <tabColor/>
@@ -11738,6 +11784,1867 @@
   <autoFilter ref="A19:N36">
     <sortState ref="A20:N36"/>
   </autoFilter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="中大附属第三医院">
+    <tabColor/>
+  </sheetPr>
+  <dimension ref="O67"/>
+  <sheetFormatPr baseColWidth="13" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="15" width="10.6523" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4">
+        <v>46203</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4">
+        <v>46204</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="4">
+        <v>46205</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="4">
+        <v>46206</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="4">
+        <v>46207</v>
+      </c>
+      <c r="L1" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="4">
+        <v>46208</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="20" t="s"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="21" t="s"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="43" t="s"/>
+      <c r="B3" s="28" t="s"/>
+      <c r="C3" s="43" t="s"/>
+      <c r="D3" s="28" t="s"/>
+      <c r="E3" s="43" t="s"/>
+      <c r="F3" s="28" t="s"/>
+      <c r="G3" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="29">
+        <v>90</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="29">
+        <v>90</v>
+      </c>
+      <c r="K3" s="27" t="s"/>
+      <c r="L3" s="28" t="s"/>
+      <c r="M3" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" s="29">
+        <v>90</v>
+      </c>
+      <c r="O3" s="11" t="s"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="9" t="s"/>
+      <c r="B4" s="10" t="s"/>
+      <c r="C4" s="9" t="s"/>
+      <c r="D4" s="10" t="s"/>
+      <c r="E4" s="9" t="s"/>
+      <c r="F4" s="10" t="s"/>
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="11">
+        <v>90</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="11">
+        <v>30</v>
+      </c>
+      <c r="K4" s="9" t="s"/>
+      <c r="L4" s="10" t="s"/>
+      <c r="M4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="11">
+        <v>30</v>
+      </c>
+      <c r="O4" s="11" t="s"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="9" t="s"/>
+      <c r="B5" s="10" t="s"/>
+      <c r="C5" s="9" t="s"/>
+      <c r="D5" s="10" t="s"/>
+      <c r="E5" s="9" t="s"/>
+      <c r="F5" s="10" t="s"/>
+      <c r="G5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="11">
+        <v>90</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="11">
+        <v>90</v>
+      </c>
+      <c r="K5" s="9" t="s"/>
+      <c r="L5" s="10" t="s"/>
+      <c r="M5" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="11">
+        <v>90</v>
+      </c>
+      <c r="O5" s="11" t="s"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="9" t="s"/>
+      <c r="B6" s="10" t="s"/>
+      <c r="C6" s="9" t="s"/>
+      <c r="D6" s="10" t="s"/>
+      <c r="E6" s="9" t="s"/>
+      <c r="F6" s="10" t="s"/>
+      <c r="G6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="11">
+        <v>90</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="11">
+        <v>90</v>
+      </c>
+      <c r="K6" s="9" t="s"/>
+      <c r="L6" s="10" t="s"/>
+      <c r="M6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" s="11">
+        <v>90</v>
+      </c>
+      <c r="O6" s="11" t="s"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="9" t="s"/>
+      <c r="B7" s="10" t="s"/>
+      <c r="C7" s="9" t="s"/>
+      <c r="D7" s="10" t="s"/>
+      <c r="E7" s="9" t="s"/>
+      <c r="F7" s="10" t="s"/>
+      <c r="G7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="11">
+        <v>90</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="11">
+        <v>90</v>
+      </c>
+      <c r="K7" s="9" t="s"/>
+      <c r="L7" s="10" t="s"/>
+      <c r="M7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="11">
+        <v>90</v>
+      </c>
+      <c r="O7" s="45" t="s"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="9" t="s"/>
+      <c r="B8" s="10" t="s"/>
+      <c r="C8" s="9" t="s"/>
+      <c r="D8" s="10" t="s"/>
+      <c r="E8" s="9" t="s"/>
+      <c r="F8" s="10" t="s"/>
+      <c r="G8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="11">
+        <v>90</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="11">
+        <v>90</v>
+      </c>
+      <c r="K8" s="9" t="s"/>
+      <c r="L8" s="10" t="s"/>
+      <c r="M8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="11">
+        <v>90</v>
+      </c>
+      <c r="O8" s="45" t="s"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="9" t="s"/>
+      <c r="B9" s="10" t="s"/>
+      <c r="C9" s="9" t="s"/>
+      <c r="D9" s="10" t="s"/>
+      <c r="E9" s="9" t="s"/>
+      <c r="F9" s="10" t="s"/>
+      <c r="G9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="11">
+        <v>90</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="11">
+        <v>90</v>
+      </c>
+      <c r="K9" s="9" t="s"/>
+      <c r="L9" s="10" t="s"/>
+      <c r="M9" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N9" s="11">
+        <v>90</v>
+      </c>
+      <c r="O9" s="45" t="s"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="9" t="s"/>
+      <c r="B10" s="10" t="s"/>
+      <c r="C10" s="9" t="s"/>
+      <c r="D10" s="10" t="s"/>
+      <c r="E10" s="9" t="s"/>
+      <c r="F10" s="10" t="s"/>
+      <c r="G10" s="9" t="s"/>
+      <c r="H10" s="11" t="s"/>
+      <c r="I10" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="10">
+        <v>90</v>
+      </c>
+      <c r="K10" s="9" t="s"/>
+      <c r="L10" s="10" t="s"/>
+      <c r="M10" s="9" t="s"/>
+      <c r="N10" s="11" t="s"/>
+      <c r="O10" s="45" t="s"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="9" t="s"/>
+      <c r="B11" s="10" t="s"/>
+      <c r="C11" s="12" t="s"/>
+      <c r="D11" s="10" t="s"/>
+      <c r="E11" s="9" t="s"/>
+      <c r="F11" s="10" t="s"/>
+      <c r="G11" s="9" t="s"/>
+      <c r="H11" s="11" t="s"/>
+      <c r="I11" s="10" t="s"/>
+      <c r="J11" s="10" t="s"/>
+      <c r="K11" s="9" t="s"/>
+      <c r="L11" s="10" t="s"/>
+      <c r="M11" s="9" t="s"/>
+      <c r="N11" s="11" t="s"/>
+      <c r="O11" s="45" t="s"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="9" t="s"/>
+      <c r="B12" s="10" t="s"/>
+      <c r="C12" s="9" t="s"/>
+      <c r="D12" s="10" t="s"/>
+      <c r="E12" s="9" t="s"/>
+      <c r="F12" s="10" t="s"/>
+      <c r="G12" s="9" t="s"/>
+      <c r="H12" s="11" t="s"/>
+      <c r="I12" s="10" t="s"/>
+      <c r="J12" s="10" t="s"/>
+      <c r="K12" s="9" t="s"/>
+      <c r="L12" s="10" t="s"/>
+      <c r="M12" s="9" t="s"/>
+      <c r="N12" s="11" t="s"/>
+      <c r="O12" s="45" t="s"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="9" t="s"/>
+      <c r="B13" s="10" t="s"/>
+      <c r="C13" s="9" t="s"/>
+      <c r="D13" s="10" t="s"/>
+      <c r="E13" s="9" t="s"/>
+      <c r="F13" s="10" t="s"/>
+      <c r="G13" s="9" t="s"/>
+      <c r="H13" s="11" t="s"/>
+      <c r="I13" s="10" t="s"/>
+      <c r="J13" s="10" t="s"/>
+      <c r="K13" s="9" t="s"/>
+      <c r="L13" s="10" t="s"/>
+      <c r="M13" s="9" t="s"/>
+      <c r="N13" s="11" t="s"/>
+      <c r="O13" s="45" t="s"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="9" t="s"/>
+      <c r="B14" s="10" t="s"/>
+      <c r="C14" s="9" t="s"/>
+      <c r="D14" s="10" t="s"/>
+      <c r="E14" s="9" t="s"/>
+      <c r="F14" s="10" t="s"/>
+      <c r="G14" s="9" t="s"/>
+      <c r="H14" s="11" t="s"/>
+      <c r="I14" s="9" t="s"/>
+      <c r="J14" s="11" t="s"/>
+      <c r="K14" s="9" t="s"/>
+      <c r="L14" s="10" t="s"/>
+      <c r="M14" s="12" t="s"/>
+      <c r="N14" s="11" t="s"/>
+      <c r="O14" s="45" t="s"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="12" t="s"/>
+      <c r="B15" s="10" t="s"/>
+      <c r="C15" s="12" t="s"/>
+      <c r="D15" s="10" t="s"/>
+      <c r="E15" s="12" t="s"/>
+      <c r="F15" s="10" t="s"/>
+      <c r="G15" s="12" t="s"/>
+      <c r="H15" s="11" t="s"/>
+      <c r="I15" s="12" t="s"/>
+      <c r="J15" s="11" t="s"/>
+      <c r="K15" s="12" t="s"/>
+      <c r="L15" s="10" t="s"/>
+      <c r="M15" s="9" t="s"/>
+      <c r="N15" s="11" t="s"/>
+      <c r="O15" s="45" t="s"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="9" t="s"/>
+      <c r="B16" s="10" t="s"/>
+      <c r="C16" s="9" t="s"/>
+      <c r="D16" s="10" t="s"/>
+      <c r="E16" s="9" t="s"/>
+      <c r="F16" s="10" t="s"/>
+      <c r="G16" s="9" t="s"/>
+      <c r="H16" s="47" t="s"/>
+      <c r="I16" s="9" t="s"/>
+      <c r="J16" s="47" t="s"/>
+      <c r="K16" s="9" t="s"/>
+      <c r="L16" s="10" t="s"/>
+      <c r="M16" s="9" t="s"/>
+      <c r="N16" s="11" t="s"/>
+      <c r="O16" s="45" t="s"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="9" t="s"/>
+      <c r="B17" s="10" t="s"/>
+      <c r="C17" s="9" t="s"/>
+      <c r="D17" s="10" t="s"/>
+      <c r="E17" s="9" t="s"/>
+      <c r="F17" s="10" t="s"/>
+      <c r="G17" s="9" t="s"/>
+      <c r="H17" s="11" t="s"/>
+      <c r="I17" s="9" t="s"/>
+      <c r="J17" s="11" t="s"/>
+      <c r="K17" s="9" t="s"/>
+      <c r="L17" s="10" t="s"/>
+      <c r="M17" s="9" t="s"/>
+      <c r="N17" s="11" t="s"/>
+      <c r="O17" s="45" t="s"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="9" t="s"/>
+      <c r="B18" s="10" t="s"/>
+      <c r="C18" s="9" t="s"/>
+      <c r="D18" s="10" t="s"/>
+      <c r="E18" s="9" t="s"/>
+      <c r="F18" s="10" t="s"/>
+      <c r="G18" s="9" t="s"/>
+      <c r="H18" s="11" t="s"/>
+      <c r="I18" s="9" t="s"/>
+      <c r="J18" s="11" t="s"/>
+      <c r="K18" s="9" t="s"/>
+      <c r="L18" s="10" t="s"/>
+      <c r="M18" s="9" t="s"/>
+      <c r="N18" s="11" t="s"/>
+      <c r="O18" s="45" t="s"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="9" t="s"/>
+      <c r="B19" s="10" t="s"/>
+      <c r="C19" s="9" t="s"/>
+      <c r="D19" s="10" t="s"/>
+      <c r="E19" s="9" t="s"/>
+      <c r="F19" s="10" t="s"/>
+      <c r="G19" s="9" t="s"/>
+      <c r="H19" s="11" t="s"/>
+      <c r="I19" s="10" t="s"/>
+      <c r="J19" s="10" t="s"/>
+      <c r="K19" s="9" t="s"/>
+      <c r="L19" s="10" t="s"/>
+      <c r="M19" s="9" t="s"/>
+      <c r="N19" s="11" t="s"/>
+      <c r="O19" s="45" t="s"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="31" t="s"/>
+      <c r="B20" s="32" t="s"/>
+      <c r="C20" s="31" t="s"/>
+      <c r="D20" s="32" t="s"/>
+      <c r="E20" s="31" t="s"/>
+      <c r="F20" s="32" t="s"/>
+      <c r="G20" s="31" t="s"/>
+      <c r="H20" s="33" t="s"/>
+      <c r="I20" s="32" t="s"/>
+      <c r="J20" s="32" t="s"/>
+      <c r="K20" s="31" t="s"/>
+      <c r="L20" s="32" t="s"/>
+      <c r="M20" s="31" t="s"/>
+      <c r="N20" s="33" t="s"/>
+      <c r="O20" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="15" t="s"/>
+      <c r="B21" s="16">
+        <f>=SUM(B3:B20)</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="15" t="s"/>
+      <c r="D21" s="16">
+        <f>=SUM(D3:D20)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="s"/>
+      <c r="F21" s="16">
+        <f>=SUM(F3:F20)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="15" t="s"/>
+      <c r="H21" s="16">
+        <f>=SUM(H3:H20)</f>
+        <v>630</v>
+      </c>
+      <c r="I21" s="15" t="s"/>
+      <c r="J21" s="17">
+        <f>=SUM(J3:J20)</f>
+        <v>660</v>
+      </c>
+      <c r="K21" s="16" t="s"/>
+      <c r="L21" s="17">
+        <f>=SUM(L3:L20)</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="16" t="s"/>
+      <c r="N21" s="16">
+        <f>=SUM(N3:N20)</f>
+        <v>570</v>
+      </c>
+      <c r="O21" s="41">
+        <f>=SUM(A21:N21)</f>
+        <v>1860</v>
+      </c>
+      <c r="P21" s="36" t="s"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4">
+        <v>46210</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4">
+        <v>46211</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46212</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="4">
+        <v>46213</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="4">
+        <v>46214</v>
+      </c>
+      <c r="L24" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="M24" s="4">
+        <v>46215</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O24" s="20" t="s"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O25" s="21" t="s"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="29">
+        <v>90</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="28">
+        <v>90</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="28">
+        <v>90</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="28">
+        <v>90</v>
+      </c>
+      <c r="I26" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="48">
+        <v>90</v>
+      </c>
+      <c r="K26" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="L26" s="28">
+        <v>90</v>
+      </c>
+      <c r="M26" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="N26" s="29">
+        <v>30</v>
+      </c>
+      <c r="O26" s="11" t="s"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="11">
+        <v>30</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="8">
+        <v>30</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="8">
+        <v>30</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="10">
+        <v>30</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" s="49">
+        <v>30</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L27" s="10">
+        <v>30</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27" s="11">
+        <v>90</v>
+      </c>
+      <c r="O27" s="11" t="s"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="11">
+        <v>90</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="8">
+        <v>90</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="8">
+        <v>90</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="10">
+        <v>90</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" s="11">
+        <v>90</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L28" s="10">
+        <v>90</v>
+      </c>
+      <c r="M28" s="9" t="s"/>
+      <c r="N28" s="11" t="s"/>
+      <c r="O28" s="11" t="s"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="11">
+        <v>90</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="8">
+        <v>90</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="8">
+        <v>90</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29" s="10">
+        <v>90</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J29" s="11">
+        <v>90</v>
+      </c>
+      <c r="K29" s="10" t="s"/>
+      <c r="L29" s="10" t="s"/>
+      <c r="M29" s="9" t="s"/>
+      <c r="N29" s="11" t="s"/>
+      <c r="O29" s="11" t="s"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="11">
+        <v>90</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="8">
+        <v>90</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="8">
+        <v>90</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="10">
+        <v>90</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="J30" s="11">
+        <v>90</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" s="10">
+        <v>90</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="49">
+        <v>90</v>
+      </c>
+      <c r="O30" s="45" t="s"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="11">
+        <v>90</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="8">
+        <v>90</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="8">
+        <v>90</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="50">
+        <v>90</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" s="11">
+        <v>90</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L31" s="22">
+        <v>90</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="N31" s="11">
+        <v>90</v>
+      </c>
+      <c r="O31" s="45" t="s"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="9" t="s"/>
+      <c r="B32" s="8" t="s"/>
+      <c r="C32" s="9" t="s"/>
+      <c r="D32" s="8" t="s"/>
+      <c r="E32" s="9" t="s"/>
+      <c r="F32" s="8" t="s"/>
+      <c r="G32" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" s="50" t="s"/>
+      <c r="I32" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="11">
+        <v>90</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L32" s="22">
+        <v>90</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="11">
+        <v>90</v>
+      </c>
+      <c r="O32" s="45" t="s"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="9" t="s"/>
+      <c r="B33" s="8" t="s"/>
+      <c r="C33" s="9" t="s"/>
+      <c r="D33" s="8" t="s"/>
+      <c r="E33" s="9" t="s"/>
+      <c r="F33" s="8" t="s"/>
+      <c r="G33" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" s="52">
+        <v>60</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J33" s="11">
+        <v>90</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L33" s="22">
+        <v>90</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="11">
+        <v>90</v>
+      </c>
+      <c r="O33" s="45" t="s"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="9" t="s"/>
+      <c r="B34" s="8" t="s"/>
+      <c r="C34" s="12" t="s"/>
+      <c r="D34" s="8" t="s"/>
+      <c r="E34" s="9" t="s"/>
+      <c r="F34" s="8" t="s"/>
+      <c r="G34" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" s="52">
+        <v>90</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="J34" s="11">
+        <v>90</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="10">
+        <v>90</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N34" s="11">
+        <v>90</v>
+      </c>
+      <c r="O34" s="45" t="s"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="9" t="s"/>
+      <c r="B35" s="8" t="s"/>
+      <c r="C35" s="9" t="s"/>
+      <c r="D35" s="8" t="s"/>
+      <c r="E35" s="9" t="s"/>
+      <c r="F35" s="8" t="s"/>
+      <c r="G35" s="9" t="s"/>
+      <c r="H35" s="52" t="s"/>
+      <c r="I35" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="J35" s="11">
+        <v>90</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L35" s="10">
+        <v>90</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="N35" s="11">
+        <v>90</v>
+      </c>
+      <c r="O35" s="45" t="s"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="9" t="s"/>
+      <c r="B36" s="8" t="s"/>
+      <c r="C36" s="9" t="s"/>
+      <c r="D36" s="8" t="s"/>
+      <c r="E36" s="9" t="s"/>
+      <c r="F36" s="8" t="s"/>
+      <c r="G36" s="9" t="s"/>
+      <c r="H36" s="52" t="s"/>
+      <c r="I36" s="51" t="s"/>
+      <c r="J36" s="11" t="s"/>
+      <c r="K36" s="10" t="s"/>
+      <c r="L36" s="10" t="s"/>
+      <c r="M36" s="9" t="s"/>
+      <c r="N36" s="11" t="s"/>
+      <c r="O36" s="45" t="s"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="9" t="s"/>
+      <c r="B37" s="8" t="s"/>
+      <c r="C37" s="9" t="s"/>
+      <c r="D37" s="8" t="s"/>
+      <c r="E37" s="9" t="s"/>
+      <c r="F37" s="8" t="s"/>
+      <c r="G37" s="9" t="s"/>
+      <c r="H37" s="52" t="s"/>
+      <c r="I37" s="51" t="s"/>
+      <c r="J37" s="11" t="s"/>
+      <c r="K37" s="10" t="s"/>
+      <c r="L37" s="10" t="s"/>
+      <c r="M37" s="12" t="s"/>
+      <c r="N37" s="11" t="s"/>
+      <c r="O37" s="45" t="s"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="12" t="s"/>
+      <c r="B38" s="11" t="s"/>
+      <c r="C38" s="9" t="s"/>
+      <c r="D38" s="8" t="s"/>
+      <c r="E38" s="9" t="s"/>
+      <c r="F38" s="8" t="s"/>
+      <c r="G38" s="9" t="s"/>
+      <c r="H38" s="10" t="s"/>
+      <c r="I38" s="9" t="s"/>
+      <c r="J38" s="11" t="s"/>
+      <c r="K38" s="10" t="s"/>
+      <c r="L38" s="47" t="s"/>
+      <c r="M38" s="9" t="s"/>
+      <c r="N38" s="11" t="s"/>
+      <c r="O38" s="45" t="s"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="9" t="s"/>
+      <c r="B39" s="47" t="s"/>
+      <c r="C39" s="9" t="s"/>
+      <c r="D39" s="8" t="s"/>
+      <c r="E39" s="9" t="s"/>
+      <c r="F39" s="8" t="s"/>
+      <c r="G39" s="9" t="s"/>
+      <c r="H39" s="10" t="s"/>
+      <c r="I39" s="9" t="s"/>
+      <c r="J39" s="11" t="s"/>
+      <c r="K39" s="10" t="s"/>
+      <c r="L39" s="47" t="s"/>
+      <c r="M39" s="9" t="s"/>
+      <c r="N39" s="11" t="s"/>
+      <c r="O39" s="45" t="s"/>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="9" t="s"/>
+      <c r="B40" s="11" t="s"/>
+      <c r="C40" s="12" t="s"/>
+      <c r="D40" s="8" t="s"/>
+      <c r="E40" s="12" t="s"/>
+      <c r="F40" s="8" t="s"/>
+      <c r="G40" s="12" t="s"/>
+      <c r="H40" s="10" t="s"/>
+      <c r="I40" s="12" t="s"/>
+      <c r="J40" s="11" t="s"/>
+      <c r="K40" s="23" t="s"/>
+      <c r="L40" s="47" t="s"/>
+      <c r="M40" s="12" t="s"/>
+      <c r="N40" s="11" t="s"/>
+      <c r="O40" s="45" t="s"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="9" t="s"/>
+      <c r="B41" s="11" t="s"/>
+      <c r="C41" s="9" t="s"/>
+      <c r="D41" s="8" t="s"/>
+      <c r="E41" s="9" t="s"/>
+      <c r="F41" s="8" t="s"/>
+      <c r="G41" s="9" t="s"/>
+      <c r="H41" s="10" t="s"/>
+      <c r="I41" s="9" t="s"/>
+      <c r="J41" s="11" t="s"/>
+      <c r="K41" s="10" t="s"/>
+      <c r="L41" s="47" t="s"/>
+      <c r="M41" s="9" t="s"/>
+      <c r="N41" s="11" t="s"/>
+      <c r="O41" s="45" t="s"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="9" t="s"/>
+      <c r="B42" s="8" t="s"/>
+      <c r="C42" s="9" t="s"/>
+      <c r="D42" s="8" t="s"/>
+      <c r="E42" s="9" t="s"/>
+      <c r="F42" s="8" t="s"/>
+      <c r="G42" s="9" t="s"/>
+      <c r="H42" s="10" t="s"/>
+      <c r="I42" s="9" t="s"/>
+      <c r="J42" s="11" t="s"/>
+      <c r="K42" s="10" t="s"/>
+      <c r="L42" s="10" t="s"/>
+      <c r="M42" s="9" t="s"/>
+      <c r="N42" s="11" t="s"/>
+      <c r="O42" s="45" t="s"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="31" t="s"/>
+      <c r="B43" s="32" t="s"/>
+      <c r="C43" s="31" t="s"/>
+      <c r="D43" s="32" t="s"/>
+      <c r="E43" s="31" t="s"/>
+      <c r="F43" s="32" t="s"/>
+      <c r="G43" s="31" t="s"/>
+      <c r="H43" s="32" t="s"/>
+      <c r="I43" s="31" t="s"/>
+      <c r="J43" s="33" t="s"/>
+      <c r="K43" s="32" t="s"/>
+      <c r="L43" s="32" t="s"/>
+      <c r="M43" s="31" t="s"/>
+      <c r="N43" s="33" t="s"/>
+      <c r="O43" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="15" t="s"/>
+      <c r="B44" s="16">
+        <f>=SUM(B26:B43)</f>
+        <v>480</v>
+      </c>
+      <c r="C44" s="15" t="s"/>
+      <c r="D44" s="16">
+        <f>=SUM(D26:D43)</f>
+        <v>480</v>
+      </c>
+      <c r="E44" s="15" t="s"/>
+      <c r="F44" s="16">
+        <f>=SUM(F26:F43)</f>
+        <v>480</v>
+      </c>
+      <c r="G44" s="15" t="s"/>
+      <c r="H44" s="16">
+        <f>=SUM(H26:H43)</f>
+        <v>630</v>
+      </c>
+      <c r="I44" s="15" t="s"/>
+      <c r="J44" s="17">
+        <f>=SUM(J26:J43)</f>
+        <v>840</v>
+      </c>
+      <c r="K44" s="16" t="s"/>
+      <c r="L44" s="17">
+        <f>=SUM(L26:L43)</f>
+        <v>750</v>
+      </c>
+      <c r="M44" s="16" t="s"/>
+      <c r="N44" s="16">
+        <f>=SUM(N26:N43)</f>
+        <v>660</v>
+      </c>
+      <c r="O44" s="41">
+        <f>=SUM(A44:N44)</f>
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="4">
+        <v>46216</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="4">
+        <v>46217</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="4">
+        <v>46218</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="4">
+        <v>46219</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="4">
+        <v>46220</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K47" s="4">
+        <v>46221</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M47" s="4">
+        <v>46222</v>
+      </c>
+      <c r="N47" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O47" s="20" t="s"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O48" s="21" t="s"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="28">
+        <v>30</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="29">
+        <v>30</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F49" s="54">
+        <v>30</v>
+      </c>
+      <c r="G49" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="54">
+        <v>30</v>
+      </c>
+      <c r="I49" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" s="53">
+        <v>30</v>
+      </c>
+      <c r="K49" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L49" s="53">
+        <v>30</v>
+      </c>
+      <c r="M49" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="N49" s="54" t="s"/>
+      <c r="O49" s="11" t="s"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="9" t="s"/>
+      <c r="B50" s="10" t="s"/>
+      <c r="C50" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="11">
+        <v>135</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F50" s="56">
+        <v>135</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H50" s="56">
+        <v>135</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J50" s="55">
+        <v>135</v>
+      </c>
+      <c r="K50" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="L50" s="55">
+        <v>135</v>
+      </c>
+      <c r="M50" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="N50" s="56">
+        <v>135</v>
+      </c>
+      <c r="O50" s="11" t="s"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="10">
+        <v>135</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="11">
+        <v>135</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" s="56">
+        <v>135</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H51" s="56">
+        <v>135</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" s="55">
+        <v>135</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L51" s="55">
+        <v>135</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="56">
+        <v>135</v>
+      </c>
+      <c r="O51" s="11" t="s"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="10">
+        <v>135</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D52" s="11">
+        <v>135</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52" s="56">
+        <v>135</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H52" s="56">
+        <v>135</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J52" s="55">
+        <v>135</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="L52" s="55">
+        <v>135</v>
+      </c>
+      <c r="M52" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="N52" s="11">
+        <v>135</v>
+      </c>
+      <c r="O52" s="11" t="s"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="10">
+        <v>135</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" s="11">
+        <v>60</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F53" s="56">
+        <v>60</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H53" s="56">
+        <v>135</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J53" s="55">
+        <v>135</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L53" s="55">
+        <v>135</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N53" s="11">
+        <v>60</v>
+      </c>
+      <c r="O53" s="45" t="s"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" s="10">
+        <v>135</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="11">
+        <v>135</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F54" s="56">
+        <v>135</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H54" s="56">
+        <v>135</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J54" s="55">
+        <v>60</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L54" s="55">
+        <v>135</v>
+      </c>
+      <c r="M54" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="N54" s="56">
+        <v>60</v>
+      </c>
+      <c r="O54" s="45" t="s"/>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="10">
+        <v>135</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="11">
+        <v>135</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="56">
+        <v>135</v>
+      </c>
+      <c r="G55" s="10" t="s"/>
+      <c r="H55" s="56" t="s"/>
+      <c r="I55" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J55" s="55">
+        <v>135</v>
+      </c>
+      <c r="K55" s="9" t="s"/>
+      <c r="L55" s="55" t="s"/>
+      <c r="M55" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N55" s="11">
+        <v>135</v>
+      </c>
+      <c r="O55" s="45" t="s"/>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="10">
+        <v>135</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="11">
+        <v>135</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" s="11">
+        <v>135</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H56" s="58">
+        <v>135</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J56" s="59">
+        <v>135</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L56" s="50">
+        <v>135</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N56" s="11">
+        <v>135</v>
+      </c>
+      <c r="O56" s="45" t="s"/>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="10">
+        <v>135</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="11">
+        <v>135</v>
+      </c>
+      <c r="E57" s="10" t="s"/>
+      <c r="F57" s="11" t="s"/>
+      <c r="G57" s="10" t="s"/>
+      <c r="H57" s="11" t="s"/>
+      <c r="I57" s="10" t="s"/>
+      <c r="J57" s="10" t="s"/>
+      <c r="K57" s="9" t="s"/>
+      <c r="L57" s="10" t="s"/>
+      <c r="M57" s="9" t="s"/>
+      <c r="N57" s="11" t="s"/>
+      <c r="O57" s="45" t="s"/>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B58" s="10">
+        <v>135</v>
+      </c>
+      <c r="C58" s="9" t="s"/>
+      <c r="D58" s="11" t="s"/>
+      <c r="E58" s="10" t="s"/>
+      <c r="F58" s="11" t="s"/>
+      <c r="G58" s="10" t="s"/>
+      <c r="H58" s="11" t="s"/>
+      <c r="I58" s="10" t="s"/>
+      <c r="J58" s="10" t="s"/>
+      <c r="K58" s="9" t="s"/>
+      <c r="L58" s="10" t="s"/>
+      <c r="M58" s="9" t="s"/>
+      <c r="N58" s="11" t="s"/>
+      <c r="O58" s="45" t="s"/>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="10">
+        <v>30</v>
+      </c>
+      <c r="C59" s="9" t="s"/>
+      <c r="D59" s="11" t="s"/>
+      <c r="E59" s="10" t="s"/>
+      <c r="F59" s="11" t="s"/>
+      <c r="G59" s="10" t="s"/>
+      <c r="H59" s="58" t="s"/>
+      <c r="I59" s="50" t="s"/>
+      <c r="J59" s="10" t="s"/>
+      <c r="K59" s="9" t="s"/>
+      <c r="L59" s="10" t="s"/>
+      <c r="M59" s="9" t="s"/>
+      <c r="N59" s="11" t="s"/>
+      <c r="O59" s="45" t="s"/>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="9" t="s"/>
+      <c r="B60" s="10" t="s"/>
+      <c r="C60" s="9" t="s"/>
+      <c r="D60" s="11" t="s"/>
+      <c r="E60" s="10" t="s"/>
+      <c r="F60" s="11" t="s"/>
+      <c r="G60" s="10" t="s"/>
+      <c r="H60" s="58" t="s"/>
+      <c r="I60" s="50" t="s"/>
+      <c r="J60" s="10" t="s"/>
+      <c r="K60" s="9" t="s"/>
+      <c r="L60" s="10" t="s"/>
+      <c r="M60" s="12" t="s"/>
+      <c r="N60" s="11" t="s"/>
+      <c r="O60" s="45" t="s"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="9" t="s"/>
+      <c r="B61" s="10" t="s"/>
+      <c r="C61" s="9" t="s"/>
+      <c r="D61" s="11" t="s"/>
+      <c r="E61" s="10" t="s"/>
+      <c r="F61" s="11" t="s"/>
+      <c r="G61" s="10" t="s"/>
+      <c r="H61" s="11" t="s"/>
+      <c r="I61" s="10" t="s"/>
+      <c r="J61" s="10" t="s"/>
+      <c r="K61" s="9" t="s"/>
+      <c r="L61" s="10" t="s"/>
+      <c r="M61" s="9" t="s"/>
+      <c r="N61" s="11" t="s"/>
+      <c r="O61" s="45" t="s"/>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="9" t="s"/>
+      <c r="B62" s="10" t="s"/>
+      <c r="C62" s="9" t="s"/>
+      <c r="D62" s="11" t="s"/>
+      <c r="E62" s="10" t="s"/>
+      <c r="F62" s="11" t="s"/>
+      <c r="G62" s="10" t="s"/>
+      <c r="H62" s="11" t="s"/>
+      <c r="I62" s="10" t="s"/>
+      <c r="J62" s="10" t="s"/>
+      <c r="K62" s="9" t="s"/>
+      <c r="L62" s="10" t="s"/>
+      <c r="M62" s="9" t="s"/>
+      <c r="N62" s="11" t="s"/>
+      <c r="O62" s="45" t="s"/>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="12" t="s"/>
+      <c r="B63" s="10" t="s"/>
+      <c r="C63" s="12" t="s"/>
+      <c r="D63" s="11" t="s"/>
+      <c r="E63" s="10" t="s"/>
+      <c r="F63" s="11" t="s"/>
+      <c r="G63" s="10" t="s"/>
+      <c r="H63" s="11" t="s"/>
+      <c r="I63" s="10" t="s"/>
+      <c r="J63" s="10" t="s"/>
+      <c r="K63" s="9" t="s"/>
+      <c r="L63" s="10" t="s"/>
+      <c r="M63" s="9" t="s"/>
+      <c r="N63" s="11" t="s"/>
+      <c r="O63" s="45" t="s"/>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="9" t="s"/>
+      <c r="B64" s="10" t="s"/>
+      <c r="C64" s="9" t="s"/>
+      <c r="D64" s="11" t="s"/>
+      <c r="E64" s="23" t="s"/>
+      <c r="F64" s="11" t="s"/>
+      <c r="G64" s="23" t="s"/>
+      <c r="H64" s="11" t="s"/>
+      <c r="I64" s="23" t="s"/>
+      <c r="J64" s="10" t="s"/>
+      <c r="K64" s="12" t="s"/>
+      <c r="L64" s="10" t="s"/>
+      <c r="M64" s="9" t="s"/>
+      <c r="N64" s="11" t="s"/>
+      <c r="O64" s="45" t="s"/>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="9" t="s"/>
+      <c r="B65" s="10" t="s"/>
+      <c r="C65" s="9" t="s"/>
+      <c r="D65" s="11" t="s"/>
+      <c r="E65" s="10" t="s"/>
+      <c r="F65" s="11" t="s"/>
+      <c r="G65" s="10" t="s"/>
+      <c r="H65" s="11" t="s"/>
+      <c r="I65" s="10" t="s"/>
+      <c r="J65" s="10" t="s"/>
+      <c r="K65" s="9" t="s"/>
+      <c r="L65" s="10" t="s"/>
+      <c r="M65" s="9" t="s"/>
+      <c r="N65" s="11" t="s"/>
+      <c r="O65" s="45" t="s"/>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="31" t="s"/>
+      <c r="B66" s="32" t="s"/>
+      <c r="C66" s="31" t="s"/>
+      <c r="D66" s="33" t="s"/>
+      <c r="E66" s="32" t="s"/>
+      <c r="F66" s="33" t="s"/>
+      <c r="G66" s="32" t="s"/>
+      <c r="H66" s="33" t="s"/>
+      <c r="I66" s="32" t="s"/>
+      <c r="J66" s="32" t="s"/>
+      <c r="K66" s="31" t="s"/>
+      <c r="L66" s="32" t="s"/>
+      <c r="M66" s="31" t="s"/>
+      <c r="N66" s="33" t="s"/>
+      <c r="O66" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" s="15" t="s"/>
+      <c r="B67" s="16">
+        <f>=SUM(B49:B66)</f>
+        <v>1140</v>
+      </c>
+      <c r="C67" s="15" t="s"/>
+      <c r="D67" s="16">
+        <f>=SUM(D49:D66)</f>
+        <v>1035</v>
+      </c>
+      <c r="E67" s="15" t="s"/>
+      <c r="F67" s="16">
+        <f>=SUM(F49:F66)</f>
+        <v>900</v>
+      </c>
+      <c r="G67" s="15" t="s"/>
+      <c r="H67" s="16">
+        <f>=SUM(H49:H66)</f>
+        <v>840</v>
+      </c>
+      <c r="I67" s="15" t="s"/>
+      <c r="J67" s="17">
+        <f>=SUM(J49:J66)</f>
+        <v>900</v>
+      </c>
+      <c r="K67" s="16" t="s"/>
+      <c r="L67" s="17">
+        <f>=SUM(L49:L66)</f>
+        <v>840</v>
+      </c>
+      <c r="M67" s="16" t="s"/>
+      <c r="N67" s="16">
+        <f>=SUM(N49:N66)</f>
+        <v>795</v>
+      </c>
+      <c r="O67" s="41">
+        <f>=SUM(A67:N67)</f>
+        <v>6450</v>
+      </c>
+    </row>
+  </sheetData>
 </worksheet>
 </file>
 
@@ -11809,25 +13716,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="9" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B3" s="10">
         <v>60</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D3" s="10">
         <v>60</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F3" s="10">
         <v>60</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H3" s="11">
         <v>60</v>
@@ -11836,25 +13743,25 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B4" s="10">
         <v>60</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D4" s="10">
         <v>60</v>
       </c>
       <c r="E4" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F4" s="10">
         <v>60</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="H4" s="11">
         <v>60</v>
@@ -11863,7 +13770,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B5" s="10">
         <v>60</v>
@@ -11875,13 +13782,13 @@
         <v>60</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F5" s="10">
         <v>60</v>
       </c>
       <c r="G5" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H5" s="11">
         <v>60</v>
@@ -11896,19 +13803,19 @@
         <v>60</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D6" s="10">
         <v>60</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F6" s="10">
         <v>60</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="H6" s="11">
         <v>60</v>
@@ -11917,7 +13824,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="12" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B7" s="10">
         <v>60</v>
@@ -11950,13 +13857,13 @@
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D8" s="10">
         <v>60</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F8" s="10">
         <v>60</v>
@@ -11971,13 +13878,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B9" s="10">
         <v>60</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D9" s="10">
         <v>60</v>
@@ -12012,7 +13919,7 @@
         <v>60</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H10" s="11">
         <v>60</v>
@@ -12027,19 +13934,19 @@
         <v>60</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D11" s="10">
         <v>60</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F11" s="10">
         <v>60</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H11" s="11">
         <v>60</v>
@@ -12204,31 +14111,31 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B18" s="28">
         <v>60</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D18" s="28">
         <v>60</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F18" s="28">
         <v>60</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H18" s="28">
         <v>60</v>
       </c>
       <c r="I18" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="J18" s="28">
         <v>60</v>
@@ -12244,37 +14151,37 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B19" s="10">
         <v>60</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D19" s="10">
         <v>60</v>
       </c>
       <c r="E19" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F19" s="10">
         <v>60</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="H19" s="10">
         <v>60</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="J19" s="10">
         <v>60</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="L19" s="11">
         <v>60</v>
@@ -12284,31 +14191,31 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="12" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B20" s="10">
         <v>60</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D20" s="10">
         <v>60</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F20" s="10">
         <v>60</v>
       </c>
       <c r="G20" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H20" s="10">
         <v>60</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J20" s="10">
         <v>60</v>
@@ -12330,25 +14237,25 @@
         <v>60</v>
       </c>
       <c r="C21" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D21" s="10">
         <v>60</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10">
         <v>60</v>
       </c>
       <c r="G21" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="H21" s="10">
         <v>60</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="J21" s="10">
         <v>60</v>
@@ -12376,13 +14283,13 @@
         <v>60</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F22" s="10">
         <v>60</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="H22" s="10">
         <v>60</v>
@@ -12442,13 +14349,13 @@
         <v>60</v>
       </c>
       <c r="C24" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D24" s="10">
         <v>60</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F24" s="10">
         <v>60</v>
@@ -12484,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="E25" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F25" s="10">
         <v>60</v>
@@ -12508,13 +14415,13 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="9" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B26" s="10">
         <v>60</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D26" s="10">
         <v>60</v>
@@ -12526,7 +14433,7 @@
         <v>60</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H26" s="10">
         <v>60</v>
@@ -12550,25 +14457,25 @@
         <v>60</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D27" s="10">
         <v>60</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F27" s="10">
         <v>60</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H27" s="10">
         <v>60</v>
       </c>
       <c r="I27" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="J27" s="10">
         <v>60</v>
@@ -12582,7 +14489,7 @@
       <c r="A28" s="31" t="s"/>
       <c r="B28" s="32" t="s"/>
       <c r="C28" s="31" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D28" s="32">
         <v>60</v>
@@ -12728,25 +14635,25 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B34" s="28">
         <v>60</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D34" s="28">
         <v>60</v>
       </c>
       <c r="E34" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F34" s="28">
         <v>60</v>
       </c>
       <c r="G34" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H34" s="28">
         <v>60</v>
@@ -12759,31 +14666,31 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B35" s="10">
         <v>60</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D35" s="10">
         <v>60</v>
       </c>
       <c r="E35" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F35" s="10">
         <v>60</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="H35" s="10">
         <v>60</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="J35" s="11">
         <v>60</v>
@@ -12794,31 +14701,31 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="12" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B36" s="10">
         <v>60</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D36" s="10">
         <v>60</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F36" s="10">
         <v>60</v>
       </c>
       <c r="G36" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H36" s="10">
         <v>60</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J36" s="11">
         <v>60</v>
@@ -12835,25 +14742,25 @@
         <v>60</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D37" s="10">
         <v>60</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="F37" s="10">
         <v>60</v>
       </c>
       <c r="G37" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="H37" s="10">
         <v>60</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="J37" s="11">
         <v>60</v>
@@ -12876,13 +14783,13 @@
         <v>60</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F38" s="10">
         <v>60</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="H38" s="10">
         <v>60</v>
@@ -12940,13 +14847,13 @@
         <v>60</v>
       </c>
       <c r="C40" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D40" s="10">
         <v>60</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F40" s="10">
         <v>60</v>
@@ -12981,7 +14888,7 @@
         <v>60</v>
       </c>
       <c r="E41" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="F41" s="10">
         <v>60</v>
@@ -13004,13 +14911,13 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="9" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B42" s="10">
         <v>60</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D42" s="10">
         <v>60</v>
@@ -13022,7 +14929,7 @@
         <v>60</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H42" s="10">
         <v>60</v>
@@ -13045,25 +14952,25 @@
         <v>60</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D43" s="10">
         <v>60</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F43" s="10">
         <v>60</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H43" s="10">
         <v>60</v>
       </c>
       <c r="I43" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="J43" s="11">
         <v>60</v>
@@ -13080,7 +14987,7 @@
         <v>60</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D44" s="32">
         <v>60</v>
@@ -13098,7 +15005,7 @@
         <v>60</v>
       </c>
       <c r="I44" s="31" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="J44" s="33">
         <v>60</v>
@@ -13225,31 +15132,31 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B50" s="28">
         <v>60</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D50" s="28">
         <v>60</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F50" s="28">
         <v>60</v>
       </c>
       <c r="G50" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H50" s="29">
         <v>60</v>
       </c>
       <c r="I50" s="28" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="J50" s="48">
         <v>60</v>
@@ -13260,31 +15167,31 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B51" s="10">
         <v>60</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D51" s="10">
         <v>60</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F51" s="10">
         <v>60</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="H51" s="11">
         <v>60</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="J51" s="65">
         <v>60</v>
@@ -13295,13 +15202,13 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B52" s="10">
         <v>60</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D52" s="10">
         <v>60</v>
@@ -13309,13 +15216,13 @@
       <c r="E52" s="9" t="s"/>
       <c r="F52" s="10" t="s"/>
       <c r="G52" s="9" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="H52" s="11">
         <v>60</v>
       </c>
       <c r="I52" s="23" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J52" s="65">
         <v>60</v>
@@ -13326,13 +15233,13 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B53" s="10">
         <v>60</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D53" s="10">
         <v>60</v>
@@ -13340,13 +15247,13 @@
       <c r="E53" s="9" t="s"/>
       <c r="F53" s="10" t="s"/>
       <c r="G53" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="H53" s="11">
         <v>60</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="J53" s="65">
         <v>60</v>
@@ -13357,13 +15264,13 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="12" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B54" s="10">
         <v>60</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="D54" s="10">
         <v>60</v>
@@ -13371,13 +15278,13 @@
       <c r="E54" s="9" t="s"/>
       <c r="F54" s="10" t="s"/>
       <c r="G54" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H54" s="11">
         <v>60</v>
       </c>
       <c r="I54" s="66" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="J54" s="65">
         <v>60</v>
@@ -13388,13 +15295,13 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="12" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B55" s="10">
         <v>60</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D55" s="10">
         <v>60</v>
@@ -13419,13 +15326,13 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="12" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B56" s="10">
         <v>60</v>
       </c>
       <c r="C56" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D56" s="10">
         <v>60</v>
@@ -13433,7 +15340,7 @@
       <c r="E56" s="12" t="s"/>
       <c r="F56" s="10" t="s"/>
       <c r="G56" s="9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H56" s="11">
         <v>60</v>
@@ -13470,7 +15377,7 @@
         <v>60</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="J57" s="65">
         <v>60</v>
@@ -13481,13 +15388,13 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="62" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B58" s="10">
         <v>60</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D58" s="10">
         <v>60</v>
@@ -13508,13 +15415,13 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="12" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B59" s="10">
         <v>60</v>
       </c>
       <c r="C59" s="62" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D59" s="10">
         <v>60</v>
@@ -13524,7 +15431,7 @@
       <c r="G59" s="9" t="s"/>
       <c r="H59" s="11" t="s"/>
       <c r="I59" s="10" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="J59" s="65">
         <v>60</v>
@@ -13541,7 +15448,7 @@
         <v>60</v>
       </c>
       <c r="C60" s="31" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D60" s="32">
         <v>60</v>
@@ -13674,31 +15581,31 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B66" s="28">
         <v>60</v>
       </c>
       <c r="C66" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D66" s="28">
         <v>60</v>
       </c>
       <c r="E66" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F66" s="28">
         <v>60</v>
       </c>
       <c r="G66" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="H66" s="28">
         <v>60</v>
       </c>
       <c r="I66" s="27" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="J66" s="29">
         <v>60</v>
@@ -13709,31 +15616,31 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="12" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B67" s="10">
         <v>60</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="D67" s="10">
         <v>60</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="F67" s="10">
         <v>60</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="H67" s="10">
         <v>60</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="J67" s="11">
         <v>60</v>
@@ -13750,25 +15657,25 @@
         <v>60</v>
       </c>
       <c r="C68" s="62" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D68" s="10">
         <v>60</v>
       </c>
       <c r="E68" s="62" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F68" s="10">
         <v>60</v>
       </c>
       <c r="G68" s="62" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="H68" s="10">
         <v>60</v>
       </c>
       <c r="I68" s="62" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="J68" s="11">
         <v>60</v>
@@ -13779,31 +15686,31 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="12" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B69" s="10">
         <v>60</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D69" s="10">
         <v>60</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F69" s="10">
         <v>60</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H69" s="10">
         <v>60</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="J69" s="11">
         <v>60</v>
@@ -13814,31 +15721,31 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="12" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B70" s="10">
         <v>60</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D70" s="10">
         <v>60</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="F70" s="10">
         <v>60</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="H70" s="10">
         <v>60</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="J70" s="11">
         <v>60</v>
@@ -13849,31 +15756,31 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B71" s="10">
         <v>60</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="D71" s="10">
         <v>60</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="F71" s="10">
         <v>60</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="H71" s="10">
         <v>60</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="J71" s="11">
         <v>60</v>
@@ -13919,31 +15826,31 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="12" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B73" s="10">
         <v>60</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D73" s="10">
         <v>60</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="F73" s="10">
         <v>60</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="H73" s="10">
         <v>60</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="J73" s="11">
         <v>60</v>
@@ -13954,31 +15861,31 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="62" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B74" s="10">
         <v>60</v>
       </c>
       <c r="C74" s="62" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D74" s="10">
         <v>60</v>
       </c>
       <c r="E74" s="62" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="F74" s="10">
         <v>60</v>
       </c>
       <c r="G74" s="62" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="H74" s="10">
         <v>60</v>
       </c>
       <c r="I74" s="62" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="J74" s="11">
         <v>60</v>
@@ -13989,31 +15896,31 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="12" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B75" s="10">
         <v>60</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D75" s="10">
         <v>60</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F75" s="59">
         <v>60</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H75" s="59">
         <v>60</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="J75" s="58">
         <v>60</v>
@@ -14024,31 +15931,31 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="67" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B76" s="32">
         <v>60</v>
       </c>
       <c r="C76" s="67" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D76" s="32">
         <v>60</v>
       </c>
       <c r="E76" s="67" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F76" s="32">
         <v>60</v>
       </c>
       <c r="G76" s="67" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H76" s="32">
         <v>60</v>
       </c>
       <c r="I76" s="67" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="J76" s="33">
         <v>60</v>
@@ -14140,32 +16047,32 @@
         <v>46192</v>
       </c>
       <c r="J1" s="71" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K1" s="72" t="s"/>
       <c r="L1" s="73" t="s"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="74" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B2" s="75">
         <v>60</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D2" s="75">
         <v>60</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F2" s="75">
         <v>60</v>
       </c>
       <c r="G2" s="74" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H2" s="75">
         <v>65</v>
@@ -14176,25 +16083,25 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B3" s="46">
         <v>60</v>
       </c>
       <c r="C3" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D3" s="46">
         <v>60</v>
       </c>
       <c r="E3" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F3" s="46">
         <v>60</v>
       </c>
       <c r="G3" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="H3" s="46">
         <v>65</v>
@@ -14205,25 +16112,25 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B4" s="46">
         <v>60</v>
       </c>
       <c r="C4" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D4" s="46">
         <v>60</v>
       </c>
       <c r="E4" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F4" s="46">
         <v>60</v>
       </c>
       <c r="G4" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H4" s="46">
         <v>65</v>
@@ -14240,7 +16147,7 @@
       <c r="E5" s="80" t="s"/>
       <c r="F5" s="81" t="s"/>
       <c r="G5" s="80" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="H5" s="81">
         <v>10</v>
@@ -14362,31 +16269,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B11" s="50">
         <v>60</v>
       </c>
       <c r="C11" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D11" s="50">
         <v>90</v>
       </c>
       <c r="E11" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F11" s="50">
         <v>60</v>
       </c>
       <c r="G11" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H11" s="50">
         <v>90</v>
       </c>
       <c r="I11" s="74" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J11" s="48">
         <v>60</v>
@@ -14395,31 +16302,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B12" s="50">
         <v>60</v>
       </c>
       <c r="C12" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D12" s="50">
         <v>90</v>
       </c>
       <c r="E12" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F12" s="50">
         <v>90</v>
       </c>
       <c r="G12" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H12" s="50">
         <v>60</v>
       </c>
       <c r="I12" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="J12" s="49">
         <v>90</v>
@@ -14428,19 +16335,19 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B13" s="50">
         <v>60</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D13" s="50">
         <v>90</v>
       </c>
       <c r="E13" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F13" s="50">
         <v>60</v>
@@ -14448,7 +16355,7 @@
       <c r="G13" s="78" t="s"/>
       <c r="H13" s="50" t="s"/>
       <c r="I13" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="J13" s="49">
         <v>60</v>
@@ -14465,13 +16372,13 @@
       <c r="G14" s="51" t="s"/>
       <c r="H14" s="50" t="s"/>
       <c r="I14" s="78" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="J14" s="49">
         <v>10</v>
       </c>
       <c r="K14" s="49" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -14607,31 +16514,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B22" s="50">
         <v>90</v>
       </c>
       <c r="C22" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D22" s="50">
         <v>90</v>
       </c>
       <c r="E22" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F22" s="50">
         <v>90</v>
       </c>
       <c r="G22" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H22" s="50">
         <v>90</v>
       </c>
       <c r="I22" s="78" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J22" s="49">
         <v>90</v>
@@ -14640,31 +16547,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B23" s="50">
         <v>60</v>
       </c>
       <c r="C23" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D23" s="50">
         <v>60</v>
       </c>
       <c r="E23" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F23" s="50">
         <v>60</v>
       </c>
       <c r="G23" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H23" s="50">
         <v>60</v>
       </c>
       <c r="I23" s="78" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="J23" s="49">
         <v>60</v>
@@ -14673,31 +16580,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="78" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B24" s="50">
         <v>60</v>
       </c>
       <c r="C24" s="78" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D24" s="50">
         <v>60</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F24" s="50">
         <v>60</v>
       </c>
       <c r="G24" s="78" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H24" s="50">
         <v>60</v>
       </c>
       <c r="I24" s="78" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="J24" s="49">
         <v>60</v>
@@ -14714,13 +16621,13 @@
       <c r="G25" s="51" t="s"/>
       <c r="H25" s="50" t="s"/>
       <c r="I25" s="51" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J25" s="49">
         <v>10</v>
       </c>
       <c r="K25" s="49" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -14769,7 +16676,7 @@
         <v>1060</v>
       </c>
       <c r="L27" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -14841,31 +16748,31 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="106" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B31" s="107">
         <v>120</v>
       </c>
       <c r="C31" s="106" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D31" s="107">
         <v>120</v>
       </c>
       <c r="E31" s="106" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F31" s="107">
         <v>120</v>
       </c>
       <c r="G31" s="106" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H31" s="107">
         <v>120</v>
       </c>
       <c r="I31" s="104" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J31" s="108">
         <v>120</v>
@@ -14874,31 +16781,31 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="106" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B32" s="107">
         <v>60</v>
       </c>
       <c r="C32" s="106" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D32" s="107">
         <v>60</v>
       </c>
       <c r="E32" s="106" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="F32" s="107">
         <v>60</v>
       </c>
       <c r="G32" s="106" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H32" s="107">
         <v>60</v>
       </c>
       <c r="I32" s="106" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="J32" s="110">
         <v>60</v>
@@ -14907,13 +16814,13 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="106" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B33" s="107">
         <v>60</v>
       </c>
       <c r="C33" s="106" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D33" s="107">
         <v>60</v>
@@ -14921,13 +16828,13 @@
       <c r="E33" s="106" t="s"/>
       <c r="F33" s="107" t="s"/>
       <c r="G33" s="106" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H33" s="107">
         <v>60</v>
       </c>
       <c r="I33" s="106" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="J33" s="110">
         <v>60</v>
@@ -14944,13 +16851,13 @@
       <c r="G34" s="51" t="s"/>
       <c r="H34" s="22" t="s"/>
       <c r="I34" s="106" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J34" s="110">
         <v>10</v>
       </c>
       <c r="K34" s="110" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -14999,7 +16906,7 @@
         <v>1150</v>
       </c>
       <c r="L36" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -15070,7 +16977,7 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="104" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B41" s="108">
         <v>120</v>
@@ -15078,19 +16985,19 @@
       <c r="C41" s="106" t="s"/>
       <c r="D41" s="107" t="s"/>
       <c r="E41" s="104" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F41" s="108">
         <v>120</v>
       </c>
       <c r="G41" s="104" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H41" s="108">
         <v>120</v>
       </c>
       <c r="I41" s="104" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J41" s="108">
         <v>120</v>
@@ -15099,7 +17006,7 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="106" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B42" s="110">
         <v>60</v>
@@ -15107,19 +17014,19 @@
       <c r="C42" s="106" t="s"/>
       <c r="D42" s="107" t="s"/>
       <c r="E42" s="106" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="F42" s="110">
         <v>60</v>
       </c>
       <c r="G42" s="106" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="H42" s="110">
         <v>60</v>
       </c>
       <c r="I42" s="106" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="J42" s="110">
         <v>60</v>
@@ -15128,7 +17035,7 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="106" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B43" s="110">
         <v>60</v>
@@ -15136,19 +17043,19 @@
       <c r="C43" s="106" t="s"/>
       <c r="D43" s="107" t="s"/>
       <c r="E43" s="106" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F43" s="110">
         <v>60</v>
       </c>
       <c r="G43" s="106" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H43" s="110">
         <v>60</v>
       </c>
       <c r="I43" s="106" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="J43" s="110">
         <v>60</v>
@@ -15165,13 +17072,13 @@
       <c r="G44" s="51" t="s"/>
       <c r="H44" s="22" t="s"/>
       <c r="I44" s="106" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J44" s="110">
         <v>10</v>
       </c>
       <c r="K44" s="110" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -15220,7 +17127,7 @@
         <v>970</v>
       </c>
       <c r="L46" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -15268,31 +17175,31 @@
         <v>46192</v>
       </c>
       <c r="J1" s="71" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K1" s="72" t="s"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B2" s="29">
         <v>60</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D2" s="29">
         <v>60</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F2" s="29">
         <v>60</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="H2" s="29">
         <v>60</v>
@@ -15303,25 +17210,25 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B3" s="11">
         <v>60</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D3" s="11">
         <v>60</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F3" s="11">
         <v>60</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="H3" s="11">
         <v>60</v>
@@ -15332,25 +17239,25 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B4" s="11">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D4" s="11">
         <v>60</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F4" s="11">
         <v>60</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H4" s="11">
         <v>60</v>
@@ -15367,7 +17274,7 @@
       <c r="E5" s="31" t="s"/>
       <c r="F5" s="33" t="s"/>
       <c r="G5" s="31" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="H5" s="33">
         <v>10</v>
@@ -15480,31 +17387,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B11" s="22">
         <v>60</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D11" s="22">
         <v>60</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F11" s="22">
         <v>60</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="H11" s="22">
         <v>60</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="J11" s="48">
         <v>60</v>
@@ -15513,31 +17420,31 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B12" s="22">
         <v>60</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D12" s="22">
         <v>60</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F12" s="22">
         <v>60</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="H12" s="22">
         <v>60</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J12" s="49">
         <v>60</v>
@@ -15546,25 +17453,25 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B13" s="22">
         <v>60</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D13" s="22">
         <v>60</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F13" s="22">
         <v>60</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H13" s="22">
         <v>60</v>
@@ -15716,31 +17623,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B22" s="22">
         <v>60</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D22" s="22">
         <v>60</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F22" s="22">
         <v>60</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="H22" s="22">
         <v>60</v>
       </c>
       <c r="I22" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="J22" s="48">
         <v>60</v>
@@ -15749,31 +17656,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B23" s="22">
         <v>60</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D23" s="22">
         <v>60</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F23" s="22">
         <v>60</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="H23" s="22">
         <v>60</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="J23" s="49">
         <v>60</v>
@@ -15782,31 +17689,31 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B24" s="22">
         <v>60</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D24" s="22">
         <v>60</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F24" s="22">
         <v>60</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H24" s="22">
         <v>60</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J24" s="49">
         <v>60</v>
@@ -15823,13 +17730,13 @@
       <c r="G25" s="51" t="s"/>
       <c r="H25" s="22" t="s"/>
       <c r="I25" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="J25" s="48">
         <v>60</v>
       </c>
       <c r="K25" s="49" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -15891,7 +17798,7 @@
         <v>960</v>
       </c>
       <c r="L28" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -15962,31 +17869,31 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B33" s="22">
         <v>60</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D33" s="22">
         <v>60</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F33" s="22">
         <v>60</v>
       </c>
       <c r="G33" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="H33" s="22">
         <v>60</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="J33" s="48">
         <v>60</v>
@@ -15995,31 +17902,31 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B34" s="22">
         <v>60</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D34" s="22">
         <v>60</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F34" s="22">
         <v>60</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="H34" s="22">
         <v>60</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="J34" s="49">
         <v>60</v>
@@ -16028,7 +17935,7 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="9" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B35" s="22">
         <v>60</v>
@@ -16036,19 +17943,19 @@
       <c r="C35" s="9" t="s"/>
       <c r="D35" s="22" t="s"/>
       <c r="E35" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F35" s="22">
         <v>60</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="H35" s="22">
         <v>60</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J35" s="49">
         <v>60</v>
@@ -16065,13 +17972,13 @@
       <c r="G36" s="51" t="s"/>
       <c r="H36" s="22" t="s"/>
       <c r="I36" s="9" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="J36" s="49">
         <v>10</v>
       </c>
       <c r="K36" s="49" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -16133,7 +18040,7 @@
         <v>850</v>
       </c>
       <c r="L39" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -16184,13 +18091,13 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B44" s="48">
         <v>60</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D44" s="48">
         <v>60</v>
@@ -16205,13 +18112,13 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B45" s="49">
         <v>60</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D45" s="49">
         <v>60</v>
@@ -16226,13 +18133,13 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B46" s="49">
         <v>60</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="D46" s="49">
         <v>60</v>
@@ -16317,7 +18224,7 @@
         <v>360</v>
       </c>
       <c r="L50" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -16365,31 +18272,31 @@
         <v>46192</v>
       </c>
       <c r="J1" s="71" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K1" s="72" t="s"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="27" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B2" s="29">
         <v>90</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D2" s="29">
         <v>90</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="F2" s="29">
         <v>90</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="H2" s="29">
         <v>90</v>
@@ -16400,25 +18307,25 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="B3" s="11">
         <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D3" s="11">
         <v>90</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F3" s="11">
         <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="H3" s="11">
         <v>90</v>
@@ -16429,25 +18336,25 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="9" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B4" s="11">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D4" s="11">
         <v>60</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F4" s="11">
         <v>60</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H4" s="11">
         <v>60</v>
@@ -16464,7 +18371,7 @@
       <c r="E5" s="31" t="s"/>
       <c r="F5" s="33" t="s"/>
       <c r="G5" s="31" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="H5" s="33">
         <v>10</v>
@@ -16577,60 +18484,60 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="27" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B11" s="22">
         <v>90</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D11" s="22">
         <v>90</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="F11" s="22">
         <v>90</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="H11" s="22">
         <v>90</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="J11" s="49">
         <v>10</v>
       </c>
       <c r="K11" s="49" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="B12" s="22">
         <v>90</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D12" s="22">
         <v>90</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F12" s="22">
         <v>60</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="H12" s="22">
         <v>60</v>
@@ -16641,19 +18548,19 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="9" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B13" s="22">
         <v>60</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D13" s="22">
         <v>60</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F13" s="22">
         <v>60</v>
@@ -16784,31 +18691,31 @@
         <v>46192</v>
       </c>
       <c r="J1" s="71" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="K1" s="72" t="s"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="B2" s="29">
         <v>90</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D2" s="29">
         <v>90</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="F2" s="29">
         <v>90</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H2" s="28">
         <v>90</v>
@@ -16819,25 +18726,25 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B3" s="11">
         <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D3" s="11">
         <v>90</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="F3" s="11">
         <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="H3" s="10">
         <v>90</v>
@@ -16850,7 +18757,7 @@
       <c r="A4" s="123" t="s"/>
       <c r="B4" s="124" t="s"/>
       <c r="C4" s="31" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="D4" s="33">
         <v>90</v>
@@ -16967,31 +18874,31 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="B10" s="22">
         <v>90</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D10" s="22">
         <v>90</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="F10" s="22">
         <v>90</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H10" s="22">
         <v>90</v>
       </c>
       <c r="I10" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="J10" s="48">
         <v>90</v>
@@ -17000,31 +18907,31 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B11" s="22">
         <v>90</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D11" s="22">
         <v>90</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="F11" s="22">
         <v>90</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="H11" s="22">
         <v>90</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J11" s="49">
         <v>90</v>
@@ -17187,31 +19094,31 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="B21" s="22">
         <v>90</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D21" s="22">
         <v>90</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="F21" s="22">
         <v>60</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H21" s="22">
         <v>60</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="J21" s="48">
         <v>60</v>
@@ -17220,31 +19127,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B22" s="22">
         <v>90</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D22" s="22">
         <v>90</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="F22" s="22">
         <v>100</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="H22" s="22">
         <v>90</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J22" s="49">
         <v>90</v>
@@ -17336,7 +19243,7 @@
         <v>820</v>
       </c>
       <c r="L27" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -17407,31 +19314,31 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="106" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B32" s="107">
         <v>90</v>
       </c>
       <c r="C32" s="106" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D32" s="107">
         <v>90</v>
       </c>
       <c r="E32" s="106" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="F32" s="107">
         <v>90</v>
       </c>
       <c r="G32" s="106" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="H32" s="107">
         <v>90</v>
       </c>
       <c r="I32" s="104" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J32" s="108">
         <v>90</v>
@@ -17440,31 +19347,31 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="106" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="B33" s="107">
         <v>60</v>
       </c>
       <c r="C33" s="106" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D33" s="107">
         <v>60</v>
       </c>
       <c r="E33" s="106" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="F33" s="107">
         <v>60</v>
       </c>
       <c r="G33" s="106" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="H33" s="107">
         <v>60</v>
       </c>
       <c r="I33" s="106" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="J33" s="110">
         <v>75</v>
@@ -17479,7 +19386,7 @@
       <c r="E34" s="106" t="s"/>
       <c r="F34" s="107" t="s"/>
       <c r="G34" s="106" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H34" s="107">
         <v>60</v>
@@ -17547,7 +19454,7 @@
         <v>825</v>
       </c>
       <c r="L37" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -17618,31 +19525,31 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="106" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B42" s="107">
         <v>90</v>
       </c>
       <c r="C42" s="106" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D42" s="107">
         <v>90</v>
       </c>
       <c r="E42" s="106" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="F42" s="107">
         <v>90</v>
       </c>
       <c r="G42" s="106" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="H42" s="107">
         <v>90</v>
       </c>
       <c r="I42" s="104" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="J42" s="108">
         <v>90</v>
@@ -17651,31 +19558,31 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="106" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="B43" s="107">
         <v>30</v>
       </c>
       <c r="C43" s="106" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="D43" s="107">
         <v>60</v>
       </c>
       <c r="E43" s="106" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="F43" s="107">
         <v>60</v>
       </c>
       <c r="G43" s="106" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="H43" s="107">
         <v>60</v>
       </c>
       <c r="I43" s="106" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="J43" s="110">
         <v>60</v>
@@ -17686,25 +19593,25 @@
       <c r="A44" s="106" t="s"/>
       <c r="B44" s="107" t="s"/>
       <c r="C44" s="106" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D44" s="107">
         <v>60</v>
       </c>
       <c r="E44" s="106" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="F44" s="107">
         <v>60</v>
       </c>
       <c r="G44" s="106" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="H44" s="107">
         <v>60</v>
       </c>
       <c r="I44" s="106" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="J44" s="110">
         <v>60</v>
@@ -17719,7 +19626,7 @@
       <c r="E45" s="51" t="s"/>
       <c r="F45" s="22" t="s"/>
       <c r="G45" s="51" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H45" s="22">
         <v>30</v>
@@ -17774,7 +19681,7 @@
         <v>990</v>
       </c>
       <c r="L47" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -17795,23 +19702,23 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="68" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B1" s="122" t="s"/>
       <c r="C1" s="68" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="D1" s="122" t="s"/>
       <c r="E1" s="68" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="F1" s="122" t="s"/>
       <c r="G1" s="131" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="H1" s="48" t="s"/>
       <c r="I1" s="68" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="J1" s="122" t="s"/>
       <c r="K1" s="72" t="s"/>
@@ -17819,25 +19726,25 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="27" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B2" s="29">
         <v>90</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="D2" s="29">
         <v>90</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="F2" s="28">
         <v>90</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H2" s="29">
         <v>45</v>
@@ -17850,19 +19757,19 @@
       <c r="A3" s="132" t="s"/>
       <c r="B3" s="133" t="s"/>
       <c r="C3" s="9" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="D3" s="11">
         <v>90</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="F3" s="10">
         <v>90</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="H3" s="11">
         <v>45</v>
@@ -17878,14 +19785,14 @@
       <c r="E4" s="132" t="s"/>
       <c r="F4" s="134" t="s"/>
       <c r="G4" s="9" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="H4" s="11">
         <v>20</v>
       </c>
       <c r="I4" s="22" t="s"/>
       <c r="K4" s="135" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -17986,13 +19893,13 @@
       <c r="E11" s="27" t="s"/>
       <c r="F11" s="22" t="s"/>
       <c r="G11" s="27" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="H11" s="22">
         <v>90</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="J11" s="48">
         <v>90</v>
@@ -18007,13 +19914,13 @@
       <c r="E12" s="9" t="s"/>
       <c r="F12" s="22" t="s"/>
       <c r="G12" s="9" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H12" s="22">
         <v>90</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="J12" s="49">
         <v>60</v>
@@ -18030,13 +19937,13 @@
       <c r="G13" s="9" t="s"/>
       <c r="H13" s="22" t="s"/>
       <c r="I13" s="51" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="J13" s="49">
         <v>5</v>
       </c>
       <c r="K13" s="49" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -18109,7 +20016,7 @@
         <v>335</v>
       </c>
       <c r="L17" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -18160,31 +20067,31 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="B22" s="22">
         <v>120</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D22" s="22">
         <v>120</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F22" s="22">
         <v>160</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H22" s="22">
         <v>130</v>
       </c>
       <c r="I22" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="J22" s="48">
         <v>130</v>
@@ -18193,31 +20100,31 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="9" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="B23" s="22">
         <v>60</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D23" s="22">
         <v>60</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="F23" s="22">
         <v>90</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="H23" s="22">
         <v>70</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="J23" s="49">
         <v>60</v>
@@ -18226,19 +20133,19 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B24" s="22">
         <v>60</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D24" s="22">
         <v>80</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="F24" s="22">
         <v>80</v>
@@ -18246,7 +20153,7 @@
       <c r="G24" s="9" t="s"/>
       <c r="H24" s="22" t="s"/>
       <c r="I24" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="J24" s="49">
         <v>60</v>
@@ -18263,7 +20170,7 @@
       <c r="G25" s="51" t="s"/>
       <c r="H25" s="22" t="s"/>
       <c r="I25" s="51" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="J25" s="49">
         <v>70</v>
@@ -18327,7 +20234,7 @@
         <v>1350</v>
       </c>
       <c r="L28" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -18378,31 +20285,31 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="B33" s="22">
         <v>120</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="D33" s="22">
         <v>120</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F33" s="22">
         <v>120</v>
       </c>
       <c r="G33" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="H33" s="22">
         <v>120</v>
       </c>
       <c r="I33" s="27" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="J33" s="48">
         <v>120</v>
@@ -18411,31 +20318,31 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="9" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="B34" s="22">
         <v>60</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D34" s="22">
         <v>60</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="F34" s="22">
         <v>60</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="H34" s="22">
         <v>60</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="J34" s="49">
         <v>60</v>
@@ -18444,31 +20351,31 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="B35" s="22">
         <v>60</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="D35" s="22">
         <v>60</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="F35" s="22">
         <v>60</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="H35" s="22">
         <v>60</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="J35" s="49">
         <v>60</v>
@@ -18479,7 +20386,7 @@
       <c r="A36" s="51" t="s"/>
       <c r="B36" s="22" t="s"/>
       <c r="C36" s="106" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D36" s="107">
         <v>60</v>
@@ -18489,7 +20396,7 @@
       <c r="G36" s="51" t="s"/>
       <c r="H36" s="22" t="s"/>
       <c r="I36" s="51" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="J36" s="49">
         <v>60</v>
@@ -18510,7 +20417,7 @@
         <v>20</v>
       </c>
       <c r="K37" s="49" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -18557,7 +20464,7 @@
         <v>1340</v>
       </c>
       <c r="L39" s="97" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
